--- a/parameters script.xlsx
+++ b/parameters script.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="146">
   <si>
     <t xml:space="preserve">6h 3</t>
   </si>
@@ -459,19 +459,10 @@
     <t xml:space="preserve">6H-1</t>
   </si>
   <si>
-    <t xml:space="preserve">more</t>
-  </si>
-  <si>
     <t xml:space="preserve">3H-1</t>
   </si>
   <si>
     <t xml:space="preserve">3H-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LESS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MORE</t>
   </si>
 </sst>
 </file>
@@ -685,7 +676,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="43">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -782,15 +773,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -846,20 +837,16 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -945,9 +932,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>471600</xdr:colOff>
+      <xdr:colOff>471240</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>28800</xdr:rowOff>
+      <xdr:rowOff>28440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -961,7 +948,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6183720" y="130320"/>
-          <a:ext cx="7992360" cy="264240"/>
+          <a:ext cx="7992000" cy="263880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6673,7 +6660,7 @@
       <c r="Y1" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="Z1" s="22" t="s">
+      <c r="Z1" s="24" t="s">
         <v>108</v>
       </c>
     </row>
@@ -6714,7 +6701,7 @@
       <c r="L2" s="20" t="n">
         <v>0.5</v>
       </c>
-      <c r="M2" s="24" t="n">
+      <c r="M2" s="25" t="n">
         <v>0.5</v>
       </c>
       <c r="N2" s="20" t="n">
@@ -6726,28 +6713,28 @@
       <c r="P2" s="20" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q2" s="24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R2" s="24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T2" s="24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U2" s="24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V2" s="24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="W2" s="24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="X2" s="24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y2" s="24" t="n">
+      <c r="Q2" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R2" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T2" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U2" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V2" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W2" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X2" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y2" s="25" t="n">
         <v>0.5</v>
       </c>
       <c r="Z2" s="20" t="n">
@@ -6791,7 +6778,7 @@
       <c r="L3" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="M3" s="24" t="n">
+      <c r="M3" s="25" t="n">
         <v>1</v>
       </c>
       <c r="N3" s="20" t="n">
@@ -6803,28 +6790,28 @@
       <c r="P3" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="Q3" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="R3" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="T3" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="V3" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="W3" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="X3" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y3" s="24" t="n">
+      <c r="Q3" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="25" t="n">
         <v>1</v>
       </c>
       <c r="Z3" s="20" t="n">
@@ -6868,7 +6855,7 @@
       <c r="L4" s="20" t="n">
         <v>0.5</v>
       </c>
-      <c r="M4" s="24" t="n">
+      <c r="M4" s="25" t="n">
         <v>0.5</v>
       </c>
       <c r="N4" s="20" t="n">
@@ -6880,28 +6867,28 @@
       <c r="P4" s="20" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q4" s="24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R4" s="24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T4" s="24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U4" s="24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V4" s="24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="W4" s="24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="X4" s="24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y4" s="24" t="n">
+      <c r="Q4" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R4" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T4" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U4" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V4" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W4" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X4" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y4" s="25" t="n">
         <v>0.5</v>
       </c>
       <c r="Z4" s="20" t="n">
@@ -6945,7 +6932,7 @@
       <c r="L5" s="20" t="n">
         <v>1.5</v>
       </c>
-      <c r="M5" s="24" t="n">
+      <c r="M5" s="25" t="n">
         <v>1.5</v>
       </c>
       <c r="N5" s="20" t="n">
@@ -6957,28 +6944,28 @@
       <c r="P5" s="20" t="n">
         <v>1.5</v>
       </c>
-      <c r="Q5" s="24" t="n">
+      <c r="Q5" s="25" t="n">
         <v>1.5</v>
       </c>
-      <c r="R5" s="24" t="n">
+      <c r="R5" s="25" t="n">
         <v>1.5</v>
       </c>
-      <c r="T5" s="24" t="n">
+      <c r="T5" s="25" t="n">
         <v>1.5</v>
       </c>
-      <c r="U5" s="24" t="n">
+      <c r="U5" s="25" t="n">
         <v>1.5</v>
       </c>
-      <c r="V5" s="24" t="n">
+      <c r="V5" s="25" t="n">
         <v>1.5</v>
       </c>
-      <c r="W5" s="24" t="n">
+      <c r="W5" s="25" t="n">
         <v>1.5</v>
       </c>
-      <c r="X5" s="24" t="n">
+      <c r="X5" s="25" t="n">
         <v>1.5</v>
       </c>
-      <c r="Y5" s="24" t="n">
+      <c r="Y5" s="25" t="n">
         <v>1.5</v>
       </c>
       <c r="Z5" s="20" t="n">
@@ -6992,28 +6979,28 @@
       <c r="B6" s="2" t="n">
         <v>0.001</v>
       </c>
-      <c r="C6" s="25" t="n">
+      <c r="C6" s="26" t="n">
         <v>0.005</v>
       </c>
-      <c r="D6" s="25" t="n">
+      <c r="D6" s="26" t="n">
         <v>0.003</v>
       </c>
-      <c r="E6" s="25" t="n">
+      <c r="E6" s="26" t="n">
         <v>0.002</v>
       </c>
-      <c r="F6" s="25" t="n">
+      <c r="F6" s="26" t="n">
         <v>0.002</v>
       </c>
-      <c r="G6" s="25" t="n">
+      <c r="G6" s="26" t="n">
         <v>0.002</v>
       </c>
-      <c r="H6" s="25" t="n">
+      <c r="H6" s="26" t="n">
         <v>0.002</v>
       </c>
-      <c r="I6" s="25" t="n">
+      <c r="I6" s="26" t="n">
         <v>0.002</v>
       </c>
-      <c r="J6" s="25" t="n">
+      <c r="J6" s="26" t="n">
         <v>0.002</v>
       </c>
       <c r="K6" s="20" t="n">
@@ -7022,7 +7009,7 @@
       <c r="L6" s="20" t="n">
         <v>0.002</v>
       </c>
-      <c r="M6" s="24" t="n">
+      <c r="M6" s="25" t="n">
         <v>0.002</v>
       </c>
       <c r="N6" s="20" t="n">
@@ -7031,7 +7018,7 @@
       <c r="O6" s="20" t="n">
         <v>0.002</v>
       </c>
-      <c r="P6" s="26" t="n">
+      <c r="P6" s="24" t="n">
         <v>0.0025</v>
       </c>
       <c r="Q6" s="23" t="n">
@@ -7058,7 +7045,7 @@
       <c r="Y6" s="23" t="n">
         <v>0.002</v>
       </c>
-      <c r="Z6" s="26" t="n">
+      <c r="Z6" s="24" t="n">
         <v>0.003</v>
       </c>
     </row>
@@ -7099,7 +7086,7 @@
       <c r="L7" s="20" t="n">
         <v>0.5</v>
       </c>
-      <c r="M7" s="24" t="n">
+      <c r="M7" s="25" t="n">
         <v>0.5</v>
       </c>
       <c r="N7" s="20" t="n">
@@ -7111,31 +7098,31 @@
       <c r="P7" s="20" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q7" s="24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R7" s="24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T7" s="24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U7" s="24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V7" s="24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="W7" s="24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="X7" s="24" t="n">
+      <c r="Q7" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R7" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T7" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U7" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V7" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W7" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X7" s="25" t="n">
         <v>0.5</v>
       </c>
       <c r="Y7" s="23" t="n">
         <v>0.4</v>
       </c>
-      <c r="Z7" s="26" t="n">
+      <c r="Z7" s="24" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -7176,7 +7163,7 @@
       <c r="L8" s="20" t="n">
         <v>0.7</v>
       </c>
-      <c r="M8" s="24" t="n">
+      <c r="M8" s="25" t="n">
         <v>0.7</v>
       </c>
       <c r="N8" s="20" t="n">
@@ -7188,31 +7175,31 @@
       <c r="P8" s="20" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q8" s="24" t="n">
+      <c r="Q8" s="25" t="n">
         <v>0.7</v>
       </c>
-      <c r="R8" s="24" t="n">
+      <c r="R8" s="25" t="n">
         <v>0.7</v>
       </c>
-      <c r="T8" s="24" t="n">
+      <c r="T8" s="25" t="n">
         <v>0.7</v>
       </c>
-      <c r="U8" s="24" t="n">
+      <c r="U8" s="25" t="n">
         <v>0.7</v>
       </c>
-      <c r="V8" s="24" t="n">
+      <c r="V8" s="25" t="n">
         <v>0.7</v>
       </c>
-      <c r="W8" s="24" t="n">
+      <c r="W8" s="25" t="n">
         <v>0.7</v>
       </c>
-      <c r="X8" s="24" t="n">
+      <c r="X8" s="25" t="n">
         <v>0.6</v>
       </c>
       <c r="Y8" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="Z8" s="26" t="n">
+      <c r="Z8" s="24" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7223,46 +7210,46 @@
       <c r="B9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="25" t="n">
+      <c r="C9" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="E9" s="25" t="n">
-        <v>6</v>
-      </c>
-      <c r="F9" s="25" t="n">
+      <c r="D9" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="G9" s="25" t="n">
+      <c r="G9" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="H9" s="25" t="n">
+      <c r="H9" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="I9" s="25" t="n">
+      <c r="I9" s="26" t="n">
         <v>12</v>
       </c>
-      <c r="J9" s="25" t="n">
+      <c r="J9" s="26" t="n">
         <v>15</v>
       </c>
-      <c r="K9" s="26" t="n">
+      <c r="K9" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="L9" s="26" t="n">
+      <c r="L9" s="24" t="n">
         <v>10</v>
       </c>
       <c r="M9" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="N9" s="26" t="n">
+      <c r="N9" s="24" t="n">
         <v>12</v>
       </c>
-      <c r="O9" s="26" t="n">
-        <v>6</v>
-      </c>
-      <c r="P9" s="26" t="n">
+      <c r="O9" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="P9" s="24" t="n">
         <v>7</v>
       </c>
       <c r="Q9" s="23" t="n">
@@ -7289,7 +7276,7 @@
       <c r="Y9" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="Z9" s="26" t="n">
+      <c r="Z9" s="24" t="n">
         <v>10</v>
       </c>
     </row>
@@ -7330,7 +7317,7 @@
       <c r="L10" s="20" t="n">
         <v>1.2</v>
       </c>
-      <c r="M10" s="24" t="n">
+      <c r="M10" s="25" t="n">
         <v>1.2</v>
       </c>
       <c r="N10" s="20" t="n">
@@ -7342,7 +7329,7 @@
       <c r="P10" s="20" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q10" s="24" t="n">
+      <c r="Q10" s="25" t="n">
         <v>1.2</v>
       </c>
       <c r="R10" s="23" t="n">
@@ -7366,7 +7353,7 @@
       <c r="Y10" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="Z10" s="26" t="n">
+      <c r="Z10" s="24" t="n">
         <v>6</v>
       </c>
     </row>
@@ -7407,7 +7394,7 @@
       <c r="L11" s="20" t="n">
         <v>0.6</v>
       </c>
-      <c r="M11" s="24" t="n">
+      <c r="M11" s="25" t="n">
         <v>0.6</v>
       </c>
       <c r="N11" s="20" t="n">
@@ -7419,7 +7406,7 @@
       <c r="P11" s="20" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q11" s="24" t="n">
+      <c r="Q11" s="25" t="n">
         <v>0.6</v>
       </c>
       <c r="R11" s="23" t="n">
@@ -7443,7 +7430,7 @@
       <c r="Y11" s="23" t="n">
         <v>0.1</v>
       </c>
-      <c r="Z11" s="26" t="n">
+      <c r="Z11" s="24" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -7457,22 +7444,22 @@
       <c r="C12" s="2" t="n">
         <v>10000</v>
       </c>
-      <c r="D12" s="25" t="n">
+      <c r="D12" s="26" t="n">
         <v>50000</v>
       </c>
-      <c r="E12" s="25" t="n">
+      <c r="E12" s="26" t="n">
         <v>50000</v>
       </c>
-      <c r="F12" s="25" t="n">
+      <c r="F12" s="26" t="n">
         <v>10000</v>
       </c>
-      <c r="G12" s="25" t="n">
+      <c r="G12" s="26" t="n">
         <v>10000</v>
       </c>
-      <c r="H12" s="25" t="n">
+      <c r="H12" s="26" t="n">
         <v>5000</v>
       </c>
-      <c r="I12" s="25" t="n">
+      <c r="I12" s="26" t="n">
         <v>5000</v>
       </c>
       <c r="J12" s="19" t="n">
@@ -7484,7 +7471,7 @@
       <c r="L12" s="20" t="n">
         <v>5000</v>
       </c>
-      <c r="M12" s="24" t="n">
+      <c r="M12" s="25" t="n">
         <v>5000</v>
       </c>
       <c r="N12" s="20" t="n">
@@ -7520,7 +7507,7 @@
       <c r="Y12" s="23" t="n">
         <v>2500</v>
       </c>
-      <c r="Z12" s="26" t="n">
+      <c r="Z12" s="24" t="n">
         <v>2500</v>
       </c>
     </row>
@@ -7594,22 +7581,22 @@
       <c r="J14" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="K14" s="26" t="n">
-        <v>6</v>
-      </c>
-      <c r="L14" s="26" t="n">
+      <c r="K14" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="L14" s="24" t="n">
         <v>12</v>
       </c>
       <c r="M14" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="N14" s="26" t="n">
+      <c r="N14" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="O14" s="26" t="n">
+      <c r="O14" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="P14" s="26" t="n">
+      <c r="P14" s="24" t="n">
         <v>9</v>
       </c>
       <c r="Q14" s="23" t="n">
@@ -7702,7 +7689,7 @@
       <c r="H16" s="32" t="s">
         <v>108</v>
       </c>
-      <c r="I16" s="22" t="s">
+      <c r="I16" s="24" t="s">
         <v>109</v>
       </c>
       <c r="S16" s="19" t="s">
@@ -7878,7 +7865,7 @@
       <c r="H21" s="36" t="n">
         <v>0.002</v>
       </c>
-      <c r="I21" s="26" t="n">
+      <c r="I21" s="24" t="n">
         <v>0.003</v>
       </c>
     </row>
@@ -7907,7 +7894,7 @@
       <c r="H22" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="I22" s="26" t="n">
+      <c r="I22" s="24" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -7936,7 +7923,7 @@
       <c r="H23" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="I23" s="26" t="n">
+      <c r="I23" s="24" t="n">
         <v>1</v>
       </c>
       <c r="V23" s="1" t="n">
@@ -7969,7 +7956,7 @@
       <c r="H24" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="I24" s="26" t="n">
+      <c r="I24" s="24" t="n">
         <v>8</v>
       </c>
     </row>
@@ -8254,7 +8241,7 @@
       <c r="A38" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B38" s="25" t="n">
+      <c r="B38" s="26" t="n">
         <v>0.002</v>
       </c>
       <c r="N38" s="1" t="n">
@@ -8282,7 +8269,7 @@
       <c r="A41" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B41" s="25" t="n">
+      <c r="B41" s="26" t="n">
         <v>9</v>
       </c>
     </row>
@@ -8306,7 +8293,7 @@
       <c r="A44" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B44" s="25" t="n">
+      <c r="B44" s="26" t="n">
         <v>2500</v>
       </c>
     </row>
@@ -8355,7 +8342,7 @@
       <c r="I49" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="J49" s="25" t="s">
+      <c r="J49" s="24" t="s">
         <v>109</v>
       </c>
     </row>
@@ -8387,7 +8374,7 @@
       <c r="I50" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="J50" s="19" t="n">
+      <c r="J50" s="20" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -8419,7 +8406,7 @@
       <c r="I51" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J51" s="19" t="n">
+      <c r="J51" s="20" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8451,7 +8438,7 @@
       <c r="I52" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="J52" s="19" t="n">
+      <c r="J52" s="20" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -8483,7 +8470,7 @@
       <c r="I53" s="19" t="n">
         <v>1.5</v>
       </c>
-      <c r="J53" s="19" t="n">
+      <c r="J53" s="20" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -8491,31 +8478,31 @@
       <c r="A54" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B54" s="25" t="n">
+      <c r="B54" s="26" t="n">
         <v>0.002</v>
       </c>
-      <c r="C54" s="25" t="n">
+      <c r="C54" s="26" t="n">
         <v>0.002</v>
       </c>
-      <c r="D54" s="25" t="n">
+      <c r="D54" s="26" t="n">
         <v>0.002</v>
       </c>
-      <c r="E54" s="25" t="n">
+      <c r="E54" s="26" t="n">
         <v>0.003</v>
       </c>
-      <c r="F54" s="25" t="n">
+      <c r="F54" s="26" t="n">
         <v>0.003</v>
       </c>
-      <c r="G54" s="25" t="n">
+      <c r="G54" s="26" t="n">
         <v>0.003</v>
       </c>
-      <c r="H54" s="25" t="n">
+      <c r="H54" s="26" t="n">
         <v>0.003</v>
       </c>
-      <c r="I54" s="25" t="n">
+      <c r="I54" s="26" t="n">
         <v>0.003</v>
       </c>
-      <c r="J54" s="25" t="n">
+      <c r="J54" s="24" t="n">
         <v>0.003</v>
       </c>
     </row>
@@ -8547,7 +8534,7 @@
       <c r="I55" s="19" t="n">
         <v>0.4</v>
       </c>
-      <c r="J55" s="19" t="n">
+      <c r="J55" s="20" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -8579,7 +8566,7 @@
       <c r="I56" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J56" s="19" t="n">
+      <c r="J56" s="20" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8587,31 +8574,31 @@
       <c r="A57" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B57" s="25" t="n">
+      <c r="B57" s="26" t="n">
         <v>9</v>
       </c>
-      <c r="C57" s="25" t="n">
+      <c r="C57" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="D57" s="25" t="n">
+      <c r="D57" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="E57" s="25" t="n">
+      <c r="E57" s="26" t="n">
         <v>12</v>
       </c>
-      <c r="F57" s="25" t="n">
+      <c r="F57" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="G57" s="25" t="n">
+      <c r="G57" s="26" t="n">
         <v>11</v>
       </c>
-      <c r="H57" s="25" t="n">
+      <c r="H57" s="26" t="n">
         <v>12</v>
       </c>
-      <c r="I57" s="25" t="n">
+      <c r="I57" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="J57" s="25" t="n">
+      <c r="J57" s="24" t="n">
         <v>10</v>
       </c>
     </row>
@@ -8643,7 +8630,7 @@
       <c r="I58" s="19" t="n">
         <v>1.2</v>
       </c>
-      <c r="J58" s="19" t="n">
+      <c r="J58" s="20" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -8675,7 +8662,7 @@
       <c r="I59" s="19" t="n">
         <v>0.6</v>
       </c>
-      <c r="J59" s="19" t="n">
+      <c r="J59" s="20" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -8683,31 +8670,31 @@
       <c r="A60" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B60" s="25" t="n">
+      <c r="B60" s="26" t="n">
         <v>2500</v>
       </c>
-      <c r="C60" s="25" t="n">
+      <c r="C60" s="26" t="n">
         <v>1000</v>
       </c>
-      <c r="D60" s="25" t="n">
+      <c r="D60" s="26" t="n">
         <v>1000</v>
       </c>
-      <c r="E60" s="25" t="n">
+      <c r="E60" s="26" t="n">
         <v>2500</v>
       </c>
-      <c r="F60" s="25" t="n">
+      <c r="F60" s="26" t="n">
         <v>2000</v>
       </c>
-      <c r="G60" s="25" t="n">
+      <c r="G60" s="26" t="n">
         <v>2500</v>
       </c>
-      <c r="H60" s="25" t="n">
+      <c r="H60" s="26" t="n">
         <v>2500</v>
       </c>
-      <c r="I60" s="25" t="n">
+      <c r="I60" s="26" t="n">
         <v>2500</v>
       </c>
-      <c r="J60" s="25" t="n">
+      <c r="J60" s="24" t="n">
         <v>2500</v>
       </c>
     </row>
@@ -8752,22 +8739,22 @@
       <c r="D63" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="E63" s="25" t="n">
+      <c r="E63" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="F63" s="25" t="n">
+      <c r="F63" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="G63" s="25" t="n">
+      <c r="G63" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="H63" s="25" t="n">
+      <c r="H63" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="I63" s="25" t="n">
+      <c r="I63" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="J63" s="25" t="n">
+      <c r="J63" s="24" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8784,22 +8771,22 @@
       <c r="D64" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="E64" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="F64" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="G64" s="25" t="n">
+      <c r="E64" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="F64" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G64" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="H64" s="25" t="n">
+      <c r="H64" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="I64" s="25" t="n">
+      <c r="I64" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="J64" s="25" t="n">
+      <c r="J64" s="24" t="n">
         <v>2</v>
       </c>
     </row>
@@ -8819,6 +8806,15 @@
       <c r="C68" s="22" t="s">
         <v>103</v>
       </c>
+      <c r="D68" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="E68" s="40" t="s">
+        <v>105</v>
+      </c>
+      <c r="F68" s="24" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="69" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2" t="s">
@@ -8830,6 +8826,15 @@
       <c r="C69" s="20" t="n">
         <v>0.5</v>
       </c>
+      <c r="D69" s="41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E69" s="41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F69" s="20" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="70" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2" t="s">
@@ -8841,6 +8846,15 @@
       <c r="C70" s="20" t="n">
         <v>1</v>
       </c>
+      <c r="D70" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" s="20" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="71" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2" t="s">
@@ -8852,6 +8866,15 @@
       <c r="C71" s="20" t="n">
         <v>0.5</v>
       </c>
+      <c r="D71" s="41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E71" s="41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F71" s="20" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="72" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2" t="s">
@@ -8863,19 +8886,34 @@
       <c r="C72" s="20" t="n">
         <v>1.5</v>
       </c>
+      <c r="D72" s="41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E72" s="41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F72" s="20" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="73" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B73" s="25" t="n">
+      <c r="B73" s="26" t="n">
         <v>0.002</v>
       </c>
-      <c r="C73" s="26" t="n">
+      <c r="C73" s="24" t="n">
         <v>0.002</v>
       </c>
-      <c r="D73" s="40" t="s">
-        <v>144</v>
+      <c r="D73" s="42" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="E73" s="42" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="F73" s="24" t="n">
+        <v>0.002</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8888,6 +8926,15 @@
       <c r="C74" s="20" t="n">
         <v>0.4</v>
       </c>
+      <c r="D74" s="41" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E74" s="41" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F74" s="20" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="75" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2" t="s">
@@ -8899,15 +8946,33 @@
       <c r="C75" s="20" t="n">
         <v>1</v>
       </c>
+      <c r="D75" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" s="20" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="76" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B76" s="25" t="n">
+      <c r="B76" s="26" t="n">
         <v>9</v>
       </c>
-      <c r="C76" s="41" t="n">
+      <c r="C76" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="D76" s="42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E76" s="42" t="n">
+        <v>10</v>
+      </c>
+      <c r="F76" s="24" t="n">
         <v>10</v>
       </c>
     </row>
@@ -8921,6 +8986,15 @@
       <c r="C77" s="20" t="n">
         <v>1.2</v>
       </c>
+      <c r="D77" s="41" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E77" s="41" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F77" s="20" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="78" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2" t="s">
@@ -8932,15 +9006,33 @@
       <c r="C78" s="20" t="n">
         <v>0.6</v>
       </c>
+      <c r="D78" s="41" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E78" s="41" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F78" s="20" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="79" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B79" s="25" t="n">
+      <c r="B79" s="26" t="n">
         <v>2500</v>
       </c>
-      <c r="C79" s="26" t="n">
+      <c r="C79" s="24" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D79" s="42" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E79" s="42" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F79" s="24" t="n">
         <v>2500</v>
       </c>
     </row>
@@ -8949,23 +9041,38 @@
         <v>126</v>
       </c>
       <c r="B80" s="37"/>
-      <c r="C80" s="42"/>
+      <c r="C80" s="28"/>
+      <c r="D80" s="28"/>
+      <c r="E80" s="28"/>
+      <c r="F80" s="28"/>
     </row>
     <row r="81" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="29" t="s">
         <v>128</v>
       </c>
       <c r="B81" s="39"/>
-      <c r="C81" s="26"/>
+      <c r="C81" s="30"/>
+      <c r="D81" s="30"/>
+      <c r="E81" s="30"/>
+      <c r="F81" s="30"/>
     </row>
     <row r="82" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="B82" s="25" t="n">
+      <c r="B82" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="C82" s="26" t="n">
+      <c r="C82" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D82" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="E82" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="F82" s="24" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8973,10 +9080,19 @@
       <c r="A83" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="B83" s="25" t="n">
+      <c r="B83" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="C83" s="26" t="n">
+      <c r="C83" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D83" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="E83" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="F83" s="24" t="n">
         <v>2</v>
       </c>
     </row>
@@ -8988,7 +9104,7 @@
     </row>
     <row r="86" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B86" s="18" t="s">
         <v>102</v>
@@ -9002,7 +9118,7 @@
       <c r="E86" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="F86" s="25" t="s">
+      <c r="F86" s="24" t="s">
         <v>106</v>
       </c>
     </row>
@@ -9022,7 +9138,7 @@
       <c r="E87" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="F87" s="19" t="n">
+      <c r="F87" s="20" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -9042,7 +9158,7 @@
       <c r="E88" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="F88" s="19" t="n">
+      <c r="F88" s="20" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9062,7 +9178,7 @@
       <c r="E89" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="F89" s="19" t="n">
+      <c r="F89" s="20" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -9082,7 +9198,7 @@
       <c r="E90" s="19" t="n">
         <v>1.5</v>
       </c>
-      <c r="F90" s="19" t="n">
+      <c r="F90" s="20" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -9090,19 +9206,19 @@
       <c r="A91" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B91" s="25" t="n">
+      <c r="B91" s="26" t="n">
         <v>0.002</v>
       </c>
-      <c r="C91" s="25" t="n">
+      <c r="C91" s="26" t="n">
         <v>0.003</v>
       </c>
-      <c r="D91" s="25" t="n">
+      <c r="D91" s="26" t="n">
         <v>0.003</v>
       </c>
-      <c r="E91" s="25" t="n">
+      <c r="E91" s="26" t="n">
         <v>0.003</v>
       </c>
-      <c r="F91" s="25" t="n">
+      <c r="F91" s="24" t="n">
         <v>0.003</v>
       </c>
     </row>
@@ -9122,7 +9238,7 @@
       <c r="E92" s="19" t="n">
         <v>0.4</v>
       </c>
-      <c r="F92" s="19" t="n">
+      <c r="F92" s="20" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -9142,7 +9258,7 @@
       <c r="E93" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="F93" s="19" t="n">
+      <c r="F93" s="20" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9150,19 +9266,19 @@
       <c r="A94" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B94" s="25" t="n">
+      <c r="B94" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="C94" s="25" t="n">
-        <v>6</v>
-      </c>
-      <c r="D94" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="E94" s="25" t="n">
+      <c r="C94" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="D94" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E94" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="F94" s="25" t="n">
+      <c r="F94" s="24" t="n">
         <v>4</v>
       </c>
     </row>
@@ -9182,7 +9298,7 @@
       <c r="E95" s="19" t="n">
         <v>1.2</v>
       </c>
-      <c r="F95" s="19" t="n">
+      <c r="F95" s="20" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -9202,7 +9318,7 @@
       <c r="E96" s="19" t="n">
         <v>0.6</v>
       </c>
-      <c r="F96" s="19" t="n">
+      <c r="F96" s="20" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -9210,19 +9326,19 @@
       <c r="A97" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B97" s="25" t="n">
+      <c r="B97" s="26" t="n">
         <v>2500</v>
       </c>
-      <c r="C97" s="25" t="n">
+      <c r="C97" s="26" t="n">
         <v>2000</v>
       </c>
-      <c r="D97" s="25" t="n">
+      <c r="D97" s="26" t="n">
         <v>2000</v>
       </c>
-      <c r="E97" s="25" t="n">
+      <c r="E97" s="26" t="n">
         <v>5000</v>
       </c>
-      <c r="F97" s="25" t="n">
+      <c r="F97" s="24" t="n">
         <v>5000</v>
       </c>
     </row>
@@ -9253,16 +9369,16 @@
       <c r="B100" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="C100" s="25" t="n">
+      <c r="C100" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="D100" s="25" t="n">
+      <c r="D100" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="E100" s="25" t="n">
+      <c r="E100" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="F100" s="25" t="n">
+      <c r="F100" s="24" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9273,16 +9389,16 @@
       <c r="B101" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="C101" s="25" t="n">
+      <c r="C101" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="D101" s="25" t="n">
+      <c r="D101" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="E101" s="25" t="n">
+      <c r="E101" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="F101" s="25" t="n">
+      <c r="F101" s="24" t="n">
         <v>2</v>
       </c>
     </row>
@@ -9293,13 +9409,25 @@
     </row>
     <row r="104" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B104" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="C104" s="1" t="s">
+      <c r="C104" s="18" t="s">
         <v>103</v>
+      </c>
+      <c r="D104" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="E104" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="F104" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="G104" s="24" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9309,6 +9437,21 @@
       <c r="B105" s="19" t="n">
         <v>0.5</v>
       </c>
+      <c r="C105" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D105" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E105" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F105" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G105" s="20" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="106" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="2" t="s">
@@ -9317,6 +9460,21 @@
       <c r="B106" s="19" t="n">
         <v>1</v>
       </c>
+      <c r="C106" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D106" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E106" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F106" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" s="20" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="107" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="2" t="s">
@@ -9325,6 +9483,21 @@
       <c r="B107" s="19" t="n">
         <v>0.5</v>
       </c>
+      <c r="C107" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D107" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E107" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F107" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G107" s="20" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="108" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="2" t="s">
@@ -9333,16 +9506,43 @@
       <c r="B108" s="19" t="n">
         <v>1.5</v>
       </c>
+      <c r="C108" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D108" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E108" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F108" s="20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G108" s="20" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="109" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B109" s="25" t="n">
+      <c r="B109" s="26" t="n">
         <v>0.002</v>
       </c>
-      <c r="C109" s="43" t="s">
-        <v>147</v>
+      <c r="C109" s="26" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D109" s="26" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="E109" s="26" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="F109" s="24" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="G109" s="24" t="n">
+        <v>0.002</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9352,6 +9552,21 @@
       <c r="B110" s="19" t="n">
         <v>0.4</v>
       </c>
+      <c r="C110" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D110" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E110" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F110" s="20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G110" s="20" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="111" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="2" t="s">
@@ -9360,16 +9575,43 @@
       <c r="B111" s="19" t="n">
         <v>1</v>
       </c>
+      <c r="C111" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D111" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E111" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F111" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" s="20" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="112" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B112" s="25" t="n">
+      <c r="B112" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="C112" s="1" t="s">
-        <v>148</v>
+      <c r="C112" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="D112" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="E112" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="F112" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="G112" s="24" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9379,6 +9621,21 @@
       <c r="B113" s="19" t="n">
         <v>1.2</v>
       </c>
+      <c r="C113" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D113" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E113" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F113" s="20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G113" s="20" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="114" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="2" t="s">
@@ -9387,13 +9644,43 @@
       <c r="B114" s="19" t="n">
         <v>0.6</v>
       </c>
+      <c r="C114" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D114" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E114" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F114" s="20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G114" s="20" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="115" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B115" s="25" t="n">
+      <c r="B115" s="26" t="n">
         <v>5000</v>
+      </c>
+      <c r="C115" s="26" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D115" s="26" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E115" s="26" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F115" s="24" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G115" s="24" t="n">
+        <v>10000</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9401,18 +9688,43 @@
         <v>126</v>
       </c>
       <c r="B116" s="37"/>
+      <c r="C116" s="37"/>
+      <c r="D116" s="37"/>
+      <c r="E116" s="37"/>
+      <c r="F116" s="37"/>
+      <c r="G116" s="37"/>
     </row>
     <row r="117" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="29" t="s">
         <v>128</v>
       </c>
       <c r="B117" s="39"/>
+      <c r="C117" s="39"/>
+      <c r="D117" s="39"/>
+      <c r="E117" s="39"/>
+      <c r="F117" s="39"/>
+      <c r="G117" s="39"/>
     </row>
     <row r="118" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="B118" s="25" t="n">
+      <c r="B118" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C118" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D118" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E118" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F118" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="G118" s="24" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9420,7 +9732,22 @@
       <c r="A119" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="B119" s="25" t="n">
+      <c r="B119" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="C119" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D119" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E119" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F119" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G119" s="24" t="n">
         <v>2</v>
       </c>
     </row>

--- a/parameters script.xlsx
+++ b/parameters script.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="144">
   <si>
     <t xml:space="preserve">6h 3</t>
   </si>
@@ -442,12 +442,6 @@
   </si>
   <si>
     <t xml:space="preserve">*0.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2-4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2-3</t>
   </si>
   <si>
     <t xml:space="preserve">AUT 2</t>
@@ -473,7 +467,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0%"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -524,8 +518,32 @@
       <family val="0"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF2A6099"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -547,7 +565,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FFB2B2B2"/>
+        <bgColor rgb="FF81D41A"/>
       </patternFill>
     </fill>
     <fill>
@@ -571,7 +589,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF999999"/>
-        <bgColor rgb="FFB2B2B2"/>
+        <bgColor rgb="FF808080"/>
       </patternFill>
     </fill>
     <fill>
@@ -588,8 +606,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF81D41A"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFB2B2B2"/>
         <bgColor rgb="FFB4C7DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF808080"/>
+        <bgColor rgb="FF999999"/>
       </patternFill>
     </fill>
   </fills>
@@ -676,7 +706,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="50">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -813,6 +843,14 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -821,11 +859,19 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="11" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="12" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -833,19 +879,31 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -875,14 +933,14 @@
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFB4C7DC"/>
-      <rgbColor rgb="FF5B9BD5"/>
+      <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF729FCF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFFFCC"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FF2A6099"/>
       <rgbColor rgb="FFBDD7EE"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
@@ -896,20 +954,20 @@
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FF92D050"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFB2B2B2"/>
       <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF92D050"/>
+      <rgbColor rgb="FF81D41A"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF860D"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF999999"/>
       <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF5B9BD5"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
@@ -932,9 +990,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>471240</xdr:colOff>
+      <xdr:colOff>470880</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>28440</xdr:rowOff>
+      <xdr:rowOff>28080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -948,7 +1006,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6183720" y="130320"/>
-          <a:ext cx="7992000" cy="263880"/>
+          <a:ext cx="7991640" cy="263520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7692,6 +7750,10 @@
       <c r="I16" s="24" t="s">
         <v>109</v>
       </c>
+      <c r="J16" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="K16" s="35"/>
       <c r="S16" s="19" t="s">
         <v>136</v>
       </c>
@@ -7721,10 +7783,10 @@
       <c r="A17" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B17" s="34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C17" s="35" t="n">
+      <c r="B17" s="36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C17" s="37" t="n">
         <v>0.5</v>
       </c>
       <c r="D17" s="32" t="n">
@@ -7745,6 +7807,10 @@
       <c r="I17" s="22" t="n">
         <v>0.5</v>
       </c>
+      <c r="J17" s="38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K17" s="39"/>
       <c r="V17" s="27"/>
       <c r="W17" s="1" t="s">
         <v>137</v>
@@ -7757,10 +7823,10 @@
       <c r="A18" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B18" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" s="35" t="n">
+      <c r="B18" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="37" t="n">
         <v>1</v>
       </c>
       <c r="D18" s="32" t="n">
@@ -7781,15 +7847,19 @@
       <c r="I18" s="22" t="n">
         <v>1</v>
       </c>
+      <c r="J18" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" s="39"/>
     </row>
     <row r="19" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B19" s="34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C19" s="35" t="n">
+      <c r="B19" s="36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C19" s="37" t="n">
         <v>0.5</v>
       </c>
       <c r="D19" s="32" t="n">
@@ -7810,15 +7880,19 @@
       <c r="I19" s="22" t="n">
         <v>0.5</v>
       </c>
+      <c r="J19" s="38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K19" s="39"/>
     </row>
     <row r="20" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B20" s="34" t="n">
+      <c r="B20" s="36" t="n">
         <v>1.5</v>
       </c>
-      <c r="C20" s="35" t="n">
+      <c r="C20" s="37" t="n">
         <v>1.5</v>
       </c>
       <c r="D20" s="32" t="n">
@@ -7839,44 +7913,52 @@
       <c r="I20" s="22" t="n">
         <v>1.5</v>
       </c>
+      <c r="J20" s="38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K20" s="39"/>
     </row>
     <row r="21" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B21" s="36" t="n">
+      <c r="B21" s="40" t="n">
         <v>0.002</v>
       </c>
-      <c r="C21" s="35" t="n">
+      <c r="C21" s="37" t="n">
         <v>0.002</v>
       </c>
       <c r="D21" s="32" t="n">
         <v>0.002</v>
       </c>
-      <c r="E21" s="35" t="n">
+      <c r="E21" s="37" t="n">
         <v>0.0015</v>
       </c>
-      <c r="F21" s="35" t="n">
+      <c r="F21" s="37" t="n">
         <v>0.002</v>
       </c>
-      <c r="G21" s="36" t="n">
+      <c r="G21" s="40" t="n">
         <v>0.002</v>
       </c>
-      <c r="H21" s="36" t="n">
+      <c r="H21" s="40" t="n">
         <v>0.002</v>
       </c>
       <c r="I21" s="24" t="n">
         <v>0.003</v>
       </c>
+      <c r="J21" s="34" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="K21" s="35"/>
     </row>
     <row r="22" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B22" s="34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C22" s="35" t="n">
+      <c r="B22" s="36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C22" s="37" t="n">
         <v>0.5</v>
       </c>
       <c r="D22" s="32" t="n">
@@ -7897,35 +7979,43 @@
       <c r="I22" s="24" t="n">
         <v>0.4</v>
       </c>
+      <c r="J22" s="34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K22" s="35"/>
     </row>
     <row r="23" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B23" s="34" t="n">
+      <c r="B23" s="36" t="n">
         <v>0.7</v>
       </c>
-      <c r="C23" s="35" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D23" s="36" t="n">
+      <c r="C23" s="37" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D23" s="40" t="n">
         <v>0.8</v>
       </c>
-      <c r="E23" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="36" t="n">
+      <c r="E23" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="40" t="n">
         <v>1</v>
       </c>
       <c r="I23" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="J23" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" s="35"/>
       <c r="V23" s="1" t="n">
         <f aca="false">1.233-0.553</f>
         <v>0.68</v>
@@ -7935,39 +8025,43 @@
       <c r="A24" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B24" s="36" t="n">
+      <c r="B24" s="40" t="n">
         <v>9</v>
       </c>
-      <c r="C24" s="35" t="n">
+      <c r="C24" s="37" t="n">
         <v>9</v>
       </c>
-      <c r="D24" s="36" t="n">
+      <c r="D24" s="40" t="n">
         <v>8</v>
       </c>
-      <c r="E24" s="35" t="n">
+      <c r="E24" s="37" t="n">
         <v>8</v>
       </c>
-      <c r="F24" s="35" t="n">
+      <c r="F24" s="37" t="n">
         <v>8</v>
       </c>
-      <c r="G24" s="36" t="n">
+      <c r="G24" s="40" t="n">
         <v>8</v>
       </c>
-      <c r="H24" s="36" t="n">
+      <c r="H24" s="40" t="n">
         <v>8</v>
       </c>
       <c r="I24" s="24" t="n">
         <v>8</v>
       </c>
+      <c r="J24" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="K24" s="35"/>
     </row>
     <row r="25" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B25" s="34" t="n">
+      <c r="B25" s="36" t="n">
         <v>1.2</v>
       </c>
-      <c r="C25" s="35" t="n">
+      <c r="C25" s="37" t="n">
         <v>1.2</v>
       </c>
       <c r="D25" s="32" t="n">
@@ -7988,15 +8082,19 @@
       <c r="I25" s="22" t="n">
         <v>1.2</v>
       </c>
+      <c r="J25" s="38" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K25" s="39"/>
     </row>
     <row r="26" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B26" s="34" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C26" s="35" t="n">
+      <c r="B26" s="36" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C26" s="37" t="n">
         <v>0.6</v>
       </c>
       <c r="D26" s="32" t="n">
@@ -8017,15 +8115,19 @@
       <c r="I26" s="22" t="n">
         <v>0.6</v>
       </c>
+      <c r="J26" s="38" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K26" s="39"/>
     </row>
     <row r="27" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B27" s="36" t="n">
+      <c r="B27" s="40" t="n">
         <v>2500</v>
       </c>
-      <c r="C27" s="35" t="n">
+      <c r="C27" s="37" t="n">
         <v>2500</v>
       </c>
       <c r="D27" s="32" t="n">
@@ -8046,77 +8148,50 @@
       <c r="I27" s="22" t="n">
         <v>2500</v>
       </c>
-      <c r="J27" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="O27" s="1" t="s">
-        <v>140</v>
-      </c>
+      <c r="J27" s="38" t="n">
+        <v>2500</v>
+      </c>
+      <c r="K27" s="39"/>
+      <c r="O27" s="1"/>
     </row>
     <row r="28" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="B28" s="37"/>
+      <c r="B28" s="41"/>
       <c r="C28" s="30"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="38"/>
-      <c r="H28" s="38"/>
-      <c r="I28" s="22"/>
-      <c r="J28" s="1" t="n">
-        <f aca="false">1.658-1.02</f>
-        <v>0.638</v>
-      </c>
-      <c r="L28" s="1" t="n">
-        <v>11657</v>
-      </c>
-      <c r="M28" s="1" t="n">
-        <v>11803</v>
-      </c>
-      <c r="O28" s="1" t="n">
-        <v>11276</v>
-      </c>
-      <c r="P28" s="1" t="n">
-        <v>11385</v>
-      </c>
-      <c r="R28" s="1" t="n">
-        <f aca="false">1.743-1.02</f>
-        <v>0.723</v>
-      </c>
-      <c r="S28" s="1" t="n">
-        <v>0.700903</v>
-      </c>
+      <c r="D28" s="42"/>
+      <c r="E28" s="42"/>
+      <c r="F28" s="42"/>
+      <c r="G28" s="42"/>
+      <c r="H28" s="42"/>
+      <c r="I28" s="42"/>
+      <c r="J28" s="43"/>
+      <c r="K28" s="39"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+      <c r="R28" s="1"/>
+      <c r="S28" s="1"/>
     </row>
     <row r="29" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="B29" s="39"/>
+      <c r="B29" s="44"/>
       <c r="C29" s="30"/>
-      <c r="D29" s="38"/>
-      <c r="E29" s="38"/>
-      <c r="F29" s="38"/>
-      <c r="G29" s="38"/>
-      <c r="H29" s="38"/>
-      <c r="I29" s="22"/>
-      <c r="J29" s="1" t="n">
-        <f aca="false">1-(0.588586/0.638)</f>
-        <v>0.0774514106583072</v>
-      </c>
-      <c r="M29" s="1" t="n">
-        <f aca="false">1-(L28/M28)</f>
-        <v>0.0123697365076676</v>
-      </c>
-      <c r="O29" s="1" t="n">
-        <f aca="false">1-(O28/P28)</f>
-        <v>0.0095740008783487</v>
-      </c>
-      <c r="R29" s="1" t="n">
-        <f aca="false">1-(S28/R28)</f>
-        <v>0.0305629322268327</v>
-      </c>
+      <c r="D29" s="42"/>
+      <c r="E29" s="42"/>
+      <c r="F29" s="42"/>
+      <c r="G29" s="42"/>
+      <c r="H29" s="42"/>
+      <c r="I29" s="42"/>
+      <c r="J29" s="43"/>
+      <c r="K29" s="39"/>
+      <c r="M29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="R29" s="1"/>
     </row>
     <row r="30" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="29" t="s">
@@ -8125,7 +8200,7 @@
       <c r="B30" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C30" s="35" t="n">
+      <c r="C30" s="37" t="n">
         <v>1</v>
       </c>
       <c r="D30" s="32" t="n">
@@ -8146,6 +8221,10 @@
       <c r="I30" s="22" t="n">
         <v>1</v>
       </c>
+      <c r="J30" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" s="39"/>
     </row>
     <row r="31" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="29" t="s">
@@ -8154,7 +8233,7 @@
       <c r="B31" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="C31" s="35" t="n">
+      <c r="C31" s="37" t="n">
         <v>2</v>
       </c>
       <c r="D31" s="32" t="n">
@@ -8175,31 +8254,29 @@
       <c r="I31" s="22" t="n">
         <v>2</v>
       </c>
+      <c r="J31" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" s="39"/>
     </row>
     <row r="32" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="M32" s="1" t="n">
-        <f aca="false">1.446-0.68</f>
-        <v>0.766</v>
-      </c>
-      <c r="N32" s="1" t="n">
-        <f aca="false">1.148-0.595</f>
-        <v>0.553</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="J32" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
     </row>
     <row r="33" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B33" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="J33" s="1" t="n">
-        <f aca="false">1.701-1.063</f>
-        <v>0.638</v>
-      </c>
+      <c r="J33" s="1"/>
     </row>
     <row r="34" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
@@ -8208,10 +8285,7 @@
       <c r="B34" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="J34" s="1" t="n">
-        <f aca="false">1-(J33/0.78)</f>
-        <v>0.182051282051282</v>
-      </c>
+      <c r="J34" s="1"/>
     </row>
     <row r="35" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
@@ -8244,10 +8318,7 @@
       <c r="B38" s="26" t="n">
         <v>0.002</v>
       </c>
-      <c r="N38" s="1" t="n">
-        <f aca="false">0.85-0.34</f>
-        <v>0.51</v>
-      </c>
+      <c r="N38" s="1"/>
     </row>
     <row r="39" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
@@ -8301,13 +8372,13 @@
       <c r="A45" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="B45" s="37"/>
+      <c r="B45" s="41"/>
     </row>
     <row r="46" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="B46" s="39"/>
+      <c r="B46" s="44"/>
     </row>
     <row r="48" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="1" t="s">
@@ -8316,7 +8387,7 @@
     </row>
     <row r="49" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B49" s="18" t="s">
         <v>102</v>
@@ -8344,6 +8415,12 @@
       </c>
       <c r="J49" s="24" t="s">
         <v>109</v>
+      </c>
+      <c r="K49" s="45" t="s">
+        <v>110</v>
+      </c>
+      <c r="L49" s="45" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8377,6 +8454,12 @@
       <c r="J50" s="20" t="n">
         <v>0.5</v>
       </c>
+      <c r="K50" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L50" s="46" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
@@ -8409,6 +8492,12 @@
       <c r="J51" s="20" t="n">
         <v>1</v>
       </c>
+      <c r="K51" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L51" s="46" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
@@ -8441,6 +8530,12 @@
       <c r="J52" s="20" t="n">
         <v>0.5</v>
       </c>
+      <c r="K52" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L52" s="46" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
@@ -8473,6 +8568,12 @@
       <c r="J53" s="20" t="n">
         <v>1.5</v>
       </c>
+      <c r="K53" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L53" s="46" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
@@ -8505,6 +8606,12 @@
       <c r="J54" s="24" t="n">
         <v>0.003</v>
       </c>
+      <c r="K54" s="45" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="L54" s="47" t="n">
+        <v>0.003</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
@@ -8537,6 +8644,12 @@
       <c r="J55" s="20" t="n">
         <v>0.4</v>
       </c>
+      <c r="K55" s="46" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L55" s="46" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
@@ -8569,6 +8682,12 @@
       <c r="J56" s="20" t="n">
         <v>1</v>
       </c>
+      <c r="K56" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L56" s="46" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
@@ -8601,6 +8720,12 @@
       <c r="J57" s="24" t="n">
         <v>10</v>
       </c>
+      <c r="K57" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="L57" s="45" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
@@ -8633,6 +8758,12 @@
       <c r="J58" s="20" t="n">
         <v>1.2</v>
       </c>
+      <c r="K58" s="46" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L58" s="46" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
@@ -8665,6 +8796,12 @@
       <c r="J59" s="20" t="n">
         <v>0.6</v>
       </c>
+      <c r="K59" s="46" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L59" s="46" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
@@ -8697,34 +8834,44 @@
       <c r="J60" s="24" t="n">
         <v>2500</v>
       </c>
+      <c r="K60" s="45" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L60" s="47" t="n">
+        <v>6000</v>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="B61" s="37"/>
-      <c r="C61" s="37"/>
-      <c r="D61" s="37"/>
-      <c r="E61" s="37"/>
-      <c r="F61" s="37"/>
-      <c r="G61" s="37"/>
-      <c r="H61" s="37"/>
-      <c r="I61" s="37"/>
-      <c r="J61" s="37"/>
+      <c r="B61" s="41"/>
+      <c r="C61" s="41"/>
+      <c r="D61" s="41"/>
+      <c r="E61" s="41"/>
+      <c r="F61" s="41"/>
+      <c r="G61" s="41"/>
+      <c r="H61" s="41"/>
+      <c r="I61" s="41"/>
+      <c r="J61" s="41"/>
+      <c r="K61" s="48"/>
+      <c r="L61" s="48"/>
     </row>
     <row r="62" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="B62" s="39"/>
-      <c r="C62" s="39"/>
-      <c r="D62" s="39"/>
-      <c r="E62" s="39"/>
-      <c r="F62" s="39"/>
-      <c r="G62" s="39"/>
-      <c r="H62" s="39"/>
-      <c r="I62" s="39"/>
-      <c r="J62" s="39"/>
+      <c r="B62" s="44"/>
+      <c r="C62" s="44"/>
+      <c r="D62" s="44"/>
+      <c r="E62" s="44"/>
+      <c r="F62" s="44"/>
+      <c r="G62" s="44"/>
+      <c r="H62" s="44"/>
+      <c r="I62" s="44"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="49"/>
+      <c r="L62" s="49"/>
     </row>
     <row r="63" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="19" t="s">
@@ -8757,6 +8904,12 @@
       <c r="J63" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="K63" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="L63" s="45" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="19" t="s">
@@ -8788,6 +8941,17 @@
       </c>
       <c r="J64" s="24" t="n">
         <v>2</v>
+      </c>
+      <c r="K64" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="L64" s="45" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L65" s="0" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8798,7 +8962,7 @@
     </row>
     <row r="68" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B68" s="18" t="s">
         <v>102</v>
@@ -8806,10 +8970,10 @@
       <c r="C68" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="D68" s="40" t="s">
+      <c r="D68" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="E68" s="40" t="s">
+      <c r="E68" s="18" t="s">
         <v>105</v>
       </c>
       <c r="F68" s="24" t="s">
@@ -8826,10 +8990,10 @@
       <c r="C69" s="20" t="n">
         <v>0.5</v>
       </c>
-      <c r="D69" s="41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E69" s="41" t="n">
+      <c r="D69" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E69" s="19" t="n">
         <v>0.5</v>
       </c>
       <c r="F69" s="20" t="n">
@@ -8846,10 +9010,10 @@
       <c r="C70" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D70" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E70" s="41" t="n">
+      <c r="D70" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" s="19" t="n">
         <v>1</v>
       </c>
       <c r="F70" s="20" t="n">
@@ -8866,10 +9030,10 @@
       <c r="C71" s="20" t="n">
         <v>0.5</v>
       </c>
-      <c r="D71" s="41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E71" s="41" t="n">
+      <c r="D71" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E71" s="19" t="n">
         <v>0.5</v>
       </c>
       <c r="F71" s="20" t="n">
@@ -8886,10 +9050,10 @@
       <c r="C72" s="20" t="n">
         <v>1.5</v>
       </c>
-      <c r="D72" s="41" t="n">
+      <c r="D72" s="19" t="n">
         <v>1.5</v>
       </c>
-      <c r="E72" s="41" t="n">
+      <c r="E72" s="19" t="n">
         <v>1.5</v>
       </c>
       <c r="F72" s="20" t="n">
@@ -8906,10 +9070,10 @@
       <c r="C73" s="24" t="n">
         <v>0.002</v>
       </c>
-      <c r="D73" s="42" t="n">
+      <c r="D73" s="26" t="n">
         <v>0.003</v>
       </c>
-      <c r="E73" s="42" t="n">
+      <c r="E73" s="26" t="n">
         <v>0.001</v>
       </c>
       <c r="F73" s="24" t="n">
@@ -8926,10 +9090,10 @@
       <c r="C74" s="20" t="n">
         <v>0.4</v>
       </c>
-      <c r="D74" s="41" t="n">
+      <c r="D74" s="19" t="n">
         <v>0.4</v>
       </c>
-      <c r="E74" s="41" t="n">
+      <c r="E74" s="19" t="n">
         <v>0.4</v>
       </c>
       <c r="F74" s="20" t="n">
@@ -8946,10 +9110,10 @@
       <c r="C75" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D75" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E75" s="41" t="n">
+      <c r="D75" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" s="19" t="n">
         <v>1</v>
       </c>
       <c r="F75" s="20" t="n">
@@ -8966,10 +9130,10 @@
       <c r="C76" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="D76" s="42" t="n">
+      <c r="D76" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="E76" s="42" t="n">
+      <c r="E76" s="26" t="n">
         <v>10</v>
       </c>
       <c r="F76" s="24" t="n">
@@ -8986,10 +9150,10 @@
       <c r="C77" s="20" t="n">
         <v>1.2</v>
       </c>
-      <c r="D77" s="41" t="n">
+      <c r="D77" s="19" t="n">
         <v>1.2</v>
       </c>
-      <c r="E77" s="41" t="n">
+      <c r="E77" s="19" t="n">
         <v>1.2</v>
       </c>
       <c r="F77" s="20" t="n">
@@ -9006,10 +9170,10 @@
       <c r="C78" s="20" t="n">
         <v>0.6</v>
       </c>
-      <c r="D78" s="41" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E78" s="41" t="n">
+      <c r="D78" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E78" s="19" t="n">
         <v>0.6</v>
       </c>
       <c r="F78" s="20" t="n">
@@ -9026,10 +9190,10 @@
       <c r="C79" s="24" t="n">
         <v>2500</v>
       </c>
-      <c r="D79" s="42" t="n">
+      <c r="D79" s="26" t="n">
         <v>2500</v>
       </c>
-      <c r="E79" s="42" t="n">
+      <c r="E79" s="26" t="n">
         <v>2500</v>
       </c>
       <c r="F79" s="24" t="n">
@@ -9040,7 +9204,7 @@
       <c r="A80" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="B80" s="37"/>
+      <c r="B80" s="41"/>
       <c r="C80" s="28"/>
       <c r="D80" s="28"/>
       <c r="E80" s="28"/>
@@ -9050,7 +9214,7 @@
       <c r="A81" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="B81" s="39"/>
+      <c r="B81" s="44"/>
       <c r="C81" s="30"/>
       <c r="D81" s="30"/>
       <c r="E81" s="30"/>
@@ -9066,10 +9230,10 @@
       <c r="C82" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="D82" s="42" t="n">
+      <c r="D82" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="E82" s="42" t="n">
+      <c r="E82" s="26" t="n">
         <v>3</v>
       </c>
       <c r="F82" s="24" t="n">
@@ -9086,10 +9250,10 @@
       <c r="C83" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="D83" s="42" t="n">
+      <c r="D83" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="E83" s="42" t="n">
+      <c r="E83" s="26" t="n">
         <v>2</v>
       </c>
       <c r="F83" s="24" t="n">
@@ -9104,7 +9268,7 @@
     </row>
     <row r="86" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B86" s="18" t="s">
         <v>102</v>
@@ -9346,21 +9510,21 @@
       <c r="A98" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="B98" s="37"/>
-      <c r="C98" s="37"/>
-      <c r="D98" s="37"/>
-      <c r="E98" s="37"/>
-      <c r="F98" s="37"/>
+      <c r="B98" s="41"/>
+      <c r="C98" s="41"/>
+      <c r="D98" s="41"/>
+      <c r="E98" s="41"/>
+      <c r="F98" s="41"/>
     </row>
     <row r="99" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="B99" s="39"/>
-      <c r="C99" s="39"/>
-      <c r="D99" s="39"/>
-      <c r="E99" s="39"/>
-      <c r="F99" s="39"/>
+      <c r="B99" s="44"/>
+      <c r="C99" s="44"/>
+      <c r="D99" s="44"/>
+      <c r="E99" s="44"/>
+      <c r="F99" s="44"/>
     </row>
     <row r="100" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="19" t="s">
@@ -9409,7 +9573,7 @@
     </row>
     <row r="104" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B104" s="18" t="s">
         <v>102</v>
@@ -9687,23 +9851,23 @@
       <c r="A116" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="B116" s="37"/>
-      <c r="C116" s="37"/>
-      <c r="D116" s="37"/>
-      <c r="E116" s="37"/>
-      <c r="F116" s="37"/>
-      <c r="G116" s="37"/>
+      <c r="B116" s="41"/>
+      <c r="C116" s="41"/>
+      <c r="D116" s="41"/>
+      <c r="E116" s="41"/>
+      <c r="F116" s="41"/>
+      <c r="G116" s="41"/>
     </row>
     <row r="117" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="B117" s="39"/>
-      <c r="C117" s="39"/>
-      <c r="D117" s="39"/>
-      <c r="E117" s="39"/>
-      <c r="F117" s="39"/>
-      <c r="G117" s="39"/>
+      <c r="B117" s="44"/>
+      <c r="C117" s="44"/>
+      <c r="D117" s="44"/>
+      <c r="E117" s="44"/>
+      <c r="F117" s="44"/>
+      <c r="G117" s="44"/>
     </row>
     <row r="118" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="19" t="s">

--- a/parameters script.xlsx
+++ b/parameters script.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="145">
   <si>
     <t xml:space="preserve">6h 3</t>
   </si>
@@ -448,6 +448,9 @@
   </si>
   <si>
     <t xml:space="preserve">0H-3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAST</t>
   </si>
   <si>
     <t xml:space="preserve">6H-1</t>
@@ -706,7 +709,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -907,6 +910,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -990,9 +997,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>470880</xdr:colOff>
+      <xdr:colOff>470520</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>28080</xdr:rowOff>
+      <xdr:rowOff>27720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1006,7 +1013,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6183720" y="130320"/>
-          <a:ext cx="7991640" cy="263520"/>
+          <a:ext cx="7991280" cy="263160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8263,7 +8270,7 @@
       <c r="B32" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="J32" s="0" t="s">
+      <c r="J32" s="1" t="s">
         <v>69</v>
       </c>
       <c r="M32" s="1"/>
@@ -8422,6 +8429,9 @@
       <c r="L49" s="45" t="s">
         <v>111</v>
       </c>
+      <c r="M49" s="45" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
@@ -8460,6 +8470,9 @@
       <c r="L50" s="46" t="n">
         <v>0.5</v>
       </c>
+      <c r="M50" s="46" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
@@ -8498,6 +8511,9 @@
       <c r="L51" s="46" t="n">
         <v>1</v>
       </c>
+      <c r="M51" s="46" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
@@ -8536,6 +8552,9 @@
       <c r="L52" s="46" t="n">
         <v>0.5</v>
       </c>
+      <c r="M52" s="46" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
@@ -8574,6 +8593,9 @@
       <c r="L53" s="46" t="n">
         <v>1.5</v>
       </c>
+      <c r="M53" s="46" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
@@ -8612,6 +8634,9 @@
       <c r="L54" s="47" t="n">
         <v>0.003</v>
       </c>
+      <c r="M54" s="47" t="n">
+        <v>0.003</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
@@ -8650,6 +8675,9 @@
       <c r="L55" s="46" t="n">
         <v>0.4</v>
       </c>
+      <c r="M55" s="46" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
@@ -8688,6 +8716,9 @@
       <c r="L56" s="46" t="n">
         <v>1</v>
       </c>
+      <c r="M56" s="46" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
@@ -8726,6 +8757,9 @@
       <c r="L57" s="45" t="n">
         <v>11</v>
       </c>
+      <c r="M57" s="45" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
@@ -8764,6 +8798,9 @@
       <c r="L58" s="46" t="n">
         <v>1.2</v>
       </c>
+      <c r="M58" s="46" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
@@ -8802,6 +8839,9 @@
       <c r="L59" s="46" t="n">
         <v>0.6</v>
       </c>
+      <c r="M59" s="46" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
@@ -8839,6 +8879,9 @@
       </c>
       <c r="L60" s="47" t="n">
         <v>6000</v>
+      </c>
+      <c r="M60" s="47" t="n">
+        <v>8000</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8856,6 +8899,7 @@
       <c r="J61" s="41"/>
       <c r="K61" s="48"/>
       <c r="L61" s="48"/>
+      <c r="M61" s="48"/>
     </row>
     <row r="62" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="29" t="s">
@@ -8872,6 +8916,7 @@
       <c r="J62" s="44"/>
       <c r="K62" s="49"/>
       <c r="L62" s="49"/>
+      <c r="M62" s="49"/>
     </row>
     <row r="63" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="19" t="s">
@@ -8910,6 +8955,9 @@
       <c r="L63" s="45" t="n">
         <v>3</v>
       </c>
+      <c r="M63" s="45" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="19" t="s">
@@ -8948,10 +8996,14 @@
       <c r="L64" s="45" t="n">
         <v>2</v>
       </c>
+      <c r="M64" s="45" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="65" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L65" s="0" t="s">
-        <v>73</v>
+      <c r="L65" s="1"/>
+      <c r="M65" s="50" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8962,7 +9014,7 @@
     </row>
     <row r="68" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B68" s="18" t="s">
         <v>102</v>
@@ -9268,7 +9320,7 @@
     </row>
     <row r="86" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B86" s="18" t="s">
         <v>102</v>
@@ -9573,7 +9625,7 @@
     </row>
     <row r="104" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B104" s="18" t="s">
         <v>102</v>

--- a/parameters script.xlsx
+++ b/parameters script.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="151">
   <si>
     <t xml:space="preserve">6h 3</t>
   </si>
@@ -460,15 +460,34 @@
   </si>
   <si>
     <t xml:space="preserve">3H-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L3-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XY sigma average</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L3-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L3-3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L3-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L3-5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0%"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -709,7 +728,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="56">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -910,7 +929,27 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -997,9 +1036,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>470520</xdr:colOff>
+      <xdr:colOff>470160</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>27720</xdr:rowOff>
+      <xdr:rowOff>27360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1013,7 +1052,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6183720" y="130320"/>
-          <a:ext cx="7991280" cy="263160"/>
+          <a:ext cx="7990920" cy="262800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6643,7 +6682,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Z119"/>
+  <dimension ref="A1:Z210"/>
   <sheetFormatPr defaultColWidth="8.90234375" defaultRowHeight="14.4" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.76"/>
@@ -9967,6 +10006,2240 @@
         <v>2</v>
       </c>
     </row>
+    <row r="121" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B121" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E121" s="51"/>
+    </row>
+    <row r="122" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B122" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="C122" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D122" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="E122" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="F122" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="G122" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="H122" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="I122" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="J122" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="K122" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="L122" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="M122" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="N122" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="O122" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="P122" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q122" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="R122" s="52"/>
+    </row>
+    <row r="123" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B123" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C123" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D123" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E123" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F123" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G123" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H123" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I123" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J123" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K123" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L123" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M123" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N123" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O123" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P123" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q123" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R123" s="53"/>
+    </row>
+    <row r="124" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B124" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C124" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D124" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E124" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F124" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G124" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H124" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I124" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J124" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K124" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L124" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M124" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N124" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O124" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="P124" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q124" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R124" s="53"/>
+    </row>
+    <row r="125" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B125" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C125" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D125" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E125" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F125" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G125" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H125" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I125" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J125" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K125" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L125" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M125" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N125" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O125" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P125" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q125" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R125" s="53"/>
+    </row>
+    <row r="126" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B126" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C126" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D126" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E126" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F126" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G126" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H126" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I126" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J126" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K126" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L126" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M126" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N126" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O126" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P126" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q126" s="20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R126" s="53"/>
+    </row>
+    <row r="127" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B127" s="26" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="C127" s="26" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D127" s="26" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="E127" s="26" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="F127" s="26" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="G127" s="26" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H127" s="26" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="I127" s="26" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="J127" s="26" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="K127" s="26" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="L127" s="26" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="M127" s="26" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="N127" s="26" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="O127" s="26" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="P127" s="26" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="Q127" s="24" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="R127" s="52"/>
+    </row>
+    <row r="128" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B128" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C128" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D128" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E128" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F128" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G128" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H128" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I128" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J128" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K128" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L128" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M128" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N128" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O128" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P128" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q128" s="20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R128" s="53"/>
+    </row>
+    <row r="129" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B129" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C129" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D129" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F129" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G129" s="26" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H129" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I129" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J129" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K129" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L129" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M129" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N129" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="O129" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="P129" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q129" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="R129" s="52"/>
+    </row>
+    <row r="130" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B130" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="C130" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="D130" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E130" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="F130" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="G130" s="26" t="n">
+        <v>11</v>
+      </c>
+      <c r="H130" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="I130" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="J130" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="K130" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="L130" s="26" t="n">
+        <v>11</v>
+      </c>
+      <c r="M130" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="N130" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="O130" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="P130" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q130" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="R130" s="52"/>
+    </row>
+    <row r="131" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B131" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C131" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D131" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E131" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F131" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G131" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H131" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I131" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J131" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K131" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L131" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M131" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N131" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O131" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P131" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q131" s="20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R131" s="53"/>
+    </row>
+    <row r="132" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B132" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C132" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D132" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E132" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F132" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G132" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H132" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I132" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J132" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K132" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L132" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M132" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N132" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O132" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P132" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q132" s="20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R132" s="53"/>
+    </row>
+    <row r="133" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B133" s="26" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C133" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D133" s="26" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E133" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F133" s="26" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G133" s="26" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H133" s="26" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I133" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J133" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K133" s="26" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L133" s="26" t="n">
+        <v>2000</v>
+      </c>
+      <c r="M133" s="26" t="n">
+        <v>5000</v>
+      </c>
+      <c r="N133" s="26" t="n">
+        <v>5000</v>
+      </c>
+      <c r="O133" s="26" t="n">
+        <v>12000</v>
+      </c>
+      <c r="P133" s="26" t="n">
+        <v>12000</v>
+      </c>
+      <c r="Q133" s="24" t="n">
+        <v>12000</v>
+      </c>
+      <c r="R133" s="52"/>
+    </row>
+    <row r="134" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="B134" s="41"/>
+      <c r="C134" s="41"/>
+      <c r="D134" s="41"/>
+      <c r="E134" s="41"/>
+      <c r="F134" s="41"/>
+      <c r="G134" s="41"/>
+      <c r="H134" s="41"/>
+      <c r="I134" s="41"/>
+      <c r="J134" s="41"/>
+      <c r="K134" s="41"/>
+      <c r="L134" s="41"/>
+      <c r="M134" s="41"/>
+      <c r="N134" s="41"/>
+      <c r="O134" s="41"/>
+      <c r="P134" s="41"/>
+      <c r="Q134" s="41"/>
+      <c r="R134" s="41"/>
+    </row>
+    <row r="135" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="B135" s="44"/>
+      <c r="C135" s="44"/>
+      <c r="D135" s="44"/>
+      <c r="E135" s="44"/>
+      <c r="F135" s="44"/>
+      <c r="G135" s="44"/>
+      <c r="H135" s="44"/>
+      <c r="I135" s="44"/>
+      <c r="J135" s="44"/>
+      <c r="K135" s="44"/>
+      <c r="L135" s="44"/>
+      <c r="M135" s="44"/>
+      <c r="N135" s="44"/>
+      <c r="O135" s="44"/>
+      <c r="P135" s="44"/>
+      <c r="Q135" s="44"/>
+      <c r="R135" s="44"/>
+    </row>
+    <row r="136" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B136" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C136" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D136" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E136" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F136" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="G136" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="H136" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="I136" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="J136" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K136" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="L136" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M136" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="N136" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="O136" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="P136" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q136" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="R136" s="52"/>
+    </row>
+    <row r="137" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B137" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="C137" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D137" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E137" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F137" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G137" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H137" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="I137" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="J137" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="K137" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="L137" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="M137" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="N137" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="O137" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="P137" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q137" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="R137" s="52"/>
+    </row>
+    <row r="138" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B138" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C138" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D138" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E138" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F138" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G138" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H138" s="0" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I138" s="0" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J138" s="0" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K138" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L138" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M138" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N138" s="54" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O138" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P138" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q138" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="R138" s="54"/>
+    </row>
+    <row r="140" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B140" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="C140" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D140" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="E140" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="F140" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="G140" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="H140" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="I140" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="J140" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="K140" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="L140" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="M140" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="N140" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="O140" s="24" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B141" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C141" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D141" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E141" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F141" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G141" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H141" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I141" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J141" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K141" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L141" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M141" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N141" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O141" s="20" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B142" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C142" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D142" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E142" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F142" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G142" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H142" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I142" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J142" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K142" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L142" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M142" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N142" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O142" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B143" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C143" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D143" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E143" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F143" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G143" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H143" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I143" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J143" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K143" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L143" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M143" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N143" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O143" s="20" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B144" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C144" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D144" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E144" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F144" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G144" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H144" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I144" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J144" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K144" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L144" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M144" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N144" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O144" s="20" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B145" s="26" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="C145" s="26" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="D145" s="26" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="E145" s="26" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="F145" s="26" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="G145" s="26" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H145" s="26" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="I145" s="26" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="J145" s="26" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="K145" s="26" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="L145" s="26" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="M145" s="26" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="N145" s="26" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="O145" s="24" t="n">
+        <v>0.004</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B146" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C146" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D146" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E146" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F146" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G146" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H146" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I146" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J146" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K146" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L146" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M146" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N146" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O146" s="20" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B147" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C147" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D147" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E147" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F147" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G147" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H147" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I147" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J147" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K147" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L147" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M147" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N147" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="O147" s="24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B148" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="C148" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="D148" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E148" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F148" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G148" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H148" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="I148" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="J148" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K148" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="L148" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M148" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="N148" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="O148" s="24" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B149" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C149" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D149" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E149" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F149" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G149" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H149" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I149" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J149" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K149" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L149" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M149" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N149" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O149" s="20" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B150" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C150" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D150" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E150" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F150" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G150" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H150" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I150" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J150" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K150" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L150" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M150" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N150" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O150" s="20" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B151" s="26" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C151" s="26" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D151" s="26" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E151" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F151" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G151" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H151" s="26" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I151" s="26" t="n">
+        <v>7000</v>
+      </c>
+      <c r="J151" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K151" s="26" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L151" s="26" t="n">
+        <v>8000</v>
+      </c>
+      <c r="M151" s="26" t="n">
+        <v>8000</v>
+      </c>
+      <c r="N151" s="26" t="n">
+        <v>8000</v>
+      </c>
+      <c r="O151" s="24" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="B152" s="41"/>
+      <c r="C152" s="41"/>
+      <c r="D152" s="41"/>
+      <c r="E152" s="41"/>
+      <c r="F152" s="41"/>
+      <c r="G152" s="41"/>
+      <c r="H152" s="41"/>
+      <c r="I152" s="41"/>
+      <c r="J152" s="41"/>
+      <c r="K152" s="41"/>
+      <c r="L152" s="41"/>
+      <c r="M152" s="41"/>
+      <c r="N152" s="41"/>
+      <c r="O152" s="41"/>
+    </row>
+    <row r="153" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="B153" s="44"/>
+      <c r="C153" s="44"/>
+      <c r="D153" s="44"/>
+      <c r="E153" s="44"/>
+      <c r="F153" s="44"/>
+      <c r="G153" s="44"/>
+      <c r="H153" s="44"/>
+      <c r="I153" s="44"/>
+      <c r="J153" s="44"/>
+      <c r="K153" s="44"/>
+      <c r="L153" s="44"/>
+      <c r="M153" s="44"/>
+      <c r="N153" s="44"/>
+      <c r="O153" s="44"/>
+    </row>
+    <row r="154" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B154" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C154" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D154" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E154" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F154" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="G154" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="H154" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="I154" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="J154" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K154" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="L154" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M154" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="N154" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="O154" s="24" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B155" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="C155" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D155" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E155" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F155" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G155" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H155" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="I155" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="J155" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="K155" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="L155" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="M155" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="N155" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="O155" s="24" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B156" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C156" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D156" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E156" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F156" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G156" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H156" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I156" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J156" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K156" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L156" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M156" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N156" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O156" s="54" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B158" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="C158" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D158" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="E158" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="F158" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="G158" s="24" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B159" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C159" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D159" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E159" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F159" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G159" s="20" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B160" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C160" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D160" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E160" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F160" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G160" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B161" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C161" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D161" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E161" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F161" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G161" s="20" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B162" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C162" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D162" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E162" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F162" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G162" s="20" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B163" s="26" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="C163" s="26" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="D163" s="26" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="E163" s="26" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="F163" s="26" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G163" s="24" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B164" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C164" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D164" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E164" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F164" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G164" s="20" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B165" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C165" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D165" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E165" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F165" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G165" s="24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B166" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="C166" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="D166" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="E166" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F166" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G166" s="24" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B167" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C167" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D167" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E167" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F167" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G167" s="20" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B168" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C168" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D168" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E168" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F168" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G168" s="20" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B169" s="26" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C169" s="26" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D169" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E169" s="26" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F169" s="26" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G169" s="24" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="B170" s="41"/>
+      <c r="C170" s="41"/>
+      <c r="D170" s="41"/>
+      <c r="E170" s="41"/>
+      <c r="F170" s="41"/>
+      <c r="G170" s="41"/>
+    </row>
+    <row r="171" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="B171" s="44"/>
+      <c r="C171" s="44"/>
+      <c r="D171" s="44"/>
+      <c r="E171" s="44"/>
+      <c r="F171" s="44"/>
+      <c r="G171" s="44"/>
+    </row>
+    <row r="172" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B172" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C172" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D172" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E172" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F172" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="G172" s="24" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B173" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="C173" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D173" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E173" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F173" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G173" s="24" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B174" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C174" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D174" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E174" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F174" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G174" s="55" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B176" s="26" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A177" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B177" s="19" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A178" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B178" s="19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A179" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B179" s="19" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B180" s="19" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A181" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B181" s="26" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A182" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B182" s="19" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A183" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B183" s="26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A184" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B184" s="26" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="185" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A185" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B185" s="19" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A186" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B186" s="19" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A187" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B187" s="26" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="188" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A188" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="B188" s="41"/>
+    </row>
+    <row r="189" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="B189" s="44"/>
+    </row>
+    <row r="190" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A190" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B190" s="26" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A191" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B191" s="26" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B192" s="54" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B194" s="26" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B195" s="19" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A196" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B196" s="19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B197" s="19" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B198" s="19" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A199" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B199" s="26" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A200" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B200" s="19" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="201" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A201" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B201" s="26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A202" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B202" s="26" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="203" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A203" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B203" s="19" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="204" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A204" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B204" s="19" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="205" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A205" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B205" s="26" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="206" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A206" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="B206" s="41"/>
+    </row>
+    <row r="207" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A207" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="B207" s="44"/>
+    </row>
+    <row r="208" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A208" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B208" s="26" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="209" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A209" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B209" s="26" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="210" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A210" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B210" s="54" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/parameters script.xlsx
+++ b/parameters script.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="151">
   <si>
     <t xml:space="preserve">6h 3</t>
   </si>
@@ -728,7 +728,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="54">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -933,23 +933,15 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1036,9 +1028,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>470160</xdr:colOff>
+      <xdr:colOff>469800</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>27360</xdr:rowOff>
+      <xdr:rowOff>27000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1052,7 +1044,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6183720" y="130320"/>
-          <a:ext cx="7990920" cy="262800"/>
+          <a:ext cx="7990560" cy="262440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -10064,7 +10056,7 @@
       <c r="Q122" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="R122" s="52"/>
+      <c r="R122" s="26"/>
     </row>
     <row r="123" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="2" t="s">
@@ -10118,7 +10110,7 @@
       <c r="Q123" s="20" t="n">
         <v>0.5</v>
       </c>
-      <c r="R123" s="53"/>
+      <c r="R123" s="19"/>
     </row>
     <row r="124" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="2" t="s">
@@ -10172,7 +10164,7 @@
       <c r="Q124" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="R124" s="53"/>
+      <c r="R124" s="19"/>
     </row>
     <row r="125" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="2" t="s">
@@ -10226,7 +10218,7 @@
       <c r="Q125" s="20" t="n">
         <v>0.5</v>
       </c>
-      <c r="R125" s="53"/>
+      <c r="R125" s="19"/>
     </row>
     <row r="126" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="2" t="s">
@@ -10280,7 +10272,7 @@
       <c r="Q126" s="20" t="n">
         <v>1.5</v>
       </c>
-      <c r="R126" s="53"/>
+      <c r="R126" s="19"/>
     </row>
     <row r="127" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="2" t="s">
@@ -10334,7 +10326,7 @@
       <c r="Q127" s="24" t="n">
         <v>0.002</v>
       </c>
-      <c r="R127" s="52"/>
+      <c r="R127" s="26"/>
     </row>
     <row r="128" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="2" t="s">
@@ -10388,7 +10380,7 @@
       <c r="Q128" s="20" t="n">
         <v>0.4</v>
       </c>
-      <c r="R128" s="53"/>
+      <c r="R128" s="19"/>
     </row>
     <row r="129" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="2" t="s">
@@ -10442,7 +10434,7 @@
       <c r="Q129" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="R129" s="52"/>
+      <c r="R129" s="26"/>
     </row>
     <row r="130" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="2" t="s">
@@ -10496,7 +10488,7 @@
       <c r="Q130" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="R130" s="52"/>
+      <c r="R130" s="26"/>
     </row>
     <row r="131" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="2" t="s">
@@ -10550,7 +10542,7 @@
       <c r="Q131" s="20" t="n">
         <v>1.2</v>
       </c>
-      <c r="R131" s="53"/>
+      <c r="R131" s="19"/>
     </row>
     <row r="132" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="2" t="s">
@@ -10604,7 +10596,7 @@
       <c r="Q132" s="20" t="n">
         <v>0.6</v>
       </c>
-      <c r="R132" s="53"/>
+      <c r="R132" s="19"/>
     </row>
     <row r="133" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="2" t="s">
@@ -10658,7 +10650,7 @@
       <c r="Q133" s="24" t="n">
         <v>12000</v>
       </c>
-      <c r="R133" s="52"/>
+      <c r="R133" s="26"/>
     </row>
     <row r="134" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="19" t="s">
@@ -10756,7 +10748,7 @@
       <c r="Q136" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="R136" s="52"/>
+      <c r="R136" s="26"/>
     </row>
     <row r="137" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="19" t="s">
@@ -10810,7 +10802,7 @@
       <c r="Q137" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="R137" s="52"/>
+      <c r="R137" s="26"/>
     </row>
     <row r="138" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="1" t="s">
@@ -10852,19 +10844,19 @@
       <c r="M138" s="0" t="n">
         <v>0.5</v>
       </c>
-      <c r="N138" s="54" t="n">
+      <c r="N138" s="52" t="n">
         <v>0.4</v>
       </c>
-      <c r="O138" s="54" t="n">
+      <c r="O138" s="52" t="n">
         <v>0.3</v>
       </c>
-      <c r="P138" s="54" t="n">
+      <c r="P138" s="52" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q138" s="54" t="n">
+      <c r="Q138" s="52" t="n">
         <v>0.3</v>
       </c>
-      <c r="R138" s="54"/>
+      <c r="R138" s="52"/>
     </row>
     <row r="140" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="2" t="s">
@@ -11566,46 +11558,46 @@
       <c r="A156" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B156" s="54" t="n">
+      <c r="B156" s="52" t="n">
         <v>0.3</v>
       </c>
-      <c r="C156" s="54" t="n">
+      <c r="C156" s="52" t="n">
         <v>0.3</v>
       </c>
-      <c r="D156" s="54" t="n">
+      <c r="D156" s="52" t="n">
         <v>0.3</v>
       </c>
-      <c r="E156" s="54" t="n">
+      <c r="E156" s="52" t="n">
         <v>0.3</v>
       </c>
-      <c r="F156" s="54" t="n">
+      <c r="F156" s="52" t="n">
         <v>0.3</v>
       </c>
-      <c r="G156" s="54" t="n">
+      <c r="G156" s="52" t="n">
         <v>0.3</v>
       </c>
-      <c r="H156" s="54" t="n">
+      <c r="H156" s="52" t="n">
         <v>0.3</v>
       </c>
-      <c r="I156" s="54" t="n">
+      <c r="I156" s="52" t="n">
         <v>0.3</v>
       </c>
-      <c r="J156" s="54" t="n">
+      <c r="J156" s="52" t="n">
         <v>0.3</v>
       </c>
-      <c r="K156" s="54" t="n">
+      <c r="K156" s="52" t="n">
         <v>0.3</v>
       </c>
-      <c r="L156" s="54" t="n">
+      <c r="L156" s="52" t="n">
         <v>0.3</v>
       </c>
-      <c r="M156" s="54" t="n">
+      <c r="M156" s="52" t="n">
         <v>0.3</v>
       </c>
-      <c r="N156" s="54" t="n">
+      <c r="N156" s="52" t="n">
         <v>0.3</v>
       </c>
-      <c r="O156" s="54" t="n">
+      <c r="O156" s="52" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -11957,22 +11949,22 @@
       <c r="A174" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B174" s="54" t="n">
+      <c r="B174" s="52" t="n">
         <v>0.3</v>
       </c>
-      <c r="C174" s="54" t="n">
+      <c r="C174" s="52" t="n">
         <v>0.3</v>
       </c>
-      <c r="D174" s="54" t="n">
+      <c r="D174" s="52" t="n">
         <v>0.3</v>
       </c>
-      <c r="E174" s="54" t="n">
+      <c r="E174" s="52" t="n">
         <v>0.3</v>
       </c>
-      <c r="F174" s="54" t="n">
+      <c r="F174" s="52" t="n">
         <v>0.3</v>
       </c>
-      <c r="G174" s="55" t="n">
+      <c r="G174" s="53" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -11980,8 +11972,11 @@
       <c r="A176" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B176" s="26" t="s">
+      <c r="B176" s="18" t="s">
         <v>102</v>
+      </c>
+      <c r="C176" s="24" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11991,6 +11986,9 @@
       <c r="B177" s="19" t="n">
         <v>0.5</v>
       </c>
+      <c r="C177" s="20" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="178" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="2" t="s">
@@ -11999,6 +11997,9 @@
       <c r="B178" s="19" t="n">
         <v>1</v>
       </c>
+      <c r="C178" s="20" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="179" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="2" t="s">
@@ -12007,6 +12008,9 @@
       <c r="B179" s="19" t="n">
         <v>0.5</v>
       </c>
+      <c r="C179" s="20" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="180" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="2" t="s">
@@ -12015,13 +12019,19 @@
       <c r="B180" s="19" t="n">
         <v>1.5</v>
       </c>
+      <c r="C180" s="20" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="181" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="2" t="s">
         <v>84</v>
       </c>
       <c r="B181" s="26" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
+      </c>
+      <c r="C181" s="24" t="n">
+        <v>0.003</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12031,6 +12041,9 @@
       <c r="B182" s="19" t="n">
         <v>0.4</v>
       </c>
+      <c r="C182" s="20" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="183" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="2" t="s">
@@ -12039,13 +12052,19 @@
       <c r="B183" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="C183" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="184" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="2" t="s">
         <v>122</v>
       </c>
       <c r="B184" s="26" t="n">
-        <v>8</v>
+        <v>2</v>
+      </c>
+      <c r="C184" s="24" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12055,6 +12074,9 @@
       <c r="B185" s="19" t="n">
         <v>1.2</v>
       </c>
+      <c r="C185" s="20" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="186" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="2" t="s">
@@ -12063,13 +12085,19 @@
       <c r="B186" s="19" t="n">
         <v>0.6</v>
       </c>
+      <c r="C186" s="20" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="187" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="2" t="s">
         <v>125</v>
       </c>
       <c r="B187" s="26" t="n">
-        <v>5000</v>
+        <v>50000</v>
+      </c>
+      <c r="C187" s="24" t="n">
+        <v>50000</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12077,12 +12105,14 @@
         <v>126</v>
       </c>
       <c r="B188" s="41"/>
+      <c r="C188" s="41"/>
     </row>
     <row r="189" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="29" t="s">
         <v>128</v>
       </c>
       <c r="B189" s="44"/>
+      <c r="C189" s="44"/>
     </row>
     <row r="190" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="19" t="s">
@@ -12091,6 +12121,9 @@
       <c r="B190" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="C190" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="191" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="19" t="s">
@@ -12099,12 +12132,18 @@
       <c r="B191" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="C191" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="192" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B192" s="54" t="n">
+      <c r="B192" s="52" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C192" s="52" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -12112,8 +12151,14 @@
       <c r="A194" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B194" s="26" t="s">
+      <c r="B194" s="18" t="s">
         <v>102</v>
+      </c>
+      <c r="C194" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D194" s="24" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12123,6 +12168,12 @@
       <c r="B195" s="19" t="n">
         <v>0.5</v>
       </c>
+      <c r="C195" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D195" s="20" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="196" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="2" t="s">
@@ -12131,6 +12182,12 @@
       <c r="B196" s="19" t="n">
         <v>1</v>
       </c>
+      <c r="C196" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D196" s="20" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="197" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="2" t="s">
@@ -12139,6 +12196,12 @@
       <c r="B197" s="19" t="n">
         <v>0.5</v>
       </c>
+      <c r="C197" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D197" s="20" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="198" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="2" t="s">
@@ -12147,13 +12210,25 @@
       <c r="B198" s="19" t="n">
         <v>1.5</v>
       </c>
+      <c r="C198" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D198" s="20" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="199" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="2" t="s">
         <v>84</v>
       </c>
       <c r="B199" s="26" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
+      </c>
+      <c r="C199" s="26" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="D199" s="24" t="n">
+        <v>0.003</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12163,6 +12238,12 @@
       <c r="B200" s="19" t="n">
         <v>0.4</v>
       </c>
+      <c r="C200" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D200" s="20" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="201" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="2" t="s">
@@ -12171,13 +12252,25 @@
       <c r="B201" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="C201" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D201" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="202" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="2" t="s">
         <v>122</v>
       </c>
       <c r="B202" s="26" t="n">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="C202" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D202" s="24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12187,6 +12280,12 @@
       <c r="B203" s="19" t="n">
         <v>1.2</v>
       </c>
+      <c r="C203" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D203" s="20" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="204" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="2" t="s">
@@ -12195,13 +12294,25 @@
       <c r="B204" s="19" t="n">
         <v>0.6</v>
       </c>
+      <c r="C204" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D204" s="20" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="205" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="2" t="s">
         <v>125</v>
       </c>
       <c r="B205" s="26" t="n">
-        <v>5000</v>
+        <v>50000</v>
+      </c>
+      <c r="C205" s="26" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D205" s="24" t="n">
+        <v>50000</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12209,12 +12320,16 @@
         <v>126</v>
       </c>
       <c r="B206" s="41"/>
+      <c r="C206" s="41"/>
+      <c r="D206" s="41"/>
     </row>
     <row r="207" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="29" t="s">
         <v>128</v>
       </c>
       <c r="B207" s="44"/>
+      <c r="C207" s="44"/>
+      <c r="D207" s="44"/>
     </row>
     <row r="208" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="19" t="s">
@@ -12223,6 +12338,12 @@
       <c r="B208" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="C208" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D208" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="209" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="19" t="s">
@@ -12231,12 +12352,24 @@
       <c r="B209" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="C209" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D209" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="210" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B210" s="54" t="n">
+      <c r="B210" s="52" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C210" s="52" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D210" s="52" t="n">
         <v>0.3</v>
       </c>
     </row>

--- a/parameters script.xlsx
+++ b/parameters script.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
@@ -14,6 +14,7 @@
     <sheet name="Sheet4" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="28-12" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="22-2-2026" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="line 129" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="154">
   <si>
     <t xml:space="preserve">6h 3</t>
   </si>
@@ -478,6 +479,15 @@
   </si>
   <si>
     <t xml:space="preserve">L3-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0H-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0H-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spotlight</t>
   </si>
 </sst>
 </file>
@@ -489,7 +499,7 @@
     <numFmt numFmtId="165" formatCode="0%"/>
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -564,8 +574,15 @@
       <family val="0"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF4000"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -599,7 +616,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
-        <bgColor rgb="FF993300"/>
+        <bgColor rgb="FFFF4000"/>
       </patternFill>
     </fill>
     <fill>
@@ -623,7 +640,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF860D"/>
-        <bgColor rgb="FFFF6600"/>
+        <bgColor rgb="FFFF8080"/>
       </patternFill>
     </fill>
     <fill>
@@ -642,6 +659,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF808080"/>
         <bgColor rgb="FF999999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFB66C"/>
+        <bgColor rgb="FFFF99CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -728,7 +751,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="64">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -933,15 +956,55 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -995,13 +1058,13 @@
       <rgbColor rgb="FF92D050"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFB2B2B2"/>
-      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FFFFB66C"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF81D41A"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF860D"/>
-      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FFFF4000"/>
       <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF999999"/>
       <rgbColor rgb="FF003366"/>
@@ -1028,9 +1091,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>469800</xdr:colOff>
+      <xdr:colOff>469440</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>27000</xdr:rowOff>
+      <xdr:rowOff>26640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1044,7 +1107,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6183720" y="130320"/>
-          <a:ext cx="7990560" cy="262440"/>
+          <a:ext cx="7990200" cy="262080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -10808,55 +10871,55 @@
       <c r="A138" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B138" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C138" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D138" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E138" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F138" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G138" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H138" s="0" t="n">
+      <c r="B138" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C138" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D138" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E138" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F138" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G138" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H138" s="1" t="n">
         <v>0.4</v>
       </c>
-      <c r="I138" s="0" t="n">
+      <c r="I138" s="1" t="n">
         <v>0.4</v>
       </c>
-      <c r="J138" s="0" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K138" s="0" t="n">
+      <c r="J138" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K138" s="1" t="n">
         <v>0.3</v>
       </c>
-      <c r="L138" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M138" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N138" s="52" t="n">
+      <c r="L138" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M138" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N138" s="5" t="n">
         <v>0.4</v>
       </c>
-      <c r="O138" s="52" t="n">
+      <c r="O138" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="P138" s="52" t="n">
+      <c r="P138" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q138" s="52" t="n">
+      <c r="Q138" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="R138" s="52"/>
+      <c r="R138" s="5"/>
     </row>
     <row r="140" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="2" t="s">
@@ -11558,46 +11621,46 @@
       <c r="A156" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B156" s="52" t="n">
+      <c r="B156" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="C156" s="52" t="n">
+      <c r="C156" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="D156" s="52" t="n">
+      <c r="D156" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="E156" s="52" t="n">
+      <c r="E156" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="F156" s="52" t="n">
+      <c r="F156" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="G156" s="52" t="n">
+      <c r="G156" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="H156" s="52" t="n">
+      <c r="H156" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="I156" s="52" t="n">
+      <c r="I156" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="J156" s="52" t="n">
+      <c r="J156" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="K156" s="52" t="n">
+      <c r="K156" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="L156" s="52" t="n">
+      <c r="L156" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="M156" s="52" t="n">
+      <c r="M156" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="N156" s="52" t="n">
+      <c r="N156" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="O156" s="52" t="n">
+      <c r="O156" s="5" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -11949,22 +12012,22 @@
       <c r="A174" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B174" s="52" t="n">
+      <c r="B174" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="C174" s="52" t="n">
+      <c r="C174" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="D174" s="52" t="n">
+      <c r="D174" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="E174" s="52" t="n">
+      <c r="E174" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="F174" s="52" t="n">
+      <c r="F174" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="G174" s="53" t="n">
+      <c r="G174" s="6" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -12140,10 +12203,10 @@
       <c r="A192" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B192" s="52" t="n">
+      <c r="B192" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="C192" s="52" t="n">
+      <c r="C192" s="5" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -12363,13 +12426,13 @@
       <c r="A210" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B210" s="52" t="n">
+      <c r="B210" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="C210" s="52" t="n">
+      <c r="C210" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="D210" s="52" t="n">
+      <c r="D210" s="5" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -12382,4 +12445,865 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H90"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19.79"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1" s="52" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" s="19" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B3" s="19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" s="19" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B5" s="19" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" s="26" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B7" s="19" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B8" s="19" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B9" s="26" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B10" s="19" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B11" s="19" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B12" s="26" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="B13" s="41"/>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="B14" s="44"/>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B15" s="19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B16" s="19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="0" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B19" s="52" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" s="19" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B21" s="19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B22" s="19" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B23" s="19" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B24" s="26" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B25" s="19" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B26" s="19" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B27" s="26" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B28" s="19" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B29" s="19" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B30" s="26" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="B31" s="41"/>
+    </row>
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="B32" s="44"/>
+    </row>
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B33" s="19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B34" s="19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="0" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B37" s="52" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B38" s="19" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B39" s="19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B40" s="19" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B41" s="19" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B42" s="26" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B43" s="19" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B44" s="19" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B45" s="26" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B46" s="19" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B47" s="19" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B48" s="26" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="B49" s="41"/>
+    </row>
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="B50" s="44"/>
+      <c r="H50" s="53"/>
+    </row>
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B51" s="19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B52" s="19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B53" s="0" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B55" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="C55" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D55" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="E55" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="F55" s="54" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B56" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C56" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D56" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E56" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F56" s="55" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B57" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" s="55" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B58" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C58" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D58" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E58" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F58" s="55" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B59" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C59" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D59" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E59" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F59" s="55" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B60" s="26" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C60" s="26" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="D60" s="26" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="E60" s="26" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="F60" s="54" t="n">
+        <v>0.003</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B61" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C61" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D61" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E61" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F61" s="55" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B62" s="19" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C62" s="19" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D62" s="19" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E62" s="19" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F62" s="55" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B63" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C63" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D63" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F63" s="54" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B64" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C64" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D64" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E64" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F64" s="55" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B65" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C65" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D65" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E65" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F65" s="55" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B66" s="26" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C66" s="26" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D66" s="26" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E66" s="26" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F66" s="54" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="B67" s="41"/>
+      <c r="C67" s="41"/>
+      <c r="D67" s="41"/>
+      <c r="E67" s="41"/>
+      <c r="F67" s="56"/>
+    </row>
+    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="B68" s="44"/>
+      <c r="C68" s="44"/>
+      <c r="D68" s="44"/>
+      <c r="E68" s="44"/>
+      <c r="F68" s="54"/>
+    </row>
+    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B69" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C69" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D69" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E69" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F69" s="54" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B70" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C70" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D70" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E70" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F70" s="54" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B71" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C71" s="53" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D71" s="53" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E71" s="53" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F71" s="57" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="58" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B74" s="59" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B75" s="60" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B76" s="60" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B77" s="60" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B78" s="60" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B79" s="61" t="n">
+        <v>0.003</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B80" s="60" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B81" s="60" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B82" s="61" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B83" s="60" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B84" s="60" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B85" s="61" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="B86" s="62"/>
+    </row>
+    <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="B87" s="61"/>
+    </row>
+    <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B88" s="61" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B89" s="61" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B90" s="63" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/parameters script.xlsx
+++ b/parameters script.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="156">
   <si>
     <t xml:space="preserve">6h 3</t>
   </si>
@@ -488,6 +488,12 @@
   </si>
   <si>
     <t xml:space="preserve">spotlight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Version 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Version 5</t>
   </si>
 </sst>
 </file>
@@ -751,7 +757,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="57">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -964,10 +970,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -980,31 +982,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1091,9 +1069,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>469440</xdr:colOff>
+      <xdr:colOff>469080</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>26640</xdr:rowOff>
+      <xdr:rowOff>26280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1107,7 +1085,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6183720" y="130320"/>
-          <a:ext cx="7990200" cy="262080"/>
+          <a:ext cx="7989840" cy="261720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -12452,10 +12430,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H90"/>
+  <dimension ref="A1:H110"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.79"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12583,7 +12561,7 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="0" t="n">
+      <c r="B17" s="1" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -12712,7 +12690,7 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="0" t="n">
+      <c r="B35" s="1" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -12823,7 +12801,7 @@
         <v>128</v>
       </c>
       <c r="B50" s="44"/>
-      <c r="H50" s="53"/>
+      <c r="H50" s="5"/>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="19" t="s">
@@ -12842,7 +12820,7 @@
       </c>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="0" t="n">
+      <c r="B53" s="1" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -12862,7 +12840,7 @@
       <c r="E55" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="F55" s="54" t="s">
+      <c r="F55" s="53" t="s">
         <v>106</v>
       </c>
     </row>
@@ -12882,7 +12860,7 @@
       <c r="E56" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="F56" s="55" t="n">
+      <c r="F56" s="54" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -12902,7 +12880,7 @@
       <c r="E57" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="F57" s="55" t="n">
+      <c r="F57" s="54" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12922,7 +12900,7 @@
       <c r="E58" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="F58" s="55" t="n">
+      <c r="F58" s="54" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -12942,7 +12920,7 @@
       <c r="E59" s="19" t="n">
         <v>1.5</v>
       </c>
-      <c r="F59" s="55" t="n">
+      <c r="F59" s="54" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -12962,7 +12940,7 @@
       <c r="E60" s="26" t="n">
         <v>0.003</v>
       </c>
-      <c r="F60" s="54" t="n">
+      <c r="F60" s="53" t="n">
         <v>0.003</v>
       </c>
     </row>
@@ -12982,7 +12960,7 @@
       <c r="E61" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="F61" s="55" t="n">
+      <c r="F61" s="54" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -13002,7 +12980,7 @@
       <c r="E62" s="19" t="n">
         <v>0.7</v>
       </c>
-      <c r="F62" s="55" t="n">
+      <c r="F62" s="54" t="n">
         <v>0.7</v>
       </c>
     </row>
@@ -13022,7 +13000,7 @@
       <c r="E63" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="F63" s="54" t="n">
+      <c r="F63" s="53" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13042,7 +13020,7 @@
       <c r="E64" s="19" t="n">
         <v>1.2</v>
       </c>
-      <c r="F64" s="55" t="n">
+      <c r="F64" s="54" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -13062,7 +13040,7 @@
       <c r="E65" s="19" t="n">
         <v>0.6</v>
       </c>
-      <c r="F65" s="55" t="n">
+      <c r="F65" s="54" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -13082,7 +13060,7 @@
       <c r="E66" s="26" t="n">
         <v>50000</v>
       </c>
-      <c r="F66" s="54" t="n">
+      <c r="F66" s="53" t="n">
         <v>50000</v>
       </c>
     </row>
@@ -13094,7 +13072,7 @@
       <c r="C67" s="41"/>
       <c r="D67" s="41"/>
       <c r="E67" s="41"/>
-      <c r="F67" s="56"/>
+      <c r="F67" s="55"/>
     </row>
     <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="29" t="s">
@@ -13104,7 +13082,7 @@
       <c r="C68" s="44"/>
       <c r="D68" s="44"/>
       <c r="E68" s="44"/>
-      <c r="F68" s="54"/>
+      <c r="F68" s="53"/>
     </row>
     <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="19" t="s">
@@ -13122,7 +13100,7 @@
       <c r="E69" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="F69" s="54" t="n">
+      <c r="F69" s="53" t="n">
         <v>2</v>
       </c>
     </row>
@@ -13142,29 +13120,29 @@
       <c r="E70" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="F70" s="54" t="n">
+      <c r="F70" s="53" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B71" s="0" t="n">
+      <c r="B71" s="1" t="n">
         <v>0.3</v>
       </c>
-      <c r="C71" s="53" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D71" s="53" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E71" s="53" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F71" s="57" t="n">
+      <c r="C71" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D71" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E71" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F71" s="56" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="58" t="s">
+      <c r="A73" s="50" t="s">
         <v>153</v>
       </c>
     </row>
@@ -13172,7 +13150,7 @@
       <c r="A74" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B74" s="59" t="s">
+      <c r="B74" s="18" t="s">
         <v>102</v>
       </c>
     </row>
@@ -13180,7 +13158,7 @@
       <c r="A75" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B75" s="60" t="n">
+      <c r="B75" s="19" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -13188,7 +13166,7 @@
       <c r="A76" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B76" s="60" t="n">
+      <c r="B76" s="19" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13196,7 +13174,7 @@
       <c r="A77" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B77" s="60" t="n">
+      <c r="B77" s="19" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -13204,7 +13182,7 @@
       <c r="A78" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B78" s="60" t="n">
+      <c r="B78" s="19" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -13212,7 +13190,7 @@
       <c r="A79" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B79" s="61" t="n">
+      <c r="B79" s="26" t="n">
         <v>0.003</v>
       </c>
     </row>
@@ -13220,7 +13198,7 @@
       <c r="A80" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B80" s="60" t="n">
+      <c r="B80" s="19" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -13228,7 +13206,7 @@
       <c r="A81" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B81" s="60" t="n">
+      <c r="B81" s="19" t="n">
         <v>0.7</v>
       </c>
     </row>
@@ -13236,7 +13214,7 @@
       <c r="A82" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B82" s="61" t="n">
+      <c r="B82" s="26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13244,7 +13222,7 @@
       <c r="A83" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B83" s="60" t="n">
+      <c r="B83" s="19" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -13252,7 +13230,7 @@
       <c r="A84" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B84" s="60" t="n">
+      <c r="B84" s="19" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -13260,7 +13238,7 @@
       <c r="A85" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B85" s="61" t="n">
+      <c r="B85" s="26" t="n">
         <v>50000</v>
       </c>
     </row>
@@ -13268,19 +13246,19 @@
       <c r="A86" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="B86" s="62"/>
+      <c r="B86" s="41"/>
     </row>
     <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="B87" s="61"/>
+      <c r="B87" s="44"/>
     </row>
     <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="B88" s="61" t="n">
+      <c r="B88" s="26" t="n">
         <v>2</v>
       </c>
     </row>
@@ -13288,13 +13266,452 @@
       <c r="A89" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="B89" s="61" t="n">
+      <c r="B89" s="26" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B90" s="63" t="n">
-        <v>0.5</v>
+      <c r="B90" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="50" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B93" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="C93" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D93" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="E93" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="F93" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="G93" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="H93" s="26" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B94" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C94" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D94" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E94" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F94" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G94" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H94" s="19" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B95" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" s="19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B96" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C96" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D96" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E96" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F96" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G96" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H96" s="19" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B97" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C97" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D97" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E97" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F97" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G97" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H97" s="19" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B98" s="26" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="C98" s="26" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="D98" s="26" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E98" s="26" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F98" s="26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G98" s="26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H98" s="26" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B99" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C99" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D99" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E99" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F99" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G99" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H99" s="19" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B100" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C100" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D100" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H100" s="19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B101" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="C101" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="D101" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="E101" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="F101" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="G101" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="H101" s="26" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B102" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C102" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D102" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E102" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F102" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G102" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H102" s="19" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B103" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C103" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D103" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E103" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F103" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G103" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H103" s="19" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B104" s="26" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C104" s="26" t="n">
+        <v>12000</v>
+      </c>
+      <c r="D104" s="26" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E104" s="26" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F104" s="26" t="n">
+        <v>12000</v>
+      </c>
+      <c r="G104" s="26" t="n">
+        <v>12000</v>
+      </c>
+      <c r="H104" s="26" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="B105" s="41"/>
+      <c r="C105" s="41"/>
+      <c r="D105" s="41"/>
+      <c r="E105" s="41"/>
+      <c r="F105" s="41"/>
+      <c r="G105" s="41"/>
+      <c r="H105" s="41"/>
+    </row>
+    <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="B106" s="44"/>
+      <c r="C106" s="44"/>
+      <c r="D106" s="44"/>
+      <c r="E106" s="44"/>
+      <c r="F106" s="44"/>
+      <c r="G106" s="44"/>
+      <c r="H106" s="44"/>
+    </row>
+    <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B107" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C107" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D107" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E107" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F107" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G107" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H107" s="26" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B108" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="C108" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D108" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E108" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F108" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G108" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H108" s="26" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B109" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C109" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D109" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E109" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F109" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G109" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H109" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B110" s="0" t="s">
+        <v>154</v>
+      </c>
+      <c r="C110" s="0" t="s">
+        <v>154</v>
+      </c>
+      <c r="D110" s="0" t="s">
+        <v>154</v>
+      </c>
+      <c r="E110" s="0" t="s">
+        <v>154</v>
+      </c>
+      <c r="F110" s="0" t="s">
+        <v>154</v>
+      </c>
+      <c r="G110" s="0" t="s">
+        <v>155</v>
+      </c>
+      <c r="H110" s="0" t="s">
+        <v>155</v>
       </c>
     </row>
   </sheetData>

--- a/parameters script.xlsx
+++ b/parameters script.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="161">
   <si>
     <t xml:space="preserve">6h 3</t>
   </si>
@@ -490,10 +490,25 @@
     <t xml:space="preserve">spotlight</t>
   </si>
   <si>
+    <t xml:space="preserve">22 marzo 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23 MARZO 26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 MARZO 26</t>
+  </si>
+  <si>
     <t xml:space="preserve">Version 1</t>
   </si>
   <si>
     <t xml:space="preserve">Version 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Version 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERSION 2</t>
   </si>
 </sst>
 </file>
@@ -757,7 +772,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="60">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -986,6 +1001,18 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1069,9 +1096,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>469080</xdr:colOff>
+      <xdr:colOff>468360</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>26280</xdr:rowOff>
+      <xdr:rowOff>25560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1085,7 +1112,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6183720" y="130320"/>
-          <a:ext cx="7989840" cy="261720"/>
+          <a:ext cx="7989120" cy="261000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -12430,7 +12457,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H110"/>
+  <dimension ref="A1:Q110"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.79"/>
@@ -13279,6 +13306,15 @@
       <c r="A92" s="50" t="s">
         <v>153</v>
       </c>
+      <c r="F92" s="0" t="s">
+        <v>154</v>
+      </c>
+      <c r="P92" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q92" s="1" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2" t="s">
@@ -13296,14 +13332,41 @@
       <c r="E93" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="F93" s="18" t="s">
+      <c r="F93" s="57" t="s">
         <v>106</v>
       </c>
       <c r="G93" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="H93" s="26" t="s">
+      <c r="H93" s="18" t="s">
         <v>108</v>
+      </c>
+      <c r="I93" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="J93" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="K93" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="L93" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="M93" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="N93" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="O93" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="P93" s="58" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q93" s="52" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13322,13 +13385,40 @@
       <c r="E94" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="F94" s="19" t="n">
+      <c r="F94" s="59" t="n">
         <v>0.5</v>
       </c>
       <c r="G94" s="19" t="n">
         <v>0.5</v>
       </c>
       <c r="H94" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I94" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J94" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K94" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L94" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M94" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N94" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O94" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P94" s="59" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q94" s="19" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -13348,13 +13438,40 @@
       <c r="E95" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="F95" s="19" t="n">
+      <c r="F95" s="59" t="n">
         <v>1</v>
       </c>
       <c r="G95" s="19" t="n">
         <v>1</v>
       </c>
       <c r="H95" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I95" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J95" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K95" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L95" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M95" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N95" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O95" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="P95" s="59" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q95" s="19" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13374,13 +13491,40 @@
       <c r="E96" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="F96" s="19" t="n">
+      <c r="F96" s="59" t="n">
         <v>0.5</v>
       </c>
       <c r="G96" s="19" t="n">
         <v>0.5</v>
       </c>
       <c r="H96" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I96" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J96" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K96" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L96" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M96" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N96" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O96" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P96" s="59" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q96" s="19" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -13400,13 +13544,40 @@
       <c r="E97" s="19" t="n">
         <v>1.5</v>
       </c>
-      <c r="F97" s="19" t="n">
+      <c r="F97" s="59" t="n">
         <v>1.5</v>
       </c>
       <c r="G97" s="19" t="n">
         <v>1.5</v>
       </c>
       <c r="H97" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I97" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J97" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K97" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L97" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M97" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N97" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O97" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P97" s="59" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q97" s="19" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -13426,7 +13597,7 @@
       <c r="E98" s="26" t="n">
         <v>0.05</v>
       </c>
-      <c r="F98" s="26" t="n">
+      <c r="F98" s="44" t="n">
         <v>0.1</v>
       </c>
       <c r="G98" s="26" t="n">
@@ -13434,6 +13605,33 @@
       </c>
       <c r="H98" s="26" t="n">
         <v>0.005</v>
+      </c>
+      <c r="I98" s="26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J98" s="26" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="K98" s="26" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L98" s="26" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M98" s="26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N98" s="26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O98" s="26" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P98" s="44" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q98" s="26" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13452,13 +13650,40 @@
       <c r="E99" s="19" t="n">
         <v>0.4</v>
       </c>
-      <c r="F99" s="19" t="n">
+      <c r="F99" s="59" t="n">
         <v>0.4</v>
       </c>
       <c r="G99" s="19" t="n">
         <v>0.4</v>
       </c>
       <c r="H99" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I99" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J99" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K99" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L99" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M99" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N99" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O99" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P99" s="59" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q99" s="19" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -13478,13 +13703,40 @@
       <c r="E100" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="F100" s="19" t="n">
+      <c r="F100" s="59" t="n">
         <v>1</v>
       </c>
       <c r="G100" s="19" t="n">
         <v>1</v>
       </c>
       <c r="H100" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I100" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J100" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K100" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L100" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M100" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N100" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O100" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="P100" s="59" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q100" s="19" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13504,13 +13756,40 @@
       <c r="E101" s="26" t="n">
         <v>9</v>
       </c>
-      <c r="F101" s="26" t="n">
+      <c r="F101" s="44" t="n">
         <v>8</v>
       </c>
       <c r="G101" s="26" t="n">
         <v>8</v>
       </c>
       <c r="H101" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="I101" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="J101" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="K101" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="L101" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="M101" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="N101" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="O101" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="P101" s="44" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q101" s="26" t="n">
         <v>8</v>
       </c>
     </row>
@@ -13530,13 +13809,40 @@
       <c r="E102" s="19" t="n">
         <v>1.2</v>
       </c>
-      <c r="F102" s="19" t="n">
+      <c r="F102" s="59" t="n">
         <v>1.2</v>
       </c>
       <c r="G102" s="19" t="n">
         <v>1.2</v>
       </c>
       <c r="H102" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I102" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J102" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K102" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L102" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M102" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N102" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O102" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P102" s="59" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q102" s="19" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -13556,13 +13862,40 @@
       <c r="E103" s="19" t="n">
         <v>0.6</v>
       </c>
-      <c r="F103" s="19" t="n">
+      <c r="F103" s="59" t="n">
         <v>0.6</v>
       </c>
       <c r="G103" s="19" t="n">
         <v>0.6</v>
       </c>
       <c r="H103" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I103" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J103" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K103" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L103" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M103" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N103" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O103" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P103" s="59" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q103" s="19" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -13582,13 +13915,40 @@
       <c r="E104" s="26" t="n">
         <v>8000</v>
       </c>
-      <c r="F104" s="26" t="n">
+      <c r="F104" s="44" t="n">
         <v>12000</v>
       </c>
       <c r="G104" s="26" t="n">
         <v>12000</v>
       </c>
       <c r="H104" s="26" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I104" s="26" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J104" s="26" t="n">
+        <v>12000</v>
+      </c>
+      <c r="K104" s="26" t="n">
+        <v>12000</v>
+      </c>
+      <c r="L104" s="26" t="n">
+        <v>12000</v>
+      </c>
+      <c r="M104" s="26" t="n">
+        <v>12000</v>
+      </c>
+      <c r="N104" s="26" t="n">
+        <v>12000</v>
+      </c>
+      <c r="O104" s="26" t="n">
+        <v>12000</v>
+      </c>
+      <c r="P104" s="44" t="n">
+        <v>12000</v>
+      </c>
+      <c r="Q104" s="26" t="n">
         <v>12000</v>
       </c>
     </row>
@@ -13603,6 +13963,15 @@
       <c r="F105" s="41"/>
       <c r="G105" s="41"/>
       <c r="H105" s="41"/>
+      <c r="I105" s="41"/>
+      <c r="J105" s="41"/>
+      <c r="K105" s="41"/>
+      <c r="L105" s="41"/>
+      <c r="M105" s="41"/>
+      <c r="N105" s="41"/>
+      <c r="O105" s="41"/>
+      <c r="P105" s="41"/>
+      <c r="Q105" s="41"/>
     </row>
     <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="29" t="s">
@@ -13615,6 +13984,15 @@
       <c r="F106" s="44"/>
       <c r="G106" s="44"/>
       <c r="H106" s="44"/>
+      <c r="I106" s="44"/>
+      <c r="J106" s="44"/>
+      <c r="K106" s="44"/>
+      <c r="L106" s="44"/>
+      <c r="M106" s="44"/>
+      <c r="N106" s="44"/>
+      <c r="O106" s="44"/>
+      <c r="P106" s="44"/>
+      <c r="Q106" s="44"/>
     </row>
     <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="19" t="s">
@@ -13632,13 +14010,40 @@
       <c r="E107" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="F107" s="26" t="n">
+      <c r="F107" s="44" t="n">
         <v>2</v>
       </c>
       <c r="G107" s="26" t="n">
         <v>2</v>
       </c>
       <c r="H107" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="I107" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="J107" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="K107" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="L107" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="M107" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="N107" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="O107" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="P107" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q107" s="26" t="n">
         <v>2</v>
       </c>
     </row>
@@ -13658,13 +14063,40 @@
       <c r="E108" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="F108" s="26" t="n">
+      <c r="F108" s="44" t="n">
         <v>2</v>
       </c>
       <c r="G108" s="26" t="n">
         <v>2</v>
       </c>
       <c r="H108" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="I108" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="J108" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="K108" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="L108" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="M108" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="N108" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="O108" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="P108" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q108" s="26" t="n">
         <v>2</v>
       </c>
     </row>
@@ -13690,29 +14122,81 @@
       <c r="H109" s="5" t="n">
         <v>0.5</v>
       </c>
+      <c r="I109" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J109" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K109" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L109" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M109" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N109" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O109" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P109" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q109" s="5" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B110" s="0" t="s">
-        <v>154</v>
-      </c>
-      <c r="C110" s="0" t="s">
-        <v>154</v>
-      </c>
-      <c r="D110" s="0" t="s">
-        <v>154</v>
-      </c>
-      <c r="E110" s="0" t="s">
-        <v>154</v>
-      </c>
-      <c r="F110" s="0" t="s">
-        <v>154</v>
-      </c>
-      <c r="G110" s="0" t="s">
-        <v>155</v>
-      </c>
-      <c r="H110" s="0" t="s">
-        <v>155</v>
-      </c>
+      <c r="B110" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G110" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="H110" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="I110" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="J110" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="K110" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="L110" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="M110" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="N110" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="O110" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="P110" s="51" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q110" s="51"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/parameters script.xlsx
+++ b/parameters script.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="168">
   <si>
     <t xml:space="preserve">6h 3</t>
   </si>
@@ -457,6 +457,9 @@
     <t xml:space="preserve">6H-1</t>
   </si>
   <si>
+    <t xml:space="preserve">MANUAL</t>
+  </si>
+  <si>
     <t xml:space="preserve">3H-1</t>
   </si>
   <si>
@@ -499,6 +502,15 @@
     <t xml:space="preserve">24 MARZO 26</t>
   </si>
   <si>
+    <t xml:space="preserve">25 MARZO 26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T19</t>
+  </si>
+  <si>
     <t xml:space="preserve">Version 1</t>
   </si>
   <si>
@@ -509,16 +521,26 @@
   </si>
   <si>
     <t xml:space="preserve">VERSION 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Version 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">###########</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T20</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0%"/>
-    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="166" formatCode="0.00%"/>
+    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -772,7 +794,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -977,7 +999,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1096,9 +1122,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>468360</xdr:colOff>
+      <xdr:colOff>468000</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>25560</xdr:rowOff>
+      <xdr:rowOff>25200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1112,13 +1138,94 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6183720" y="130320"/>
-          <a:ext cx="7989120" cy="261000"/>
+          <a:ext cx="7988760" cy="260640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:noFill/>
         <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>234720</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>30600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>570600</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>66600</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9763560" y="14112360"/>
+          <a:ext cx="10145160" cy="2047680"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>115</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>421920</xdr:colOff>
+      <xdr:row>126</xdr:row>
+      <xdr:rowOff>102600</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Image 2"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6275160" y="21031200"/>
+          <a:ext cx="10182960" cy="2114280"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
         </a:ln>
       </xdr:spPr>
@@ -9230,6 +9337,9 @@
       <c r="F73" s="24" t="n">
         <v>0.002</v>
       </c>
+      <c r="M73" s="0" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="74" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2" t="s">
@@ -9250,6 +9360,19 @@
       <c r="F74" s="20" t="n">
         <v>0.4</v>
       </c>
+      <c r="L74" s="0" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="M74" s="0" t="n">
+        <v>0.552</v>
+      </c>
+      <c r="N74" s="0" t="n">
+        <v>0.4778070152</v>
+      </c>
+      <c r="O74" s="51" t="n">
+        <f aca="false">1-(N74/M74)</f>
+        <v>0.13440758115942</v>
+      </c>
     </row>
     <row r="75" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2" t="s">
@@ -9270,6 +9393,19 @@
       <c r="F75" s="20" t="n">
         <v>1</v>
       </c>
+      <c r="L75" s="0" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M75" s="0" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="N75" s="0" t="n">
+        <v>0.485653758</v>
+      </c>
+      <c r="O75" s="51" t="n">
+        <f aca="false">1-(N75/M75)</f>
+        <v>-0.271344916230367</v>
+      </c>
     </row>
     <row r="76" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2" t="s">
@@ -9290,6 +9426,19 @@
       <c r="F76" s="24" t="n">
         <v>10</v>
       </c>
+      <c r="L76" s="0" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M76" s="0" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="N76" s="0" t="n">
+        <v>0.5555944741</v>
+      </c>
+      <c r="O76" s="51" t="n">
+        <f aca="false">1-(N76/M76)</f>
+        <v>-0.189709794646681</v>
+      </c>
     </row>
     <row r="77" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2" t="s">
@@ -9309,6 +9458,19 @@
       </c>
       <c r="F77" s="20" t="n">
         <v>1.2</v>
+      </c>
+      <c r="L77" s="0" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="M77" s="0" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="N77" s="0" t="n">
+        <v>0.5027</v>
+      </c>
+      <c r="O77" s="51" t="n">
+        <f aca="false">1-(N77/M77)</f>
+        <v>-0.0764453961456102</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9419,7 +9581,7 @@
     </row>
     <row r="86" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B86" s="18" t="s">
         <v>102</v>
@@ -9724,7 +9886,7 @@
     </row>
     <row r="104" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B104" s="18" t="s">
         <v>102</v>
@@ -10070,11 +10232,11 @@
       <c r="B121" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E121" s="51"/>
+      <c r="E121" s="52"/>
     </row>
     <row r="122" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B122" s="18" t="s">
         <v>102</v>
@@ -10874,7 +11036,7 @@
     </row>
     <row r="138" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B138" s="1" t="n">
         <v>0.5</v>
@@ -10928,7 +11090,7 @@
     </row>
     <row r="140" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B140" s="18" t="s">
         <v>102</v>
@@ -11624,7 +11786,7 @@
     </row>
     <row r="156" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B156" s="5" t="n">
         <v>0.3</v>
@@ -11671,7 +11833,7 @@
     </row>
     <row r="158" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B158" s="18" t="s">
         <v>102</v>
@@ -12015,7 +12177,7 @@
     </row>
     <row r="174" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B174" s="5" t="n">
         <v>0.3</v>
@@ -12038,7 +12200,7 @@
     </row>
     <row r="176" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B176" s="18" t="s">
         <v>102</v>
@@ -12206,7 +12368,7 @@
     </row>
     <row r="192" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B192" s="5" t="n">
         <v>0.3</v>
@@ -12217,7 +12379,7 @@
     </row>
     <row r="194" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B194" s="18" t="s">
         <v>102</v>
@@ -12429,7 +12591,7 @@
     </row>
     <row r="210" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B210" s="5" t="n">
         <v>0.3</v>
@@ -12457,21 +12619,22 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q110"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:T130"/>
+  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="14.4" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="12.23"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B1" s="52" t="s">
+      <c r="B1" s="53" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>80</v>
       </c>
@@ -12479,7 +12642,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>120</v>
       </c>
@@ -12487,7 +12650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
         <v>82</v>
       </c>
@@ -12495,7 +12658,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>121</v>
       </c>
@@ -12503,7 +12666,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
         <v>84</v>
       </c>
@@ -12511,7 +12674,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
         <v>79</v>
       </c>
@@ -12519,7 +12682,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
         <v>85</v>
       </c>
@@ -12527,7 +12690,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
         <v>122</v>
       </c>
@@ -12535,7 +12698,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
         <v>123</v>
       </c>
@@ -12543,7 +12706,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
         <v>124</v>
       </c>
@@ -12551,7 +12714,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
         <v>125</v>
       </c>
@@ -12559,19 +12722,19 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="19" t="s">
         <v>126</v>
       </c>
       <c r="B13" s="41"/>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="29" t="s">
         <v>128</v>
       </c>
       <c r="B14" s="44"/>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
         <v>134</v>
       </c>
@@ -12579,7 +12742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="19" t="s">
         <v>136</v>
       </c>
@@ -12587,20 +12750,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="1" t="n">
         <v>0.3</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="B19" s="52" t="s">
+        <v>152</v>
+      </c>
+      <c r="B19" s="53" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
         <v>80</v>
       </c>
@@ -12608,7 +12771,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
         <v>120</v>
       </c>
@@ -12616,7 +12779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
         <v>82</v>
       </c>
@@ -12624,7 +12787,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
         <v>121</v>
       </c>
@@ -12632,7 +12795,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
         <v>84</v>
       </c>
@@ -12640,7 +12803,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
         <v>79</v>
       </c>
@@ -12648,7 +12811,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
         <v>85</v>
       </c>
@@ -12656,7 +12819,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
         <v>122</v>
       </c>
@@ -12664,7 +12827,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
         <v>123</v>
       </c>
@@ -12672,7 +12835,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
         <v>124</v>
       </c>
@@ -12680,7 +12843,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
         <v>125</v>
       </c>
@@ -12688,19 +12851,19 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="19" t="s">
         <v>126</v>
       </c>
       <c r="B31" s="41"/>
     </row>
-    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="29" t="s">
         <v>128</v>
       </c>
       <c r="B32" s="44"/>
     </row>
-    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="19" t="s">
         <v>134</v>
       </c>
@@ -12708,7 +12871,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="19" t="s">
         <v>136</v>
       </c>
@@ -12716,20 +12879,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="1" t="n">
         <v>0.3</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="B37" s="52" t="s">
+        <v>153</v>
+      </c>
+      <c r="B37" s="53" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
         <v>80</v>
       </c>
@@ -12737,7 +12900,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
         <v>120</v>
       </c>
@@ -12745,7 +12908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
         <v>82</v>
       </c>
@@ -12753,7 +12916,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
         <v>121</v>
       </c>
@@ -12761,7 +12924,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
         <v>84</v>
       </c>
@@ -12769,7 +12932,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
         <v>79</v>
       </c>
@@ -12777,7 +12940,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
         <v>85</v>
       </c>
@@ -12785,7 +12948,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
         <v>122</v>
       </c>
@@ -12793,7 +12956,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
         <v>123</v>
       </c>
@@ -12801,7 +12964,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
         <v>124</v>
       </c>
@@ -12809,7 +12972,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
         <v>125</v>
       </c>
@@ -12817,20 +12980,20 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="19" t="s">
         <v>126</v>
       </c>
       <c r="B49" s="41"/>
     </row>
-    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="29" t="s">
         <v>128</v>
       </c>
       <c r="B50" s="44"/>
       <c r="H50" s="5"/>
     </row>
-    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="19" t="s">
         <v>134</v>
       </c>
@@ -12838,7 +13001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="19" t="s">
         <v>136</v>
       </c>
@@ -12846,14 +13009,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="1" t="n">
         <v>0.3</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B55" s="18" t="s">
         <v>102</v>
@@ -12867,11 +13030,11 @@
       <c r="E55" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="F55" s="53" t="s">
+      <c r="F55" s="54" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
         <v>80</v>
       </c>
@@ -12887,11 +13050,11 @@
       <c r="E56" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="F56" s="54" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F56" s="55" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
         <v>120</v>
       </c>
@@ -12907,11 +13070,11 @@
       <c r="E57" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="F57" s="54" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F57" s="55" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
         <v>82</v>
       </c>
@@ -12927,11 +13090,11 @@
       <c r="E58" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="F58" s="54" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F58" s="55" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
         <v>121</v>
       </c>
@@ -12947,11 +13110,11 @@
       <c r="E59" s="19" t="n">
         <v>1.5</v>
       </c>
-      <c r="F59" s="54" t="n">
+      <c r="F59" s="55" t="n">
         <v>1.5</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
         <v>84</v>
       </c>
@@ -12967,11 +13130,11 @@
       <c r="E60" s="26" t="n">
         <v>0.003</v>
       </c>
-      <c r="F60" s="53" t="n">
+      <c r="F60" s="54" t="n">
         <v>0.003</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="s">
         <v>79</v>
       </c>
@@ -12987,11 +13150,11 @@
       <c r="E61" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="F61" s="54" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F61" s="55" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
         <v>85</v>
       </c>
@@ -13007,11 +13170,11 @@
       <c r="E62" s="19" t="n">
         <v>0.7</v>
       </c>
-      <c r="F62" s="54" t="n">
+      <c r="F62" s="55" t="n">
         <v>0.7</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
         <v>122</v>
       </c>
@@ -13027,11 +13190,11 @@
       <c r="E63" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="F63" s="53" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F63" s="54" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="s">
         <v>123</v>
       </c>
@@ -13047,11 +13210,11 @@
       <c r="E64" s="19" t="n">
         <v>1.2</v>
       </c>
-      <c r="F64" s="54" t="n">
+      <c r="F64" s="55" t="n">
         <v>1.2</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2" t="s">
         <v>124</v>
       </c>
@@ -13067,11 +13230,11 @@
       <c r="E65" s="19" t="n">
         <v>0.6</v>
       </c>
-      <c r="F65" s="54" t="n">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F65" s="55" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2" t="s">
         <v>125</v>
       </c>
@@ -13087,11 +13250,11 @@
       <c r="E66" s="26" t="n">
         <v>50000</v>
       </c>
-      <c r="F66" s="53" t="n">
+      <c r="F66" s="54" t="n">
         <v>50000</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="19" t="s">
         <v>126</v>
       </c>
@@ -13099,9 +13262,9 @@
       <c r="C67" s="41"/>
       <c r="D67" s="41"/>
       <c r="E67" s="41"/>
-      <c r="F67" s="55"/>
-    </row>
-    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F67" s="56"/>
+    </row>
+    <row r="68" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="29" t="s">
         <v>128</v>
       </c>
@@ -13109,9 +13272,9 @@
       <c r="C68" s="44"/>
       <c r="D68" s="44"/>
       <c r="E68" s="44"/>
-      <c r="F68" s="53"/>
-    </row>
-    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F68" s="54"/>
+    </row>
+    <row r="69" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="19" t="s">
         <v>134</v>
       </c>
@@ -13127,11 +13290,11 @@
       <c r="E69" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="F69" s="53" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F69" s="54" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="19" t="s">
         <v>136</v>
       </c>
@@ -13147,11 +13310,11 @@
       <c r="E70" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="F70" s="53" t="n">
+      <c r="F70" s="54" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B71" s="1" t="n">
         <v>0.3</v>
       </c>
@@ -13164,24 +13327,24 @@
       <c r="E71" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="F71" s="56" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F71" s="57" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="50" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B74" s="18" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2" t="s">
         <v>80</v>
       </c>
@@ -13189,7 +13352,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2" t="s">
         <v>120</v>
       </c>
@@ -13197,7 +13360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2" t="s">
         <v>82</v>
       </c>
@@ -13205,7 +13368,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2" t="s">
         <v>121</v>
       </c>
@@ -13213,7 +13376,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2" t="s">
         <v>84</v>
       </c>
@@ -13221,7 +13384,7 @@
         <v>0.003</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2" t="s">
         <v>79</v>
       </c>
@@ -13229,7 +13392,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2" t="s">
         <v>85</v>
       </c>
@@ -13237,7 +13400,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="2" t="s">
         <v>122</v>
       </c>
@@ -13245,7 +13408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="2" t="s">
         <v>123</v>
       </c>
@@ -13253,7 +13416,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2" t="s">
         <v>124</v>
       </c>
@@ -13261,7 +13424,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2" t="s">
         <v>125</v>
       </c>
@@ -13269,19 +13432,19 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="19" t="s">
         <v>126</v>
       </c>
       <c r="B86" s="41"/>
     </row>
-    <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="29" t="s">
         <v>128</v>
       </c>
       <c r="B87" s="44"/>
     </row>
-    <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="19" t="s">
         <v>134</v>
       </c>
@@ -13289,7 +13452,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="19" t="s">
         <v>136</v>
       </c>
@@ -13297,28 +13460,37 @@
         <v>3</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B90" s="5" t="n">
         <v>0.5</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="50" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F92" s="0" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P92" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q92" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>157</v>
+      </c>
+      <c r="R92" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="S92" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="T92" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B93" s="18" t="s">
         <v>102</v>
@@ -13332,7 +13504,7 @@
       <c r="E93" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="F93" s="57" t="s">
+      <c r="F93" s="58" t="s">
         <v>106</v>
       </c>
       <c r="G93" s="18" t="s">
@@ -13362,14 +13534,23 @@
       <c r="O93" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="P93" s="58" t="s">
+      <c r="P93" s="59" t="s">
         <v>116</v>
       </c>
-      <c r="Q93" s="52" t="s">
+      <c r="Q93" s="53" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R93" s="53" t="s">
+        <v>118</v>
+      </c>
+      <c r="S93" s="53" t="s">
+        <v>159</v>
+      </c>
+      <c r="T93" s="53" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2" t="s">
         <v>80</v>
       </c>
@@ -13385,7 +13566,7 @@
       <c r="E94" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="F94" s="59" t="n">
+      <c r="F94" s="60" t="n">
         <v>0.5</v>
       </c>
       <c r="G94" s="19" t="n">
@@ -13415,14 +13596,23 @@
       <c r="O94" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="P94" s="59" t="n">
+      <c r="P94" s="60" t="n">
         <v>0.5</v>
       </c>
       <c r="Q94" s="19" t="n">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R94" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S94" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T94" s="19" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2" t="s">
         <v>120</v>
       </c>
@@ -13438,7 +13628,7 @@
       <c r="E95" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="F95" s="59" t="n">
+      <c r="F95" s="60" t="n">
         <v>1</v>
       </c>
       <c r="G95" s="19" t="n">
@@ -13468,14 +13658,23 @@
       <c r="O95" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="P95" s="59" t="n">
+      <c r="P95" s="60" t="n">
         <v>1</v>
       </c>
       <c r="Q95" s="19" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R95" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S95" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T95" s="19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2" t="s">
         <v>82</v>
       </c>
@@ -13491,7 +13690,7 @@
       <c r="E96" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="F96" s="59" t="n">
+      <c r="F96" s="60" t="n">
         <v>0.5</v>
       </c>
       <c r="G96" s="19" t="n">
@@ -13521,14 +13720,23 @@
       <c r="O96" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="P96" s="59" t="n">
+      <c r="P96" s="60" t="n">
         <v>0.5</v>
       </c>
       <c r="Q96" s="19" t="n">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R96" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S96" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T96" s="19" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2" t="s">
         <v>121</v>
       </c>
@@ -13544,7 +13752,7 @@
       <c r="E97" s="19" t="n">
         <v>1.5</v>
       </c>
-      <c r="F97" s="59" t="n">
+      <c r="F97" s="60" t="n">
         <v>1.5</v>
       </c>
       <c r="G97" s="19" t="n">
@@ -13574,14 +13782,23 @@
       <c r="O97" s="19" t="n">
         <v>1.5</v>
       </c>
-      <c r="P97" s="59" t="n">
+      <c r="P97" s="60" t="n">
         <v>1.5</v>
       </c>
       <c r="Q97" s="19" t="n">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R97" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S97" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T97" s="19" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2" t="s">
         <v>84</v>
       </c>
@@ -13633,8 +13850,17 @@
       <c r="Q98" s="26" t="n">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R98" s="26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S98" s="26" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="T98" s="26" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2" t="s">
         <v>79</v>
       </c>
@@ -13650,7 +13876,7 @@
       <c r="E99" s="19" t="n">
         <v>0.4</v>
       </c>
-      <c r="F99" s="59" t="n">
+      <c r="F99" s="60" t="n">
         <v>0.4</v>
       </c>
       <c r="G99" s="19" t="n">
@@ -13680,14 +13906,23 @@
       <c r="O99" s="19" t="n">
         <v>0.4</v>
       </c>
-      <c r="P99" s="59" t="n">
+      <c r="P99" s="60" t="n">
         <v>0.4</v>
       </c>
       <c r="Q99" s="19" t="n">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R99" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S99" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T99" s="19" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2" t="s">
         <v>85</v>
       </c>
@@ -13703,7 +13938,7 @@
       <c r="E100" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="F100" s="59" t="n">
+      <c r="F100" s="60" t="n">
         <v>1</v>
       </c>
       <c r="G100" s="19" t="n">
@@ -13733,14 +13968,23 @@
       <c r="O100" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="P100" s="59" t="n">
+      <c r="P100" s="60" t="n">
         <v>1</v>
       </c>
       <c r="Q100" s="19" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R100" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S100" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T100" s="19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2" t="s">
         <v>122</v>
       </c>
@@ -13792,8 +14036,17 @@
       <c r="Q101" s="26" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R101" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="S101" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="T101" s="26" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2" t="s">
         <v>123</v>
       </c>
@@ -13809,7 +14062,7 @@
       <c r="E102" s="19" t="n">
         <v>1.2</v>
       </c>
-      <c r="F102" s="59" t="n">
+      <c r="F102" s="60" t="n">
         <v>1.2</v>
       </c>
       <c r="G102" s="19" t="n">
@@ -13839,14 +14092,23 @@
       <c r="O102" s="19" t="n">
         <v>1.2</v>
       </c>
-      <c r="P102" s="59" t="n">
+      <c r="P102" s="60" t="n">
         <v>1.2</v>
       </c>
       <c r="Q102" s="19" t="n">
         <v>1.2</v>
       </c>
-    </row>
-    <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R102" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S102" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T102" s="19" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2" t="s">
         <v>124</v>
       </c>
@@ -13862,7 +14124,7 @@
       <c r="E103" s="19" t="n">
         <v>0.6</v>
       </c>
-      <c r="F103" s="59" t="n">
+      <c r="F103" s="60" t="n">
         <v>0.6</v>
       </c>
       <c r="G103" s="19" t="n">
@@ -13892,14 +14154,23 @@
       <c r="O103" s="19" t="n">
         <v>0.6</v>
       </c>
-      <c r="P103" s="59" t="n">
+      <c r="P103" s="60" t="n">
         <v>0.6</v>
       </c>
       <c r="Q103" s="19" t="n">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R103" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="S103" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T103" s="19" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="s">
         <v>125</v>
       </c>
@@ -13951,8 +14222,17 @@
       <c r="Q104" s="26" t="n">
         <v>12000</v>
       </c>
-    </row>
-    <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R104" s="26" t="n">
+        <v>12000</v>
+      </c>
+      <c r="S104" s="26" t="n">
+        <v>12000</v>
+      </c>
+      <c r="T104" s="26" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="19" t="s">
         <v>126</v>
       </c>
@@ -13972,8 +14252,11 @@
       <c r="O105" s="41"/>
       <c r="P105" s="41"/>
       <c r="Q105" s="41"/>
-    </row>
-    <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R105" s="41"/>
+      <c r="S105" s="41"/>
+      <c r="T105" s="41"/>
+    </row>
+    <row r="106" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="29" t="s">
         <v>128</v>
       </c>
@@ -13993,8 +14276,11 @@
       <c r="O106" s="44"/>
       <c r="P106" s="44"/>
       <c r="Q106" s="44"/>
-    </row>
-    <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R106" s="44"/>
+      <c r="S106" s="44"/>
+      <c r="T106" s="44"/>
+    </row>
+    <row r="107" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="19" t="s">
         <v>134</v>
       </c>
@@ -14046,8 +14332,17 @@
       <c r="Q107" s="26" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R107" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="S107" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="T107" s="26" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="19" t="s">
         <v>136</v>
       </c>
@@ -14099,8 +14394,17 @@
       <c r="Q108" s="26" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R108" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="S108" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="T108" s="26" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B109" s="5" t="n">
         <v>0.5</v>
       </c>
@@ -14149,54 +14453,165 @@
       <c r="Q109" s="5" t="n">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R109" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S109" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T109" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B110" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="G110" s="5" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="H110" s="5" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="I110" s="5" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="J110" s="5" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="K110" s="5" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="L110" s="5" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="M110" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="N110" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="O110" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="P110" s="51" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q110" s="51"/>
+        <v>161</v>
+      </c>
+      <c r="P110" s="52" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q110" s="52" t="s">
+        <v>165</v>
+      </c>
+      <c r="R110" s="0" t="s">
+        <v>166</v>
+      </c>
+      <c r="S110" s="0" t="s">
+        <v>166</v>
+      </c>
+      <c r="T110" s="0" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P112" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P113" s="59" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P114" s="60" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P115" s="60" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P116" s="60" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P117" s="60" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P118" s="44" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P119" s="60" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P120" s="60" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P121" s="44" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P122" s="60" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P123" s="60" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P124" s="44" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P125" s="41"/>
+    </row>
+    <row r="126" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P126" s="44"/>
+    </row>
+    <row r="127" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P127" s="44" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P128" s="44" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P129" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P130" s="52" t="s">
+        <v>164</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -14206,5 +14621,6 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/parameters script.xlsx
+++ b/parameters script.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
@@ -15,6 +15,7 @@
     <sheet name="28-12" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="22-2-2026" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="line 129" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="linea 132" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="952" uniqueCount="185">
   <si>
     <t xml:space="preserve">6h 3</t>
   </si>
@@ -466,30 +467,117 @@
     <t xml:space="preserve">3H-2</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">th</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> march</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Linea 129  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEST</t>
+  </si>
+  <si>
     <t xml:space="preserve">L3-1</t>
   </si>
   <si>
+    <t xml:space="preserve">T18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T24</t>
+  </si>
+  <si>
     <t xml:space="preserve">XY sigma average</t>
   </si>
   <si>
+    <t xml:space="preserve">12 ABRIL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0-0.7 UM</t>
+  </si>
+  <si>
     <t xml:space="preserve">L3-2</t>
   </si>
   <si>
+    <t xml:space="preserve">12 APRIL</t>
+  </si>
+  <si>
     <t xml:space="preserve">L3-3</t>
   </si>
   <si>
+    <t xml:space="preserve">0-0.65 UM</t>
+  </si>
+  <si>
     <t xml:space="preserve">L3-4</t>
   </si>
   <si>
+    <t xml:space="preserve">12 april</t>
+  </si>
+  <si>
     <t xml:space="preserve">L3-5</t>
   </si>
   <si>
     <t xml:space="preserve">0H-4</t>
   </si>
   <si>
+    <t xml:space="preserve">3H-3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3H-4</t>
+  </si>
+  <si>
     <t xml:space="preserve">0H-5</t>
   </si>
   <si>
+    <t xml:space="preserve">3H-5</t>
+  </si>
+  <si>
     <t xml:space="preserve">spotlight</t>
   </si>
   <si>
@@ -505,10 +593,7 @@
     <t xml:space="preserve">25 MARZO 26</t>
   </si>
   <si>
-    <t xml:space="preserve">T18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T19</t>
+    <t xml:space="preserve">30 marzo 26</t>
   </si>
   <si>
     <t xml:space="preserve">Version 1</t>
@@ -529,7 +614,7 @@
     <t xml:space="preserve">###########</t>
   </si>
   <si>
-    <t xml:space="preserve">T20</t>
+    <t xml:space="preserve">SPOTIFLOW FINAL</t>
   </si>
 </sst>
 </file>
@@ -542,7 +627,7 @@
     <numFmt numFmtId="166" formatCode="0.00%"/>
     <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -618,6 +703,15 @@
       <charset val="134"/>
     </font>
     <font>
+      <b val="true"/>
+      <vertAlign val="superscript"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF4000"/>
       <name val="Calibri"/>
@@ -625,7 +719,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -683,7 +777,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF860D"/>
-        <bgColor rgb="FFFF8080"/>
+        <bgColor rgb="FFFF8000"/>
       </patternFill>
     </fill>
     <fill>
@@ -706,12 +800,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFAA95"/>
+        <bgColor rgb="FFFFB66C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFBF00"/>
+        <bgColor rgb="FFFF972F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF8000"/>
+        <bgColor rgb="FFFF860D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF972F"/>
+        <bgColor rgb="FFFF860D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFB66C"/>
-        <bgColor rgb="FFFF99CC"/>
+        <bgColor rgb="FFFFAA95"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="10">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -768,6 +886,20 @@
       <bottom style="medium"/>
       <diagonal/>
     </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -794,7 +926,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="96">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -999,7 +1131,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1007,7 +1143,35 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="15" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="15" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1015,15 +1179,95 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="15" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="15" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="15" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="16" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="16" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="16" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="16" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="16" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="17" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="17" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="17" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="18" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="18" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="18" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="18" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1031,12 +1275,40 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="12" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1071,7 +1343,7 @@
       <rgbColor rgb="FFFFFFCC"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FFFF972F"/>
       <rgbColor rgb="FF2A6099"/>
       <rgbColor rgb="FFBDD7EE"/>
       <rgbColor rgb="FF000080"/>
@@ -1087,22 +1359,22 @@
       <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF92D050"/>
-      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFFFAA95"/>
       <rgbColor rgb="FFB2B2B2"/>
       <rgbColor rgb="FFFFB66C"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF81D41A"/>
-      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFFBF00"/>
       <rgbColor rgb="FFFF860D"/>
-      <rgbColor rgb="FFFF4000"/>
+      <rgbColor rgb="FFFF8000"/>
       <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF999999"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF5B9BD5"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FFFF4000"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
@@ -1122,9 +1394,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>468000</xdr:colOff>
+      <xdr:colOff>466920</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>25200</xdr:rowOff>
+      <xdr:rowOff>24120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1138,7 +1410,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6183720" y="130320"/>
-          <a:ext cx="7988760" cy="260640"/>
+          <a:ext cx="7987680" cy="259560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1164,10 +1436,10 @@
       <xdr:rowOff>30600</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>570600</xdr:colOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>221040</xdr:colOff>
       <xdr:row>88</xdr:row>
-      <xdr:rowOff>66600</xdr:rowOff>
+      <xdr:rowOff>65520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1180,8 +1452,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9763560" y="14112360"/>
-          <a:ext cx="10145160" cy="2047680"/>
+          <a:off x="10345680" y="14112360"/>
+          <a:ext cx="10146600" cy="2046600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1202,10 +1474,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>421920</xdr:colOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>885960</xdr:colOff>
       <xdr:row>126</xdr:row>
-      <xdr:rowOff>102600</xdr:rowOff>
+      <xdr:rowOff>101520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1218,8 +1490,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6275160" y="21031200"/>
-          <a:ext cx="10182960" cy="2114280"/>
+          <a:off x="6275880" y="21031200"/>
+          <a:ext cx="10183320" cy="2113200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9337,7 +9609,7 @@
       <c r="F73" s="24" t="n">
         <v>0.002</v>
       </c>
-      <c r="M73" s="0" t="s">
+      <c r="M73" s="1" t="s">
         <v>143</v>
       </c>
     </row>
@@ -9360,13 +9632,13 @@
       <c r="F74" s="20" t="n">
         <v>0.4</v>
       </c>
-      <c r="L74" s="0" t="n">
+      <c r="L74" s="1" t="n">
         <v>6.3</v>
       </c>
-      <c r="M74" s="0" t="n">
+      <c r="M74" s="1" t="n">
         <v>0.552</v>
       </c>
-      <c r="N74" s="0" t="n">
+      <c r="N74" s="1" t="n">
         <v>0.4778070152</v>
       </c>
       <c r="O74" s="51" t="n">
@@ -9393,13 +9665,13 @@
       <c r="F75" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="L75" s="0" t="n">
+      <c r="L75" s="1" t="n">
         <v>6.6</v>
       </c>
-      <c r="M75" s="0" t="n">
+      <c r="M75" s="1" t="n">
         <v>0.382</v>
       </c>
-      <c r="N75" s="0" t="n">
+      <c r="N75" s="1" t="n">
         <v>0.485653758</v>
       </c>
       <c r="O75" s="51" t="n">
@@ -9426,13 +9698,13 @@
       <c r="F76" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="L76" s="0" t="n">
+      <c r="L76" s="1" t="n">
         <v>6.7</v>
       </c>
-      <c r="M76" s="0" t="n">
+      <c r="M76" s="1" t="n">
         <v>0.467</v>
       </c>
-      <c r="N76" s="0" t="n">
+      <c r="N76" s="1" t="n">
         <v>0.5555944741</v>
       </c>
       <c r="O76" s="51" t="n">
@@ -9459,13 +9731,13 @@
       <c r="F77" s="20" t="n">
         <v>1.2</v>
       </c>
-      <c r="L77" s="0" t="n">
+      <c r="L77" s="1" t="n">
         <v>6.8</v>
       </c>
-      <c r="M77" s="0" t="n">
+      <c r="M77" s="1" t="n">
         <v>0.467</v>
       </c>
-      <c r="N77" s="0" t="n">
+      <c r="N77" s="1" t="n">
         <v>0.5027</v>
       </c>
       <c r="O77" s="51" t="n">
@@ -10228,15 +10500,26 @@
         <v>2</v>
       </c>
     </row>
+    <row r="120" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R120" s="52" t="s">
+        <v>146</v>
+      </c>
+    </row>
     <row r="121" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B121" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E121" s="52"/>
+      <c r="E121" s="53"/>
+      <c r="R121" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="V121" s="55" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="122" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B122" s="18" t="s">
         <v>102</v>
@@ -10283,10 +10566,33 @@
       <c r="P122" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="Q122" s="24" t="s">
+      <c r="Q122" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="R122" s="26"/>
+      <c r="R122" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="S122" s="56" t="s">
+        <v>150</v>
+      </c>
+      <c r="T122" s="56" t="s">
+        <v>151</v>
+      </c>
+      <c r="U122" s="56" t="s">
+        <v>152</v>
+      </c>
+      <c r="V122" s="57" t="s">
+        <v>153</v>
+      </c>
+      <c r="W122" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="X122" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="Y122" s="22" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="123" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="2" t="s">
@@ -10340,7 +10646,30 @@
       <c r="Q123" s="20" t="n">
         <v>0.5</v>
       </c>
-      <c r="R123" s="19"/>
+      <c r="R123" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S123" s="58" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T123" s="58" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U123" s="58" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V123" s="59" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W123" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X123" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y123" s="20" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="124" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="2" t="s">
@@ -10394,7 +10723,14 @@
       <c r="Q124" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="R124" s="19"/>
+      <c r="R124" s="60"/>
+      <c r="S124" s="60"/>
+      <c r="T124" s="60"/>
+      <c r="U124" s="60"/>
+      <c r="V124" s="61"/>
+      <c r="W124" s="60"/>
+      <c r="X124" s="60"/>
+      <c r="Y124" s="60"/>
     </row>
     <row r="125" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="2" t="s">
@@ -10448,7 +10784,14 @@
       <c r="Q125" s="20" t="n">
         <v>0.5</v>
       </c>
-      <c r="R125" s="19"/>
+      <c r="R125" s="60"/>
+      <c r="S125" s="60"/>
+      <c r="T125" s="60"/>
+      <c r="U125" s="60"/>
+      <c r="V125" s="61"/>
+      <c r="W125" s="60"/>
+      <c r="X125" s="60"/>
+      <c r="Y125" s="60"/>
     </row>
     <row r="126" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="2" t="s">
@@ -10502,7 +10845,14 @@
       <c r="Q126" s="20" t="n">
         <v>1.5</v>
       </c>
-      <c r="R126" s="19"/>
+      <c r="R126" s="60"/>
+      <c r="S126" s="60"/>
+      <c r="T126" s="60"/>
+      <c r="U126" s="60"/>
+      <c r="V126" s="61"/>
+      <c r="W126" s="60"/>
+      <c r="X126" s="60"/>
+      <c r="Y126" s="60"/>
     </row>
     <row r="127" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="2" t="s">
@@ -10556,7 +10906,30 @@
       <c r="Q127" s="24" t="n">
         <v>0.002</v>
       </c>
-      <c r="R127" s="26"/>
+      <c r="R127" s="24" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="S127" s="62" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="T127" s="62" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="U127" s="62" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="V127" s="63" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="W127" s="24" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="X127" s="24" t="n">
+        <v>0.00225</v>
+      </c>
+      <c r="Y127" s="24" t="n">
+        <v>0.002</v>
+      </c>
     </row>
     <row r="128" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="2" t="s">
@@ -10610,7 +10983,30 @@
       <c r="Q128" s="20" t="n">
         <v>0.4</v>
       </c>
-      <c r="R128" s="19"/>
+      <c r="R128" s="20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S128" s="58" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T128" s="58" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U128" s="58" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="V128" s="59" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W128" s="20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="X128" s="20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y128" s="20" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="129" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="2" t="s">
@@ -10664,7 +11060,30 @@
       <c r="Q129" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="R129" s="26"/>
+      <c r="R129" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S129" s="62" t="n">
+        <v>1</v>
+      </c>
+      <c r="T129" s="62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U129" s="62" t="n">
+        <v>1</v>
+      </c>
+      <c r="V129" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="W129" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="X129" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y129" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="130" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="2" t="s">
@@ -10718,7 +11137,30 @@
       <c r="Q130" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="R130" s="26"/>
+      <c r="R130" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="S130" s="62" t="n">
+        <v>8</v>
+      </c>
+      <c r="T130" s="62" t="n">
+        <v>8</v>
+      </c>
+      <c r="U130" s="62" t="n">
+        <v>8</v>
+      </c>
+      <c r="V130" s="63" t="n">
+        <v>8</v>
+      </c>
+      <c r="W130" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="X130" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y130" s="24" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="131" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="2" t="s">
@@ -10772,7 +11214,30 @@
       <c r="Q131" s="20" t="n">
         <v>1.2</v>
       </c>
-      <c r="R131" s="19"/>
+      <c r="R131" s="20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S131" s="58" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T131" s="58" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="U131" s="58" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V131" s="59" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W131" s="20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X131" s="20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Y131" s="20" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="132" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="2" t="s">
@@ -10826,7 +11291,30 @@
       <c r="Q132" s="20" t="n">
         <v>0.6</v>
       </c>
-      <c r="R132" s="19"/>
+      <c r="R132" s="20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="S132" s="58" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T132" s="58" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="U132" s="58" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="V132" s="59" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="W132" s="20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="X132" s="20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Y132" s="20" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="133" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="2" t="s">
@@ -10880,7 +11368,30 @@
       <c r="Q133" s="24" t="n">
         <v>12000</v>
       </c>
-      <c r="R133" s="26"/>
+      <c r="R133" s="24" t="n">
+        <v>12000</v>
+      </c>
+      <c r="S133" s="62" t="n">
+        <v>12000</v>
+      </c>
+      <c r="T133" s="62" t="n">
+        <v>12000</v>
+      </c>
+      <c r="U133" s="62" t="n">
+        <v>12000</v>
+      </c>
+      <c r="V133" s="63" t="n">
+        <v>12000</v>
+      </c>
+      <c r="W133" s="24" t="n">
+        <v>12000</v>
+      </c>
+      <c r="X133" s="24" t="n">
+        <v>12000</v>
+      </c>
+      <c r="Y133" s="24" t="n">
+        <v>12000</v>
+      </c>
     </row>
     <row r="134" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="19" t="s">
@@ -10903,6 +11414,13 @@
       <c r="P134" s="41"/>
       <c r="Q134" s="41"/>
       <c r="R134" s="41"/>
+      <c r="S134" s="41"/>
+      <c r="T134" s="41"/>
+      <c r="U134" s="41"/>
+      <c r="V134" s="61"/>
+      <c r="W134" s="41"/>
+      <c r="X134" s="41"/>
+      <c r="Y134" s="41"/>
     </row>
     <row r="135" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="29" t="s">
@@ -10925,6 +11443,13 @@
       <c r="P135" s="44"/>
       <c r="Q135" s="44"/>
       <c r="R135" s="44"/>
+      <c r="S135" s="44"/>
+      <c r="T135" s="44"/>
+      <c r="U135" s="44"/>
+      <c r="V135" s="64"/>
+      <c r="W135" s="44"/>
+      <c r="X135" s="44"/>
+      <c r="Y135" s="44"/>
     </row>
     <row r="136" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="19" t="s">
@@ -10978,7 +11503,30 @@
       <c r="Q136" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="R136" s="26"/>
+      <c r="R136" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="S136" s="62" t="n">
+        <v>2</v>
+      </c>
+      <c r="T136" s="62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U136" s="62" t="n">
+        <v>2</v>
+      </c>
+      <c r="V136" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="W136" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="X136" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y136" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="137" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="19" t="s">
@@ -11032,11 +11580,34 @@
       <c r="Q137" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="R137" s="26"/>
+      <c r="R137" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="S137" s="62" t="n">
+        <v>3</v>
+      </c>
+      <c r="T137" s="62" t="n">
+        <v>3</v>
+      </c>
+      <c r="U137" s="62" t="n">
+        <v>3</v>
+      </c>
+      <c r="V137" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="W137" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="X137" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y137" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="138" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="1" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="B138" s="1" t="n">
         <v>0.5</v>
@@ -11086,11 +11657,51 @@
       <c r="Q138" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="R138" s="5"/>
+      <c r="R138" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="S138" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="T138" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U138" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="V138" s="65" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="W138" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="X138" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Y138" s="5" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P139" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q139" s="50" t="s">
+        <v>158</v>
+      </c>
+      <c r="R139" s="66" t="s">
+        <v>148</v>
+      </c>
+      <c r="V139" s="67" t="s">
+        <v>159</v>
+      </c>
+      <c r="Y139" s="1" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="140" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="2" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="B140" s="18" t="s">
         <v>102</v>
@@ -11133,6 +11744,15 @@
       </c>
       <c r="O140" s="24" t="s">
         <v>115</v>
+      </c>
+      <c r="P140" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q140" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="R140" s="69" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11181,6 +11801,15 @@
       <c r="O141" s="20" t="n">
         <v>0.5</v>
       </c>
+      <c r="P141" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q141" s="70" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R141" s="71" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="142" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="2" t="s">
@@ -11228,6 +11857,9 @@
       <c r="O142" s="20" t="n">
         <v>1</v>
       </c>
+      <c r="P142" s="60"/>
+      <c r="Q142" s="60"/>
+      <c r="R142" s="61"/>
     </row>
     <row r="143" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="2" t="s">
@@ -11275,6 +11907,9 @@
       <c r="O143" s="20" t="n">
         <v>0.5</v>
       </c>
+      <c r="P143" s="60"/>
+      <c r="Q143" s="60"/>
+      <c r="R143" s="61"/>
     </row>
     <row r="144" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="2" t="s">
@@ -11322,6 +11957,9 @@
       <c r="O144" s="20" t="n">
         <v>1.5</v>
       </c>
+      <c r="P144" s="60"/>
+      <c r="Q144" s="60"/>
+      <c r="R144" s="61"/>
     </row>
     <row r="145" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="2" t="s">
@@ -11369,6 +12007,15 @@
       <c r="O145" s="24" t="n">
         <v>0.004</v>
       </c>
+      <c r="P145" s="24" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="Q145" s="72" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="R145" s="69" t="n">
+        <v>0.005</v>
+      </c>
     </row>
     <row r="146" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="2" t="s">
@@ -11416,6 +12063,15 @@
       <c r="O146" s="20" t="n">
         <v>0.4</v>
       </c>
+      <c r="P146" s="20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q146" s="70" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R146" s="71" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="147" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="2" t="s">
@@ -11463,6 +12119,15 @@
       <c r="O147" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="P147" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q147" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="R147" s="69" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="148" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="2" t="s">
@@ -11510,6 +12175,15 @@
       <c r="O148" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="P148" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q148" s="72" t="n">
+        <v>3</v>
+      </c>
+      <c r="R148" s="69" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="149" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="2" t="s">
@@ -11557,6 +12231,15 @@
       <c r="O149" s="20" t="n">
         <v>1.2</v>
       </c>
+      <c r="P149" s="20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q149" s="70" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R149" s="71" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="150" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="2" t="s">
@@ -11604,6 +12287,15 @@
       <c r="O150" s="20" t="n">
         <v>0.6</v>
       </c>
+      <c r="P150" s="20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q150" s="70" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R150" s="71" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="151" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="2" t="s">
@@ -11649,6 +12341,15 @@
         <v>8000</v>
       </c>
       <c r="O151" s="24" t="n">
+        <v>4000</v>
+      </c>
+      <c r="P151" s="24" t="n">
+        <v>4000</v>
+      </c>
+      <c r="Q151" s="72" t="n">
+        <v>4000</v>
+      </c>
+      <c r="R151" s="69" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -11670,6 +12371,9 @@
       <c r="M152" s="41"/>
       <c r="N152" s="41"/>
       <c r="O152" s="41"/>
+      <c r="P152" s="41"/>
+      <c r="Q152" s="41"/>
+      <c r="R152" s="48"/>
     </row>
     <row r="153" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="29" t="s">
@@ -11689,6 +12393,9 @@
       <c r="M153" s="44"/>
       <c r="N153" s="44"/>
       <c r="O153" s="44"/>
+      <c r="P153" s="44"/>
+      <c r="Q153" s="44"/>
+      <c r="R153" s="49"/>
     </row>
     <row r="154" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="19" t="s">
@@ -11736,6 +12443,15 @@
       <c r="O154" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="P154" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q154" s="72" t="n">
+        <v>2</v>
+      </c>
+      <c r="R154" s="69" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="155" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="19" t="s">
@@ -11783,10 +12499,19 @@
       <c r="O155" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="P155" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q155" s="72" t="n">
+        <v>3</v>
+      </c>
+      <c r="R155" s="69" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="156" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="1" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="B156" s="5" t="n">
         <v>0.3</v>
@@ -11830,10 +12555,33 @@
       <c r="O156" s="5" t="n">
         <v>0.3</v>
       </c>
+      <c r="P156" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q156" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R156" s="31" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H157" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="I157" s="50" t="s">
+        <v>161</v>
+      </c>
+      <c r="K157" s="50" t="s">
+        <v>148</v>
+      </c>
+      <c r="R157" s="50" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="158" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="2" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="B158" s="18" t="s">
         <v>102</v>
@@ -11850,8 +12598,20 @@
       <c r="F158" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="G158" s="24" t="s">
+      <c r="G158" s="22" t="s">
         <v>107</v>
+      </c>
+      <c r="H158" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="I158" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="J158" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="K158" s="72" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11876,6 +12636,18 @@
       <c r="G159" s="20" t="n">
         <v>0.5</v>
       </c>
+      <c r="H159" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I159" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J159" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K159" s="70" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="160" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="2" t="s">
@@ -11899,6 +12671,10 @@
       <c r="G160" s="20" t="n">
         <v>1</v>
       </c>
+      <c r="H160" s="60"/>
+      <c r="I160" s="60"/>
+      <c r="J160" s="60"/>
+      <c r="K160" s="60"/>
     </row>
     <row r="161" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="2" t="s">
@@ -11922,6 +12698,10 @@
       <c r="G161" s="20" t="n">
         <v>0.5</v>
       </c>
+      <c r="H161" s="60"/>
+      <c r="I161" s="60"/>
+      <c r="J161" s="60"/>
+      <c r="K161" s="60"/>
     </row>
     <row r="162" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="2" t="s">
@@ -11945,6 +12725,10 @@
       <c r="G162" s="20" t="n">
         <v>1.5</v>
       </c>
+      <c r="H162" s="60"/>
+      <c r="I162" s="60"/>
+      <c r="J162" s="60"/>
+      <c r="K162" s="60"/>
     </row>
     <row r="163" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="2" t="s">
@@ -11968,6 +12752,18 @@
       <c r="G163" s="24" t="n">
         <v>0.005</v>
       </c>
+      <c r="H163" s="24" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="I163" s="24" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="J163" s="24" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="K163" s="72" t="n">
+        <v>0.006</v>
+      </c>
     </row>
     <row r="164" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="2" t="s">
@@ -11991,6 +12787,18 @@
       <c r="G164" s="20" t="n">
         <v>0.4</v>
       </c>
+      <c r="H164" s="20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I164" s="20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J164" s="20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K164" s="70" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="165" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="2" t="s">
@@ -12014,6 +12822,18 @@
       <c r="G165" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="H165" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I165" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J165" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K165" s="72" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="166" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="2" t="s">
@@ -12037,6 +12857,18 @@
       <c r="G166" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="H166" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I166" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J166" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K166" s="72" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="167" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="2" t="s">
@@ -12060,6 +12892,18 @@
       <c r="G167" s="20" t="n">
         <v>1.2</v>
       </c>
+      <c r="H167" s="20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I167" s="20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J167" s="20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K167" s="70" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="168" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="2" t="s">
@@ -12083,6 +12927,18 @@
       <c r="G168" s="20" t="n">
         <v>0.6</v>
       </c>
+      <c r="H168" s="20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I168" s="20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J168" s="20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K168" s="70" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="169" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="2" t="s">
@@ -12104,6 +12960,18 @@
         <v>30000</v>
       </c>
       <c r="G169" s="24" t="n">
+        <v>50000</v>
+      </c>
+      <c r="H169" s="24" t="n">
+        <v>50000</v>
+      </c>
+      <c r="I169" s="24" t="n">
+        <v>50000</v>
+      </c>
+      <c r="J169" s="24" t="n">
+        <v>50000</v>
+      </c>
+      <c r="K169" s="72" t="n">
         <v>50000</v>
       </c>
     </row>
@@ -12117,6 +12985,10 @@
       <c r="E170" s="41"/>
       <c r="F170" s="41"/>
       <c r="G170" s="41"/>
+      <c r="H170" s="41"/>
+      <c r="I170" s="41"/>
+      <c r="J170" s="41"/>
+      <c r="K170" s="41"/>
     </row>
     <row r="171" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="29" t="s">
@@ -12128,6 +13000,10 @@
       <c r="E171" s="44"/>
       <c r="F171" s="44"/>
       <c r="G171" s="44"/>
+      <c r="H171" s="44"/>
+      <c r="I171" s="44"/>
+      <c r="J171" s="44"/>
+      <c r="K171" s="44"/>
     </row>
     <row r="172" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="19" t="s">
@@ -12151,6 +13027,18 @@
       <c r="G172" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="H172" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I172" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J172" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K172" s="72" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="173" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="19" t="s">
@@ -12174,10 +13062,22 @@
       <c r="G173" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="H173" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="I173" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J173" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="K173" s="72" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="174" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="1" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="B174" s="5" t="n">
         <v>0.3</v>
@@ -12197,16 +13097,57 @@
       <c r="G174" s="6" t="n">
         <v>0.3</v>
       </c>
+      <c r="H174" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I174" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J174" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K174" s="73" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D175" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="E175" s="50" t="s">
+        <v>161</v>
+      </c>
+      <c r="H175" s="50" t="s">
+        <v>148</v>
+      </c>
+      <c r="K175" s="50" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="176" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="2" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="B176" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="C176" s="24" t="s">
+      <c r="C176" s="22" t="s">
         <v>103</v>
+      </c>
+      <c r="D176" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="E176" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="F176" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="G176" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="H176" s="72" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12219,6 +13160,21 @@
       <c r="C177" s="20" t="n">
         <v>0.5</v>
       </c>
+      <c r="D177" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E177" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F177" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G177" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H177" s="70" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="178" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="2" t="s">
@@ -12230,6 +13186,11 @@
       <c r="C178" s="20" t="n">
         <v>1</v>
       </c>
+      <c r="D178" s="60"/>
+      <c r="E178" s="60"/>
+      <c r="F178" s="60"/>
+      <c r="G178" s="60"/>
+      <c r="H178" s="60"/>
     </row>
     <row r="179" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="2" t="s">
@@ -12241,6 +13202,11 @@
       <c r="C179" s="20" t="n">
         <v>0.5</v>
       </c>
+      <c r="D179" s="60"/>
+      <c r="E179" s="60"/>
+      <c r="F179" s="60"/>
+      <c r="G179" s="60"/>
+      <c r="H179" s="60"/>
     </row>
     <row r="180" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="2" t="s">
@@ -12252,6 +13218,11 @@
       <c r="C180" s="20" t="n">
         <v>1.5</v>
       </c>
+      <c r="D180" s="60"/>
+      <c r="E180" s="60"/>
+      <c r="F180" s="60"/>
+      <c r="G180" s="60"/>
+      <c r="H180" s="60"/>
     </row>
     <row r="181" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="2" t="s">
@@ -12263,6 +13234,21 @@
       <c r="C181" s="24" t="n">
         <v>0.003</v>
       </c>
+      <c r="D181" s="24" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="E181" s="24" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F181" s="24" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="G181" s="24" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="H181" s="72" t="n">
+        <v>0.00525</v>
+      </c>
     </row>
     <row r="182" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="2" t="s">
@@ -12274,6 +13260,21 @@
       <c r="C182" s="20" t="n">
         <v>0.4</v>
       </c>
+      <c r="D182" s="20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E182" s="20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F182" s="20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G182" s="20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H182" s="70" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="183" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="2" t="s">
@@ -12285,6 +13286,21 @@
       <c r="C183" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="D183" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E183" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F183" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G183" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H183" s="72" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="184" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="2" t="s">
@@ -12296,6 +13312,21 @@
       <c r="C184" s="24" t="n">
         <v>4</v>
       </c>
+      <c r="D184" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="E184" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="F184" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="G184" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="H184" s="72" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="185" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="2" t="s">
@@ -12307,6 +13338,21 @@
       <c r="C185" s="20" t="n">
         <v>1.2</v>
       </c>
+      <c r="D185" s="20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E185" s="20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F185" s="20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G185" s="20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H185" s="70" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="186" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="2" t="s">
@@ -12318,6 +13364,21 @@
       <c r="C186" s="20" t="n">
         <v>0.6</v>
       </c>
+      <c r="D186" s="20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E186" s="20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F186" s="20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G186" s="20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H186" s="70" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="187" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="2" t="s">
@@ -12329,6 +13390,21 @@
       <c r="C187" s="24" t="n">
         <v>50000</v>
       </c>
+      <c r="D187" s="24" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E187" s="24" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F187" s="24" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G187" s="24" t="n">
+        <v>50000</v>
+      </c>
+      <c r="H187" s="72" t="n">
+        <v>50000</v>
+      </c>
     </row>
     <row r="188" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="19" t="s">
@@ -12336,6 +13412,11 @@
       </c>
       <c r="B188" s="41"/>
       <c r="C188" s="41"/>
+      <c r="D188" s="41"/>
+      <c r="E188" s="41"/>
+      <c r="F188" s="41"/>
+      <c r="G188" s="41"/>
+      <c r="H188" s="41"/>
     </row>
     <row r="189" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="29" t="s">
@@ -12343,6 +13424,11 @@
       </c>
       <c r="B189" s="44"/>
       <c r="C189" s="44"/>
+      <c r="D189" s="44"/>
+      <c r="E189" s="44"/>
+      <c r="F189" s="44"/>
+      <c r="G189" s="44"/>
+      <c r="H189" s="44"/>
     </row>
     <row r="190" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="19" t="s">
@@ -12354,6 +13440,21 @@
       <c r="C190" s="24" t="n">
         <v>3</v>
       </c>
+      <c r="D190" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E190" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F190" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G190" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H190" s="72" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="191" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="19" t="s">
@@ -12365,10 +13466,25 @@
       <c r="C191" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="D191" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E191" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="F191" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="G191" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="H191" s="72" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="192" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="1" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="B192" s="5" t="n">
         <v>0.3</v>
@@ -12376,10 +13492,36 @@
       <c r="C192" s="5" t="n">
         <v>0.3</v>
       </c>
+      <c r="D192" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E192" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F192" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G192" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H192" s="73" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E193" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="F193" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="G193" s="50" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="194" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="2" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B194" s="18" t="s">
         <v>102</v>
@@ -12387,8 +13529,17 @@
       <c r="C194" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="D194" s="24" t="s">
+      <c r="D194" s="22" t="s">
         <v>104</v>
+      </c>
+      <c r="E194" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="F194" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="G194" s="74" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12404,6 +13555,15 @@
       <c r="D195" s="20" t="n">
         <v>0.5</v>
       </c>
+      <c r="E195" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F195" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G195" s="75" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="196" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="2" t="s">
@@ -12418,6 +13578,9 @@
       <c r="D196" s="20" t="n">
         <v>1</v>
       </c>
+      <c r="E196" s="60"/>
+      <c r="F196" s="60"/>
+      <c r="G196" s="60"/>
     </row>
     <row r="197" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="2" t="s">
@@ -12432,6 +13595,9 @@
       <c r="D197" s="20" t="n">
         <v>0.5</v>
       </c>
+      <c r="E197" s="60"/>
+      <c r="F197" s="60"/>
+      <c r="G197" s="60"/>
     </row>
     <row r="198" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="2" t="s">
@@ -12446,6 +13612,9 @@
       <c r="D198" s="20" t="n">
         <v>1.5</v>
       </c>
+      <c r="E198" s="60"/>
+      <c r="F198" s="60"/>
+      <c r="G198" s="60"/>
     </row>
     <row r="199" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="2" t="s">
@@ -12460,6 +13629,15 @@
       <c r="D199" s="24" t="n">
         <v>0.003</v>
       </c>
+      <c r="E199" s="24" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="F199" s="24" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="G199" s="74" t="n">
+        <v>0.0035</v>
+      </c>
     </row>
     <row r="200" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="2" t="s">
@@ -12474,6 +13652,15 @@
       <c r="D200" s="20" t="n">
         <v>0.4</v>
       </c>
+      <c r="E200" s="20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F200" s="20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G200" s="75" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="201" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="2" t="s">
@@ -12488,6 +13675,15 @@
       <c r="D201" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="E201" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F201" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G201" s="74" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="202" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="2" t="s">
@@ -12502,6 +13698,15 @@
       <c r="D202" s="24" t="n">
         <v>2</v>
       </c>
+      <c r="E202" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F202" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G202" s="74" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="203" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="2" t="s">
@@ -12516,6 +13721,15 @@
       <c r="D203" s="20" t="n">
         <v>1.2</v>
       </c>
+      <c r="E203" s="20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F203" s="20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G203" s="75" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="204" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="2" t="s">
@@ -12530,6 +13744,15 @@
       <c r="D204" s="20" t="n">
         <v>0.6</v>
       </c>
+      <c r="E204" s="20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F204" s="20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G204" s="75" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="205" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="2" t="s">
@@ -12544,6 +13767,15 @@
       <c r="D205" s="24" t="n">
         <v>50000</v>
       </c>
+      <c r="E205" s="24" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F205" s="24" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G205" s="74" t="n">
+        <v>50000</v>
+      </c>
     </row>
     <row r="206" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="19" t="s">
@@ -12552,6 +13784,9 @@
       <c r="B206" s="41"/>
       <c r="C206" s="41"/>
       <c r="D206" s="41"/>
+      <c r="E206" s="41"/>
+      <c r="F206" s="41"/>
+      <c r="G206" s="41"/>
     </row>
     <row r="207" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="29" t="s">
@@ -12560,6 +13795,9 @@
       <c r="B207" s="44"/>
       <c r="C207" s="44"/>
       <c r="D207" s="44"/>
+      <c r="E207" s="44"/>
+      <c r="F207" s="44"/>
+      <c r="G207" s="44"/>
     </row>
     <row r="208" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="19" t="s">
@@ -12574,6 +13812,15 @@
       <c r="D208" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="E208" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F208" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G208" s="74" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="209" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="19" t="s">
@@ -12588,10 +13835,19 @@
       <c r="D209" s="24" t="n">
         <v>1</v>
       </c>
+      <c r="E209" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="F209" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="G209" s="74" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="210" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="1" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="B210" s="5" t="n">
         <v>0.3</v>
@@ -12601,6 +13857,15 @@
       </c>
       <c r="D210" s="5" t="n">
         <v>0.3</v>
+      </c>
+      <c r="E210" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F210" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G210" s="76" t="n">
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -12619,19 +13884,52 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:T130"/>
+  <dimension ref="A1:W1048576"/>
   <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="14.4" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="12.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="19.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="19.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="19.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="12.23"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B1" s="53" t="s">
+      <c r="B1" s="18" t="s">
         <v>102</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="I1" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="P1" s="77" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q1" s="45" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12641,6 +13939,36 @@
       <c r="B2" s="19" t="n">
         <v>0.5</v>
       </c>
+      <c r="C2" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D2" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E2" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F2" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G2" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H2" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I2" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="P2" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q2" s="46" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
@@ -12649,6 +13977,18 @@
       <c r="B3" s="19" t="n">
         <v>1</v>
       </c>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="60"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="O3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="P3" s="61"/>
+      <c r="Q3" s="61"/>
     </row>
     <row r="4" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
@@ -12657,6 +13997,18 @@
       <c r="B4" s="19" t="n">
         <v>0.5</v>
       </c>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="O4" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="P4" s="61"/>
+      <c r="Q4" s="61"/>
     </row>
     <row r="5" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
@@ -12665,6 +14017,18 @@
       <c r="B5" s="19" t="n">
         <v>1.5</v>
       </c>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="O5" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="P5" s="61"/>
+      <c r="Q5" s="61"/>
     </row>
     <row r="6" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
@@ -12673,6 +14037,36 @@
       <c r="B6" s="26" t="n">
         <v>0.01</v>
       </c>
+      <c r="C6" s="26" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D6" s="26" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F6" s="26" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="G6" s="26" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H6" s="26" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="I6" s="24" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="P6" s="45" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="Q6" s="45" t="n">
+        <v>0.003</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
@@ -12681,6 +14075,36 @@
       <c r="B7" s="19" t="n">
         <v>0.5</v>
       </c>
+      <c r="C7" s="26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D7" s="26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F7" s="26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G7" s="26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H7" s="26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I7" s="24" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="P7" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q7" s="46" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
@@ -12689,6 +14113,36 @@
       <c r="B8" s="19" t="n">
         <v>0.7</v>
       </c>
+      <c r="C8" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="P8" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="46" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
@@ -12697,6 +14151,36 @@
       <c r="B9" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="C9" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="G9" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="H9" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="P9" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="45" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
@@ -12705,6 +14189,36 @@
       <c r="B10" s="19" t="n">
         <v>1.2</v>
       </c>
+      <c r="C10" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D10" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E10" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H10" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I10" s="20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="P10" s="46" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q10" s="46" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
@@ -12713,6 +14227,36 @@
       <c r="B11" s="19" t="n">
         <v>0.6</v>
       </c>
+      <c r="C11" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D11" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E11" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F11" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H11" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I11" s="20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="P11" s="46" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q11" s="46" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
@@ -12721,18 +14265,72 @@
       <c r="B12" s="26" t="n">
         <v>5000</v>
       </c>
+      <c r="C12" s="26" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D12" s="26" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E12" s="26" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F12" s="26" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G12" s="26" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H12" s="26" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I12" s="24" t="n">
+        <v>10000</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P12" s="45" t="n">
+        <v>60000</v>
+      </c>
+      <c r="Q12" s="45" t="n">
+        <v>60000</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="19" t="s">
         <v>126</v>
       </c>
       <c r="B13" s="41"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="41"/>
+      <c r="O13" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="P13" s="61"/>
+      <c r="Q13" s="61"/>
     </row>
     <row r="14" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="29" t="s">
         <v>128</v>
       </c>
       <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="44"/>
+      <c r="O14" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="P14" s="64"/>
+      <c r="Q14" s="64"/>
     </row>
     <row r="15" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
@@ -12741,6 +14339,36 @@
       <c r="B15" s="19" t="n">
         <v>1</v>
       </c>
+      <c r="C15" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="P15" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" s="45" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="19" t="s">
@@ -12749,18 +14377,84 @@
       <c r="B16" s="19" t="n">
         <v>1</v>
       </c>
+      <c r="C16" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="P16" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q16" s="45" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="1" t="n">
         <v>0.3</v>
       </c>
+      <c r="C17" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P17" s="78" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Q17" s="78" t="n">
+        <v>0.45</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="B19" s="53" t="s">
+        <v>167</v>
+      </c>
+      <c r="B19" s="18" t="s">
         <v>102</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12770,6 +14464,48 @@
       <c r="B20" s="19" t="n">
         <v>0.5</v>
       </c>
+      <c r="C20" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D20" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E20" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="K20" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="L20" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="M20" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="N20" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="S20" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="T20" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="U20" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="V20" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="W20" s="22" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
@@ -12778,6 +14514,42 @@
       <c r="B21" s="19" t="n">
         <v>1</v>
       </c>
+      <c r="C21" s="60"/>
+      <c r="D21" s="60"/>
+      <c r="E21" s="60"/>
+      <c r="J21" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="K21" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L21" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M21" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N21" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="S21" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T21" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U21" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V21" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W21" s="22" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
@@ -12786,6 +14558,24 @@
       <c r="B22" s="19" t="n">
         <v>0.5</v>
       </c>
+      <c r="C22" s="60"/>
+      <c r="D22" s="60"/>
+      <c r="E22" s="60"/>
+      <c r="J22" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="K22" s="60"/>
+      <c r="L22" s="60"/>
+      <c r="M22" s="60"/>
+      <c r="N22" s="60"/>
+      <c r="R22" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="S22" s="60"/>
+      <c r="T22" s="60"/>
+      <c r="U22" s="60"/>
+      <c r="V22" s="60"/>
+      <c r="W22" s="60"/>
     </row>
     <row r="23" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
@@ -12794,6 +14584,24 @@
       <c r="B23" s="19" t="n">
         <v>1.5</v>
       </c>
+      <c r="C23" s="60"/>
+      <c r="D23" s="60"/>
+      <c r="E23" s="60"/>
+      <c r="J23" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K23" s="60"/>
+      <c r="L23" s="60"/>
+      <c r="M23" s="60"/>
+      <c r="N23" s="60"/>
+      <c r="R23" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="S23" s="60"/>
+      <c r="T23" s="60"/>
+      <c r="U23" s="60"/>
+      <c r="V23" s="60"/>
+      <c r="W23" s="60"/>
     </row>
     <row r="24" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
@@ -12802,6 +14610,30 @@
       <c r="B24" s="26" t="n">
         <v>0.01</v>
       </c>
+      <c r="C24" s="26" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="D24" s="26" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="E24" s="24" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="K24" s="60"/>
+      <c r="L24" s="60"/>
+      <c r="M24" s="60"/>
+      <c r="N24" s="60"/>
+      <c r="R24" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="S24" s="60"/>
+      <c r="T24" s="60"/>
+      <c r="U24" s="60"/>
+      <c r="V24" s="60"/>
+      <c r="W24" s="60"/>
     </row>
     <row r="25" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
@@ -12810,6 +14642,48 @@
       <c r="B25" s="19" t="n">
         <v>0.5</v>
       </c>
+      <c r="C25" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D25" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E25" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="K25" s="26" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="L25" s="18" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="M25" s="18" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="N25" s="22" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="R25" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="S25" s="18" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="T25" s="18" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="U25" s="22" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="V25" s="18" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="W25" s="22" t="n">
+        <v>0.00175</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
@@ -12818,6 +14692,48 @@
       <c r="B26" s="19" t="n">
         <v>0.7</v>
       </c>
+      <c r="C26" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="K26" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L26" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M26" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N26" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R26" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="S26" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T26" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U26" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V26" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W26" s="22" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
@@ -12826,6 +14742,48 @@
       <c r="B27" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="C27" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="D27" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="E27" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="K27" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="S27" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" s="22" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
@@ -12834,6 +14792,48 @@
       <c r="B28" s="19" t="n">
         <v>1.2</v>
       </c>
+      <c r="C28" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D28" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E28" s="20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="K28" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="L28" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="M28" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="N28" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="R28" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="S28" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T28" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="V28" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="W28" s="22" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
@@ -12842,6 +14842,48 @@
       <c r="B29" s="19" t="n">
         <v>0.6</v>
       </c>
+      <c r="C29" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D29" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E29" s="20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="K29" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L29" s="18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M29" s="18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N29" s="22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R29" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="S29" s="18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T29" s="18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="U29" s="22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V29" s="18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W29" s="22" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
@@ -12850,18 +14892,114 @@
       <c r="B30" s="26" t="n">
         <v>5000</v>
       </c>
+      <c r="C30" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D30" s="26" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E30" s="24" t="n">
+        <v>40000</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="K30" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L30" s="18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M30" s="18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N30" s="22" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R30" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="S30" s="18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T30" s="18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="U30" s="22" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="V30" s="18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="W30" s="22" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="19" t="s">
         <v>126</v>
       </c>
       <c r="B31" s="41"/>
+      <c r="C31" s="41"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="41"/>
+      <c r="J31" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="K31" s="26" t="n">
+        <v>60000</v>
+      </c>
+      <c r="L31" s="18" t="n">
+        <v>60000</v>
+      </c>
+      <c r="M31" s="18" t="n">
+        <v>60000</v>
+      </c>
+      <c r="N31" s="22" t="n">
+        <v>60000</v>
+      </c>
+      <c r="R31" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="S31" s="18" t="n">
+        <v>60000</v>
+      </c>
+      <c r="T31" s="18" t="n">
+        <v>60000</v>
+      </c>
+      <c r="U31" s="22" t="n">
+        <v>60000</v>
+      </c>
+      <c r="V31" s="18" t="n">
+        <v>60000</v>
+      </c>
+      <c r="W31" s="22" t="n">
+        <v>60000</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="29" t="s">
         <v>128</v>
       </c>
       <c r="B32" s="44"/>
+      <c r="C32" s="44"/>
+      <c r="D32" s="44"/>
+      <c r="E32" s="44"/>
+      <c r="J32" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="K32" s="60"/>
+      <c r="L32" s="60"/>
+      <c r="M32" s="60"/>
+      <c r="N32" s="60"/>
+      <c r="R32" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="S32" s="60"/>
+      <c r="T32" s="60"/>
+      <c r="U32" s="60"/>
+      <c r="V32" s="60"/>
+      <c r="W32" s="60"/>
     </row>
     <row r="33" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="19" t="s">
@@ -12870,6 +15008,30 @@
       <c r="B33" s="19" t="n">
         <v>1</v>
       </c>
+      <c r="C33" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="K33" s="30"/>
+      <c r="L33" s="30"/>
+      <c r="M33" s="30"/>
+      <c r="N33" s="30"/>
+      <c r="R33" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="S33" s="30"/>
+      <c r="T33" s="30"/>
+      <c r="U33" s="30"/>
+      <c r="V33" s="30"/>
+      <c r="W33" s="30"/>
     </row>
     <row r="34" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="19" t="s">
@@ -12878,18 +15040,173 @@
       <c r="B34" s="19" t="n">
         <v>1</v>
       </c>
+      <c r="C34" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="K34" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="L34" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="N34" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="R34" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="S34" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T34" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V34" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="W34" s="22" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="1" t="n">
         <v>0.3</v>
       </c>
+      <c r="C35" s="1" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D35" s="1" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J35" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="K35" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="L35" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="N35" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="R35" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="S35" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T35" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V35" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="W35" s="22" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K36" s="5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L36" s="79" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="M36" s="79" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="N36" s="80" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="S36" s="79" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="T36" s="79" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="U36" s="80" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="V36" s="79" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="W36" s="80" t="n">
+        <v>0.45</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="B37" s="53" t="s">
+        <v>170</v>
+      </c>
+      <c r="B37" s="18" t="s">
         <v>102</v>
+      </c>
+      <c r="C37" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D37" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="E37" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="F37" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="G37" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="H37" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="I37" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="O37" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="P37" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q37" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="R37" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="S37" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="T37" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="U37" s="24" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12899,6 +15216,48 @@
       <c r="B38" s="19" t="n">
         <v>0.5</v>
       </c>
+      <c r="C38" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D38" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E38" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F38" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G38" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H38" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I38" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O38" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="P38" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q38" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R38" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S38" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T38" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U38" s="22" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
@@ -12907,6 +15266,22 @@
       <c r="B39" s="19" t="n">
         <v>1</v>
       </c>
+      <c r="C39" s="60"/>
+      <c r="D39" s="60"/>
+      <c r="E39" s="60"/>
+      <c r="F39" s="60"/>
+      <c r="G39" s="60"/>
+      <c r="H39" s="60"/>
+      <c r="I39" s="60"/>
+      <c r="O39" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="P39" s="60"/>
+      <c r="Q39" s="60"/>
+      <c r="R39" s="60"/>
+      <c r="S39" s="60"/>
+      <c r="T39" s="60"/>
+      <c r="U39" s="60"/>
     </row>
     <row r="40" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
@@ -12915,6 +15290,22 @@
       <c r="B40" s="19" t="n">
         <v>0.5</v>
       </c>
+      <c r="C40" s="60"/>
+      <c r="D40" s="60"/>
+      <c r="E40" s="60"/>
+      <c r="F40" s="60"/>
+      <c r="G40" s="60"/>
+      <c r="H40" s="60"/>
+      <c r="I40" s="60"/>
+      <c r="O40" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="P40" s="60"/>
+      <c r="Q40" s="60"/>
+      <c r="R40" s="60"/>
+      <c r="S40" s="60"/>
+      <c r="T40" s="60"/>
+      <c r="U40" s="60"/>
     </row>
     <row r="41" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
@@ -12923,6 +15314,22 @@
       <c r="B41" s="19" t="n">
         <v>1.5</v>
       </c>
+      <c r="C41" s="60"/>
+      <c r="D41" s="60"/>
+      <c r="E41" s="60"/>
+      <c r="F41" s="60"/>
+      <c r="G41" s="60"/>
+      <c r="H41" s="60"/>
+      <c r="I41" s="60"/>
+      <c r="O41" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="P41" s="60"/>
+      <c r="Q41" s="60"/>
+      <c r="R41" s="60"/>
+      <c r="S41" s="60"/>
+      <c r="T41" s="60"/>
+      <c r="U41" s="60"/>
     </row>
     <row r="42" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
@@ -12931,6 +15338,48 @@
       <c r="B42" s="26" t="n">
         <v>0.01</v>
       </c>
+      <c r="C42" s="26" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D42" s="26" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E42" s="26" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="F42" s="26" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="G42" s="24" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H42" s="24" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="I42" s="24" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O42" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="P42" s="18" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="Q42" s="26" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="R42" s="26" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="S42" s="26" t="n">
+        <v>0.00225</v>
+      </c>
+      <c r="T42" s="26" t="n">
+        <v>0.00225</v>
+      </c>
+      <c r="U42" s="24" t="n">
+        <v>0.00225</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
@@ -12939,6 +15388,48 @@
       <c r="B43" s="19" t="n">
         <v>0.5</v>
       </c>
+      <c r="C43" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D43" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E43" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F43" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G43" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H43" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I43" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O43" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="P43" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q43" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R43" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S43" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T43" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U43" s="22" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
@@ -12947,6 +15438,48 @@
       <c r="B44" s="19" t="n">
         <v>0.7</v>
       </c>
+      <c r="C44" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O44" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="P44" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q44" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R44" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S44" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T44" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" s="22" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
@@ -12955,6 +15488,48 @@
       <c r="B45" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="C45" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="D45" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E45" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F45" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O45" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="P45" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="R45" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="S45" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="T45" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
@@ -12963,6 +15538,48 @@
       <c r="B46" s="19" t="n">
         <v>1.2</v>
       </c>
+      <c r="C46" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D46" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E46" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F46" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G46" s="20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H46" s="20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I46" s="20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O46" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="P46" s="18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q46" s="18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R46" s="18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S46" s="18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T46" s="18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="U46" s="22" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
@@ -12971,6 +15588,48 @@
       <c r="B47" s="19" t="n">
         <v>0.6</v>
       </c>
+      <c r="C47" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D47" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E47" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F47" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G47" s="20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H47" s="20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I47" s="20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O47" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="P47" s="18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q47" s="18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R47" s="18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="S47" s="18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T47" s="18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="U47" s="22" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
@@ -12979,19 +15638,92 @@
       <c r="B48" s="26" t="n">
         <v>5000</v>
       </c>
+      <c r="C48" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D48" s="26" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E48" s="26" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F48" s="26" t="n">
+        <v>60000</v>
+      </c>
+      <c r="G48" s="24" t="n">
+        <v>80000</v>
+      </c>
+      <c r="H48" s="24" t="n">
+        <v>100000</v>
+      </c>
+      <c r="I48" s="24" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O48" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P48" s="18" t="n">
+        <v>60000</v>
+      </c>
+      <c r="Q48" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="R48" s="26" t="n">
+        <v>30000</v>
+      </c>
+      <c r="S48" s="26" t="n">
+        <v>60000</v>
+      </c>
+      <c r="T48" s="26" t="n">
+        <v>30000</v>
+      </c>
+      <c r="U48" s="24" t="n">
+        <v>20000</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="19" t="s">
         <v>126</v>
       </c>
       <c r="B49" s="41"/>
+      <c r="C49" s="41"/>
+      <c r="D49" s="41"/>
+      <c r="E49" s="41"/>
+      <c r="F49" s="41"/>
+      <c r="G49" s="41"/>
+      <c r="H49" s="41"/>
+      <c r="I49" s="41"/>
+      <c r="O49" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="P49" s="60"/>
+      <c r="Q49" s="60"/>
+      <c r="R49" s="60"/>
+      <c r="S49" s="60"/>
+      <c r="T49" s="60"/>
+      <c r="U49" s="60"/>
     </row>
     <row r="50" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="29" t="s">
         <v>128</v>
       </c>
       <c r="B50" s="44"/>
-      <c r="H50" s="5"/>
+      <c r="C50" s="44"/>
+      <c r="D50" s="44"/>
+      <c r="E50" s="44"/>
+      <c r="F50" s="44"/>
+      <c r="G50" s="44"/>
+      <c r="H50" s="44"/>
+      <c r="I50" s="44"/>
+      <c r="O50" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="P50" s="30"/>
+      <c r="Q50" s="30"/>
+      <c r="R50" s="30"/>
+      <c r="S50" s="30"/>
+      <c r="T50" s="30"/>
+      <c r="U50" s="30"/>
     </row>
     <row r="51" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="19" t="s">
@@ -13000,6 +15732,48 @@
       <c r="B51" s="19" t="n">
         <v>1</v>
       </c>
+      <c r="C51" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E51" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="G51" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H51" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I51" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="O51" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="P51" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q51" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="R51" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="S51" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T51" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" s="22" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="19" t="s">
@@ -13008,11 +15782,92 @@
       <c r="B52" s="19" t="n">
         <v>1</v>
       </c>
+      <c r="C52" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E52" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="G52" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H52" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="I52" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="O52" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="P52" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q52" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="R52" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="S52" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T52" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" s="22" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="1" t="n">
         <v>0.3</v>
       </c>
+      <c r="C53" s="1" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D53" s="1" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E53" s="1" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F53" s="1" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H53" s="4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I53" s="4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P53" s="79" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Q53" s="79" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="R53" s="79" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="S53" s="79" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="T53" s="79" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="U53" s="80" t="n">
+        <v>0.45</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
@@ -13030,8 +15885,32 @@
       <c r="E55" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="F55" s="54" t="s">
+      <c r="F55" s="81" t="s">
         <v>106</v>
+      </c>
+      <c r="G55" s="81" t="s">
+        <v>107</v>
+      </c>
+      <c r="H55" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="I55" s="81" t="s">
+        <v>109</v>
+      </c>
+      <c r="J55" s="81" t="s">
+        <v>110</v>
+      </c>
+      <c r="K55" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="L55" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="M55" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="N55" s="45" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13050,7 +15929,31 @@
       <c r="E56" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="F56" s="55" t="n">
+      <c r="F56" s="82" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G56" s="82" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H56" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I56" s="82" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J56" s="82" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K56" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L56" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M56" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N56" s="46" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -13070,9 +15973,17 @@
       <c r="E57" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="F57" s="55" t="n">
-        <v>1</v>
-      </c>
+      <c r="F57" s="82" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="60"/>
+      <c r="H57" s="60"/>
+      <c r="I57" s="60"/>
+      <c r="J57" s="60"/>
+      <c r="K57" s="60"/>
+      <c r="L57" s="60"/>
+      <c r="M57" s="60"/>
+      <c r="N57" s="61"/>
     </row>
     <row r="58" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
@@ -13090,9 +16001,17 @@
       <c r="E58" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="F58" s="55" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="F58" s="82" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G58" s="60"/>
+      <c r="H58" s="60"/>
+      <c r="I58" s="60"/>
+      <c r="J58" s="60"/>
+      <c r="K58" s="60"/>
+      <c r="L58" s="60"/>
+      <c r="M58" s="60"/>
+      <c r="N58" s="61"/>
     </row>
     <row r="59" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
@@ -13110,9 +16029,17 @@
       <c r="E59" s="19" t="n">
         <v>1.5</v>
       </c>
-      <c r="F59" s="55" t="n">
+      <c r="F59" s="82" t="n">
         <v>1.5</v>
       </c>
+      <c r="G59" s="60"/>
+      <c r="H59" s="60"/>
+      <c r="I59" s="60"/>
+      <c r="J59" s="60"/>
+      <c r="K59" s="60"/>
+      <c r="L59" s="60"/>
+      <c r="M59" s="60"/>
+      <c r="N59" s="61"/>
     </row>
     <row r="60" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
@@ -13130,8 +16057,32 @@
       <c r="E60" s="26" t="n">
         <v>0.003</v>
       </c>
-      <c r="F60" s="54" t="n">
+      <c r="F60" s="83" t="n">
         <v>0.003</v>
+      </c>
+      <c r="G60" s="83" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H60" s="24" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="I60" s="83" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="J60" s="83" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="K60" s="24" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="L60" s="24" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="M60" s="24" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N60" s="45" t="n">
+        <v>0.0035</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13150,7 +16101,31 @@
       <c r="E61" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="F61" s="55" t="n">
+      <c r="F61" s="82" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G61" s="82" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H61" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I61" s="82" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J61" s="82" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K61" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L61" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M61" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N61" s="46" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -13170,8 +16145,32 @@
       <c r="E62" s="19" t="n">
         <v>0.7</v>
       </c>
-      <c r="F62" s="55" t="n">
+      <c r="F62" s="82" t="n">
         <v>0.7</v>
+      </c>
+      <c r="G62" s="82" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I62" s="82" t="n">
+        <v>1</v>
+      </c>
+      <c r="J62" s="82" t="n">
+        <v>1</v>
+      </c>
+      <c r="K62" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L62" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M62" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N62" s="46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13190,8 +16189,32 @@
       <c r="E63" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="F63" s="54" t="n">
-        <v>1</v>
+      <c r="F63" s="83" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="83" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I63" s="83" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" s="83" t="n">
+        <v>3</v>
+      </c>
+      <c r="K63" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="L63" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="M63" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="N63" s="45" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13210,7 +16233,31 @@
       <c r="E64" s="19" t="n">
         <v>1.2</v>
       </c>
-      <c r="F64" s="55" t="n">
+      <c r="F64" s="82" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G64" s="82" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H64" s="20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I64" s="82" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J64" s="82" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K64" s="20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L64" s="20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M64" s="20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N64" s="46" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -13230,7 +16277,31 @@
       <c r="E65" s="19" t="n">
         <v>0.6</v>
       </c>
-      <c r="F65" s="55" t="n">
+      <c r="F65" s="82" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G65" s="82" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H65" s="20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I65" s="82" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J65" s="82" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K65" s="20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L65" s="20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M65" s="20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N65" s="46" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -13250,8 +16321,32 @@
       <c r="E66" s="26" t="n">
         <v>50000</v>
       </c>
-      <c r="F66" s="54" t="n">
+      <c r="F66" s="83" t="n">
         <v>50000</v>
+      </c>
+      <c r="G66" s="83" t="n">
+        <v>50000</v>
+      </c>
+      <c r="H66" s="24" t="n">
+        <v>50000</v>
+      </c>
+      <c r="I66" s="83" t="n">
+        <v>50000</v>
+      </c>
+      <c r="J66" s="83" t="n">
+        <v>60000</v>
+      </c>
+      <c r="K66" s="24" t="n">
+        <v>60000</v>
+      </c>
+      <c r="L66" s="24" t="n">
+        <v>60000</v>
+      </c>
+      <c r="M66" s="24" t="n">
+        <v>60000</v>
+      </c>
+      <c r="N66" s="45" t="n">
+        <v>60000</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13262,7 +16357,15 @@
       <c r="C67" s="41"/>
       <c r="D67" s="41"/>
       <c r="E67" s="41"/>
-      <c r="F67" s="56"/>
+      <c r="F67" s="28"/>
+      <c r="G67" s="28"/>
+      <c r="H67" s="28"/>
+      <c r="I67" s="28"/>
+      <c r="J67" s="28"/>
+      <c r="K67" s="28"/>
+      <c r="L67" s="28"/>
+      <c r="M67" s="60"/>
+      <c r="N67" s="61"/>
     </row>
     <row r="68" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="29" t="s">
@@ -13272,7 +16375,15 @@
       <c r="C68" s="44"/>
       <c r="D68" s="44"/>
       <c r="E68" s="44"/>
-      <c r="F68" s="54"/>
+      <c r="F68" s="30"/>
+      <c r="G68" s="30"/>
+      <c r="H68" s="30"/>
+      <c r="I68" s="30"/>
+      <c r="J68" s="30"/>
+      <c r="K68" s="30"/>
+      <c r="L68" s="30"/>
+      <c r="M68" s="30"/>
+      <c r="N68" s="64"/>
     </row>
     <row r="69" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="19" t="s">
@@ -13290,7 +16401,31 @@
       <c r="E69" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="F69" s="54" t="n">
+      <c r="F69" s="83" t="n">
+        <v>2</v>
+      </c>
+      <c r="G69" s="83" t="n">
+        <v>2</v>
+      </c>
+      <c r="H69" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I69" s="83" t="n">
+        <v>2</v>
+      </c>
+      <c r="J69" s="83" t="n">
+        <v>2</v>
+      </c>
+      <c r="K69" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="L69" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="M69" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="N69" s="45" t="n">
         <v>2</v>
       </c>
     </row>
@@ -13310,7 +16445,31 @@
       <c r="E70" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="F70" s="54" t="n">
+      <c r="F70" s="83" t="n">
+        <v>3</v>
+      </c>
+      <c r="G70" s="83" t="n">
+        <v>3</v>
+      </c>
+      <c r="H70" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="I70" s="83" t="n">
+        <v>3</v>
+      </c>
+      <c r="J70" s="83" t="n">
+        <v>3</v>
+      </c>
+      <c r="K70" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="L70" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="M70" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="N70" s="45" t="n">
         <v>3</v>
       </c>
     </row>
@@ -13327,13 +16486,37 @@
       <c r="E71" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="F71" s="57" t="n">
-        <v>0.5</v>
+      <c r="F71" s="84" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G71" s="84" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H71" s="6" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I71" s="84" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J71" s="84" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K71" s="6" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L71" s="6" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="M71" s="6" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="N71" s="78" t="n">
+        <v>0.45</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="50" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13467,30 +16650,36 @@
     </row>
     <row r="92" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="50" t="s">
-        <v>154</v>
-      </c>
-      <c r="F92" s="0" t="s">
-        <v>155</v>
+        <v>172</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>173</v>
       </c>
       <c r="P92" s="1" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="Q92" s="1" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="R92" s="1" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="S92" s="1" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="T92" s="1" t="s">
-        <v>158</v>
+        <v>176</v>
+      </c>
+      <c r="U92" s="85" t="s">
+        <v>177</v>
+      </c>
+      <c r="V92" s="85" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B93" s="18" t="s">
         <v>102</v>
@@ -13504,7 +16693,7 @@
       <c r="E93" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="F93" s="58" t="s">
+      <c r="F93" s="86" t="s">
         <v>106</v>
       </c>
       <c r="G93" s="18" t="s">
@@ -13534,20 +16723,26 @@
       <c r="O93" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="P93" s="59" t="s">
+      <c r="P93" s="87" t="s">
         <v>116</v>
       </c>
-      <c r="Q93" s="53" t="s">
+      <c r="Q93" s="88" t="s">
         <v>117</v>
       </c>
-      <c r="R93" s="53" t="s">
+      <c r="R93" s="88" t="s">
         <v>118</v>
       </c>
-      <c r="S93" s="53" t="s">
-        <v>159</v>
-      </c>
-      <c r="T93" s="53" t="s">
-        <v>160</v>
+      <c r="S93" s="88" t="s">
+        <v>150</v>
+      </c>
+      <c r="T93" s="88" t="s">
+        <v>151</v>
+      </c>
+      <c r="U93" s="88" t="s">
+        <v>152</v>
+      </c>
+      <c r="V93" s="88" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13566,7 +16761,7 @@
       <c r="E94" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="F94" s="60" t="n">
+      <c r="F94" s="89" t="n">
         <v>0.5</v>
       </c>
       <c r="G94" s="19" t="n">
@@ -13596,7 +16791,7 @@
       <c r="O94" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="P94" s="60" t="n">
+      <c r="P94" s="89" t="n">
         <v>0.5</v>
       </c>
       <c r="Q94" s="19" t="n">
@@ -13609,6 +16804,12 @@
         <v>0.5</v>
       </c>
       <c r="T94" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U94" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V94" s="19" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -13628,7 +16829,7 @@
       <c r="E95" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="F95" s="60" t="n">
+      <c r="F95" s="89" t="n">
         <v>1</v>
       </c>
       <c r="G95" s="19" t="n">
@@ -13658,7 +16859,7 @@
       <c r="O95" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="P95" s="60" t="n">
+      <c r="P95" s="89" t="n">
         <v>1</v>
       </c>
       <c r="Q95" s="19" t="n">
@@ -13671,6 +16872,12 @@
         <v>1</v>
       </c>
       <c r="T95" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U95" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="V95" s="19" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13690,7 +16897,7 @@
       <c r="E96" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="F96" s="60" t="n">
+      <c r="F96" s="89" t="n">
         <v>0.5</v>
       </c>
       <c r="G96" s="19" t="n">
@@ -13720,7 +16927,7 @@
       <c r="O96" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="P96" s="60" t="n">
+      <c r="P96" s="89" t="n">
         <v>0.5</v>
       </c>
       <c r="Q96" s="19" t="n">
@@ -13733,6 +16940,12 @@
         <v>0.5</v>
       </c>
       <c r="T96" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U96" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V96" s="19" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -13752,7 +16965,7 @@
       <c r="E97" s="19" t="n">
         <v>1.5</v>
       </c>
-      <c r="F97" s="60" t="n">
+      <c r="F97" s="89" t="n">
         <v>1.5</v>
       </c>
       <c r="G97" s="19" t="n">
@@ -13782,7 +16995,7 @@
       <c r="O97" s="19" t="n">
         <v>1.5</v>
       </c>
-      <c r="P97" s="60" t="n">
+      <c r="P97" s="89" t="n">
         <v>1.5</v>
       </c>
       <c r="Q97" s="19" t="n">
@@ -13795,6 +17008,12 @@
         <v>1.5</v>
       </c>
       <c r="T97" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U97" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V97" s="19" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -13859,6 +17078,12 @@
       <c r="T98" s="26" t="n">
         <v>0.002</v>
       </c>
+      <c r="U98" s="26" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="V98" s="26" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="99" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2" t="s">
@@ -13876,7 +17101,7 @@
       <c r="E99" s="19" t="n">
         <v>0.4</v>
       </c>
-      <c r="F99" s="60" t="n">
+      <c r="F99" s="89" t="n">
         <v>0.4</v>
       </c>
       <c r="G99" s="19" t="n">
@@ -13906,7 +17131,7 @@
       <c r="O99" s="19" t="n">
         <v>0.4</v>
       </c>
-      <c r="P99" s="60" t="n">
+      <c r="P99" s="89" t="n">
         <v>0.4</v>
       </c>
       <c r="Q99" s="19" t="n">
@@ -13919,6 +17144,12 @@
         <v>0.4</v>
       </c>
       <c r="T99" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U99" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="V99" s="19" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -13938,7 +17169,7 @@
       <c r="E100" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="F100" s="60" t="n">
+      <c r="F100" s="89" t="n">
         <v>1</v>
       </c>
       <c r="G100" s="19" t="n">
@@ -13968,7 +17199,7 @@
       <c r="O100" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="P100" s="60" t="n">
+      <c r="P100" s="89" t="n">
         <v>1</v>
       </c>
       <c r="Q100" s="19" t="n">
@@ -13981,6 +17212,12 @@
         <v>1</v>
       </c>
       <c r="T100" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U100" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="V100" s="19" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14045,6 +17282,12 @@
       <c r="T101" s="26" t="n">
         <v>8</v>
       </c>
+      <c r="U101" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="V101" s="26" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="102" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2" t="s">
@@ -14062,7 +17305,7 @@
       <c r="E102" s="19" t="n">
         <v>1.2</v>
       </c>
-      <c r="F102" s="60" t="n">
+      <c r="F102" s="89" t="n">
         <v>1.2</v>
       </c>
       <c r="G102" s="19" t="n">
@@ -14092,7 +17335,7 @@
       <c r="O102" s="19" t="n">
         <v>1.2</v>
       </c>
-      <c r="P102" s="60" t="n">
+      <c r="P102" s="89" t="n">
         <v>1.2</v>
       </c>
       <c r="Q102" s="19" t="n">
@@ -14105,6 +17348,12 @@
         <v>1.2</v>
       </c>
       <c r="T102" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="U102" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V102" s="19" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -14124,7 +17373,7 @@
       <c r="E103" s="19" t="n">
         <v>0.6</v>
       </c>
-      <c r="F103" s="60" t="n">
+      <c r="F103" s="89" t="n">
         <v>0.6</v>
       </c>
       <c r="G103" s="19" t="n">
@@ -14154,7 +17403,7 @@
       <c r="O103" s="19" t="n">
         <v>0.6</v>
       </c>
-      <c r="P103" s="60" t="n">
+      <c r="P103" s="89" t="n">
         <v>0.6</v>
       </c>
       <c r="Q103" s="19" t="n">
@@ -14167,6 +17416,12 @@
         <v>0.6</v>
       </c>
       <c r="T103" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="U103" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="V103" s="19" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -14229,6 +17484,12 @@
         <v>12000</v>
       </c>
       <c r="T104" s="26" t="n">
+        <v>12000</v>
+      </c>
+      <c r="U104" s="26" t="n">
+        <v>12000</v>
+      </c>
+      <c r="V104" s="26" t="n">
         <v>12000</v>
       </c>
     </row>
@@ -14255,6 +17516,8 @@
       <c r="R105" s="41"/>
       <c r="S105" s="41"/>
       <c r="T105" s="41"/>
+      <c r="U105" s="28"/>
+      <c r="V105" s="28"/>
     </row>
     <row r="106" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="29" t="s">
@@ -14279,6 +17542,8 @@
       <c r="R106" s="44"/>
       <c r="S106" s="44"/>
       <c r="T106" s="44"/>
+      <c r="U106" s="30"/>
+      <c r="V106" s="30"/>
     </row>
     <row r="107" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="19" t="s">
@@ -14341,6 +17606,12 @@
       <c r="T107" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="U107" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="V107" s="26" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="108" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="19" t="s">
@@ -14403,6 +17674,12 @@
       <c r="T108" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="U108" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="V108" s="26" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="109" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B109" s="5" t="n">
@@ -14462,93 +17739,100 @@
       <c r="T109" s="5" t="n">
         <v>0.5</v>
       </c>
+      <c r="U109" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V109" s="5" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="110" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B110" s="1" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="G110" s="5" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="H110" s="5" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="I110" s="5" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="J110" s="5" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="K110" s="5" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="L110" s="5" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="M110" s="1" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="N110" s="1" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="O110" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="P110" s="52" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q110" s="52" t="s">
-        <v>165</v>
-      </c>
-      <c r="R110" s="0" t="s">
-        <v>166</v>
-      </c>
-      <c r="S110" s="0" t="s">
-        <v>166</v>
-      </c>
-      <c r="T110" s="0" t="s">
-        <v>166</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="P110" s="53" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q110" s="53" t="s">
+        <v>182</v>
+      </c>
+      <c r="R110" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="S110" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="T110" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="U110" s="53"/>
     </row>
     <row r="112" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="P112" s="1" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P113" s="59" t="s">
-        <v>167</v>
+      <c r="P113" s="87" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P114" s="60" t="n">
+      <c r="P114" s="89" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P115" s="60" t="n">
+      <c r="P115" s="89" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P116" s="60" t="n">
+      <c r="P116" s="89" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P117" s="60" t="n">
+      <c r="P117" s="89" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -14558,12 +17842,12 @@
       </c>
     </row>
     <row r="119" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P119" s="60" t="n">
+      <c r="P119" s="89" t="n">
         <v>0.4</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P120" s="60" t="n">
+      <c r="P120" s="89" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14573,12 +17857,12 @@
       </c>
     </row>
     <row r="122" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P122" s="60" t="n">
+      <c r="P122" s="89" t="n">
         <v>1.2</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P123" s="60" t="n">
+      <c r="P123" s="89" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -14604,15 +17888,323 @@
       </c>
     </row>
     <row r="129" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="P129" s="5" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P130" s="52" t="s">
-        <v>164</v>
-      </c>
-    </row>
+      <c r="A130" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B130" s="90" t="s">
+        <v>102</v>
+      </c>
+      <c r="C130" s="90" t="s">
+        <v>103</v>
+      </c>
+      <c r="D130" s="86" t="s">
+        <v>104</v>
+      </c>
+      <c r="E130" s="90" t="s">
+        <v>105</v>
+      </c>
+      <c r="F130" s="91" t="s">
+        <v>106</v>
+      </c>
+      <c r="P130" s="53" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B131" s="92" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C131" s="92" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D131" s="89" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E131" s="92" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F131" s="92" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B132" s="89"/>
+      <c r="C132" s="89"/>
+      <c r="D132" s="89"/>
+      <c r="E132" s="89"/>
+      <c r="F132" s="89"/>
+    </row>
+    <row r="133" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B133" s="89"/>
+      <c r="C133" s="89"/>
+      <c r="D133" s="89"/>
+      <c r="E133" s="89"/>
+      <c r="F133" s="89"/>
+    </row>
+    <row r="134" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B134" s="89"/>
+      <c r="C134" s="89"/>
+      <c r="D134" s="89"/>
+      <c r="E134" s="89"/>
+      <c r="F134" s="89"/>
+    </row>
+    <row r="135" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B135" s="91" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="C135" s="91" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="D135" s="44" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="E135" s="91" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="F135" s="91" t="n">
+        <v>0.0005</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B136" s="92" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C136" s="92" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D136" s="89" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E136" s="92" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F136" s="92" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B137" s="91" t="n">
+        <v>1</v>
+      </c>
+      <c r="C137" s="91" t="n">
+        <v>1</v>
+      </c>
+      <c r="D137" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E137" s="91" t="n">
+        <v>1</v>
+      </c>
+      <c r="F137" s="91" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B138" s="91" t="n">
+        <v>8</v>
+      </c>
+      <c r="C138" s="91" t="n">
+        <v>8</v>
+      </c>
+      <c r="D138" s="44" t="n">
+        <v>8</v>
+      </c>
+      <c r="E138" s="91" t="n">
+        <v>8</v>
+      </c>
+      <c r="F138" s="91" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B139" s="92" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C139" s="92" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D139" s="89" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E139" s="92" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F139" s="92" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B140" s="92" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C140" s="92" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D140" s="89" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E140" s="92" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F140" s="92" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B141" s="91" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C141" s="91" t="n">
+        <v>12000</v>
+      </c>
+      <c r="D141" s="44" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E141" s="91" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F141" s="91" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="B142" s="89"/>
+      <c r="C142" s="89"/>
+      <c r="D142" s="89"/>
+      <c r="E142" s="89"/>
+      <c r="F142" s="89"/>
+    </row>
+    <row r="143" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="B143" s="44"/>
+      <c r="C143" s="44"/>
+      <c r="D143" s="44"/>
+      <c r="E143" s="44"/>
+      <c r="F143" s="44"/>
+    </row>
+    <row r="144" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B144" s="91" t="n">
+        <v>2</v>
+      </c>
+      <c r="C144" s="91" t="n">
+        <v>2</v>
+      </c>
+      <c r="D144" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="E144" s="91" t="n">
+        <v>2</v>
+      </c>
+      <c r="F144" s="91" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B145" s="91" t="n">
+        <v>3</v>
+      </c>
+      <c r="C145" s="91" t="n">
+        <v>3</v>
+      </c>
+      <c r="D145" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="E145" s="91" t="n">
+        <v>3</v>
+      </c>
+      <c r="F145" s="91" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B146" s="93" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C146" s="93" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D146" s="94" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E146" s="93" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F146" s="93" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B147" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C147" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D147" s="95" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E147" s="0" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F147" s="0" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -14623,4 +18215,152 @@
   </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B1" s="90" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" s="92" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B3" s="60"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" s="60"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B5" s="60"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" s="91" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B7" s="92" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B8" s="91" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B9" s="91" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B10" s="92" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B11" s="92" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B12" s="91" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="B13" s="41"/>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="B14" s="44"/>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B15" s="91" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B16" s="91" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/parameters script.xlsx
+++ b/parameters script.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="952" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="187">
   <si>
     <t xml:space="preserve">6h 3</t>
   </si>
@@ -615,6 +615,12 @@
   </si>
   <si>
     <t xml:space="preserve">SPOTIFLOW FINAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OTSU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISODATA</t>
   </si>
 </sst>
 </file>
@@ -926,7 +932,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="93">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1287,18 +1293,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1307,7 +1301,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="12" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="12" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1394,9 +1388,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>466920</xdr:colOff>
+      <xdr:colOff>466560</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>24120</xdr:rowOff>
+      <xdr:rowOff>23760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1410,7 +1404,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6183720" y="130320"/>
-          <a:ext cx="7987680" cy="259560"/>
+          <a:ext cx="7987320" cy="259200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1437,9 +1431,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>221040</xdr:colOff>
+      <xdr:colOff>220680</xdr:colOff>
       <xdr:row>88</xdr:row>
-      <xdr:rowOff>65520</xdr:rowOff>
+      <xdr:rowOff>65160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1453,7 +1447,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="10345680" y="14112360"/>
-          <a:ext cx="10146600" cy="2046600"/>
+          <a:ext cx="10146240" cy="2046240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1475,9 +1469,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>885960</xdr:colOff>
+      <xdr:colOff>885600</xdr:colOff>
       <xdr:row>126</xdr:row>
-      <xdr:rowOff>101520</xdr:rowOff>
+      <xdr:rowOff>101160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1491,7 +1485,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6275880" y="21031200"/>
-          <a:ext cx="10183320" cy="2113200"/>
+          <a:ext cx="10182960" cy="2112840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -17899,20 +17893,26 @@
       <c r="A130" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B130" s="90" t="s">
+      <c r="B130" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="C130" s="90" t="s">
+      <c r="C130" s="18" t="s">
         <v>103</v>
       </c>
       <c r="D130" s="86" t="s">
         <v>104</v>
       </c>
-      <c r="E130" s="90" t="s">
+      <c r="E130" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="F130" s="91" t="s">
+      <c r="F130" s="18" t="s">
         <v>106</v>
+      </c>
+      <c r="G130" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="H130" s="26" t="s">
+        <v>108</v>
       </c>
       <c r="P130" s="53" t="s">
         <v>181</v>
@@ -17922,19 +17922,25 @@
       <c r="A131" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B131" s="92" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C131" s="92" t="n">
+      <c r="B131" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C131" s="19" t="n">
         <v>0.5</v>
       </c>
       <c r="D131" s="89" t="n">
         <v>0.5</v>
       </c>
-      <c r="E131" s="92" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F131" s="92" t="n">
+      <c r="E131" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F131" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G131" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H131" s="19" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -17947,6 +17953,8 @@
       <c r="D132" s="89"/>
       <c r="E132" s="89"/>
       <c r="F132" s="89"/>
+      <c r="G132" s="89"/>
+      <c r="H132" s="89"/>
     </row>
     <row r="133" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="2" t="s">
@@ -17957,6 +17965,8 @@
       <c r="D133" s="89"/>
       <c r="E133" s="89"/>
       <c r="F133" s="89"/>
+      <c r="G133" s="89"/>
+      <c r="H133" s="89"/>
     </row>
     <row r="134" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="2" t="s">
@@ -17967,44 +17977,58 @@
       <c r="D134" s="89"/>
       <c r="E134" s="89"/>
       <c r="F134" s="89"/>
+      <c r="G134" s="89"/>
+      <c r="H134" s="89"/>
     </row>
     <row r="135" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B135" s="91" t="n">
+      <c r="B135" s="26" t="n">
         <v>0.0025</v>
       </c>
-      <c r="C135" s="91" t="n">
+      <c r="C135" s="26" t="n">
         <v>0.002</v>
       </c>
       <c r="D135" s="44" t="n">
         <v>0.001</v>
       </c>
-      <c r="E135" s="91" t="n">
+      <c r="E135" s="26" t="n">
         <v>0.001</v>
       </c>
-      <c r="F135" s="91" t="n">
+      <c r="F135" s="26" t="n">
         <v>0.0005</v>
+      </c>
+      <c r="G135" s="26" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H135" s="26" t="n">
+        <v>0.001</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B136" s="92" t="n">
+      <c r="B136" s="19" t="n">
         <v>0.4</v>
       </c>
-      <c r="C136" s="92" t="n">
+      <c r="C136" s="19" t="n">
         <v>0.4</v>
       </c>
       <c r="D136" s="89" t="n">
         <v>0.4</v>
       </c>
-      <c r="E136" s="92" t="n">
+      <c r="E136" s="19" t="n">
         <v>0.4</v>
       </c>
-      <c r="F136" s="92" t="n">
+      <c r="F136" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G136" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H136" s="19" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -18012,19 +18036,25 @@
       <c r="A137" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B137" s="91" t="n">
-        <v>1</v>
-      </c>
-      <c r="C137" s="91" t="n">
+      <c r="B137" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C137" s="26" t="n">
         <v>1</v>
       </c>
       <c r="D137" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="E137" s="91" t="n">
-        <v>1</v>
-      </c>
-      <c r="F137" s="91" t="n">
+      <c r="E137" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F137" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G137" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H137" s="26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -18032,19 +18062,25 @@
       <c r="A138" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B138" s="91" t="n">
+      <c r="B138" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="C138" s="91" t="n">
+      <c r="C138" s="26" t="n">
         <v>8</v>
       </c>
       <c r="D138" s="44" t="n">
         <v>8</v>
       </c>
-      <c r="E138" s="91" t="n">
+      <c r="E138" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="F138" s="91" t="n">
+      <c r="F138" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="G138" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="H138" s="26" t="n">
         <v>8</v>
       </c>
     </row>
@@ -18052,19 +18088,25 @@
       <c r="A139" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B139" s="92" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C139" s="92" t="n">
+      <c r="B139" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C139" s="19" t="n">
         <v>1.2</v>
       </c>
       <c r="D139" s="89" t="n">
         <v>1.2</v>
       </c>
-      <c r="E139" s="92" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F139" s="92" t="n">
+      <c r="E139" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F139" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G139" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H139" s="19" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -18072,19 +18114,25 @@
       <c r="A140" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B140" s="92" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C140" s="92" t="n">
+      <c r="B140" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C140" s="19" t="n">
         <v>0.6</v>
       </c>
       <c r="D140" s="89" t="n">
         <v>0.6</v>
       </c>
-      <c r="E140" s="92" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F140" s="92" t="n">
+      <c r="E140" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F140" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G140" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H140" s="19" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -18092,19 +18140,25 @@
       <c r="A141" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B141" s="91" t="n">
+      <c r="B141" s="26" t="n">
         <v>12000</v>
       </c>
-      <c r="C141" s="91" t="n">
+      <c r="C141" s="26" t="n">
         <v>12000</v>
       </c>
       <c r="D141" s="44" t="n">
         <v>12000</v>
       </c>
-      <c r="E141" s="91" t="n">
+      <c r="E141" s="26" t="n">
         <v>12000</v>
       </c>
-      <c r="F141" s="91" t="n">
+      <c r="F141" s="26" t="n">
+        <v>12000</v>
+      </c>
+      <c r="G141" s="26" t="n">
+        <v>12000</v>
+      </c>
+      <c r="H141" s="26" t="n">
         <v>12000</v>
       </c>
     </row>
@@ -18117,6 +18171,8 @@
       <c r="D142" s="89"/>
       <c r="E142" s="89"/>
       <c r="F142" s="89"/>
+      <c r="G142" s="89"/>
+      <c r="H142" s="89"/>
     </row>
     <row r="143" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="29" t="s">
@@ -18127,24 +18183,32 @@
       <c r="D143" s="44"/>
       <c r="E143" s="44"/>
       <c r="F143" s="44"/>
+      <c r="G143" s="44"/>
+      <c r="H143" s="44"/>
     </row>
     <row r="144" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="B144" s="91" t="n">
-        <v>2</v>
-      </c>
-      <c r="C144" s="91" t="n">
+      <c r="B144" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="C144" s="26" t="n">
         <v>2</v>
       </c>
       <c r="D144" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="E144" s="91" t="n">
-        <v>2</v>
-      </c>
-      <c r="F144" s="91" t="n">
+      <c r="E144" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F144" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G144" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H144" s="26" t="n">
         <v>2</v>
       </c>
     </row>
@@ -18152,54 +18216,95 @@
       <c r="A145" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="B145" s="91" t="n">
-        <v>3</v>
-      </c>
-      <c r="C145" s="91" t="n">
+      <c r="B145" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C145" s="26" t="n">
         <v>3</v>
       </c>
       <c r="D145" s="44" t="n">
         <v>3</v>
       </c>
-      <c r="E145" s="91" t="n">
-        <v>3</v>
-      </c>
-      <c r="F145" s="91" t="n">
+      <c r="E145" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F145" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="G145" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="H145" s="26" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B146" s="93" t="n">
+      <c r="B146" s="90" t="n">
         <v>0.25</v>
       </c>
-      <c r="C146" s="93" t="n">
+      <c r="C146" s="90" t="n">
         <v>0.25</v>
       </c>
-      <c r="D146" s="94" t="n">
+      <c r="D146" s="91" t="n">
         <v>0.25</v>
       </c>
-      <c r="E146" s="93" t="n">
+      <c r="E146" s="90" t="n">
         <v>0.25</v>
       </c>
-      <c r="F146" s="93" t="n">
+      <c r="F146" s="90" t="n">
         <v>0.25</v>
       </c>
+      <c r="G146" s="90" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H146" s="90" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="147" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B147" s="0" t="n">
+      <c r="B147" s="1" t="n">
         <v>0.3</v>
       </c>
-      <c r="C147" s="0" t="n">
+      <c r="C147" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="D147" s="95" t="n">
+      <c r="D147" s="92" t="n">
         <v>0.2</v>
       </c>
-      <c r="E147" s="0" t="n">
+      <c r="E147" s="1" t="n">
         <v>0.15</v>
       </c>
-      <c r="F147" s="0" t="n">
+      <c r="F147" s="1" t="n">
         <v>0.15</v>
+      </c>
+      <c r="G147" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H147" s="1" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B148" s="0" t="s">
+        <v>185</v>
+      </c>
+      <c r="C148" s="0" t="s">
+        <v>185</v>
+      </c>
+      <c r="D148" s="0" t="s">
+        <v>185</v>
+      </c>
+      <c r="E148" s="0" t="s">
+        <v>185</v>
+      </c>
+      <c r="F148" s="0" t="s">
+        <v>185</v>
+      </c>
+      <c r="G148" s="0" t="s">
+        <v>186</v>
+      </c>
+      <c r="H148" s="0" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -18225,14 +18330,14 @@
   <dimension ref="A1:B17"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B1" s="90" t="s">
+      <c r="B1" s="18" t="s">
         <v>102</v>
       </c>
     </row>
@@ -18240,7 +18345,7 @@
       <c r="A2" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B2" s="92" t="n">
+      <c r="B2" s="19" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -18266,7 +18371,7 @@
       <c r="A6" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B6" s="91" t="n">
+      <c r="B6" s="26" t="n">
         <v>0.002</v>
       </c>
     </row>
@@ -18274,7 +18379,7 @@
       <c r="A7" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B7" s="92" t="n">
+      <c r="B7" s="19" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -18282,7 +18387,7 @@
       <c r="A8" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B8" s="91" t="n">
+      <c r="B8" s="26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -18290,7 +18395,7 @@
       <c r="A9" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B9" s="91" t="n">
+      <c r="B9" s="26" t="n">
         <v>8</v>
       </c>
     </row>
@@ -18298,7 +18403,7 @@
       <c r="A10" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B10" s="92" t="n">
+      <c r="B10" s="19" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -18306,7 +18411,7 @@
       <c r="A11" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B11" s="92" t="n">
+      <c r="B11" s="19" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -18314,7 +18419,7 @@
       <c r="A12" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B12" s="91" t="n">
+      <c r="B12" s="26" t="n">
         <v>12000</v>
       </c>
     </row>
@@ -18334,7 +18439,7 @@
       <c r="A15" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="B15" s="91" t="n">
+      <c r="B15" s="26" t="n">
         <v>2</v>
       </c>
     </row>
@@ -18342,7 +18447,7 @@
       <c r="A16" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="B16" s="91" t="n">
+      <c r="B16" s="26" t="n">
         <v>3</v>
       </c>
     </row>

--- a/parameters script.xlsx
+++ b/parameters script.xlsx
@@ -18081,7 +18081,7 @@
         <v>8</v>
       </c>
       <c r="H138" s="26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/parameters script.xlsx
+++ b/parameters script.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="188">
   <si>
     <t xml:space="preserve">6h 3</t>
   </si>
@@ -621,6 +621,9 @@
   </si>
   <si>
     <t xml:space="preserve">ISODATA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OTSU SMOOTH</t>
   </si>
 </sst>
 </file>
@@ -18304,7 +18307,7 @@
         <v>186</v>
       </c>
       <c r="H148" s="0" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/parameters script.xlsx
+++ b/parameters script.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="190">
   <si>
     <t xml:space="preserve">6h 3</t>
   </si>
@@ -624,6 +624,12 @@
   </si>
   <si>
     <t xml:space="preserve">OTSU SMOOTH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIGMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">some thresholding</t>
   </si>
 </sst>
 </file>
@@ -17914,8 +17920,29 @@
       <c r="G130" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="H130" s="26" t="s">
+      <c r="H130" s="18" t="s">
         <v>108</v>
+      </c>
+      <c r="I130" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="J130" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="K130" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="L130" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="M130" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="N130" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="O130" s="22" t="s">
+        <v>115</v>
       </c>
       <c r="P130" s="53" t="s">
         <v>181</v>
@@ -17944,6 +17971,27 @@
         <v>0.5</v>
       </c>
       <c r="H131" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I131" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J131" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K131" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L131" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M131" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N131" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O131" s="20" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -17958,6 +18006,13 @@
       <c r="F132" s="89"/>
       <c r="G132" s="89"/>
       <c r="H132" s="89"/>
+      <c r="I132" s="89"/>
+      <c r="J132" s="89"/>
+      <c r="K132" s="89"/>
+      <c r="L132" s="89"/>
+      <c r="M132" s="89"/>
+      <c r="N132" s="89"/>
+      <c r="O132" s="89"/>
     </row>
     <row r="133" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="2" t="s">
@@ -17970,6 +18025,13 @@
       <c r="F133" s="89"/>
       <c r="G133" s="89"/>
       <c r="H133" s="89"/>
+      <c r="I133" s="89"/>
+      <c r="J133" s="89"/>
+      <c r="K133" s="89"/>
+      <c r="L133" s="89"/>
+      <c r="M133" s="89"/>
+      <c r="N133" s="89"/>
+      <c r="O133" s="89"/>
     </row>
     <row r="134" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="2" t="s">
@@ -17982,6 +18044,13 @@
       <c r="F134" s="89"/>
       <c r="G134" s="89"/>
       <c r="H134" s="89"/>
+      <c r="I134" s="89"/>
+      <c r="J134" s="89"/>
+      <c r="K134" s="89"/>
+      <c r="L134" s="89"/>
+      <c r="M134" s="89"/>
+      <c r="N134" s="89"/>
+      <c r="O134" s="89"/>
     </row>
     <row r="135" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="2" t="s">
@@ -18008,6 +18077,27 @@
       <c r="H135" s="26" t="n">
         <v>0.001</v>
       </c>
+      <c r="I135" s="26" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="J135" s="26" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="K135" s="26" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="L135" s="26" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="M135" s="26" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="N135" s="26" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="O135" s="24" t="n">
+        <v>0.0025</v>
+      </c>
     </row>
     <row r="136" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="2" t="s">
@@ -18034,6 +18124,27 @@
       <c r="H136" s="19" t="n">
         <v>0.4</v>
       </c>
+      <c r="I136" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J136" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K136" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L136" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M136" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N136" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O136" s="20" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="137" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="2" t="s">
@@ -18060,6 +18171,27 @@
       <c r="H137" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="I137" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J137" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K137" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L137" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M137" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N137" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="O137" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="138" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="2" t="s">
@@ -18086,6 +18218,27 @@
       <c r="H138" s="26" t="n">
         <v>10</v>
       </c>
+      <c r="I138" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="J138" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="K138" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="L138" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="M138" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="N138" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="O138" s="24" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="139" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="2" t="s">
@@ -18112,6 +18265,27 @@
       <c r="H139" s="19" t="n">
         <v>1.2</v>
       </c>
+      <c r="I139" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J139" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K139" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L139" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M139" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N139" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O139" s="20" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="140" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="2" t="s">
@@ -18138,6 +18312,27 @@
       <c r="H140" s="19" t="n">
         <v>0.6</v>
       </c>
+      <c r="I140" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J140" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K140" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L140" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M140" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N140" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O140" s="20" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="141" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="2" t="s">
@@ -18162,6 +18357,27 @@
         <v>12000</v>
       </c>
       <c r="H141" s="26" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I141" s="26" t="n">
+        <v>20000</v>
+      </c>
+      <c r="J141" s="26" t="n">
+        <v>15000</v>
+      </c>
+      <c r="K141" s="26" t="n">
+        <v>12000</v>
+      </c>
+      <c r="L141" s="26" t="n">
+        <v>12000</v>
+      </c>
+      <c r="M141" s="26" t="n">
+        <v>12000</v>
+      </c>
+      <c r="N141" s="26" t="n">
+        <v>12000</v>
+      </c>
+      <c r="O141" s="24" t="n">
         <v>12000</v>
       </c>
     </row>
@@ -18176,6 +18392,13 @@
       <c r="F142" s="89"/>
       <c r="G142" s="89"/>
       <c r="H142" s="89"/>
+      <c r="I142" s="89"/>
+      <c r="J142" s="89"/>
+      <c r="K142" s="89"/>
+      <c r="L142" s="89"/>
+      <c r="M142" s="89"/>
+      <c r="N142" s="89"/>
+      <c r="O142" s="89"/>
     </row>
     <row r="143" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="29" t="s">
@@ -18188,6 +18411,13 @@
       <c r="F143" s="44"/>
       <c r="G143" s="44"/>
       <c r="H143" s="44"/>
+      <c r="I143" s="44"/>
+      <c r="J143" s="44"/>
+      <c r="K143" s="44"/>
+      <c r="L143" s="44"/>
+      <c r="M143" s="44"/>
+      <c r="N143" s="44"/>
+      <c r="O143" s="44"/>
     </row>
     <row r="144" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="19" t="s">
@@ -18214,6 +18444,27 @@
       <c r="H144" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="I144" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="J144" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="K144" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="L144" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="M144" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="N144" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="O144" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="145" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="19" t="s">
@@ -18240,6 +18491,27 @@
       <c r="H145" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="I145" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="J145" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K145" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="L145" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M145" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="N145" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="O145" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="146" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B146" s="90" t="n">
@@ -18263,6 +18535,27 @@
       <c r="H146" s="90" t="n">
         <v>0.25</v>
       </c>
+      <c r="I146" s="90" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J146" s="90" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K146" s="90" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L146" s="90" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M146" s="90" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N146" s="90" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O146" s="90" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="147" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B147" s="1" t="n">
@@ -18286,6 +18579,27 @@
       <c r="H147" s="1" t="n">
         <v>0.2</v>
       </c>
+      <c r="I147" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J147" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K147" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L147" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M147" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N147" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O147" s="1" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="148" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B148" s="0" t="s">
@@ -18308,6 +18622,103 @@
       </c>
       <c r="H148" s="0" t="s">
         <v>187</v>
+      </c>
+      <c r="I148" s="0" t="s">
+        <v>187</v>
+      </c>
+      <c r="J148" s="0" t="s">
+        <v>187</v>
+      </c>
+      <c r="K148" s="0" t="s">
+        <v>187</v>
+      </c>
+      <c r="L148" s="0" t="s">
+        <v>187</v>
+      </c>
+      <c r="M148" s="0" t="s">
+        <v>187</v>
+      </c>
+      <c r="N148" s="0" t="s">
+        <v>187</v>
+      </c>
+      <c r="O148" s="0" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="H149" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I149" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J149" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K149" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L149" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M149" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="N149" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="O149" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B150" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C150" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D150" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E150" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F150" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G150" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H150" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I150" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J150" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K150" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="L150" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M150" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N150" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="O150" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/parameters script.xlsx
+++ b/parameters script.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
@@ -16,6 +16,7 @@
     <sheet name="22-2-2026" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="line 129" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="linea 132" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="PLASMA M-P" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1279" uniqueCount="204">
   <si>
     <t xml:space="preserve">6h 3</t>
   </si>
@@ -631,6 +632,48 @@
   <si>
     <t xml:space="preserve">some thresholding</t>
   </si>
+  <si>
+    <t xml:space="preserve">0.1-0.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2-0.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2-0.75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2-0.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2-0.65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.22-0.65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0-0.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0-0.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROBAR EN MY PC &gt;0.01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L3-6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12H-3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 may v2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 may V3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12H-4</t>
+  </si>
 </sst>
 </file>
 
@@ -941,7 +984,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="95">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1314,6 +1357,14 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1397,9 +1448,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>466560</xdr:colOff>
+      <xdr:colOff>464040</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>23760</xdr:rowOff>
+      <xdr:rowOff>21240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1413,7 +1464,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6183720" y="130320"/>
-          <a:ext cx="7987320" cy="259200"/>
+          <a:ext cx="7984800" cy="256680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1440,9 +1491,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>220680</xdr:colOff>
+      <xdr:colOff>218160</xdr:colOff>
       <xdr:row>88</xdr:row>
-      <xdr:rowOff>65160</xdr:rowOff>
+      <xdr:rowOff>62640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1456,7 +1507,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="10345680" y="14112360"/>
-          <a:ext cx="10146240" cy="2046240"/>
+          <a:ext cx="10143720" cy="2043720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1478,9 +1529,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>885600</xdr:colOff>
+      <xdr:colOff>883080</xdr:colOff>
       <xdr:row>126</xdr:row>
-      <xdr:rowOff>101160</xdr:rowOff>
+      <xdr:rowOff>98640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1494,7 +1545,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6275880" y="21031200"/>
-          <a:ext cx="10182960" cy="2112840"/>
+          <a:ext cx="10180440" cy="2110320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -17891,7 +17942,7 @@
       </c>
     </row>
     <row r="129" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="1" t="s">
+      <c r="A129" s="50" t="s">
         <v>184</v>
       </c>
       <c r="P129" s="5" t="n">
@@ -18602,46 +18653,46 @@
       </c>
     </row>
     <row r="148" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B148" s="0" t="s">
+      <c r="B148" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="C148" s="0" t="s">
+      <c r="C148" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="D148" s="0" t="s">
+      <c r="D148" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="E148" s="0" t="s">
+      <c r="E148" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="F148" s="0" t="s">
+      <c r="F148" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="G148" s="0" t="s">
+      <c r="G148" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="H148" s="0" t="s">
+      <c r="H148" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="I148" s="0" t="s">
+      <c r="I148" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="J148" s="0" t="s">
+      <c r="J148" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="K148" s="0" t="s">
+      <c r="K148" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="L148" s="0" t="s">
+      <c r="L148" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="M148" s="0" t="s">
+      <c r="M148" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="N148" s="0" t="s">
+      <c r="N148" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="O148" s="0" t="s">
+      <c r="O148" s="1" t="s">
         <v>187</v>
       </c>
     </row>
@@ -18649,10 +18700,10 @@
       <c r="A149" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="H149" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I149" s="0" t="n">
+      <c r="H149" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I149" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J149" s="1" t="n">
@@ -18678,49 +18729,634 @@
       <c r="A150" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B150" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C150" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D150" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E150" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="F150" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G150" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H150" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I150" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J150" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K150" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L150" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M150" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="N150" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="O150" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
+      <c r="B150" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C150" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D150" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E150" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F150" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G150" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H150" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I150" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J150" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K150" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L150" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M150" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N150" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O150" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B152" s="18" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B153" s="19" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B154" s="89"/>
+    </row>
+    <row r="155" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B155" s="89"/>
+    </row>
+    <row r="156" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B156" s="89"/>
+    </row>
+    <row r="157" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B157" s="26" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B158" s="19" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B159" s="26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B160" s="26" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B161" s="19" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B162" s="19" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B163" s="26" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="B164" s="89"/>
+    </row>
+    <row r="165" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="B165" s="44"/>
+    </row>
+    <row r="166" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B166" s="26" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B167" s="26" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B168" s="90" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B169" s="1" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B170" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B172" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B174" s="18" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B175" s="19" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B176" s="89"/>
+    </row>
+    <row r="177" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A177" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B177" s="89"/>
+    </row>
+    <row r="178" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A178" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B178" s="89"/>
+    </row>
+    <row r="179" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A179" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B179" s="26" t="n">
+        <v>0.006</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B180" s="19" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A181" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B181" s="26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A182" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B182" s="26" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A183" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B183" s="19" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="184" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A184" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B184" s="19" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="185" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A185" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B185" s="26" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A186" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="B186" s="89"/>
+    </row>
+    <row r="187" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A187" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="B187" s="44"/>
+    </row>
+    <row r="188" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A188" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B188" s="26" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B189" s="26" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="190" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B190" s="90" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B191" s="1" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B192" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A193" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B194" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A196" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B196" s="18" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B197" s="19" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B198" s="89"/>
+    </row>
+    <row r="199" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A199" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B199" s="89"/>
+    </row>
+    <row r="200" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A200" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B200" s="89"/>
+    </row>
+    <row r="201" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A201" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B201" s="26" t="n">
+        <v>0.00525</v>
+      </c>
+    </row>
+    <row r="202" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A202" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B202" s="19" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="203" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A203" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B203" s="26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A204" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B204" s="26" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="205" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A205" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B205" s="19" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="206" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A206" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B206" s="19" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="207" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A207" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B207" s="26" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="208" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A208" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="B208" s="89"/>
+    </row>
+    <row r="209" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A209" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="B209" s="44"/>
+    </row>
+    <row r="210" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A210" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B210" s="26" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="211" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A211" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B211" s="26" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B212" s="90" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="213" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B213" s="1" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="214" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B214" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="215" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A215" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="216" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A216" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B216" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A218" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B218" s="18" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="219" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A219" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B219" s="19" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="220" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A220" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B220" s="89"/>
+    </row>
+    <row r="221" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A221" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B221" s="89"/>
+    </row>
+    <row r="222" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A222" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B222" s="89"/>
+    </row>
+    <row r="223" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A223" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B223" s="26" t="n">
+        <v>0.0035</v>
+      </c>
+    </row>
+    <row r="224" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A224" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B224" s="19" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="225" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A225" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B225" s="26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A226" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B226" s="26" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="227" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A227" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B227" s="19" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="228" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A228" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B228" s="19" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="229" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A229" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B229" s="26" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="230" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A230" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="B230" s="89"/>
+    </row>
+    <row r="231" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A231" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="B231" s="44"/>
+    </row>
+    <row r="232" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A232" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B232" s="26" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="233" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A233" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B233" s="26" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="234" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B234" s="90" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="235" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B235" s="1" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="236" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B236" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="237" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A237" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="238" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A238" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B238" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -18741,7 +19377,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:U114"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20.53"/>
@@ -18754,6 +19390,39 @@
       <c r="B1" s="18" t="s">
         <v>102</v>
       </c>
+      <c r="C1" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="I1" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="J1" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="K1" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="L1" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="M1" s="22" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
@@ -18762,24 +19431,90 @@
       <c r="B2" s="19" t="n">
         <v>0.5</v>
       </c>
+      <c r="C2" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D2" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E2" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F2" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G2" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H2" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I2" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J2" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K2" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L2" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M2" s="20" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>120</v>
       </c>
       <c r="B3" s="60"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="60"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="60"/>
+      <c r="K3" s="60"/>
+      <c r="L3" s="60"/>
+      <c r="M3" s="60"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
         <v>82</v>
       </c>
       <c r="B4" s="60"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="60"/>
+      <c r="K4" s="60"/>
+      <c r="L4" s="60"/>
+      <c r="M4" s="60"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>121</v>
       </c>
       <c r="B5" s="60"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="60"/>
+      <c r="L5" s="60"/>
+      <c r="M5" s="60"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
@@ -18788,6 +19523,39 @@
       <c r="B6" s="26" t="n">
         <v>0.002</v>
       </c>
+      <c r="C6" s="26" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="D6" s="26" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F6" s="26" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="G6" s="26" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="H6" s="26" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I6" s="26" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="J6" s="26" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="K6" s="26" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="L6" s="26" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="M6" s="24" t="n">
+        <v>0.015</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
@@ -18796,6 +19564,39 @@
       <c r="B7" s="19" t="n">
         <v>0.4</v>
       </c>
+      <c r="C7" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E7" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F7" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G7" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H7" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I7" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J7" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K7" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L7" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M7" s="20" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
@@ -18804,6 +19605,39 @@
       <c r="B8" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="C8" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
@@ -18812,6 +19646,39 @@
       <c r="B9" s="26" t="n">
         <v>8</v>
       </c>
+      <c r="C9" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="G9" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="H9" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="I9" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="J9" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="K9" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="L9" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="M9" s="24" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
@@ -18820,6 +19687,39 @@
       <c r="B10" s="19" t="n">
         <v>1.2</v>
       </c>
+      <c r="C10" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D10" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E10" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H10" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I10" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J10" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K10" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L10" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M10" s="20" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
@@ -18828,6 +19728,39 @@
       <c r="B11" s="19" t="n">
         <v>0.6</v>
       </c>
+      <c r="C11" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D11" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E11" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F11" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H11" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I11" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J11" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K11" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L11" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M11" s="20" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
@@ -18836,18 +19769,73 @@
       <c r="B12" s="26" t="n">
         <v>12000</v>
       </c>
+      <c r="C12" s="26" t="n">
+        <v>12000</v>
+      </c>
+      <c r="D12" s="26" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E12" s="26" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F12" s="26" t="n">
+        <v>12000</v>
+      </c>
+      <c r="G12" s="26" t="n">
+        <v>12000</v>
+      </c>
+      <c r="H12" s="26" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I12" s="26" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J12" s="26" t="n">
+        <v>12000</v>
+      </c>
+      <c r="K12" s="26" t="n">
+        <v>12000</v>
+      </c>
+      <c r="L12" s="26" t="n">
+        <v>12000</v>
+      </c>
+      <c r="M12" s="24" t="n">
+        <v>12000</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="19" t="s">
         <v>126</v>
       </c>
       <c r="B13" s="41"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="41"/>
+      <c r="J13" s="41"/>
+      <c r="K13" s="41"/>
+      <c r="L13" s="41"/>
+      <c r="M13" s="41"/>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="29" t="s">
         <v>128</v>
       </c>
       <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="44"/>
+      <c r="J14" s="44"/>
+      <c r="K14" s="44"/>
+      <c r="L14" s="44"/>
+      <c r="M14" s="44"/>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
@@ -18856,6 +19844,39 @@
       <c r="B15" s="26" t="n">
         <v>2</v>
       </c>
+      <c r="C15" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" s="24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="19" t="s">
@@ -18864,6 +19885,39 @@
       <c r="B16" s="26" t="n">
         <v>3</v>
       </c>
+      <c r="C16" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="H16" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="L16" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M16" s="24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
@@ -18871,6 +19925,3040 @@
       </c>
       <c r="B17" s="5" t="n">
         <v>0.25</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M17" s="6" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H18" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="L18" s="93" t="s">
+        <v>190</v>
+      </c>
+      <c r="M18" s="94" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="F21" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="G21" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="H21" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="I21" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="J21" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="K21" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="L21" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="M21" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="N21" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="O21" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="P21" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q21" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="R21" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="S21" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="T21" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="U21" s="22" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B22" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C22" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D22" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E22" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F22" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G22" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H22" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I22" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J22" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K22" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L22" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M22" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N22" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O22" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P22" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q22" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R22" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S22" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T22" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U22" s="20" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B23" s="60"/>
+      <c r="C23" s="60"/>
+      <c r="D23" s="60"/>
+      <c r="E23" s="60"/>
+      <c r="F23" s="60"/>
+      <c r="G23" s="60"/>
+      <c r="H23" s="60"/>
+      <c r="I23" s="60"/>
+      <c r="J23" s="60"/>
+      <c r="K23" s="60"/>
+      <c r="L23" s="60"/>
+      <c r="M23" s="60"/>
+      <c r="N23" s="60"/>
+      <c r="O23" s="60"/>
+      <c r="P23" s="60"/>
+      <c r="Q23" s="60"/>
+      <c r="R23" s="60"/>
+      <c r="S23" s="60"/>
+      <c r="T23" s="60"/>
+      <c r="U23" s="60"/>
+    </row>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B24" s="60"/>
+      <c r="C24" s="60"/>
+      <c r="D24" s="60"/>
+      <c r="E24" s="60"/>
+      <c r="F24" s="60"/>
+      <c r="G24" s="60"/>
+      <c r="H24" s="60"/>
+      <c r="I24" s="60"/>
+      <c r="J24" s="60"/>
+      <c r="K24" s="60"/>
+      <c r="L24" s="60"/>
+      <c r="M24" s="60"/>
+      <c r="N24" s="60"/>
+      <c r="O24" s="60"/>
+      <c r="P24" s="60"/>
+      <c r="Q24" s="60"/>
+      <c r="R24" s="60"/>
+      <c r="S24" s="60"/>
+      <c r="T24" s="60"/>
+      <c r="U24" s="60"/>
+    </row>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B25" s="60"/>
+      <c r="C25" s="60"/>
+      <c r="D25" s="60"/>
+      <c r="E25" s="60"/>
+      <c r="F25" s="60"/>
+      <c r="G25" s="60"/>
+      <c r="H25" s="60"/>
+      <c r="I25" s="60"/>
+      <c r="J25" s="60"/>
+      <c r="K25" s="60"/>
+      <c r="L25" s="60"/>
+      <c r="M25" s="60"/>
+      <c r="N25" s="60"/>
+      <c r="O25" s="60"/>
+      <c r="P25" s="60"/>
+      <c r="Q25" s="60"/>
+      <c r="R25" s="60"/>
+      <c r="S25" s="60"/>
+      <c r="T25" s="60"/>
+      <c r="U25" s="60"/>
+    </row>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B26" s="26" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="C26" s="26" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="D26" s="26" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="E26" s="26" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F26" s="26" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G26" s="26" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="H26" s="26" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="I26" s="26" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J26" s="26" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="K26" s="26" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="L26" s="26" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="M26" s="26" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="N26" s="26" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O26" s="26" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="P26" s="26" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="Q26" s="26" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="R26" s="26" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="S26" s="26" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="T26" s="26" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="U26" s="24" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B27" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C27" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D27" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E27" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F27" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G27" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H27" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I27" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J27" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K27" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L27" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M27" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N27" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O27" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P27" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q27" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R27" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S27" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T27" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U27" s="20" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B28" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="P28" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q28" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="R28" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="S28" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" s="24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B29" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="C29" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="D29" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="E29" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="F29" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="G29" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="H29" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="I29" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="J29" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="K29" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="L29" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="M29" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="N29" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="O29" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="P29" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q29" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="R29" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="S29" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="T29" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="U29" s="24" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B30" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C30" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D30" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E30" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F30" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G30" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H30" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I30" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J30" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K30" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L30" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M30" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N30" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O30" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P30" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q30" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R30" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S30" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T30" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="U30" s="20" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B31" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C31" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D31" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E31" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F31" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G31" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H31" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I31" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J31" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K31" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L31" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M31" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N31" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O31" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P31" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q31" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R31" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="S31" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T31" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="U31" s="20" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B32" s="26" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C32" s="26" t="n">
+        <v>6000</v>
+      </c>
+      <c r="D32" s="26" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E32" s="26" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F32" s="26" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G32" s="26" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H32" s="26" t="n">
+        <v>4000</v>
+      </c>
+      <c r="I32" s="26" t="n">
+        <v>4000</v>
+      </c>
+      <c r="J32" s="26" t="n">
+        <v>4000</v>
+      </c>
+      <c r="K32" s="26" t="n">
+        <v>4000</v>
+      </c>
+      <c r="L32" s="26" t="n">
+        <v>4000</v>
+      </c>
+      <c r="M32" s="26" t="n">
+        <v>4000</v>
+      </c>
+      <c r="N32" s="26" t="n">
+        <v>4000</v>
+      </c>
+      <c r="O32" s="26" t="n">
+        <v>4000</v>
+      </c>
+      <c r="P32" s="26" t="n">
+        <v>4000</v>
+      </c>
+      <c r="Q32" s="26" t="n">
+        <v>4000</v>
+      </c>
+      <c r="R32" s="26" t="n">
+        <v>4000</v>
+      </c>
+      <c r="S32" s="26" t="n">
+        <v>4000</v>
+      </c>
+      <c r="T32" s="26" t="n">
+        <v>4000</v>
+      </c>
+      <c r="U32" s="24" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="B33" s="41"/>
+      <c r="C33" s="41"/>
+      <c r="D33" s="41"/>
+      <c r="E33" s="41"/>
+      <c r="F33" s="41"/>
+      <c r="G33" s="41"/>
+      <c r="H33" s="41"/>
+      <c r="I33" s="41"/>
+      <c r="J33" s="41"/>
+      <c r="K33" s="41"/>
+      <c r="L33" s="41"/>
+      <c r="M33" s="41"/>
+      <c r="N33" s="41"/>
+      <c r="O33" s="41"/>
+      <c r="P33" s="41"/>
+      <c r="Q33" s="41"/>
+      <c r="R33" s="41"/>
+      <c r="S33" s="41"/>
+      <c r="T33" s="41"/>
+      <c r="U33" s="41"/>
+    </row>
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="B34" s="44"/>
+      <c r="C34" s="44"/>
+      <c r="D34" s="44"/>
+      <c r="E34" s="44"/>
+      <c r="F34" s="44"/>
+      <c r="G34" s="44"/>
+      <c r="H34" s="44"/>
+      <c r="I34" s="44"/>
+      <c r="J34" s="44"/>
+      <c r="K34" s="44"/>
+      <c r="L34" s="44"/>
+      <c r="M34" s="44"/>
+      <c r="N34" s="44"/>
+      <c r="O34" s="44"/>
+      <c r="P34" s="44"/>
+      <c r="Q34" s="44"/>
+      <c r="R34" s="44"/>
+      <c r="S34" s="44"/>
+      <c r="T34" s="44"/>
+      <c r="U34" s="44"/>
+    </row>
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B35" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="C35" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="N35" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="O35" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="P35" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q35" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="R35" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="S35" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="T35" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" s="24" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B36" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C36" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D36" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L36" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="N36" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="O36" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="P36" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q36" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="R36" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="S36" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="T36" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U36" s="24" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J37" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M37" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N37" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O37" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P37" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q37" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="R37" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="S37" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="T37" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="U37" s="6" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G38" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="L38" s="93" t="s">
+        <v>193</v>
+      </c>
+      <c r="M38" s="93" t="s">
+        <v>193</v>
+      </c>
+      <c r="N38" s="93" t="s">
+        <v>191</v>
+      </c>
+      <c r="O38" s="93" t="s">
+        <v>191</v>
+      </c>
+      <c r="P38" s="93" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q38" s="93" t="s">
+        <v>195</v>
+      </c>
+      <c r="R38" s="93" t="s">
+        <v>193</v>
+      </c>
+      <c r="S38" s="93" t="s">
+        <v>193</v>
+      </c>
+      <c r="T38" s="93" t="s">
+        <v>193</v>
+      </c>
+      <c r="U38" s="94" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B40" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="C40" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D40" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="E40" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="F40" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="G40" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="H40" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="I40" s="22" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B41" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C41" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D41" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E41" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F41" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G41" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H41" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I41" s="20" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B42" s="60"/>
+      <c r="C42" s="60"/>
+      <c r="D42" s="60"/>
+      <c r="E42" s="60"/>
+      <c r="F42" s="60"/>
+      <c r="G42" s="60"/>
+      <c r="H42" s="60"/>
+      <c r="I42" s="60"/>
+    </row>
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B43" s="60"/>
+      <c r="C43" s="60"/>
+      <c r="D43" s="60"/>
+      <c r="E43" s="60"/>
+      <c r="F43" s="60"/>
+      <c r="G43" s="60"/>
+      <c r="H43" s="60"/>
+      <c r="I43" s="60"/>
+    </row>
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B44" s="60"/>
+      <c r="C44" s="60"/>
+      <c r="D44" s="60"/>
+      <c r="E44" s="60"/>
+      <c r="F44" s="60"/>
+      <c r="G44" s="60"/>
+      <c r="H44" s="60"/>
+      <c r="I44" s="60"/>
+    </row>
+    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B45" s="26" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C45" s="26" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="D45" s="26" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="E45" s="26" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="F45" s="26" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="G45" s="26" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H45" s="26" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="I45" s="24" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B46" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C46" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D46" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E46" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F46" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G46" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H46" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I46" s="20" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B47" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" s="24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B48" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="C48" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="D48" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="E48" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="F48" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G48" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H48" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="I48" s="24" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B49" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C49" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D49" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E49" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F49" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G49" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H49" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I49" s="20" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B50" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C50" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D50" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E50" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F50" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G50" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H50" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I50" s="20" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B51" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C51" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D51" s="26" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E51" s="26" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F51" s="26" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G51" s="26" t="n">
+        <v>8000</v>
+      </c>
+      <c r="H51" s="26" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I51" s="24" t="n">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="B52" s="41"/>
+      <c r="C52" s="41"/>
+      <c r="D52" s="41"/>
+      <c r="E52" s="41"/>
+      <c r="F52" s="41"/>
+      <c r="G52" s="41"/>
+      <c r="H52" s="41"/>
+      <c r="I52" s="41"/>
+    </row>
+    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="B53" s="44"/>
+      <c r="C53" s="44"/>
+      <c r="D53" s="44"/>
+      <c r="E53" s="44"/>
+      <c r="F53" s="44"/>
+      <c r="G53" s="44"/>
+      <c r="H53" s="44"/>
+      <c r="I53" s="44"/>
+    </row>
+    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B54" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D54" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E54" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F54" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G54" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H54" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="I54" s="24" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B55" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D55" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E55" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F55" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G55" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H55" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="I55" s="24" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I56" s="6" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D57" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B59" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="C59" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D59" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="E59" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="F59" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="G59" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="H59" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="I59" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="J59" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="K59" s="22" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B60" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C60" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D60" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E60" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F60" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G60" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H60" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I60" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J60" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K60" s="20" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B61" s="60"/>
+      <c r="C61" s="60"/>
+      <c r="D61" s="60"/>
+      <c r="E61" s="60"/>
+      <c r="F61" s="60"/>
+      <c r="G61" s="60"/>
+      <c r="H61" s="60"/>
+      <c r="I61" s="60"/>
+      <c r="J61" s="60"/>
+      <c r="K61" s="60"/>
+    </row>
+    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B62" s="60"/>
+      <c r="C62" s="60"/>
+      <c r="D62" s="60"/>
+      <c r="E62" s="60"/>
+      <c r="F62" s="60"/>
+      <c r="G62" s="60"/>
+      <c r="H62" s="60"/>
+      <c r="I62" s="60"/>
+      <c r="J62" s="60"/>
+      <c r="K62" s="60"/>
+    </row>
+    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B63" s="60"/>
+      <c r="C63" s="60"/>
+      <c r="D63" s="60"/>
+      <c r="E63" s="60"/>
+      <c r="F63" s="60"/>
+      <c r="G63" s="60"/>
+      <c r="H63" s="60"/>
+      <c r="I63" s="60"/>
+      <c r="J63" s="60"/>
+      <c r="K63" s="60"/>
+    </row>
+    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B64" s="26" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C64" s="26" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D64" s="26" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="E64" s="26" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="F64" s="26" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G64" s="26" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H64" s="26" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="I64" s="26" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="J64" s="26" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K64" s="24" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B65" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C65" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D65" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E65" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F65" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G65" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H65" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I65" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J65" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K65" s="20" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B66" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C66" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I66" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J66" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K66" s="24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B67" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="C67" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="D67" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E67" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="F67" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="G67" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="H67" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="I67" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="J67" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="K67" s="24" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B68" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C68" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D68" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E68" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F68" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G68" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H68" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I68" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J68" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K68" s="20" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B69" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C69" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D69" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E69" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F69" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G69" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H69" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I69" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J69" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K69" s="20" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B70" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C70" s="26" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D70" s="26" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E70" s="26" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F70" s="26" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G70" s="26" t="n">
+        <v>15000</v>
+      </c>
+      <c r="H70" s="26" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I70" s="26" t="n">
+        <v>15000</v>
+      </c>
+      <c r="J70" s="26" t="n">
+        <v>15000</v>
+      </c>
+      <c r="K70" s="24" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="B71" s="41"/>
+      <c r="C71" s="41"/>
+      <c r="D71" s="41"/>
+      <c r="E71" s="41"/>
+      <c r="F71" s="41"/>
+      <c r="G71" s="41"/>
+      <c r="H71" s="41"/>
+      <c r="I71" s="41"/>
+      <c r="J71" s="41"/>
+      <c r="K71" s="41"/>
+    </row>
+    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="B72" s="44"/>
+      <c r="C72" s="44"/>
+      <c r="D72" s="44"/>
+      <c r="E72" s="44"/>
+      <c r="F72" s="44"/>
+      <c r="G72" s="44"/>
+      <c r="H72" s="44"/>
+      <c r="I72" s="44"/>
+      <c r="J72" s="44"/>
+      <c r="K72" s="44"/>
+    </row>
+    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B73" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="C73" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D73" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I73" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J73" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K73" s="24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B74" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C74" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D74" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I74" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J74" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K74" s="24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D75" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E75" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H75" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I75" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J75" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K75" s="6" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F76" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="K76" s="94" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B79" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="C79" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D79" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="E79" s="22" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B80" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C80" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D80" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E80" s="20" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B81" s="60"/>
+      <c r="C81" s="60"/>
+      <c r="D81" s="60"/>
+      <c r="E81" s="60"/>
+    </row>
+    <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B82" s="60"/>
+      <c r="C82" s="60"/>
+      <c r="D82" s="60"/>
+      <c r="E82" s="60"/>
+    </row>
+    <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B83" s="60"/>
+      <c r="C83" s="60"/>
+      <c r="D83" s="60"/>
+      <c r="E83" s="60"/>
+    </row>
+    <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B84" s="26" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C84" s="26" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D84" s="26" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E84" s="24" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B85" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C85" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D85" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E85" s="20" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B86" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C86" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" s="24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B87" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="C87" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="D87" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="E87" s="24" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B88" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C88" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D88" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E88" s="20" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B89" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C89" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D89" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E89" s="20" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B90" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C90" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D90" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E90" s="24" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="B91" s="41"/>
+      <c r="C91" s="41"/>
+      <c r="D91" s="41"/>
+      <c r="E91" s="41"/>
+    </row>
+    <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="B92" s="44"/>
+      <c r="C92" s="44"/>
+      <c r="D92" s="44"/>
+      <c r="E92" s="44"/>
+    </row>
+    <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B93" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C93" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" s="24" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B94" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C94" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D94" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" s="24" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B95" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C95" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D95" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E95" s="6" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E96" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B98" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="C98" s="22" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B99" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C99" s="20" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B100" s="60"/>
+      <c r="C100" s="60"/>
+    </row>
+    <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B101" s="60"/>
+      <c r="C101" s="60"/>
+    </row>
+    <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B102" s="60"/>
+      <c r="C102" s="60"/>
+    </row>
+    <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B103" s="26" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C103" s="24" t="n">
+        <v>0.008</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B104" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C104" s="20" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B105" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C105" s="24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B106" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="C106" s="24" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B107" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C107" s="20" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B108" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C108" s="20" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B109" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C109" s="24" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="B110" s="41"/>
+      <c r="C110" s="41"/>
+    </row>
+    <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="B111" s="44"/>
+      <c r="C111" s="44"/>
+    </row>
+    <row r="112" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B112" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C112" s="24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B113" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C113" s="24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B114" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C114" s="6" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:G36"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C2" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D2" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E2" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F2" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G2" s="19" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B3" s="60"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="60"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" s="60"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B5" s="60"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" s="26" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="C6" s="26" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="D6" s="26" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="F6" s="26" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="G6" s="26" t="n">
+        <v>0.0085</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B7" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C7" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E7" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F7" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G7" s="19" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B8" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B9" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="E9" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="G9" s="26" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B10" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C10" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D10" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E10" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B11" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C11" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D11" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E11" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F11" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B12" s="26" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C12" s="26" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D12" s="26" t="n">
+        <v>18000</v>
+      </c>
+      <c r="E12" s="26" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F12" s="26" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G12" s="26" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="B13" s="41"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41"/>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B15" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C15" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G15" s="26" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B16" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C16" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="F16" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G16" s="26" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="0" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="0" t="s">
+        <v>201</v>
+      </c>
+      <c r="C19" s="0" t="s">
+        <v>201</v>
+      </c>
+      <c r="D19" s="0" t="s">
+        <v>201</v>
+      </c>
+      <c r="E19" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="F19" s="0" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="F20" s="26" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B21" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C21" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D21" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E21" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F21" s="19" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B22" s="60"/>
+      <c r="C22" s="60"/>
+      <c r="D22" s="60"/>
+      <c r="E22" s="60"/>
+      <c r="F22" s="60"/>
+    </row>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B23" s="60"/>
+      <c r="C23" s="60"/>
+      <c r="D23" s="60"/>
+      <c r="E23" s="60"/>
+      <c r="F23" s="60"/>
+    </row>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B24" s="60"/>
+      <c r="C24" s="60"/>
+      <c r="D24" s="60"/>
+      <c r="E24" s="60"/>
+      <c r="F24" s="60"/>
+    </row>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B25" s="26" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="C25" s="26" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="D25" s="26" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="E25" s="26" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="F25" s="26" t="n">
+        <v>0.009</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B26" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C26" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D26" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E26" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F26" s="19" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B27" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B28" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="C28" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="D28" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="E28" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="F28" s="26" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B29" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C29" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D29" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E29" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F29" s="19" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B30" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C30" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D30" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E30" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F30" s="19" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B31" s="26" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C31" s="26" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D31" s="26" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E31" s="26" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F31" s="26" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="B32" s="41"/>
+      <c r="C32" s="41"/>
+      <c r="D32" s="41"/>
+      <c r="E32" s="41"/>
+      <c r="F32" s="41"/>
+    </row>
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="B33" s="44"/>
+      <c r="C33" s="44"/>
+      <c r="D33" s="44"/>
+      <c r="E33" s="44"/>
+      <c r="F33" s="44"/>
+    </row>
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B34" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C34" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="D34" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E34" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="F34" s="26" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B35" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C35" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="D35" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E35" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="F35" s="26" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>

--- a/parameters script.xlsx
+++ b/parameters script.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1279" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1304" uniqueCount="206">
   <si>
     <t xml:space="preserve">6h 3</t>
   </si>
@@ -672,7 +672,13 @@
     <t xml:space="preserve">5 may V3</t>
   </si>
   <si>
+    <t xml:space="preserve">5 may V2</t>
+  </si>
+  <si>
     <t xml:space="preserve">12H-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12H-5</t>
   </si>
 </sst>
 </file>
@@ -1448,9 +1454,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>464040</xdr:colOff>
+      <xdr:colOff>463680</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>21240</xdr:rowOff>
+      <xdr:rowOff>20880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1464,7 +1470,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6183720" y="130320"/>
-          <a:ext cx="7984800" cy="256680"/>
+          <a:ext cx="7984440" cy="256320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1491,9 +1497,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>218160</xdr:colOff>
+      <xdr:colOff>217800</xdr:colOff>
       <xdr:row>88</xdr:row>
-      <xdr:rowOff>62640</xdr:rowOff>
+      <xdr:rowOff>62280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1507,7 +1513,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="10345680" y="14112360"/>
-          <a:ext cx="10143720" cy="2043720"/>
+          <a:ext cx="10143360" cy="2043360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1529,9 +1535,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>883080</xdr:colOff>
+      <xdr:colOff>882720</xdr:colOff>
       <xdr:row>126</xdr:row>
-      <xdr:rowOff>98640</xdr:rowOff>
+      <xdr:rowOff>98280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1545,7 +1551,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6275880" y="21031200"/>
-          <a:ext cx="10180440" cy="2110320"/>
+          <a:ext cx="10180080" cy="2109960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -22315,7 +22321,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22337,7 +22343,7 @@
       <c r="F1" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="G1" s="22" t="s">
         <v>107</v>
       </c>
     </row>
@@ -22360,7 +22366,7 @@
       <c r="F2" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="G2" s="19" t="n">
+      <c r="G2" s="20" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -22416,7 +22422,7 @@
       <c r="F6" s="26" t="n">
         <v>0.008</v>
       </c>
-      <c r="G6" s="26" t="n">
+      <c r="G6" s="24" t="n">
         <v>0.0085</v>
       </c>
     </row>
@@ -22439,7 +22445,7 @@
       <c r="F7" s="19" t="n">
         <v>0.4</v>
       </c>
-      <c r="G7" s="19" t="n">
+      <c r="G7" s="20" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -22462,7 +22468,7 @@
       <c r="F8" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="26" t="n">
+      <c r="G8" s="24" t="n">
         <v>1</v>
       </c>
     </row>
@@ -22485,7 +22491,7 @@
       <c r="F9" s="26" t="n">
         <v>9</v>
       </c>
-      <c r="G9" s="26" t="n">
+      <c r="G9" s="24" t="n">
         <v>9</v>
       </c>
     </row>
@@ -22508,7 +22514,7 @@
       <c r="F10" s="19" t="n">
         <v>1.2</v>
       </c>
-      <c r="G10" s="19" t="n">
+      <c r="G10" s="20" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -22531,7 +22537,7 @@
       <c r="F11" s="19" t="n">
         <v>0.6</v>
       </c>
-      <c r="G11" s="19" t="n">
+      <c r="G11" s="20" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -22554,7 +22560,7 @@
       <c r="F12" s="26" t="n">
         <v>20000</v>
       </c>
-      <c r="G12" s="26" t="n">
+      <c r="G12" s="24" t="n">
         <v>20000</v>
       </c>
     </row>
@@ -22599,7 +22605,7 @@
       <c r="F15" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="G15" s="26" t="n">
+      <c r="G15" s="24" t="n">
         <v>4</v>
       </c>
     </row>
@@ -22622,7 +22628,7 @@
       <c r="F16" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="G16" s="26" t="n">
+      <c r="G16" s="24" t="n">
         <v>4</v>
       </c>
     </row>
@@ -22649,31 +22655,40 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="0" t="s">
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="1" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="C19" s="0" t="s">
+      <c r="C19" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="D19" s="0" t="s">
+      <c r="D19" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="E19" s="0" t="s">
+      <c r="E19" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="F19" s="0" t="s">
+      <c r="F19" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="I19" s="1" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B20" s="18" t="s">
         <v>102</v>
@@ -22687,8 +22702,17 @@
       <c r="E20" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="F20" s="26" t="s">
+      <c r="F20" s="18" t="s">
         <v>106</v>
+      </c>
+      <c r="G20" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="H20" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="I20" s="26" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22708,6 +22732,15 @@
         <v>0.5</v>
       </c>
       <c r="F21" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G21" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H21" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I21" s="19" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -22720,6 +22753,9 @@
       <c r="D22" s="60"/>
       <c r="E22" s="60"/>
       <c r="F22" s="60"/>
+      <c r="G22" s="60"/>
+      <c r="H22" s="60"/>
+      <c r="I22" s="60"/>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
@@ -22730,6 +22766,9 @@
       <c r="D23" s="60"/>
       <c r="E23" s="60"/>
       <c r="F23" s="60"/>
+      <c r="G23" s="60"/>
+      <c r="H23" s="60"/>
+      <c r="I23" s="60"/>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
@@ -22740,6 +22779,9 @@
       <c r="D24" s="60"/>
       <c r="E24" s="60"/>
       <c r="F24" s="60"/>
+      <c r="G24" s="60"/>
+      <c r="H24" s="60"/>
+      <c r="I24" s="60"/>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
@@ -22760,6 +22802,15 @@
       <c r="F25" s="26" t="n">
         <v>0.009</v>
       </c>
+      <c r="G25" s="26" t="n">
+        <v>0.009</v>
+      </c>
+      <c r="H25" s="26" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I25" s="26" t="n">
+        <v>0.015</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
@@ -22780,6 +22831,15 @@
       <c r="F26" s="19" t="n">
         <v>0.4</v>
       </c>
+      <c r="G26" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H26" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I26" s="19" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
@@ -22800,6 +22860,15 @@
       <c r="F27" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="G27" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
@@ -22820,6 +22889,15 @@
       <c r="F28" s="26" t="n">
         <v>8</v>
       </c>
+      <c r="G28" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="H28" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="I28" s="26" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
@@ -22840,6 +22918,15 @@
       <c r="F29" s="19" t="n">
         <v>1.2</v>
       </c>
+      <c r="G29" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H29" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I29" s="19" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
@@ -22860,6 +22947,15 @@
       <c r="F30" s="19" t="n">
         <v>0.6</v>
       </c>
+      <c r="G30" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H30" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I30" s="19" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
@@ -22878,6 +22974,15 @@
         <v>15000</v>
       </c>
       <c r="F31" s="26" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G31" s="26" t="n">
+        <v>15000</v>
+      </c>
+      <c r="H31" s="26" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I31" s="26" t="n">
         <v>15000</v>
       </c>
     </row>
@@ -22890,6 +22995,9 @@
       <c r="D32" s="41"/>
       <c r="E32" s="41"/>
       <c r="F32" s="41"/>
+      <c r="G32" s="41"/>
+      <c r="H32" s="41"/>
+      <c r="I32" s="41"/>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="29" t="s">
@@ -22900,6 +23008,9 @@
       <c r="D33" s="44"/>
       <c r="E33" s="44"/>
       <c r="F33" s="44"/>
+      <c r="G33" s="44"/>
+      <c r="H33" s="44"/>
+      <c r="I33" s="44"/>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="19" t="s">
@@ -22920,6 +23031,15 @@
       <c r="F34" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="G34" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H34" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="I34" s="26" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="19" t="s">
@@ -22940,6 +23060,15 @@
       <c r="F35" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="G35" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H35" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="I35" s="26" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
@@ -22958,6 +23087,182 @@
         <v>0.5</v>
       </c>
       <c r="F36" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B38" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="C38" s="26" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B39" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C39" s="19" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B40" s="60"/>
+      <c r="C40" s="60"/>
+    </row>
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B41" s="60"/>
+      <c r="C41" s="60"/>
+    </row>
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B42" s="60"/>
+      <c r="C42" s="60"/>
+    </row>
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B43" s="26" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="C43" s="26" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B44" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C44" s="19" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B45" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" s="26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B46" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="C46" s="26" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B47" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C47" s="19" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B48" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C48" s="19" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B49" s="26" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C49" s="26" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="B50" s="41"/>
+      <c r="C50" s="41"/>
+    </row>
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="B51" s="44"/>
+      <c r="C51" s="44"/>
+    </row>
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B52" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C52" s="26" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B53" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C53" s="26" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C54" s="5" t="n">
         <v>0.5</v>
       </c>
     </row>

--- a/parameters script.xlsx
+++ b/parameters script.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1304" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1337" uniqueCount="211">
   <si>
     <t xml:space="preserve">6h 3</t>
   </si>
@@ -666,6 +666,9 @@
     <t xml:space="preserve">12H-3</t>
   </si>
   <si>
+    <t xml:space="preserve">SOLO PEGAR LOS DATASETS</t>
+  </si>
+  <si>
     <t xml:space="preserve">5 may v2</t>
   </si>
   <si>
@@ -678,7 +681,19 @@
     <t xml:space="preserve">12H-4</t>
   </si>
   <si>
+    <t xml:space="preserve">V2</t>
+  </si>
+  <si>
     <t xml:space="preserve">12H-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12H-6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 may V3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EJECUTAR DE NUEVO EN v2, para chequear valores de senal</t>
   </si>
 </sst>
 </file>
@@ -22321,8 +22336,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:I74"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
@@ -22585,6 +22600,9 @@
       <c r="E14" s="44"/>
       <c r="F14" s="44"/>
       <c r="G14" s="44"/>
+      <c r="H14" s="0" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
@@ -22662,33 +22680,33 @@
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G19" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="I19" s="1" t="s">
         <v>203</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B20" s="18" t="s">
         <v>102</v>
@@ -23099,15 +23117,35 @@
         <v>0.5</v>
       </c>
     </row>
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="C37" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="D37" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="E37" s="0" t="s">
+        <v>206</v>
+      </c>
+    </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B38" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="C38" s="26" t="s">
+      <c r="C38" s="18" t="s">
         <v>103</v>
+      </c>
+      <c r="D38" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="E38" s="22" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23120,6 +23158,12 @@
       <c r="C39" s="19" t="n">
         <v>0.5</v>
       </c>
+      <c r="D39" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E39" s="20" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
@@ -23127,6 +23171,8 @@
       </c>
       <c r="B40" s="60"/>
       <c r="C40" s="60"/>
+      <c r="D40" s="60"/>
+      <c r="E40" s="60"/>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
@@ -23134,6 +23180,8 @@
       </c>
       <c r="B41" s="60"/>
       <c r="C41" s="60"/>
+      <c r="D41" s="60"/>
+      <c r="E41" s="60"/>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
@@ -23141,6 +23189,8 @@
       </c>
       <c r="B42" s="60"/>
       <c r="C42" s="60"/>
+      <c r="D42" s="60"/>
+      <c r="E42" s="60"/>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
@@ -23152,6 +23202,12 @@
       <c r="C43" s="26" t="n">
         <v>0.005</v>
       </c>
+      <c r="D43" s="26" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="E43" s="24" t="n">
+        <v>0.004</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
@@ -23163,6 +23219,12 @@
       <c r="C44" s="19" t="n">
         <v>0.4</v>
       </c>
+      <c r="D44" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E44" s="20" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
@@ -23174,6 +23236,12 @@
       <c r="C45" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="D45" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
@@ -23185,6 +23253,12 @@
       <c r="C46" s="26" t="n">
         <v>9</v>
       </c>
+      <c r="D46" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" s="24" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
@@ -23196,6 +23270,12 @@
       <c r="C47" s="19" t="n">
         <v>1.2</v>
       </c>
+      <c r="D47" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E47" s="20" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
@@ -23207,6 +23287,12 @@
       <c r="C48" s="19" t="n">
         <v>0.6</v>
       </c>
+      <c r="D48" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E48" s="20" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
@@ -23218,6 +23304,12 @@
       <c r="C49" s="26" t="n">
         <v>15000</v>
       </c>
+      <c r="D49" s="26" t="n">
+        <v>18000</v>
+      </c>
+      <c r="E49" s="24" t="n">
+        <v>22000</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="19" t="s">
@@ -23225,6 +23317,8 @@
       </c>
       <c r="B50" s="41"/>
       <c r="C50" s="41"/>
+      <c r="D50" s="41"/>
+      <c r="E50" s="41"/>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="29" t="s">
@@ -23232,6 +23326,8 @@
       </c>
       <c r="B51" s="44"/>
       <c r="C51" s="44"/>
+      <c r="D51" s="44"/>
+      <c r="E51" s="44"/>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="19" t="s">
@@ -23243,6 +23339,12 @@
       <c r="C52" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="D52" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E52" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="19" t="s">
@@ -23254,6 +23356,12 @@
       <c r="C53" s="26" t="n">
         <v>4</v>
       </c>
+      <c r="D53" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E53" s="24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
@@ -23264,6 +23372,280 @@
       </c>
       <c r="C54" s="5" t="n">
         <v>0.5</v>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B56" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="C56" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D56" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="E56" s="22" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B57" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C57" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D57" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E57" s="20" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B58" s="60"/>
+      <c r="C58" s="60"/>
+      <c r="D58" s="60"/>
+      <c r="E58" s="60"/>
+    </row>
+    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B59" s="60"/>
+      <c r="C59" s="60"/>
+      <c r="D59" s="60"/>
+      <c r="E59" s="60"/>
+    </row>
+    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B60" s="60"/>
+      <c r="C60" s="60"/>
+      <c r="D60" s="60"/>
+      <c r="E60" s="60"/>
+    </row>
+    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B61" s="26" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="C61" s="26" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="D61" s="26" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="E61" s="24" t="n">
+        <v>0.0045</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B62" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C62" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D62" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E62" s="20" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B63" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B64" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="C64" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="D64" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E64" s="24" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B65" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C65" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D65" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E65" s="20" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B66" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C66" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D66" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E66" s="20" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B67" s="26" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C67" s="26" t="n">
+        <v>18000</v>
+      </c>
+      <c r="D67" s="26" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E67" s="24" t="n">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="B68" s="41"/>
+      <c r="C68" s="41"/>
+      <c r="D68" s="41"/>
+      <c r="E68" s="41"/>
+    </row>
+    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="B69" s="44"/>
+      <c r="C69" s="44"/>
+      <c r="D69" s="44"/>
+      <c r="E69" s="44"/>
+    </row>
+    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B70" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C70" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="D70" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E70" s="24" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B71" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C71" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="D71" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E71" s="24" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C72" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D72" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E72" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B73" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E74" s="0" t="s">
+        <v>210</v>
       </c>
     </row>
   </sheetData>

--- a/parameters script.xlsx
+++ b/parameters script.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1987" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2004" uniqueCount="241">
   <si>
     <t xml:space="preserve">6h 3</t>
   </si>
@@ -796,7 +796,7 @@
     <numFmt numFmtId="166" formatCode="0.00%"/>
     <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -855,6 +855,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1085,7 +1092,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="73">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1310,7 +1317,15 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1326,10 +1341,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="18" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="21" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1338,12 +1349,20 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -1351,14 +1370,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1457,9 +1468,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>460440</xdr:colOff>
+      <xdr:colOff>459360</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>17640</xdr:rowOff>
+      <xdr:rowOff>16560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1473,7 +1484,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6183720" y="130320"/>
-          <a:ext cx="7981200" cy="253080"/>
+          <a:ext cx="7980120" cy="252000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1500,9 +1511,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>214560</xdr:colOff>
+      <xdr:colOff>213480</xdr:colOff>
       <xdr:row>85</xdr:row>
-      <xdr:rowOff>20880</xdr:rowOff>
+      <xdr:rowOff>19800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1516,7 +1527,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="10345680" y="13525560"/>
-          <a:ext cx="10140120" cy="2040120"/>
+          <a:ext cx="10139040" cy="2039040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1538,9 +1549,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>879480</xdr:colOff>
+      <xdr:colOff>878400</xdr:colOff>
       <xdr:row>121</xdr:row>
-      <xdr:rowOff>133200</xdr:rowOff>
+      <xdr:rowOff>132120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1554,7 +1565,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6275880" y="20154960"/>
-          <a:ext cx="10176840" cy="2106720"/>
+          <a:ext cx="10175760" cy="2105640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -22280,10 +22291,10 @@
       <c r="F1" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="G1" s="56" t="s">
         <v>107</v>
       </c>
-      <c r="H1" s="56" t="s">
+      <c r="H1" s="57" t="s">
         <v>108</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -22309,10 +22320,10 @@
       <c r="F2" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="G2" s="18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H2" s="56" t="n">
+      <c r="G2" s="56" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H2" s="57" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -22371,10 +22382,10 @@
       <c r="F6" s="17" t="n">
         <v>0.008</v>
       </c>
-      <c r="G6" s="18" t="n">
+      <c r="G6" s="56" t="n">
         <v>0.0085</v>
       </c>
-      <c r="H6" s="56" t="n">
+      <c r="H6" s="57" t="n">
         <v>0.0085</v>
       </c>
     </row>
@@ -22397,10 +22408,10 @@
       <c r="F7" s="17" t="n">
         <v>0.4</v>
       </c>
-      <c r="G7" s="18" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H7" s="56" t="n">
+      <c r="G7" s="56" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H7" s="57" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -22423,10 +22434,10 @@
       <c r="F8" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="56" t="n">
+      <c r="G8" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="57" t="n">
         <v>1</v>
       </c>
     </row>
@@ -22449,10 +22460,10 @@
       <c r="F9" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="G9" s="18" t="n">
+      <c r="G9" s="56" t="n">
         <v>9</v>
       </c>
-      <c r="H9" s="56" t="n">
+      <c r="H9" s="57" t="n">
         <v>9</v>
       </c>
     </row>
@@ -22475,10 +22486,10 @@
       <c r="F10" s="17" t="n">
         <v>1.2</v>
       </c>
-      <c r="G10" s="18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H10" s="56" t="n">
+      <c r="G10" s="56" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H10" s="57" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -22501,10 +22512,10 @@
       <c r="F11" s="17" t="n">
         <v>0.6</v>
       </c>
-      <c r="G11" s="18" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H11" s="56" t="n">
+      <c r="G11" s="56" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H11" s="57" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -22527,10 +22538,10 @@
       <c r="F12" s="17" t="n">
         <v>20000</v>
       </c>
-      <c r="G12" s="18" t="n">
+      <c r="G12" s="56" t="n">
         <v>20000</v>
       </c>
-      <c r="H12" s="56" t="n">
+      <c r="H12" s="57" t="n">
         <v>20000</v>
       </c>
     </row>
@@ -22577,10 +22588,10 @@
       <c r="F15" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="G15" s="18" t="n">
+      <c r="G15" s="56" t="n">
         <v>4</v>
       </c>
-      <c r="H15" s="56" t="n">
+      <c r="H15" s="57" t="n">
         <v>4</v>
       </c>
     </row>
@@ -22603,10 +22614,10 @@
       <c r="F16" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="G16" s="18" t="n">
+      <c r="G16" s="56" t="n">
         <v>4</v>
       </c>
-      <c r="H16" s="56" t="n">
+      <c r="H16" s="57" t="n">
         <v>4</v>
       </c>
     </row>
@@ -22675,6 +22686,9 @@
       <c r="L19" s="1" t="s">
         <v>202</v>
       </c>
+      <c r="M19" s="24" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
@@ -22713,6 +22727,9 @@
       <c r="L20" s="18" t="s">
         <v>112</v>
       </c>
+      <c r="M20" s="27" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
@@ -22749,6 +22766,9 @@
         <v>0.5</v>
       </c>
       <c r="L21" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M21" s="27" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -22767,6 +22787,7 @@
       <c r="J22" s="23"/>
       <c r="K22" s="23"/>
       <c r="L22" s="23"/>
+      <c r="M22" s="23"/>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
@@ -22783,6 +22804,7 @@
       <c r="J23" s="23"/>
       <c r="K23" s="23"/>
       <c r="L23" s="23"/>
+      <c r="M23" s="23"/>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
@@ -22799,6 +22821,7 @@
       <c r="J24" s="23"/>
       <c r="K24" s="23"/>
       <c r="L24" s="23"/>
+      <c r="M24" s="23"/>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
@@ -22837,6 +22860,9 @@
       <c r="L25" s="18" t="n">
         <v>0.0125</v>
       </c>
+      <c r="M25" s="27" t="n">
+        <v>0.0125</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
@@ -22875,6 +22901,9 @@
       <c r="L26" s="18" t="n">
         <v>0.4</v>
       </c>
+      <c r="M26" s="27" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
@@ -22913,6 +22942,9 @@
       <c r="L27" s="18" t="n">
         <v>1</v>
       </c>
+      <c r="M27" s="27" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
@@ -22951,6 +22983,9 @@
       <c r="L28" s="18" t="n">
         <v>8</v>
       </c>
+      <c r="M28" s="27" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
@@ -22989,6 +23024,9 @@
       <c r="L29" s="18" t="n">
         <v>1.2</v>
       </c>
+      <c r="M29" s="27" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
@@ -23027,6 +23065,9 @@
       <c r="L30" s="18" t="n">
         <v>0.6</v>
       </c>
+      <c r="M30" s="27" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
@@ -23063,6 +23104,9 @@
         <v>15000</v>
       </c>
       <c r="L31" s="18" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M31" s="27" t="n">
         <v>15000</v>
       </c>
     </row>
@@ -23081,6 +23125,7 @@
       <c r="J32" s="29"/>
       <c r="K32" s="29"/>
       <c r="L32" s="29"/>
+      <c r="M32" s="29"/>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="22" t="s">
@@ -23097,6 +23142,7 @@
       <c r="J33" s="31"/>
       <c r="K33" s="31"/>
       <c r="L33" s="31"/>
+      <c r="M33" s="31"/>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="17" t="s">
@@ -23135,6 +23181,9 @@
       <c r="L34" s="18" t="n">
         <v>4</v>
       </c>
+      <c r="M34" s="27" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="17" t="s">
@@ -23173,6 +23222,9 @@
       <c r="L35" s="18" t="n">
         <v>4</v>
       </c>
+      <c r="M35" s="27" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
@@ -23211,6 +23263,9 @@
       <c r="L36" s="5" t="n">
         <v>0.5</v>
       </c>
+      <c r="M36" s="5" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="1" t="s">
@@ -23225,6 +23280,21 @@
       <c r="E37" s="1" t="s">
         <v>202</v>
       </c>
+      <c r="G37" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
@@ -23245,8 +23315,20 @@
       <c r="F38" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="G38" s="18" t="s">
+      <c r="G38" s="27" t="s">
         <v>107</v>
+      </c>
+      <c r="H38" s="56" t="s">
+        <v>108</v>
+      </c>
+      <c r="I38" s="56" t="s">
+        <v>109</v>
+      </c>
+      <c r="J38" s="56" t="s">
+        <v>110</v>
+      </c>
+      <c r="K38" s="56" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23265,7 +23347,19 @@
       <c r="E39" s="18" t="n">
         <v>0.5</v>
       </c>
-      <c r="G39" s="18" t="n">
+      <c r="G39" s="27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H39" s="27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I39" s="27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J39" s="58" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K39" s="56" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -23278,6 +23372,10 @@
       <c r="D40" s="23"/>
       <c r="E40" s="23"/>
       <c r="G40" s="23"/>
+      <c r="H40" s="23"/>
+      <c r="I40" s="23"/>
+      <c r="J40" s="23"/>
+      <c r="K40" s="23"/>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
@@ -23288,6 +23386,10 @@
       <c r="D41" s="23"/>
       <c r="E41" s="23"/>
       <c r="G41" s="23"/>
+      <c r="H41" s="23"/>
+      <c r="I41" s="23"/>
+      <c r="J41" s="23"/>
+      <c r="K41" s="23"/>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
@@ -23298,6 +23400,10 @@
       <c r="D42" s="23"/>
       <c r="E42" s="23"/>
       <c r="G42" s="23"/>
+      <c r="H42" s="23"/>
+      <c r="I42" s="23"/>
+      <c r="J42" s="23"/>
+      <c r="K42" s="23"/>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
@@ -23315,8 +23421,20 @@
       <c r="E43" s="18" t="n">
         <v>0.004</v>
       </c>
-      <c r="G43" s="18" t="n">
+      <c r="G43" s="27" t="n">
         <v>0.003</v>
+      </c>
+      <c r="H43" s="56" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="I43" s="56" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="J43" s="58" t="n">
+        <v>0.00225</v>
+      </c>
+      <c r="K43" s="56" t="n">
+        <v>0.00225</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23335,7 +23453,19 @@
       <c r="E44" s="18" t="n">
         <v>0.4</v>
       </c>
-      <c r="G44" s="18" t="n">
+      <c r="G44" s="27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H44" s="27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I44" s="27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J44" s="58" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K44" s="56" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -23355,7 +23485,19 @@
       <c r="E45" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G45" s="18" t="n">
+      <c r="G45" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" s="56" t="n">
         <v>1</v>
       </c>
     </row>
@@ -23375,8 +23517,20 @@
       <c r="E46" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="G46" s="18" t="n">
+      <c r="G46" s="27" t="n">
         <v>10</v>
+      </c>
+      <c r="H46" s="56" t="n">
+        <v>11</v>
+      </c>
+      <c r="I46" s="56" t="n">
+        <v>12</v>
+      </c>
+      <c r="J46" s="58" t="n">
+        <v>14</v>
+      </c>
+      <c r="K46" s="56" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23395,7 +23549,19 @@
       <c r="E47" s="18" t="n">
         <v>1.2</v>
       </c>
-      <c r="G47" s="18" t="n">
+      <c r="G47" s="27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H47" s="27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I47" s="27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J47" s="58" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K47" s="56" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -23415,7 +23581,19 @@
       <c r="E48" s="18" t="n">
         <v>0.6</v>
       </c>
-      <c r="G48" s="18" t="n">
+      <c r="G48" s="27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H48" s="27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I48" s="27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J48" s="58" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K48" s="56" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -23435,7 +23613,19 @@
       <c r="E49" s="18" t="n">
         <v>22000</v>
       </c>
-      <c r="G49" s="18" t="n">
+      <c r="G49" s="27" t="n">
+        <v>22000</v>
+      </c>
+      <c r="H49" s="27" t="n">
+        <v>22000</v>
+      </c>
+      <c r="I49" s="27" t="n">
+        <v>22000</v>
+      </c>
+      <c r="J49" s="58" t="n">
+        <v>22000</v>
+      </c>
+      <c r="K49" s="56" t="n">
         <v>22000</v>
       </c>
     </row>
@@ -23448,6 +23638,10 @@
       <c r="D50" s="29"/>
       <c r="E50" s="29"/>
       <c r="G50" s="29"/>
+      <c r="H50" s="29"/>
+      <c r="I50" s="29"/>
+      <c r="J50" s="29"/>
+      <c r="K50" s="29"/>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="22" t="s">
@@ -23458,6 +23652,10 @@
       <c r="D51" s="31"/>
       <c r="E51" s="31"/>
       <c r="G51" s="31"/>
+      <c r="H51" s="31"/>
+      <c r="I51" s="31"/>
+      <c r="J51" s="31"/>
+      <c r="K51" s="31"/>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="17" t="s">
@@ -23475,7 +23673,19 @@
       <c r="E52" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="G52" s="18" t="n">
+      <c r="G52" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="H52" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="I52" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="J52" s="58" t="n">
+        <v>4</v>
+      </c>
+      <c r="K52" s="56" t="n">
         <v>4</v>
       </c>
     </row>
@@ -23495,7 +23705,19 @@
       <c r="E53" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="G53" s="18" t="n">
+      <c r="G53" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="H53" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="I53" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="J53" s="58" t="n">
+        <v>4</v>
+      </c>
+      <c r="K53" s="56" t="n">
         <v>4</v>
       </c>
     </row>
@@ -23518,8 +23740,24 @@
       <c r="G54" s="5" t="n">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="H54" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J54" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H55" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
         <v>207</v>
@@ -23533,7 +23771,7 @@
       <c r="D56" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="E56" s="57" t="s">
+      <c r="E56" s="59" t="s">
         <v>105</v>
       </c>
       <c r="F56" s="18" t="s">
@@ -23541,6 +23779,9 @@
       </c>
       <c r="G56" s="6" t="s">
         <v>208</v>
+      </c>
+      <c r="H56" s="56" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23556,10 +23797,13 @@
       <c r="D57" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="E57" s="57" t="n">
+      <c r="E57" s="59" t="n">
         <v>0.5</v>
       </c>
       <c r="F57" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H57" s="56" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -23572,6 +23816,7 @@
       <c r="D58" s="23"/>
       <c r="E58" s="23"/>
       <c r="F58" s="23"/>
+      <c r="H58" s="23"/>
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
@@ -23582,6 +23827,7 @@
       <c r="D59" s="23"/>
       <c r="E59" s="23"/>
       <c r="F59" s="23"/>
+      <c r="H59" s="23"/>
     </row>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
@@ -23592,6 +23838,7 @@
       <c r="D60" s="23"/>
       <c r="E60" s="23"/>
       <c r="F60" s="23"/>
+      <c r="H60" s="23"/>
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="s">
@@ -23606,10 +23853,13 @@
       <c r="D61" s="17" t="n">
         <v>0.004</v>
       </c>
-      <c r="E61" s="57" t="n">
+      <c r="E61" s="59" t="n">
         <v>0.0045</v>
       </c>
       <c r="F61" s="18" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="H61" s="56" t="n">
         <v>0.0045</v>
       </c>
     </row>
@@ -23626,10 +23876,13 @@
       <c r="D62" s="17" t="n">
         <v>0.4</v>
       </c>
-      <c r="E62" s="57" t="n">
+      <c r="E62" s="59" t="n">
         <v>0.4</v>
       </c>
       <c r="F62" s="18" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H62" s="56" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -23646,10 +23899,13 @@
       <c r="D63" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="E63" s="57" t="n">
+      <c r="E63" s="59" t="n">
         <v>1</v>
       </c>
       <c r="F63" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" s="56" t="n">
         <v>1</v>
       </c>
     </row>
@@ -23666,10 +23922,13 @@
       <c r="D64" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="E64" s="57" t="n">
+      <c r="E64" s="59" t="n">
         <v>10</v>
       </c>
       <c r="F64" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="H64" s="56" t="n">
         <v>10</v>
       </c>
     </row>
@@ -23686,10 +23945,13 @@
       <c r="D65" s="17" t="n">
         <v>1.2</v>
       </c>
-      <c r="E65" s="57" t="n">
+      <c r="E65" s="59" t="n">
         <v>1.2</v>
       </c>
       <c r="F65" s="18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H65" s="56" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -23706,10 +23968,13 @@
       <c r="D66" s="17" t="n">
         <v>0.6</v>
       </c>
-      <c r="E66" s="57" t="n">
+      <c r="E66" s="59" t="n">
         <v>0.6</v>
       </c>
       <c r="F66" s="18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H66" s="56" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -23726,10 +23991,13 @@
       <c r="D67" s="17" t="n">
         <v>20000</v>
       </c>
-      <c r="E67" s="57" t="n">
+      <c r="E67" s="59" t="n">
         <v>25000</v>
       </c>
       <c r="F67" s="18" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H67" s="56" t="n">
         <v>25000</v>
       </c>
     </row>
@@ -23742,6 +24010,7 @@
       <c r="D68" s="29"/>
       <c r="E68" s="29"/>
       <c r="F68" s="29"/>
+      <c r="H68" s="29"/>
     </row>
     <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="22" t="s">
@@ -23752,6 +24021,7 @@
       <c r="D69" s="31"/>
       <c r="E69" s="31"/>
       <c r="F69" s="31"/>
+      <c r="H69" s="31"/>
     </row>
     <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="17" t="s">
@@ -23766,10 +24036,13 @@
       <c r="D70" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="E70" s="57" t="n">
+      <c r="E70" s="59" t="n">
         <v>4</v>
       </c>
       <c r="F70" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="H70" s="56" t="n">
         <v>4</v>
       </c>
     </row>
@@ -23786,10 +24059,13 @@
       <c r="D71" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="E71" s="57" t="n">
+      <c r="E71" s="59" t="n">
         <v>4</v>
       </c>
       <c r="F71" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="H71" s="56" t="n">
         <v>4</v>
       </c>
     </row>
@@ -23812,6 +24088,9 @@
       <c r="F72" s="5" t="n">
         <v>0.5</v>
       </c>
+      <c r="H72" s="5" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B73" s="1" t="s">
@@ -23827,6 +24106,9 @@
         <v>209</v>
       </c>
       <c r="F73" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="H73" s="1" t="s">
         <v>202</v>
       </c>
     </row>
@@ -23843,7 +24125,7 @@
       <c r="A75" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="B75" s="58" t="s">
+      <c r="B75" s="60" t="s">
         <v>102</v>
       </c>
       <c r="C75" s="17" t="s">
@@ -23891,10 +24173,10 @@
       <c r="Q75" s="31" t="s">
         <v>117</v>
       </c>
-      <c r="R75" s="59" t="s">
+      <c r="R75" s="61" t="s">
         <v>118</v>
       </c>
-      <c r="S75" s="60" t="s">
+      <c r="S75" s="56" t="s">
         <v>150</v>
       </c>
     </row>
@@ -23902,7 +24184,7 @@
       <c r="A76" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B76" s="58" t="n">
+      <c r="B76" s="60" t="n">
         <v>0.5</v>
       </c>
       <c r="C76" s="17" t="n">
@@ -23947,13 +24229,13 @@
       <c r="P76" s="18" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q76" s="61" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R76" s="62" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S76" s="60" t="n">
+      <c r="Q76" s="62" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R76" s="63" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S76" s="56" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -24030,7 +24312,7 @@
       <c r="A80" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B80" s="58" t="n">
+      <c r="B80" s="60" t="n">
         <v>0.006</v>
       </c>
       <c r="C80" s="17" t="n">
@@ -24075,13 +24357,13 @@
       <c r="P80" s="18" t="n">
         <v>0.015</v>
       </c>
-      <c r="Q80" s="61" t="n">
+      <c r="Q80" s="62" t="n">
         <v>0.015</v>
       </c>
-      <c r="R80" s="62" t="n">
+      <c r="R80" s="63" t="n">
         <v>0.015</v>
       </c>
-      <c r="S80" s="60" t="n">
+      <c r="S80" s="56" t="n">
         <v>0.015</v>
       </c>
     </row>
@@ -24089,7 +24371,7 @@
       <c r="A81" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B81" s="58" t="n">
+      <c r="B81" s="60" t="n">
         <v>0.4</v>
       </c>
       <c r="C81" s="17" t="n">
@@ -24134,13 +24416,13 @@
       <c r="P81" s="18" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q81" s="61" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="R81" s="62" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="S81" s="60" t="n">
+      <c r="Q81" s="62" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R81" s="63" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S81" s="56" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -24148,7 +24430,7 @@
       <c r="A82" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B82" s="58" t="n">
+      <c r="B82" s="60" t="n">
         <v>1</v>
       </c>
       <c r="C82" s="17" t="n">
@@ -24193,13 +24475,13 @@
       <c r="P82" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="Q82" s="61" t="n">
-        <v>1</v>
-      </c>
-      <c r="R82" s="62" t="n">
-        <v>1</v>
-      </c>
-      <c r="S82" s="60" t="n">
+      <c r="Q82" s="62" t="n">
+        <v>1</v>
+      </c>
+      <c r="R82" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="S82" s="56" t="n">
         <v>1</v>
       </c>
     </row>
@@ -24207,7 +24489,7 @@
       <c r="A83" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B83" s="58" t="n">
+      <c r="B83" s="60" t="n">
         <v>8</v>
       </c>
       <c r="C83" s="17" t="n">
@@ -24252,13 +24534,13 @@
       <c r="P83" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="Q83" s="61" t="n">
+      <c r="Q83" s="62" t="n">
         <v>8</v>
       </c>
-      <c r="R83" s="62" t="n">
+      <c r="R83" s="63" t="n">
         <v>8</v>
       </c>
-      <c r="S83" s="60" t="n">
+      <c r="S83" s="56" t="n">
         <v>8</v>
       </c>
     </row>
@@ -24266,7 +24548,7 @@
       <c r="A84" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B84" s="58" t="n">
+      <c r="B84" s="60" t="n">
         <v>1.2</v>
       </c>
       <c r="C84" s="17" t="n">
@@ -24311,13 +24593,13 @@
       <c r="P84" s="18" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q84" s="61" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="R84" s="62" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S84" s="60" t="n">
+      <c r="Q84" s="62" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R84" s="63" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S84" s="56" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -24325,7 +24607,7 @@
       <c r="A85" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B85" s="58" t="n">
+      <c r="B85" s="60" t="n">
         <v>0.6</v>
       </c>
       <c r="C85" s="17" t="n">
@@ -24370,13 +24652,13 @@
       <c r="P85" s="18" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q85" s="61" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="R85" s="62" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="S85" s="60" t="n">
+      <c r="Q85" s="62" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R85" s="63" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="S85" s="56" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -24384,7 +24666,7 @@
       <c r="A86" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B86" s="58" t="n">
+      <c r="B86" s="60" t="n">
         <v>15000</v>
       </c>
       <c r="C86" s="17" t="n">
@@ -24429,13 +24711,13 @@
       <c r="P86" s="18" t="n">
         <v>10000</v>
       </c>
-      <c r="Q86" s="61" t="n">
+      <c r="Q86" s="62" t="n">
         <v>10000</v>
       </c>
-      <c r="R86" s="62" t="n">
+      <c r="R86" s="63" t="n">
         <v>10000</v>
       </c>
-      <c r="S86" s="60" t="n">
+      <c r="S86" s="56" t="n">
         <v>10000</v>
       </c>
     </row>
@@ -24489,7 +24771,7 @@
       <c r="A89" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="B89" s="58" t="n">
+      <c r="B89" s="60" t="n">
         <v>4</v>
       </c>
       <c r="C89" s="17" t="n">
@@ -24534,13 +24816,13 @@
       <c r="P89" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="Q89" s="61" t="n">
-        <v>2</v>
-      </c>
-      <c r="R89" s="62" t="n">
-        <v>2</v>
-      </c>
-      <c r="S89" s="60" t="n">
+      <c r="Q89" s="62" t="n">
+        <v>2</v>
+      </c>
+      <c r="R89" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="S89" s="56" t="n">
         <v>2</v>
       </c>
     </row>
@@ -24548,7 +24830,7 @@
       <c r="A90" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="B90" s="58" t="n">
+      <c r="B90" s="60" t="n">
         <v>4</v>
       </c>
       <c r="C90" s="17" t="n">
@@ -24593,13 +24875,13 @@
       <c r="P90" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="Q90" s="61" t="n">
-        <v>2</v>
-      </c>
-      <c r="R90" s="62" t="n">
-        <v>2</v>
-      </c>
-      <c r="S90" s="60" t="n">
+      <c r="Q90" s="62" t="n">
+        <v>2</v>
+      </c>
+      <c r="R90" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="S90" s="56" t="n">
         <v>2</v>
       </c>
     </row>
@@ -24754,7 +25036,7 @@
       <c r="J94" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="K94" s="63" t="s">
+      <c r="K94" s="56" t="s">
         <v>111</v>
       </c>
     </row>
@@ -24789,7 +25071,7 @@
       <c r="J95" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="K95" s="18" t="n">
+      <c r="K95" s="56" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -24869,7 +25151,7 @@
       <c r="J99" s="19" t="n">
         <v>0.04</v>
       </c>
-      <c r="K99" s="18" t="n">
+      <c r="K99" s="56" t="n">
         <v>0.04</v>
       </c>
     </row>
@@ -24904,7 +25186,7 @@
       <c r="J100" s="19" t="n">
         <v>0.4</v>
       </c>
-      <c r="K100" s="18" t="n">
+      <c r="K100" s="56" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -24939,7 +25221,7 @@
       <c r="J101" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="K101" s="18" t="n">
+      <c r="K101" s="56" t="n">
         <v>1</v>
       </c>
     </row>
@@ -24974,7 +25256,7 @@
       <c r="J102" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="K102" s="18" t="n">
+      <c r="K102" s="56" t="n">
         <v>4</v>
       </c>
     </row>
@@ -25009,7 +25291,7 @@
       <c r="J103" s="19" t="n">
         <v>1.2</v>
       </c>
-      <c r="K103" s="18" t="n">
+      <c r="K103" s="56" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -25044,7 +25326,7 @@
       <c r="J104" s="19" t="n">
         <v>0.6</v>
       </c>
-      <c r="K104" s="18" t="n">
+      <c r="K104" s="56" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -25079,7 +25361,7 @@
       <c r="J105" s="19" t="n">
         <v>10000</v>
       </c>
-      <c r="K105" s="18" t="n">
+      <c r="K105" s="56" t="n">
         <v>20000</v>
       </c>
     </row>
@@ -25144,7 +25426,7 @@
       <c r="J108" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="K108" s="18" t="n">
+      <c r="K108" s="56" t="n">
         <v>4</v>
       </c>
     </row>
@@ -25179,7 +25461,7 @@
       <c r="J109" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="K109" s="18" t="n">
+      <c r="K109" s="56" t="n">
         <v>4</v>
       </c>
     </row>
@@ -25255,7 +25537,11 @@
         <v>217</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J113" s="64" t="s">
+        <v>201</v>
+      </c>
+    </row>
     <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="2" t="s">
         <v>218</v>
@@ -25278,11 +25564,14 @@
       <c r="G114" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="H114" s="58" t="s">
+      <c r="H114" s="60" t="s">
         <v>108</v>
       </c>
-      <c r="I114" s="18" t="s">
+      <c r="I114" s="56" t="s">
         <v>109</v>
+      </c>
+      <c r="J114" s="57" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25307,10 +25596,13 @@
       <c r="G115" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="H115" s="58" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I115" s="18" t="n">
+      <c r="H115" s="60" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I115" s="56" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J115" s="57" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -25325,7 +25617,8 @@
       <c r="F116" s="23"/>
       <c r="G116" s="23"/>
       <c r="H116" s="23"/>
-      <c r="I116" s="23"/>
+      <c r="I116" s="40"/>
+      <c r="J116" s="65"/>
     </row>
     <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="2" t="s">
@@ -25338,7 +25631,8 @@
       <c r="F117" s="23"/>
       <c r="G117" s="23"/>
       <c r="H117" s="23"/>
-      <c r="I117" s="23"/>
+      <c r="I117" s="40"/>
+      <c r="J117" s="65"/>
     </row>
     <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="2" t="s">
@@ -25351,7 +25645,8 @@
       <c r="F118" s="23"/>
       <c r="G118" s="23"/>
       <c r="H118" s="23"/>
-      <c r="I118" s="23"/>
+      <c r="I118" s="40"/>
+      <c r="J118" s="65"/>
     </row>
     <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="2" t="s">
@@ -25375,10 +25670,13 @@
       <c r="G119" s="17" t="n">
         <v>0.025</v>
       </c>
-      <c r="H119" s="58" t="n">
+      <c r="H119" s="60" t="n">
         <v>0.025</v>
       </c>
-      <c r="I119" s="18" t="n">
+      <c r="I119" s="56" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="J119" s="57" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -25404,10 +25702,13 @@
       <c r="G120" s="17" t="n">
         <v>0.4</v>
       </c>
-      <c r="H120" s="58" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I120" s="18" t="n">
+      <c r="H120" s="60" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I120" s="56" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J120" s="57" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -25433,10 +25734,13 @@
       <c r="G121" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="H121" s="58" t="n">
-        <v>1</v>
-      </c>
-      <c r="I121" s="18" t="n">
+      <c r="H121" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="I121" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J121" s="57" t="n">
         <v>1</v>
       </c>
     </row>
@@ -25462,10 +25766,13 @@
       <c r="G122" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="H122" s="58" t="n">
+      <c r="H122" s="60" t="n">
         <v>4</v>
       </c>
-      <c r="I122" s="18" t="n">
+      <c r="I122" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="J122" s="57" t="n">
         <v>4</v>
       </c>
     </row>
@@ -25491,10 +25798,13 @@
       <c r="G123" s="17" t="n">
         <v>1.2</v>
       </c>
-      <c r="H123" s="58" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I123" s="18" t="n">
+      <c r="H123" s="60" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I123" s="56" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J123" s="57" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -25520,10 +25830,13 @@
       <c r="G124" s="17" t="n">
         <v>0.6</v>
       </c>
-      <c r="H124" s="58" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I124" s="18" t="n">
+      <c r="H124" s="60" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I124" s="56" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J124" s="57" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -25549,10 +25862,13 @@
       <c r="G125" s="17" t="n">
         <v>10000</v>
       </c>
-      <c r="H125" s="58" t="n">
+      <c r="H125" s="60" t="n">
         <v>10000</v>
       </c>
-      <c r="I125" s="18" t="n">
+      <c r="I125" s="56" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J125" s="57" t="n">
         <v>10000</v>
       </c>
     </row>
@@ -25567,7 +25883,8 @@
       <c r="F126" s="29"/>
       <c r="G126" s="29"/>
       <c r="H126" s="29"/>
-      <c r="I126" s="29"/>
+      <c r="I126" s="33"/>
+      <c r="J126" s="66"/>
     </row>
     <row r="127" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="22" t="s">
@@ -25580,7 +25897,8 @@
       <c r="F127" s="31"/>
       <c r="G127" s="31"/>
       <c r="H127" s="31"/>
-      <c r="I127" s="31"/>
+      <c r="I127" s="33"/>
+      <c r="J127" s="66"/>
     </row>
     <row r="128" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="17" t="s">
@@ -25604,10 +25922,13 @@
       <c r="G128" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="H128" s="58" t="n">
+      <c r="H128" s="60" t="n">
         <v>4</v>
       </c>
-      <c r="I128" s="18" t="n">
+      <c r="I128" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="J128" s="57" t="n">
         <v>4</v>
       </c>
     </row>
@@ -25633,10 +25954,13 @@
       <c r="G129" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="H129" s="58" t="n">
+      <c r="H129" s="60" t="n">
         <v>4</v>
       </c>
-      <c r="I129" s="18" t="n">
+      <c r="I129" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="J129" s="57" t="n">
         <v>4</v>
       </c>
     </row>
@@ -25668,6 +25992,9 @@
       <c r="I130" s="5" t="n">
         <v>0.5</v>
       </c>
+      <c r="J130" s="67" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="131" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B131" s="1" t="s">
@@ -25692,6 +26019,9 @@
         <v>202</v>
       </c>
       <c r="I131" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="J131" s="67" t="s">
         <v>213</v>
       </c>
     </row>
@@ -25773,7 +26103,7 @@
       <c r="T135" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="U135" s="64" t="s">
+      <c r="U135" s="56" t="s">
         <v>152</v>
       </c>
     </row>
@@ -25838,7 +26168,7 @@
       <c r="T136" s="18" t="n">
         <v>0.5</v>
       </c>
-      <c r="U136" s="64" t="n">
+      <c r="U136" s="56" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -25978,7 +26308,7 @@
       <c r="T140" s="18" t="n">
         <v>0.05</v>
       </c>
-      <c r="U140" s="64" t="n">
+      <c r="U140" s="56" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -26043,7 +26373,7 @@
       <c r="T141" s="18" t="n">
         <v>0.4</v>
       </c>
-      <c r="U141" s="64" t="n">
+      <c r="U141" s="56" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -26108,7 +26438,7 @@
       <c r="T142" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="U142" s="64" t="n">
+      <c r="U142" s="56" t="n">
         <v>1</v>
       </c>
     </row>
@@ -26173,7 +26503,7 @@
       <c r="T143" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="U143" s="64" t="n">
+      <c r="U143" s="56" t="n">
         <v>4</v>
       </c>
     </row>
@@ -26226,19 +26556,19 @@
       <c r="P144" s="17" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q144" s="62" t="n">
+      <c r="Q144" s="63" t="n">
         <v>0.8</v>
       </c>
-      <c r="R144" s="62" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S144" s="62" t="n">
+      <c r="R144" s="63" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S144" s="63" t="n">
         <v>0.4</v>
       </c>
       <c r="T144" s="18" t="n">
         <v>0.3</v>
       </c>
-      <c r="U144" s="64" t="n">
+      <c r="U144" s="56" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -26303,7 +26633,7 @@
       <c r="T145" s="18" t="n">
         <v>0.6</v>
       </c>
-      <c r="U145" s="64" t="n">
+      <c r="U145" s="56" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -26368,7 +26698,7 @@
       <c r="T146" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="U146" s="64" t="n">
+      <c r="U146" s="56" t="n">
         <v>12000</v>
       </c>
     </row>
@@ -26483,7 +26813,7 @@
       <c r="T149" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="U149" s="64" t="n">
+      <c r="U149" s="56" t="n">
         <v>2</v>
       </c>
     </row>
@@ -26548,7 +26878,7 @@
       <c r="T150" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="U150" s="64" t="n">
+      <c r="U150" s="56" t="n">
         <v>3</v>
       </c>
     </row>
@@ -26839,10 +27169,10 @@
       <c r="I158" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="J158" s="56" t="s">
+      <c r="J158" s="57" t="s">
         <v>111</v>
       </c>
-      <c r="K158" s="64" t="s">
+      <c r="K158" s="56" t="s">
         <v>112</v>
       </c>
     </row>
@@ -26874,10 +27204,10 @@
       <c r="I159" s="18" t="n">
         <v>0.5</v>
       </c>
-      <c r="J159" s="56" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K159" s="64" t="n">
+      <c r="J159" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K159" s="56" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -26954,10 +27284,10 @@
       <c r="I163" s="18" t="n">
         <v>0.02</v>
       </c>
-      <c r="J163" s="56" t="n">
+      <c r="J163" s="57" t="n">
         <v>0.02</v>
       </c>
-      <c r="K163" s="64" t="n">
+      <c r="K163" s="56" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -26989,10 +27319,10 @@
       <c r="I164" s="18" t="n">
         <v>0.4</v>
       </c>
-      <c r="J164" s="56" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K164" s="64" t="n">
+      <c r="J164" s="57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K164" s="56" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -27024,10 +27354,10 @@
       <c r="I165" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="J165" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="K165" s="64" t="n">
+      <c r="J165" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="K165" s="56" t="n">
         <v>1</v>
       </c>
     </row>
@@ -27059,10 +27389,10 @@
       <c r="I166" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="J166" s="56" t="n">
-        <v>2</v>
-      </c>
-      <c r="K166" s="64" t="n">
+      <c r="J166" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="K166" s="56" t="n">
         <v>2</v>
       </c>
     </row>
@@ -27094,10 +27424,10 @@
       <c r="I167" s="18" t="n">
         <v>1.2</v>
       </c>
-      <c r="J167" s="56" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K167" s="64" t="n">
+      <c r="J167" s="57" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K167" s="56" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -27129,10 +27459,10 @@
       <c r="I168" s="18" t="n">
         <v>0.6</v>
       </c>
-      <c r="J168" s="56" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K168" s="64" t="n">
+      <c r="J168" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K168" s="56" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -27164,10 +27494,10 @@
       <c r="I169" s="18" t="n">
         <v>15000</v>
       </c>
-      <c r="J169" s="56" t="n">
+      <c r="J169" s="57" t="n">
         <v>15000</v>
       </c>
-      <c r="K169" s="64" t="n">
+      <c r="K169" s="56" t="n">
         <v>15000</v>
       </c>
     </row>
@@ -27229,10 +27559,10 @@
       <c r="I172" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="J172" s="56" t="n">
-        <v>2</v>
-      </c>
-      <c r="K172" s="64" t="n">
+      <c r="J172" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="K172" s="56" t="n">
         <v>2</v>
       </c>
     </row>
@@ -27264,10 +27594,10 @@
       <c r="I173" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="J173" s="56" t="n">
-        <v>2</v>
-      </c>
-      <c r="K173" s="64" t="n">
+      <c r="J173" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="K173" s="56" t="n">
         <v>2</v>
       </c>
     </row>
@@ -27427,7 +27757,7 @@
       <c r="E180" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="F180" s="56" t="s">
+      <c r="F180" s="57" t="s">
         <v>106</v>
       </c>
     </row>
@@ -27447,7 +27777,7 @@
       <c r="E181" s="27" t="n">
         <v>0.5</v>
       </c>
-      <c r="F181" s="56" t="n">
+      <c r="F181" s="57" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -27497,7 +27827,7 @@
       <c r="E185" s="27" t="n">
         <v>0.015</v>
       </c>
-      <c r="F185" s="56" t="n">
+      <c r="F185" s="57" t="n">
         <v>0.015</v>
       </c>
     </row>
@@ -27517,7 +27847,7 @@
       <c r="E186" s="27" t="n">
         <v>0.4</v>
       </c>
-      <c r="F186" s="56" t="n">
+      <c r="F186" s="57" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -27537,7 +27867,7 @@
       <c r="E187" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="F187" s="56" t="n">
+      <c r="F187" s="57" t="n">
         <v>1</v>
       </c>
     </row>
@@ -27557,7 +27887,7 @@
       <c r="E188" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="F188" s="56" t="n">
+      <c r="F188" s="57" t="n">
         <v>6</v>
       </c>
     </row>
@@ -27577,7 +27907,7 @@
       <c r="E189" s="27" t="n">
         <v>1.2</v>
       </c>
-      <c r="F189" s="56" t="n">
+      <c r="F189" s="57" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -27597,7 +27927,7 @@
       <c r="E190" s="27" t="n">
         <v>0.6</v>
       </c>
-      <c r="F190" s="56" t="n">
+      <c r="F190" s="57" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -27617,7 +27947,7 @@
       <c r="E191" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="F191" s="56" t="n">
+      <c r="F191" s="57" t="n">
         <v>10000</v>
       </c>
     </row>
@@ -27657,7 +27987,7 @@
       <c r="E194" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="F194" s="56" t="n">
+      <c r="F194" s="57" t="n">
         <v>2</v>
       </c>
     </row>
@@ -27677,7 +28007,7 @@
       <c r="E195" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="F195" s="56" t="n">
+      <c r="F195" s="57" t="n">
         <v>2</v>
       </c>
     </row>
@@ -27719,10 +28049,10 @@
       </c>
     </row>
     <row r="198" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E198" s="65" t="s">
+      <c r="E198" s="68" t="s">
         <v>222</v>
       </c>
-      <c r="F198" s="65" t="s">
+      <c r="F198" s="68" t="s">
         <v>223</v>
       </c>
     </row>
@@ -27797,7 +28127,7 @@
       <c r="H203" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="I203" s="56" t="s">
+      <c r="I203" s="57" t="s">
         <v>109</v>
       </c>
     </row>
@@ -27826,7 +28156,7 @@
       <c r="H204" s="27" t="n">
         <v>0.5</v>
       </c>
-      <c r="I204" s="56" t="n">
+      <c r="I204" s="57" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -27894,7 +28224,7 @@
       <c r="H208" s="27" t="n">
         <v>0.005</v>
       </c>
-      <c r="I208" s="56" t="n">
+      <c r="I208" s="57" t="n">
         <v>0.005</v>
       </c>
     </row>
@@ -27923,7 +28253,7 @@
       <c r="H209" s="27" t="n">
         <v>0.4</v>
       </c>
-      <c r="I209" s="56" t="n">
+      <c r="I209" s="57" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -27952,7 +28282,7 @@
       <c r="H210" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="I210" s="56" t="n">
+      <c r="I210" s="57" t="n">
         <v>1</v>
       </c>
     </row>
@@ -27981,7 +28311,7 @@
       <c r="H211" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="I211" s="56" t="n">
+      <c r="I211" s="57" t="n">
         <v>9</v>
       </c>
     </row>
@@ -28010,7 +28340,7 @@
       <c r="H212" s="27" t="n">
         <v>1.2</v>
       </c>
-      <c r="I212" s="56" t="n">
+      <c r="I212" s="57" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -28039,7 +28369,7 @@
       <c r="H213" s="27" t="n">
         <v>0.6</v>
       </c>
-      <c r="I213" s="56" t="n">
+      <c r="I213" s="57" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -28068,7 +28398,7 @@
       <c r="H214" s="27" t="n">
         <v>27000</v>
       </c>
-      <c r="I214" s="56" t="n">
+      <c r="I214" s="57" t="n">
         <v>27000</v>
       </c>
     </row>
@@ -28123,7 +28453,7 @@
       <c r="H217" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="I217" s="56" t="n">
+      <c r="I217" s="57" t="n">
         <v>2</v>
       </c>
     </row>
@@ -28152,7 +28482,7 @@
       <c r="H218" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="I218" s="56" t="n">
+      <c r="I218" s="57" t="n">
         <v>2</v>
       </c>
     </row>
@@ -28291,10 +28621,10 @@
       <c r="E225" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="F225" s="66" t="s">
+      <c r="F225" s="69" t="s">
         <v>228</v>
       </c>
-      <c r="J225" s="56" t="s">
+      <c r="J225" s="57" t="s">
         <v>107</v>
       </c>
     </row>
@@ -28632,7 +28962,7 @@
       <c r="G247" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="H247" s="67" t="s">
+      <c r="H247" s="24" t="s">
         <v>201</v>
       </c>
     </row>
@@ -28658,7 +28988,7 @@
       <c r="G248" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="H248" s="56" t="s">
+      <c r="H248" s="57" t="s">
         <v>108</v>
       </c>
     </row>
@@ -28684,7 +29014,7 @@
       <c r="G249" s="27" t="n">
         <v>0.5</v>
       </c>
-      <c r="H249" s="56" t="n">
+      <c r="H249" s="57" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -28746,7 +29076,7 @@
       <c r="G253" s="27" t="n">
         <v>0.004</v>
       </c>
-      <c r="H253" s="56" t="n">
+      <c r="H253" s="57" t="n">
         <v>0.004</v>
       </c>
     </row>
@@ -28772,7 +29102,7 @@
       <c r="G254" s="27" t="n">
         <v>0.4</v>
       </c>
-      <c r="H254" s="56" t="n">
+      <c r="H254" s="57" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -28798,7 +29128,7 @@
       <c r="G255" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="H255" s="56" t="n">
+      <c r="H255" s="57" t="n">
         <v>1</v>
       </c>
     </row>
@@ -28824,7 +29154,7 @@
       <c r="G256" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="H256" s="56" t="n">
+      <c r="H256" s="57" t="n">
         <v>4</v>
       </c>
     </row>
@@ -28850,7 +29180,7 @@
       <c r="G257" s="27" t="n">
         <v>1.2</v>
       </c>
-      <c r="H257" s="56" t="n">
+      <c r="H257" s="57" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -28876,7 +29206,7 @@
       <c r="G258" s="27" t="n">
         <v>0.6</v>
       </c>
-      <c r="H258" s="56" t="n">
+      <c r="H258" s="57" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -28902,7 +29232,7 @@
       <c r="G259" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="H259" s="56" t="n">
+      <c r="H259" s="57" t="n">
         <v>10000</v>
       </c>
     </row>
@@ -28952,7 +29282,7 @@
       <c r="G262" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="H262" s="56" t="n">
+      <c r="H262" s="57" t="n">
         <v>3</v>
       </c>
     </row>
@@ -28978,7 +29308,7 @@
       <c r="G263" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="H263" s="56" t="n">
+      <c r="H263" s="57" t="n">
         <v>3</v>
       </c>
     </row>
@@ -29129,10 +29459,10 @@
       <c r="G270" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="H270" s="56" t="s">
+      <c r="H270" s="57" t="s">
         <v>108</v>
       </c>
-      <c r="I270" s="67" t="s">
+      <c r="I270" s="24" t="s">
         <v>201</v>
       </c>
     </row>
@@ -29158,7 +29488,7 @@
       <c r="G271" s="27" t="n">
         <v>0.5</v>
       </c>
-      <c r="H271" s="56" t="n">
+      <c r="H271" s="57" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -29220,7 +29550,7 @@
       <c r="G275" s="27" t="n">
         <v>0.003</v>
       </c>
-      <c r="H275" s="56" t="n">
+      <c r="H275" s="57" t="n">
         <v>0.003</v>
       </c>
     </row>
@@ -29246,7 +29576,7 @@
       <c r="G276" s="27" t="n">
         <v>0.4</v>
       </c>
-      <c r="H276" s="56" t="n">
+      <c r="H276" s="57" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -29272,7 +29602,7 @@
       <c r="G277" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="H277" s="56" t="n">
+      <c r="H277" s="57" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29298,7 +29628,7 @@
       <c r="G278" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="H278" s="56" t="n">
+      <c r="H278" s="57" t="n">
         <v>10</v>
       </c>
     </row>
@@ -29324,7 +29654,7 @@
       <c r="G279" s="27" t="n">
         <v>1.2</v>
       </c>
-      <c r="H279" s="56" t="n">
+      <c r="H279" s="57" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -29350,7 +29680,7 @@
       <c r="G280" s="27" t="n">
         <v>0.6</v>
       </c>
-      <c r="H280" s="56" t="n">
+      <c r="H280" s="57" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -29376,7 +29706,7 @@
       <c r="G281" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="H281" s="56" t="n">
+      <c r="H281" s="57" t="n">
         <v>10000</v>
       </c>
     </row>
@@ -29426,7 +29756,7 @@
       <c r="G284" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="H284" s="56" t="n">
+      <c r="H284" s="57" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29452,7 +29782,7 @@
       <c r="G285" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="H285" s="56" t="n">
+      <c r="H285" s="57" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29506,7 +29836,7 @@
       </c>
     </row>
     <row r="288" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N288" s="68"/>
+      <c r="N288" s="69"/>
     </row>
     <row r="289" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B289" s="1" t="n">
@@ -29588,7 +29918,7 @@
       <c r="I291" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="J291" s="67" t="s">
+      <c r="J291" s="24" t="s">
         <v>201</v>
       </c>
     </row>
@@ -29620,7 +29950,7 @@
       <c r="I292" s="27" t="s">
         <v>109</v>
       </c>
-      <c r="J292" s="56" t="s">
+      <c r="J292" s="57" t="s">
         <v>110</v>
       </c>
     </row>
@@ -29652,7 +29982,7 @@
       <c r="I293" s="27" t="n">
         <v>0.5</v>
       </c>
-      <c r="J293" s="56" t="n">
+      <c r="J293" s="57" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -29726,7 +30056,7 @@
       <c r="I297" s="27" t="n">
         <v>0.02</v>
       </c>
-      <c r="J297" s="56" t="n">
+      <c r="J297" s="57" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -29758,7 +30088,7 @@
       <c r="I298" s="27" t="n">
         <v>0.4</v>
       </c>
-      <c r="J298" s="56" t="n">
+      <c r="J298" s="57" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -29790,7 +30120,7 @@
       <c r="I299" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="J299" s="56" t="n">
+      <c r="J299" s="57" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29822,7 +30152,7 @@
       <c r="I300" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="J300" s="56" t="n">
+      <c r="J300" s="57" t="n">
         <v>5</v>
       </c>
     </row>
@@ -29854,7 +30184,7 @@
       <c r="I301" s="27" t="n">
         <v>1.2</v>
       </c>
-      <c r="J301" s="56" t="n">
+      <c r="J301" s="57" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -29886,7 +30216,7 @@
       <c r="I302" s="27" t="n">
         <v>0.6</v>
       </c>
-      <c r="J302" s="56" t="n">
+      <c r="J302" s="57" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -29918,7 +30248,7 @@
       <c r="I303" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="J303" s="56" t="n">
+      <c r="J303" s="57" t="n">
         <v>10000</v>
       </c>
     </row>
@@ -29978,7 +30308,7 @@
       <c r="I306" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="J306" s="56" t="n">
+      <c r="J306" s="57" t="n">
         <v>2</v>
       </c>
     </row>
@@ -30010,7 +30340,7 @@
       <c r="I307" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="J307" s="56" t="n">
+      <c r="J307" s="57" t="n">
         <v>2</v>
       </c>
     </row>
@@ -30170,7 +30500,7 @@
       </c>
     </row>
     <row r="314" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A314" s="69" t="s">
+      <c r="A314" s="70" t="s">
         <v>234</v>
       </c>
       <c r="B314" s="17" t="s">
@@ -30184,7 +30514,7 @@
       </c>
     </row>
     <row r="315" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A315" s="69" t="s">
+      <c r="A315" s="70" t="s">
         <v>80</v>
       </c>
       <c r="B315" s="17" t="n">
@@ -30195,28 +30525,28 @@
       </c>
     </row>
     <row r="316" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A316" s="69" t="s">
+      <c r="A316" s="70" t="s">
         <v>120</v>
       </c>
       <c r="B316" s="23"/>
       <c r="C316" s="23"/>
     </row>
     <row r="317" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A317" s="69" t="s">
+      <c r="A317" s="70" t="s">
         <v>82</v>
       </c>
       <c r="B317" s="23"/>
       <c r="C317" s="23"/>
     </row>
     <row r="318" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A318" s="69" t="s">
+      <c r="A318" s="70" t="s">
         <v>121</v>
       </c>
       <c r="B318" s="23"/>
       <c r="C318" s="23"/>
     </row>
     <row r="319" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A319" s="69" t="s">
+      <c r="A319" s="70" t="s">
         <v>84</v>
       </c>
       <c r="B319" s="17" t="n">
@@ -30227,7 +30557,7 @@
       </c>
     </row>
     <row r="320" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A320" s="69" t="s">
+      <c r="A320" s="70" t="s">
         <v>79</v>
       </c>
       <c r="B320" s="17" t="n">
@@ -30238,7 +30568,7 @@
       </c>
     </row>
     <row r="321" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A321" s="69" t="s">
+      <c r="A321" s="70" t="s">
         <v>85</v>
       </c>
       <c r="B321" s="17" t="n">
@@ -30249,7 +30579,7 @@
       </c>
     </row>
     <row r="322" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A322" s="69" t="s">
+      <c r="A322" s="70" t="s">
         <v>122</v>
       </c>
       <c r="B322" s="17" t="n">
@@ -30260,7 +30590,7 @@
       </c>
     </row>
     <row r="323" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A323" s="69" t="s">
+      <c r="A323" s="70" t="s">
         <v>123</v>
       </c>
       <c r="B323" s="17" t="n">
@@ -30271,7 +30601,7 @@
       </c>
     </row>
     <row r="324" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A324" s="69" t="s">
+      <c r="A324" s="70" t="s">
         <v>124</v>
       </c>
       <c r="B324" s="17" t="n">
@@ -30282,7 +30612,7 @@
       </c>
     </row>
     <row r="325" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A325" s="69" t="s">
+      <c r="A325" s="70" t="s">
         <v>125</v>
       </c>
       <c r="B325" s="17" t="n">
@@ -30293,21 +30623,21 @@
       </c>
     </row>
     <row r="326" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A326" s="69" t="s">
+      <c r="A326" s="70" t="s">
         <v>126</v>
       </c>
       <c r="B326" s="29"/>
       <c r="C326" s="29"/>
     </row>
     <row r="327" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A327" s="70" t="s">
+      <c r="A327" s="71" t="s">
         <v>128</v>
       </c>
       <c r="B327" s="31"/>
       <c r="C327" s="31"/>
     </row>
     <row r="328" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A328" s="69" t="s">
+      <c r="A328" s="70" t="s">
         <v>134</v>
       </c>
       <c r="B328" s="17" t="n">
@@ -30318,7 +30648,7 @@
       </c>
     </row>
     <row r="329" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A329" s="69" t="s">
+      <c r="A329" s="70" t="s">
         <v>136</v>
       </c>
       <c r="B329" s="17" t="n">
@@ -30329,7 +30659,7 @@
       </c>
     </row>
     <row r="330" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A330" s="71" t="s">
+      <c r="A330" s="72" t="s">
         <v>157</v>
       </c>
       <c r="B330" s="5" t="n">
@@ -30379,7 +30709,7 @@
       </c>
     </row>
     <row r="336" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A336" s="69" t="s">
+      <c r="A336" s="70" t="s">
         <v>236</v>
       </c>
       <c r="B336" s="17" t="s">
@@ -30387,7 +30717,7 @@
       </c>
     </row>
     <row r="337" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A337" s="69" t="s">
+      <c r="A337" s="70" t="s">
         <v>80</v>
       </c>
       <c r="B337" s="17" t="n">
@@ -30395,25 +30725,25 @@
       </c>
     </row>
     <row r="338" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A338" s="69" t="s">
+      <c r="A338" s="70" t="s">
         <v>120</v>
       </c>
       <c r="B338" s="23"/>
     </row>
     <row r="339" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A339" s="69" t="s">
+      <c r="A339" s="70" t="s">
         <v>82</v>
       </c>
       <c r="B339" s="23"/>
     </row>
     <row r="340" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A340" s="69" t="s">
+      <c r="A340" s="70" t="s">
         <v>121</v>
       </c>
       <c r="B340" s="23"/>
     </row>
     <row r="341" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A341" s="69" t="s">
+      <c r="A341" s="70" t="s">
         <v>84</v>
       </c>
       <c r="B341" s="17" t="n">
@@ -30421,7 +30751,7 @@
       </c>
     </row>
     <row r="342" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A342" s="69" t="s">
+      <c r="A342" s="70" t="s">
         <v>79</v>
       </c>
       <c r="B342" s="17" t="n">
@@ -30429,7 +30759,7 @@
       </c>
     </row>
     <row r="343" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A343" s="69" t="s">
+      <c r="A343" s="70" t="s">
         <v>85</v>
       </c>
       <c r="B343" s="17" t="n">
@@ -30437,7 +30767,7 @@
       </c>
     </row>
     <row r="344" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A344" s="69" t="s">
+      <c r="A344" s="70" t="s">
         <v>122</v>
       </c>
       <c r="B344" s="17" t="n">
@@ -30445,7 +30775,7 @@
       </c>
     </row>
     <row r="345" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A345" s="69" t="s">
+      <c r="A345" s="70" t="s">
         <v>123</v>
       </c>
       <c r="B345" s="17" t="n">
@@ -30453,7 +30783,7 @@
       </c>
     </row>
     <row r="346" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A346" s="69" t="s">
+      <c r="A346" s="70" t="s">
         <v>124</v>
       </c>
       <c r="B346" s="17" t="n">
@@ -30461,7 +30791,7 @@
       </c>
     </row>
     <row r="347" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A347" s="69" t="s">
+      <c r="A347" s="70" t="s">
         <v>125</v>
       </c>
       <c r="B347" s="17" t="n">
@@ -30469,19 +30799,19 @@
       </c>
     </row>
     <row r="348" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A348" s="69" t="s">
+      <c r="A348" s="70" t="s">
         <v>126</v>
       </c>
       <c r="B348" s="29"/>
     </row>
     <row r="349" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A349" s="70" t="s">
+      <c r="A349" s="71" t="s">
         <v>128</v>
       </c>
       <c r="B349" s="31"/>
     </row>
     <row r="350" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A350" s="69" t="s">
+      <c r="A350" s="70" t="s">
         <v>134</v>
       </c>
       <c r="B350" s="17" t="n">
@@ -30489,7 +30819,7 @@
       </c>
     </row>
     <row r="351" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A351" s="69" t="s">
+      <c r="A351" s="70" t="s">
         <v>136</v>
       </c>
       <c r="B351" s="17" t="n">
@@ -30497,7 +30827,7 @@
       </c>
     </row>
     <row r="352" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A352" s="71" t="s">
+      <c r="A352" s="72" t="s">
         <v>157</v>
       </c>
       <c r="B352" s="5" t="n">
@@ -30530,7 +30860,7 @@
       <c r="B357" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="G357" s="67" t="s">
+      <c r="G357" s="24" t="s">
         <v>237</v>
       </c>
     </row>
@@ -30553,7 +30883,7 @@
       <c r="F358" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="G358" s="56" t="s">
+      <c r="G358" s="57" t="s">
         <v>107</v>
       </c>
     </row>
@@ -30576,7 +30906,7 @@
       <c r="F359" s="18" t="n">
         <v>0.5</v>
       </c>
-      <c r="G359" s="56" t="n">
+      <c r="G359" s="57" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -30632,7 +30962,7 @@
       <c r="F363" s="18" t="n">
         <v>0.008</v>
       </c>
-      <c r="G363" s="56" t="n">
+      <c r="G363" s="57" t="n">
         <v>0.008</v>
       </c>
     </row>
@@ -30655,7 +30985,7 @@
       <c r="F364" s="18" t="n">
         <v>0.4</v>
       </c>
-      <c r="G364" s="56" t="n">
+      <c r="G364" s="57" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -30678,7 +31008,7 @@
       <c r="F365" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G365" s="56" t="n">
+      <c r="G365" s="57" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30701,7 +31031,7 @@
       <c r="F366" s="18" t="n">
         <v>9</v>
       </c>
-      <c r="G366" s="56" t="n">
+      <c r="G366" s="57" t="n">
         <v>9</v>
       </c>
     </row>
@@ -30724,7 +31054,7 @@
       <c r="F367" s="18" t="n">
         <v>1.2</v>
       </c>
-      <c r="G367" s="56" t="n">
+      <c r="G367" s="57" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -30747,7 +31077,7 @@
       <c r="F368" s="18" t="n">
         <v>0.6</v>
       </c>
-      <c r="G368" s="56" t="n">
+      <c r="G368" s="57" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -30770,7 +31100,7 @@
       <c r="F369" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="G369" s="56" t="n">
+      <c r="G369" s="57" t="n">
         <v>12000</v>
       </c>
     </row>
@@ -30815,7 +31145,7 @@
       <c r="F372" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="G372" s="56" t="n">
+      <c r="G372" s="57" t="n">
         <v>4</v>
       </c>
     </row>
@@ -30838,7 +31168,7 @@
       <c r="F373" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="G373" s="56" t="n">
+      <c r="G373" s="57" t="n">
         <v>4</v>
       </c>
     </row>
@@ -30965,7 +31295,7 @@
       <c r="D380" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="E380" s="56" t="s">
+      <c r="E380" s="57" t="s">
         <v>105</v>
       </c>
     </row>
@@ -30982,7 +31312,7 @@
       <c r="D381" s="27" t="n">
         <v>0.5</v>
       </c>
-      <c r="E381" s="56" t="n">
+      <c r="E381" s="57" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -31026,7 +31356,7 @@
       <c r="D385" s="27" t="n">
         <v>0.005</v>
       </c>
-      <c r="E385" s="56" t="n">
+      <c r="E385" s="57" t="n">
         <v>0.005</v>
       </c>
     </row>
@@ -31043,7 +31373,7 @@
       <c r="D386" s="27" t="n">
         <v>0.4</v>
       </c>
-      <c r="E386" s="56" t="n">
+      <c r="E386" s="57" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -31060,7 +31390,7 @@
       <c r="D387" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="E387" s="56" t="n">
+      <c r="E387" s="57" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31077,7 +31407,7 @@
       <c r="D388" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="E388" s="56" t="n">
+      <c r="E388" s="57" t="n">
         <v>3</v>
       </c>
     </row>
@@ -31094,7 +31424,7 @@
       <c r="D389" s="27" t="n">
         <v>1.2</v>
       </c>
-      <c r="E389" s="56" t="n">
+      <c r="E389" s="57" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -31111,7 +31441,7 @@
       <c r="D390" s="27" t="n">
         <v>0.6</v>
       </c>
-      <c r="E390" s="56" t="n">
+      <c r="E390" s="57" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -31128,7 +31458,7 @@
       <c r="D391" s="27" t="n">
         <v>25000</v>
       </c>
-      <c r="E391" s="56" t="n">
+      <c r="E391" s="57" t="n">
         <v>25000</v>
       </c>
     </row>
@@ -31163,7 +31493,7 @@
       <c r="D394" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="E394" s="56" t="n">
+      <c r="E394" s="57" t="n">
         <v>2</v>
       </c>
     </row>
@@ -31180,7 +31510,7 @@
       <c r="D395" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="E395" s="56" t="n">
+      <c r="E395" s="57" t="n">
         <v>2</v>
       </c>
     </row>
@@ -31216,7 +31546,7 @@
       </c>
     </row>
     <row r="398" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E398" s="67" t="s">
+      <c r="E398" s="24" t="s">
         <v>201</v>
       </c>
     </row>
@@ -31258,7 +31588,7 @@
       <c r="B401" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="K401" s="67" t="s">
+      <c r="K401" s="24" t="s">
         <v>201</v>
       </c>
     </row>
@@ -31293,7 +31623,7 @@
       <c r="J402" s="27" t="s">
         <v>110</v>
       </c>
-      <c r="K402" s="56" t="s">
+      <c r="K402" s="57" t="s">
         <v>111</v>
       </c>
     </row>
@@ -31328,7 +31658,7 @@
       <c r="J403" s="27" t="n">
         <v>0.5</v>
       </c>
-      <c r="K403" s="56" t="n">
+      <c r="K403" s="57" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -31408,7 +31738,7 @@
       <c r="J407" s="27" t="n">
         <v>0.00425</v>
       </c>
-      <c r="K407" s="56" t="n">
+      <c r="K407" s="57" t="n">
         <v>0.00425</v>
       </c>
     </row>
@@ -31443,7 +31773,7 @@
       <c r="J408" s="27" t="n">
         <v>0.4</v>
       </c>
-      <c r="K408" s="56" t="n">
+      <c r="K408" s="57" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -31478,7 +31808,7 @@
       <c r="J409" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="K409" s="56" t="n">
+      <c r="K409" s="57" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31513,7 +31843,7 @@
       <c r="J410" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="K410" s="56" t="n">
+      <c r="K410" s="57" t="n">
         <v>6</v>
       </c>
     </row>
@@ -31548,7 +31878,7 @@
       <c r="J411" s="27" t="n">
         <v>1.2</v>
       </c>
-      <c r="K411" s="56" t="n">
+      <c r="K411" s="57" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -31583,7 +31913,7 @@
       <c r="J412" s="27" t="n">
         <v>0.6</v>
       </c>
-      <c r="K412" s="56" t="n">
+      <c r="K412" s="57" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -31618,7 +31948,7 @@
       <c r="J413" s="27" t="n">
         <v>25000</v>
       </c>
-      <c r="K413" s="56" t="n">
+      <c r="K413" s="57" t="n">
         <v>25000</v>
       </c>
     </row>
@@ -31683,7 +32013,7 @@
       <c r="J416" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="K416" s="56" t="n">
+      <c r="K416" s="57" t="n">
         <v>5</v>
       </c>
     </row>
@@ -31718,7 +32048,7 @@
       <c r="J417" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="K417" s="56" t="n">
+      <c r="K417" s="57" t="n">
         <v>5</v>
       </c>
     </row>

--- a/parameters script.xlsx
+++ b/parameters script.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2004" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2019" uniqueCount="243">
   <si>
     <t xml:space="preserve">6h 3</t>
   </si>
@@ -720,6 +720,12 @@
     <t xml:space="preserve">18H-3-VAMP7</t>
   </si>
   <si>
+    <t xml:space="preserve">25-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T25</t>
+  </si>
+  <si>
     <t xml:space="preserve">*1</t>
   </si>
   <si>
@@ -1092,7 +1098,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="72">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1349,10 +1355,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1468,9 +1470,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>459360</xdr:colOff>
+      <xdr:colOff>459000</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>16560</xdr:rowOff>
+      <xdr:rowOff>16200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1484,7 +1486,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6183720" y="130320"/>
-          <a:ext cx="7980120" cy="252000"/>
+          <a:ext cx="7979760" cy="251640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1511,9 +1513,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>213480</xdr:colOff>
+      <xdr:colOff>213120</xdr:colOff>
       <xdr:row>85</xdr:row>
-      <xdr:rowOff>19800</xdr:rowOff>
+      <xdr:rowOff>19440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1527,7 +1529,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="10345680" y="13525560"/>
-          <a:ext cx="10139040" cy="2039040"/>
+          <a:ext cx="10138680" cy="2038680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1549,9 +1551,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>878400</xdr:colOff>
+      <xdr:colOff>878040</xdr:colOff>
       <xdr:row>121</xdr:row>
-      <xdr:rowOff>132120</xdr:rowOff>
+      <xdr:rowOff>131760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1565,7 +1567,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6275880" y="20154960"/>
-          <a:ext cx="10175760" cy="2105640"/>
+          <a:ext cx="10175400" cy="2105280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -22269,7 +22271,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:U423"/>
+  <dimension ref="A1:Z423"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25538,7 +25540,7 @@
       </c>
     </row>
     <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J113" s="64" t="s">
+      <c r="J113" s="24" t="s">
         <v>201</v>
       </c>
     </row>
@@ -25618,7 +25620,7 @@
       <c r="G116" s="23"/>
       <c r="H116" s="23"/>
       <c r="I116" s="40"/>
-      <c r="J116" s="65"/>
+      <c r="J116" s="64"/>
     </row>
     <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="2" t="s">
@@ -25632,7 +25634,7 @@
       <c r="G117" s="23"/>
       <c r="H117" s="23"/>
       <c r="I117" s="40"/>
-      <c r="J117" s="65"/>
+      <c r="J117" s="64"/>
     </row>
     <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="2" t="s">
@@ -25646,7 +25648,7 @@
       <c r="G118" s="23"/>
       <c r="H118" s="23"/>
       <c r="I118" s="40"/>
-      <c r="J118" s="65"/>
+      <c r="J118" s="64"/>
     </row>
     <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="2" t="s">
@@ -25884,7 +25886,7 @@
       <c r="G126" s="29"/>
       <c r="H126" s="29"/>
       <c r="I126" s="33"/>
-      <c r="J126" s="66"/>
+      <c r="J126" s="65"/>
     </row>
     <row r="127" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="22" t="s">
@@ -25898,7 +25900,7 @@
       <c r="G127" s="31"/>
       <c r="H127" s="31"/>
       <c r="I127" s="33"/>
-      <c r="J127" s="66"/>
+      <c r="J127" s="65"/>
     </row>
     <row r="128" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="17" t="s">
@@ -25992,7 +25994,7 @@
       <c r="I130" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="J130" s="67" t="n">
+      <c r="J130" s="66" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -26021,7 +26023,7 @@
       <c r="I131" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="J131" s="67" t="s">
+      <c r="J131" s="66" t="s">
         <v>213</v>
       </c>
     </row>
@@ -26041,6 +26043,21 @@
       <c r="U134" s="24" t="s">
         <v>201</v>
       </c>
+      <c r="V134" s="24" t="s">
+        <v>219</v>
+      </c>
+      <c r="W134" s="24" t="s">
+        <v>219</v>
+      </c>
+      <c r="X134" s="24" t="s">
+        <v>219</v>
+      </c>
+      <c r="Y134" s="24" t="s">
+        <v>219</v>
+      </c>
+      <c r="Z134" s="24" t="s">
+        <v>219</v>
+      </c>
     </row>
     <row r="135" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="2" t="s">
@@ -26103,8 +26120,23 @@
       <c r="T135" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="U135" s="56" t="s">
+      <c r="U135" s="57" t="s">
         <v>152</v>
+      </c>
+      <c r="V135" s="57" t="s">
+        <v>153</v>
+      </c>
+      <c r="W135" s="57" t="s">
+        <v>154</v>
+      </c>
+      <c r="X135" s="57" t="s">
+        <v>155</v>
+      </c>
+      <c r="Y135" s="57" t="s">
+        <v>156</v>
+      </c>
+      <c r="Z135" s="56" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26168,7 +26200,22 @@
       <c r="T136" s="18" t="n">
         <v>0.5</v>
       </c>
-      <c r="U136" s="56" t="n">
+      <c r="U136" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V136" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W136" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X136" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y136" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z136" s="56" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -26196,6 +26243,11 @@
       <c r="S137" s="23"/>
       <c r="T137" s="23"/>
       <c r="U137" s="23"/>
+      <c r="V137" s="23"/>
+      <c r="W137" s="23"/>
+      <c r="X137" s="23"/>
+      <c r="Y137" s="23"/>
+      <c r="Z137" s="23"/>
     </row>
     <row r="138" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="2" t="s">
@@ -26221,6 +26273,11 @@
       <c r="S138" s="23"/>
       <c r="T138" s="23"/>
       <c r="U138" s="23"/>
+      <c r="V138" s="23"/>
+      <c r="W138" s="23"/>
+      <c r="X138" s="23"/>
+      <c r="Y138" s="23"/>
+      <c r="Z138" s="23"/>
     </row>
     <row r="139" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="2" t="s">
@@ -26246,6 +26303,11 @@
       <c r="S139" s="23"/>
       <c r="T139" s="23"/>
       <c r="U139" s="23"/>
+      <c r="V139" s="23"/>
+      <c r="W139" s="23"/>
+      <c r="X139" s="23"/>
+      <c r="Y139" s="23"/>
+      <c r="Z139" s="23"/>
     </row>
     <row r="140" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="2" t="s">
@@ -26308,7 +26370,22 @@
       <c r="T140" s="18" t="n">
         <v>0.05</v>
       </c>
-      <c r="U140" s="56" t="n">
+      <c r="U140" s="57" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="V140" s="57" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="W140" s="57" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X140" s="57" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Y140" s="57" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Z140" s="56" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -26373,7 +26450,22 @@
       <c r="T141" s="18" t="n">
         <v>0.4</v>
       </c>
-      <c r="U141" s="56" t="n">
+      <c r="U141" s="57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="V141" s="57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W141" s="57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="X141" s="57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y141" s="57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z141" s="56" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -26438,7 +26530,22 @@
       <c r="T142" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="U142" s="56" t="n">
+      <c r="U142" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="V142" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="W142" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="X142" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y142" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z142" s="56" t="n">
         <v>1</v>
       </c>
     </row>
@@ -26503,8 +26610,23 @@
       <c r="T143" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="U143" s="56" t="n">
+      <c r="U143" s="57" t="n">
         <v>4</v>
+      </c>
+      <c r="V143" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W143" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="X143" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y143" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z143" s="56" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26568,7 +26690,22 @@
       <c r="T144" s="18" t="n">
         <v>0.3</v>
       </c>
-      <c r="U144" s="56" t="n">
+      <c r="U144" s="57" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V144" s="57" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W144" s="57" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="X144" s="57" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y144" s="57" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Z144" s="56" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -26633,7 +26770,22 @@
       <c r="T145" s="18" t="n">
         <v>0.6</v>
       </c>
-      <c r="U145" s="56" t="n">
+      <c r="U145" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="V145" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="W145" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="X145" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Y145" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Z145" s="56" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -26698,8 +26850,23 @@
       <c r="T146" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="U146" s="56" t="n">
+      <c r="U146" s="57" t="n">
         <v>12000</v>
+      </c>
+      <c r="V146" s="57" t="n">
+        <v>2000</v>
+      </c>
+      <c r="W146" s="57" t="n">
+        <v>5000</v>
+      </c>
+      <c r="X146" s="57" t="n">
+        <v>5000</v>
+      </c>
+      <c r="Y146" s="57" t="n">
+        <v>5000</v>
+      </c>
+      <c r="Z146" s="56" t="n">
+        <v>5000</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26726,6 +26893,11 @@
       <c r="S147" s="29"/>
       <c r="T147" s="29"/>
       <c r="U147" s="29"/>
+      <c r="V147" s="29"/>
+      <c r="W147" s="29"/>
+      <c r="X147" s="29"/>
+      <c r="Y147" s="29"/>
+      <c r="Z147" s="29"/>
     </row>
     <row r="148" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="22" t="s">
@@ -26751,6 +26923,11 @@
       <c r="S148" s="31"/>
       <c r="T148" s="31"/>
       <c r="U148" s="31"/>
+      <c r="V148" s="31"/>
+      <c r="W148" s="31"/>
+      <c r="X148" s="31"/>
+      <c r="Y148" s="31"/>
+      <c r="Z148" s="31"/>
     </row>
     <row r="149" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="17" t="s">
@@ -26813,8 +26990,23 @@
       <c r="T149" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="U149" s="56" t="n">
-        <v>2</v>
+      <c r="U149" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="V149" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="W149" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="X149" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y149" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z149" s="56" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26878,8 +27070,23 @@
       <c r="T150" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="U150" s="56" t="n">
+      <c r="U150" s="57" t="n">
         <v>3</v>
+      </c>
+      <c r="V150" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="W150" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="X150" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y150" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z150" s="56" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26946,6 +27153,21 @@
       <c r="U151" s="1" t="n">
         <v>0.6</v>
       </c>
+      <c r="V151" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="W151" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="X151" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Y151" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Z151" s="1" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="152" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B152" s="1" t="s">
@@ -27008,6 +27230,21 @@
       <c r="U152" s="1" t="s">
         <v>202</v>
       </c>
+      <c r="V152" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="W152" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="X152" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="Y152" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="Z152" s="1" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="153" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E153" s="1" t="s">
@@ -27025,13 +27262,13 @@
         <v>137</v>
       </c>
       <c r="H154" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="I154" s="1" t="s">
         <v>138</v>
       </c>
       <c r="J154" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="K154" s="1" t="n">
         <v>1</v>
@@ -27066,10 +27303,25 @@
       <c r="U154" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="V154" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W154" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X154" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y154" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z154" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="155" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B155" s="1" t="n">
         <v>0.4</v>
@@ -27129,6 +27381,21 @@
         <v>0.3</v>
       </c>
       <c r="U155" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V155" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W155" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="X155" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y155" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Z155" s="1" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -27703,7 +27970,7 @@
     </row>
     <row r="178" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B178" s="1" t="n">
         <v>0.3</v>
@@ -28049,11 +28316,11 @@
       </c>
     </row>
     <row r="198" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E198" s="68" t="s">
-        <v>222</v>
-      </c>
-      <c r="F198" s="68" t="s">
-        <v>223</v>
+      <c r="E198" s="67" t="s">
+        <v>224</v>
+      </c>
+      <c r="F198" s="67" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28075,7 +28342,7 @@
     </row>
     <row r="200" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B200" s="1" t="n">
         <v>0.3</v>
@@ -28096,7 +28363,7 @@
     <row r="201" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="202" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H202" s="24" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I202" s="24" t="s">
         <v>201</v>
@@ -28549,7 +28816,7 @@
     </row>
     <row r="223" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B223" s="1" t="n">
         <v>0.3</v>
@@ -28578,31 +28845,31 @@
     </row>
     <row r="224" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G224" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="H224" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="I224" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="J224" s="24" t="s">
         <v>201</v>
       </c>
       <c r="K224" s="24" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28621,8 +28888,8 @@
       <c r="E225" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="F225" s="69" t="s">
-        <v>228</v>
+      <c r="F225" s="68" t="s">
+        <v>230</v>
       </c>
       <c r="J225" s="57" t="s">
         <v>107</v>
@@ -28926,7 +29193,7 @@
     </row>
     <row r="245" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B245" s="1" t="n">
         <v>0.4</v>
@@ -28946,21 +29213,21 @@
     </row>
     <row r="246" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="J246" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G247" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="H247" s="24" t="s">
         <v>201</v>
@@ -28968,7 +29235,7 @@
     </row>
     <row r="248" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B248" s="17" t="s">
         <v>102</v>
@@ -29387,7 +29654,7 @@
     </row>
     <row r="268" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B268" s="1" t="n">
         <v>0.4</v>
@@ -29413,33 +29680,33 @@
     </row>
     <row r="269" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G269" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="H269" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B270" s="17" t="s">
         <v>102</v>
@@ -29836,7 +30103,7 @@
       </c>
     </row>
     <row r="288" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N288" s="69"/>
+      <c r="N288" s="68"/>
     </row>
     <row r="289" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B289" s="1" t="n">
@@ -29863,7 +30130,7 @@
     </row>
     <row r="290" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B290" s="1" t="n">
         <v>0.4</v>
@@ -29892,31 +30159,31 @@
     </row>
     <row r="291" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G291" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="H291" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="I291" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J291" s="24" t="s">
         <v>201</v>
@@ -29924,7 +30191,7 @@
     </row>
     <row r="292" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B292" s="17" t="s">
         <v>102</v>
@@ -30437,7 +30704,7 @@
     </row>
     <row r="312" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A312" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B312" s="1" t="n">
         <v>0.4</v>
@@ -30469,39 +30736,39 @@
     </row>
     <row r="313" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G313" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="H313" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="I313" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="J313" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="314" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A314" s="70" t="s">
-        <v>234</v>
+      <c r="A314" s="69" t="s">
+        <v>236</v>
       </c>
       <c r="B314" s="17" t="s">
         <v>102</v>
@@ -30510,11 +30777,11 @@
         <v>103</v>
       </c>
       <c r="D314" s="24" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="315" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A315" s="70" t="s">
+      <c r="A315" s="69" t="s">
         <v>80</v>
       </c>
       <c r="B315" s="17" t="n">
@@ -30525,28 +30792,28 @@
       </c>
     </row>
     <row r="316" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A316" s="70" t="s">
+      <c r="A316" s="69" t="s">
         <v>120</v>
       </c>
       <c r="B316" s="23"/>
       <c r="C316" s="23"/>
     </row>
     <row r="317" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A317" s="70" t="s">
+      <c r="A317" s="69" t="s">
         <v>82</v>
       </c>
       <c r="B317" s="23"/>
       <c r="C317" s="23"/>
     </row>
     <row r="318" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A318" s="70" t="s">
+      <c r="A318" s="69" t="s">
         <v>121</v>
       </c>
       <c r="B318" s="23"/>
       <c r="C318" s="23"/>
     </row>
     <row r="319" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A319" s="70" t="s">
+      <c r="A319" s="69" t="s">
         <v>84</v>
       </c>
       <c r="B319" s="17" t="n">
@@ -30557,7 +30824,7 @@
       </c>
     </row>
     <row r="320" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A320" s="70" t="s">
+      <c r="A320" s="69" t="s">
         <v>79</v>
       </c>
       <c r="B320" s="17" t="n">
@@ -30568,7 +30835,7 @@
       </c>
     </row>
     <row r="321" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A321" s="70" t="s">
+      <c r="A321" s="69" t="s">
         <v>85</v>
       </c>
       <c r="B321" s="17" t="n">
@@ -30579,7 +30846,7 @@
       </c>
     </row>
     <row r="322" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A322" s="70" t="s">
+      <c r="A322" s="69" t="s">
         <v>122</v>
       </c>
       <c r="B322" s="17" t="n">
@@ -30590,7 +30857,7 @@
       </c>
     </row>
     <row r="323" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A323" s="70" t="s">
+      <c r="A323" s="69" t="s">
         <v>123</v>
       </c>
       <c r="B323" s="17" t="n">
@@ -30601,7 +30868,7 @@
       </c>
     </row>
     <row r="324" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A324" s="70" t="s">
+      <c r="A324" s="69" t="s">
         <v>124</v>
       </c>
       <c r="B324" s="17" t="n">
@@ -30612,7 +30879,7 @@
       </c>
     </row>
     <row r="325" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A325" s="70" t="s">
+      <c r="A325" s="69" t="s">
         <v>125</v>
       </c>
       <c r="B325" s="17" t="n">
@@ -30623,21 +30890,21 @@
       </c>
     </row>
     <row r="326" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A326" s="70" t="s">
+      <c r="A326" s="69" t="s">
         <v>126</v>
       </c>
       <c r="B326" s="29"/>
       <c r="C326" s="29"/>
     </row>
     <row r="327" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A327" s="71" t="s">
+      <c r="A327" s="70" t="s">
         <v>128</v>
       </c>
       <c r="B327" s="31"/>
       <c r="C327" s="31"/>
     </row>
     <row r="328" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A328" s="70" t="s">
+      <c r="A328" s="69" t="s">
         <v>134</v>
       </c>
       <c r="B328" s="17" t="n">
@@ -30648,7 +30915,7 @@
       </c>
     </row>
     <row r="329" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A329" s="70" t="s">
+      <c r="A329" s="69" t="s">
         <v>136</v>
       </c>
       <c r="B329" s="17" t="n">
@@ -30659,7 +30926,7 @@
       </c>
     </row>
     <row r="330" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A330" s="72" t="s">
+      <c r="A330" s="71" t="s">
         <v>157</v>
       </c>
       <c r="B330" s="5" t="n">
@@ -30688,7 +30955,7 @@
     </row>
     <row r="334" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A334" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B334" s="1" t="n">
         <v>0.4</v>
@@ -30699,25 +30966,25 @@
     </row>
     <row r="335" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A335" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="336" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A336" s="70" t="s">
-        <v>236</v>
+      <c r="A336" s="69" t="s">
+        <v>238</v>
       </c>
       <c r="B336" s="17" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="337" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A337" s="70" t="s">
+      <c r="A337" s="69" t="s">
         <v>80</v>
       </c>
       <c r="B337" s="17" t="n">
@@ -30725,25 +30992,25 @@
       </c>
     </row>
     <row r="338" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A338" s="70" t="s">
+      <c r="A338" s="69" t="s">
         <v>120</v>
       </c>
       <c r="B338" s="23"/>
     </row>
     <row r="339" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A339" s="70" t="s">
+      <c r="A339" s="69" t="s">
         <v>82</v>
       </c>
       <c r="B339" s="23"/>
     </row>
     <row r="340" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A340" s="70" t="s">
+      <c r="A340" s="69" t="s">
         <v>121</v>
       </c>
       <c r="B340" s="23"/>
     </row>
     <row r="341" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A341" s="70" t="s">
+      <c r="A341" s="69" t="s">
         <v>84</v>
       </c>
       <c r="B341" s="17" t="n">
@@ -30751,7 +31018,7 @@
       </c>
     </row>
     <row r="342" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A342" s="70" t="s">
+      <c r="A342" s="69" t="s">
         <v>79</v>
       </c>
       <c r="B342" s="17" t="n">
@@ -30759,7 +31026,7 @@
       </c>
     </row>
     <row r="343" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A343" s="70" t="s">
+      <c r="A343" s="69" t="s">
         <v>85</v>
       </c>
       <c r="B343" s="17" t="n">
@@ -30767,7 +31034,7 @@
       </c>
     </row>
     <row r="344" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A344" s="70" t="s">
+      <c r="A344" s="69" t="s">
         <v>122</v>
       </c>
       <c r="B344" s="17" t="n">
@@ -30775,7 +31042,7 @@
       </c>
     </row>
     <row r="345" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A345" s="70" t="s">
+      <c r="A345" s="69" t="s">
         <v>123</v>
       </c>
       <c r="B345" s="17" t="n">
@@ -30783,7 +31050,7 @@
       </c>
     </row>
     <row r="346" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A346" s="70" t="s">
+      <c r="A346" s="69" t="s">
         <v>124</v>
       </c>
       <c r="B346" s="17" t="n">
@@ -30791,7 +31058,7 @@
       </c>
     </row>
     <row r="347" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A347" s="70" t="s">
+      <c r="A347" s="69" t="s">
         <v>125</v>
       </c>
       <c r="B347" s="17" t="n">
@@ -30799,19 +31066,19 @@
       </c>
     </row>
     <row r="348" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A348" s="70" t="s">
+      <c r="A348" s="69" t="s">
         <v>126</v>
       </c>
       <c r="B348" s="29"/>
     </row>
     <row r="349" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A349" s="71" t="s">
+      <c r="A349" s="70" t="s">
         <v>128</v>
       </c>
       <c r="B349" s="31"/>
     </row>
     <row r="350" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A350" s="70" t="s">
+      <c r="A350" s="69" t="s">
         <v>134</v>
       </c>
       <c r="B350" s="17" t="n">
@@ -30819,7 +31086,7 @@
       </c>
     </row>
     <row r="351" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A351" s="70" t="s">
+      <c r="A351" s="69" t="s">
         <v>136</v>
       </c>
       <c r="B351" s="17" t="n">
@@ -30827,7 +31094,7 @@
       </c>
     </row>
     <row r="352" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A352" s="72" t="s">
+      <c r="A352" s="71" t="s">
         <v>157</v>
       </c>
       <c r="B352" s="5" t="n">
@@ -30847,7 +31114,7 @@
     </row>
     <row r="356" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B356" s="1" t="n">
         <v>0.4</v>
@@ -30855,18 +31122,18 @@
     </row>
     <row r="357" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A357" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G357" s="24" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="358" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B358" s="17" t="s">
         <v>102</v>
@@ -31238,7 +31505,7 @@
     </row>
     <row r="378" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A378" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B378" s="1" t="n">
         <v>0.4</v>
@@ -31261,30 +31528,30 @@
     </row>
     <row r="379" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A379" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B379" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C379" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D379" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E379" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F379" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G379" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="380" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A380" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B380" s="17" t="s">
         <v>102</v>
@@ -31566,7 +31833,7 @@
     </row>
     <row r="400" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A400" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B400" s="1" t="n">
         <v>0.4</v>
@@ -31583,10 +31850,10 @@
     </row>
     <row r="401" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A401" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K401" s="24" t="s">
         <v>201</v>
@@ -31594,7 +31861,7 @@
     </row>
     <row r="402" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A402" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B402" s="17" t="s">
         <v>102</v>
@@ -32154,7 +32421,7 @@
     </row>
     <row r="422" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A422" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B422" s="1" t="n">
         <v>0.4</v>
@@ -32189,37 +32456,37 @@
     </row>
     <row r="423" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A423" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C423" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D423" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E423" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F423" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G423" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="H423" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="I423" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="J423" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K423" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
   </sheetData>

--- a/parameters script.xlsx
+++ b/parameters script.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2019" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2065" uniqueCount="258">
   <si>
     <t xml:space="preserve">6h 3</t>
   </si>
@@ -720,10 +720,40 @@
     <t xml:space="preserve">18H-3-VAMP7</t>
   </si>
   <si>
+    <t xml:space="preserve">WITHOUT FILL HOLES MASK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-5 </t>
+  </si>
+  <si>
     <t xml:space="preserve">25-5</t>
   </si>
   <si>
+    <t xml:space="preserve">25-5 L1-L2-L4</t>
+  </si>
+  <si>
     <t xml:space="preserve">T25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T32</t>
   </si>
   <si>
     <t xml:space="preserve">*1</t>
@@ -741,7 +771,22 @@
     <t xml:space="preserve">NOT GOOD</t>
   </si>
   <si>
+    <t xml:space="preserve">THICKNESS 5</t>
+  </si>
+  <si>
     <t xml:space="preserve">DEFINITIVO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-5 0H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPTION 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPTION 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V2 </t>
   </si>
   <si>
     <t xml:space="preserve">PCT-MAX RAD NM</t>
@@ -873,7 +918,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="22">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1000,6 +1045,12 @@
         <bgColor rgb="FFBDD7EE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77BC65"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border diagonalUp="false" diagonalDown="false">
@@ -1098,7 +1149,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="75">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1367,7 +1418,19 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="22" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="15" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1439,7 +1502,7 @@
       <rgbColor rgb="FFB2B2B2"/>
       <rgbColor rgb="FFFFB66C"/>
       <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF77BC65"/>
       <rgbColor rgb="FF81D41A"/>
       <rgbColor rgb="FFFFBF00"/>
       <rgbColor rgb="FFFF860D"/>
@@ -1470,9 +1533,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>459000</xdr:colOff>
+      <xdr:colOff>457560</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>16200</xdr:rowOff>
+      <xdr:rowOff>14760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1486,7 +1549,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6183720" y="130320"/>
-          <a:ext cx="7979760" cy="251640"/>
+          <a:ext cx="7978320" cy="250200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1513,9 +1576,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>213120</xdr:colOff>
+      <xdr:colOff>211680</xdr:colOff>
       <xdr:row>85</xdr:row>
-      <xdr:rowOff>19440</xdr:rowOff>
+      <xdr:rowOff>18000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1529,7 +1592,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="10345680" y="13525560"/>
-          <a:ext cx="10138680" cy="2038680"/>
+          <a:ext cx="10137240" cy="2037240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1551,9 +1614,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>878040</xdr:colOff>
+      <xdr:colOff>876600</xdr:colOff>
       <xdr:row>121</xdr:row>
-      <xdr:rowOff>131760</xdr:rowOff>
+      <xdr:rowOff>130320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1567,7 +1630,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6275880" y="20154960"/>
-          <a:ext cx="10175400" cy="2105280"/>
+          <a:ext cx="10173960" cy="2103840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -22271,7 +22334,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Z423"/>
+  <dimension ref="A1:AG423"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26038,25 +26101,58 @@
       <c r="F133" s="1" t="n">
         <v>0.0225</v>
       </c>
+      <c r="AD133" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="AE133" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="AF133" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="AG133" s="1" t="s">
+        <v>219</v>
+      </c>
     </row>
     <row r="134" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="U134" s="24" t="s">
         <v>201</v>
       </c>
       <c r="V134" s="24" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="W134" s="24" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="X134" s="24" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Y134" s="24" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Z134" s="24" t="s">
-        <v>219</v>
+        <v>222</v>
+      </c>
+      <c r="AA134" s="24" t="s">
+        <v>222</v>
+      </c>
+      <c r="AB134" s="24" t="s">
+        <v>222</v>
+      </c>
+      <c r="AC134" s="24" t="s">
+        <v>222</v>
+      </c>
+      <c r="AD134" s="24" t="s">
+        <v>222</v>
+      </c>
+      <c r="AE134" s="24" t="s">
+        <v>222</v>
+      </c>
+      <c r="AF134" s="24" t="s">
+        <v>222</v>
+      </c>
+      <c r="AG134" s="24" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26120,7 +26216,7 @@
       <c r="T135" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="U135" s="57" t="s">
+      <c r="U135" s="67" t="s">
         <v>152</v>
       </c>
       <c r="V135" s="57" t="s">
@@ -26136,7 +26232,28 @@
         <v>156</v>
       </c>
       <c r="Z135" s="56" t="s">
-        <v>220</v>
+        <v>223</v>
+      </c>
+      <c r="AA135" s="57" t="s">
+        <v>224</v>
+      </c>
+      <c r="AB135" s="57" t="s">
+        <v>225</v>
+      </c>
+      <c r="AC135" s="57" t="s">
+        <v>226</v>
+      </c>
+      <c r="AD135" s="57" t="s">
+        <v>227</v>
+      </c>
+      <c r="AE135" s="68" t="s">
+        <v>228</v>
+      </c>
+      <c r="AF135" s="57" t="s">
+        <v>229</v>
+      </c>
+      <c r="AG135" s="57" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26200,7 +26317,7 @@
       <c r="T136" s="18" t="n">
         <v>0.5</v>
       </c>
-      <c r="U136" s="57" t="n">
+      <c r="U136" s="67" t="n">
         <v>0.5</v>
       </c>
       <c r="V136" s="57" t="n">
@@ -26216,6 +26333,27 @@
         <v>0.5</v>
       </c>
       <c r="Z136" s="56" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA136" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB136" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC136" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD136" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE136" s="68" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF136" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG136" s="57" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -26248,6 +26386,13 @@
       <c r="X137" s="23"/>
       <c r="Y137" s="23"/>
       <c r="Z137" s="23"/>
+      <c r="AA137" s="23"/>
+      <c r="AB137" s="23"/>
+      <c r="AC137" s="23"/>
+      <c r="AD137" s="23"/>
+      <c r="AE137" s="23"/>
+      <c r="AF137" s="23"/>
+      <c r="AG137" s="23"/>
     </row>
     <row r="138" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="2" t="s">
@@ -26278,6 +26423,13 @@
       <c r="X138" s="23"/>
       <c r="Y138" s="23"/>
       <c r="Z138" s="23"/>
+      <c r="AA138" s="23"/>
+      <c r="AB138" s="23"/>
+      <c r="AC138" s="23"/>
+      <c r="AD138" s="23"/>
+      <c r="AE138" s="23"/>
+      <c r="AF138" s="23"/>
+      <c r="AG138" s="23"/>
     </row>
     <row r="139" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="2" t="s">
@@ -26308,6 +26460,13 @@
       <c r="X139" s="23"/>
       <c r="Y139" s="23"/>
       <c r="Z139" s="23"/>
+      <c r="AA139" s="23"/>
+      <c r="AB139" s="23"/>
+      <c r="AC139" s="23"/>
+      <c r="AD139" s="23"/>
+      <c r="AE139" s="23"/>
+      <c r="AF139" s="23"/>
+      <c r="AG139" s="23"/>
     </row>
     <row r="140" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="2" t="s">
@@ -26370,7 +26529,7 @@
       <c r="T140" s="18" t="n">
         <v>0.05</v>
       </c>
-      <c r="U140" s="57" t="n">
+      <c r="U140" s="67" t="n">
         <v>0.05</v>
       </c>
       <c r="V140" s="57" t="n">
@@ -26386,6 +26545,27 @@
         <v>0.05</v>
       </c>
       <c r="Z140" s="56" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AA140" s="57" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AB140" s="57" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC140" s="57" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AD140" s="57" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AE140" s="68" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AF140" s="57" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AG140" s="57" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -26450,7 +26630,7 @@
       <c r="T141" s="18" t="n">
         <v>0.4</v>
       </c>
-      <c r="U141" s="57" t="n">
+      <c r="U141" s="67" t="n">
         <v>0.4</v>
       </c>
       <c r="V141" s="57" t="n">
@@ -26466,6 +26646,27 @@
         <v>0.4</v>
       </c>
       <c r="Z141" s="56" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AA141" s="57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AB141" s="57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC141" s="57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AD141" s="57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AE141" s="68" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AF141" s="57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AG141" s="57" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -26530,7 +26731,7 @@
       <c r="T142" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="U142" s="57" t="n">
+      <c r="U142" s="67" t="n">
         <v>1</v>
       </c>
       <c r="V142" s="57" t="n">
@@ -26546,6 +26747,27 @@
         <v>1</v>
       </c>
       <c r="Z142" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA142" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB142" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC142" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD142" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE142" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF142" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG142" s="57" t="n">
         <v>1</v>
       </c>
     </row>
@@ -26610,7 +26832,7 @@
       <c r="T143" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="U143" s="57" t="n">
+      <c r="U143" s="67" t="n">
         <v>4</v>
       </c>
       <c r="V143" s="57" t="n">
@@ -26627,6 +26849,27 @@
       </c>
       <c r="Z143" s="56" t="n">
         <v>3</v>
+      </c>
+      <c r="AA143" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB143" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC143" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD143" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE143" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF143" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG143" s="57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26690,7 +26933,7 @@
       <c r="T144" s="18" t="n">
         <v>0.3</v>
       </c>
-      <c r="U144" s="57" t="n">
+      <c r="U144" s="67" t="n">
         <v>0.3</v>
       </c>
       <c r="V144" s="57" t="n">
@@ -26706,6 +26949,27 @@
         <v>0.3</v>
       </c>
       <c r="Z144" s="56" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AA144" s="57" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AB144" s="57" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AC144" s="57" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AD144" s="57" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AE144" s="68" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AF144" s="57" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AG144" s="57" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -26770,7 +27034,7 @@
       <c r="T145" s="18" t="n">
         <v>0.6</v>
       </c>
-      <c r="U145" s="57" t="n">
+      <c r="U145" s="67" t="n">
         <v>0.6</v>
       </c>
       <c r="V145" s="57" t="n">
@@ -26786,6 +27050,27 @@
         <v>0.6</v>
       </c>
       <c r="Z145" s="56" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA145" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AB145" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AC145" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AD145" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AE145" s="68" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AF145" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AG145" s="57" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -26850,7 +27135,7 @@
       <c r="T146" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="U146" s="57" t="n">
+      <c r="U146" s="67" t="n">
         <v>12000</v>
       </c>
       <c r="V146" s="57" t="n">
@@ -26867,6 +27152,27 @@
       </c>
       <c r="Z146" s="56" t="n">
         <v>5000</v>
+      </c>
+      <c r="AA146" s="57" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AB146" s="57" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AC146" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD146" s="57" t="n">
+        <v>5000</v>
+      </c>
+      <c r="AE146" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF146" s="57" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG146" s="57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26898,6 +27204,13 @@
       <c r="X147" s="29"/>
       <c r="Y147" s="29"/>
       <c r="Z147" s="29"/>
+      <c r="AA147" s="29"/>
+      <c r="AB147" s="29"/>
+      <c r="AC147" s="29"/>
+      <c r="AD147" s="29"/>
+      <c r="AE147" s="21"/>
+      <c r="AF147" s="29"/>
+      <c r="AG147" s="29"/>
     </row>
     <row r="148" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="22" t="s">
@@ -26928,6 +27241,13 @@
       <c r="X148" s="31"/>
       <c r="Y148" s="31"/>
       <c r="Z148" s="31"/>
+      <c r="AA148" s="31"/>
+      <c r="AB148" s="31"/>
+      <c r="AC148" s="31"/>
+      <c r="AD148" s="31"/>
+      <c r="AE148" s="23"/>
+      <c r="AF148" s="31"/>
+      <c r="AG148" s="31"/>
     </row>
     <row r="149" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="17" t="s">
@@ -26990,7 +27310,7 @@
       <c r="T149" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="U149" s="57" t="n">
+      <c r="U149" s="67" t="n">
         <v>2</v>
       </c>
       <c r="V149" s="57" t="n">
@@ -27006,6 +27326,27 @@
         <v>5</v>
       </c>
       <c r="Z149" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA149" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB149" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC149" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD149" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE149" s="68" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF149" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG149" s="57" t="n">
         <v>5</v>
       </c>
     </row>
@@ -27070,7 +27411,7 @@
       <c r="T150" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="U150" s="57" t="n">
+      <c r="U150" s="67" t="n">
         <v>3</v>
       </c>
       <c r="V150" s="57" t="n">
@@ -27086,6 +27427,27 @@
         <v>5</v>
       </c>
       <c r="Z150" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA150" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB150" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC150" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD150" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE150" s="68" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF150" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG150" s="57" t="n">
         <v>5</v>
       </c>
     </row>
@@ -27168,6 +27530,27 @@
       <c r="Z151" s="1" t="n">
         <v>0.6</v>
       </c>
+      <c r="AA151" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AB151" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AC151" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AD151" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AE151" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AF151" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AG151" s="1" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="152" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B152" s="1" t="s">
@@ -27245,6 +27628,27 @@
       <c r="Z152" s="1" t="s">
         <v>202</v>
       </c>
+      <c r="AA152" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="AB152" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="AC152" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="AD152" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="AE152" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="AF152" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="AG152" s="1" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="153" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E153" s="1" t="s">
@@ -27262,13 +27666,13 @@
         <v>137</v>
       </c>
       <c r="H154" s="1" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="I154" s="1" t="s">
         <v>138</v>
       </c>
       <c r="J154" s="1" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="K154" s="1" t="n">
         <v>1</v>
@@ -27318,10 +27722,31 @@
       <c r="Z154" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AA154" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB154" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC154" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD154" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE154" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF154" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG154" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="155" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="1" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="B155" s="1" t="n">
         <v>0.4</v>
@@ -27396,6 +27821,27 @@
         <v>0.3</v>
       </c>
       <c r="Z155" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AA155" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AB155" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AC155" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AD155" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AE155" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AF155" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AG155" s="1" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -27970,7 +28416,7 @@
     </row>
     <row r="178" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="1" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="B178" s="1" t="n">
         <v>0.3</v>
@@ -28316,11 +28762,11 @@
       </c>
     </row>
     <row r="198" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E198" s="67" t="s">
-        <v>224</v>
-      </c>
-      <c r="F198" s="67" t="s">
-        <v>225</v>
+      <c r="E198" s="69" t="s">
+        <v>234</v>
+      </c>
+      <c r="F198" s="69" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28342,7 +28788,7 @@
     </row>
     <row r="200" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="1" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="B200" s="1" t="n">
         <v>0.3</v>
@@ -28360,13 +28806,41 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="201" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="201" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M201" s="70" t="s">
+        <v>236</v>
+      </c>
+      <c r="N201" s="70" t="s">
+        <v>236</v>
+      </c>
+      <c r="O201" s="70" t="s">
+        <v>236</v>
+      </c>
+    </row>
     <row r="202" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H202" s="24" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="I202" s="24" t="s">
         <v>201</v>
+      </c>
+      <c r="J202" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="K202" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="L202" s="24" t="s">
+        <v>239</v>
+      </c>
+      <c r="M202" s="70" t="s">
+        <v>240</v>
+      </c>
+      <c r="N202" s="70" t="s">
+        <v>240</v>
+      </c>
+      <c r="O202" s="70" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28397,6 +28871,24 @@
       <c r="I203" s="57" t="s">
         <v>109</v>
       </c>
+      <c r="J203" s="32" t="s">
+        <v>110</v>
+      </c>
+      <c r="K203" s="32" t="s">
+        <v>111</v>
+      </c>
+      <c r="L203" s="27" t="s">
+        <v>112</v>
+      </c>
+      <c r="M203" s="27" t="s">
+        <v>113</v>
+      </c>
+      <c r="N203" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="O203" s="27" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="204" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="2" t="s">
@@ -28424,6 +28916,24 @@
         <v>0.5</v>
       </c>
       <c r="I204" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J204" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K204" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L204" s="27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M204" s="27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N204" s="27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O204" s="27" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -28439,6 +28949,12 @@
       <c r="G205" s="23"/>
       <c r="H205" s="23"/>
       <c r="I205" s="23"/>
+      <c r="J205" s="23"/>
+      <c r="K205" s="23"/>
+      <c r="L205" s="23"/>
+      <c r="M205" s="23"/>
+      <c r="N205" s="23"/>
+      <c r="O205" s="23"/>
     </row>
     <row r="206" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="2" t="s">
@@ -28452,6 +28968,12 @@
       <c r="G206" s="23"/>
       <c r="H206" s="23"/>
       <c r="I206" s="23"/>
+      <c r="J206" s="23"/>
+      <c r="K206" s="23"/>
+      <c r="L206" s="23"/>
+      <c r="M206" s="23"/>
+      <c r="N206" s="23"/>
+      <c r="O206" s="23"/>
     </row>
     <row r="207" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="2" t="s">
@@ -28465,6 +28987,12 @@
       <c r="G207" s="23"/>
       <c r="H207" s="23"/>
       <c r="I207" s="23"/>
+      <c r="J207" s="23"/>
+      <c r="K207" s="23"/>
+      <c r="L207" s="23"/>
+      <c r="M207" s="23"/>
+      <c r="N207" s="23"/>
+      <c r="O207" s="23"/>
     </row>
     <row r="208" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="2" t="s">
@@ -28494,6 +29022,24 @@
       <c r="I208" s="57" t="n">
         <v>0.005</v>
       </c>
+      <c r="J208" s="32" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="K208" s="32" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="L208" s="27" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="M208" s="27" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N208" s="27" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O208" s="27" t="n">
+        <v>0.005</v>
+      </c>
     </row>
     <row r="209" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="2" t="s">
@@ -28523,6 +29069,24 @@
       <c r="I209" s="57" t="n">
         <v>0.4</v>
       </c>
+      <c r="J209" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K209" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L209" s="27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M209" s="27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N209" s="27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O209" s="27" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="210" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="2" t="s">
@@ -28552,6 +29116,24 @@
       <c r="I210" s="57" t="n">
         <v>1</v>
       </c>
+      <c r="J210" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="K210" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L210" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M210" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="N210" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="O210" s="27" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="211" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="2" t="s">
@@ -28581,6 +29163,24 @@
       <c r="I211" s="57" t="n">
         <v>9</v>
       </c>
+      <c r="J211" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="K211" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="L211" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="M211" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="N211" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="O211" s="27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="212" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="2" t="s">
@@ -28610,6 +29210,24 @@
       <c r="I212" s="57" t="n">
         <v>1.2</v>
       </c>
+      <c r="J212" s="32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K212" s="32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L212" s="27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M212" s="27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N212" s="27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O212" s="27" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="213" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="2" t="s">
@@ -28639,6 +29257,24 @@
       <c r="I213" s="57" t="n">
         <v>0.6</v>
       </c>
+      <c r="J213" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K213" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L213" s="27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M213" s="27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N213" s="27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O213" s="27" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="214" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="2" t="s">
@@ -28667,6 +29303,24 @@
       </c>
       <c r="I214" s="57" t="n">
         <v>27000</v>
+      </c>
+      <c r="J214" s="32" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K214" s="32" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L214" s="27" t="n">
+        <v>27000</v>
+      </c>
+      <c r="M214" s="27" t="n">
+        <v>27000</v>
+      </c>
+      <c r="N214" s="27" t="n">
+        <v>27000</v>
+      </c>
+      <c r="O214" s="27" t="n">
+        <v>15000</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28681,6 +29335,12 @@
       <c r="G215" s="29"/>
       <c r="H215" s="29"/>
       <c r="I215" s="29"/>
+      <c r="J215" s="29"/>
+      <c r="K215" s="29"/>
+      <c r="L215" s="29"/>
+      <c r="M215" s="29"/>
+      <c r="N215" s="29"/>
+      <c r="O215" s="29"/>
     </row>
     <row r="216" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="22" t="s">
@@ -28694,6 +29354,12 @@
       <c r="G216" s="31"/>
       <c r="H216" s="31"/>
       <c r="I216" s="31"/>
+      <c r="J216" s="31"/>
+      <c r="K216" s="31"/>
+      <c r="L216" s="31"/>
+      <c r="M216" s="31"/>
+      <c r="N216" s="31"/>
+      <c r="O216" s="31"/>
     </row>
     <row r="217" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="17" t="s">
@@ -28723,6 +29389,24 @@
       <c r="I217" s="57" t="n">
         <v>2</v>
       </c>
+      <c r="J217" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="K217" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="L217" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="M217" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N217" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="O217" s="27" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="218" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="17" t="s">
@@ -28752,6 +29436,24 @@
       <c r="I218" s="57" t="n">
         <v>2</v>
       </c>
+      <c r="J218" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="K218" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="L218" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="M218" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N218" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="O218" s="27" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="219" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="1" t="s">
@@ -28781,6 +29483,24 @@
       <c r="I219" s="5" t="n">
         <v>0.6</v>
       </c>
+      <c r="J219" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K219" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L219" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M219" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N219" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O219" s="5" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="220" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B220" s="1" t="s">
@@ -28807,6 +29527,24 @@
       <c r="I220" s="1" t="s">
         <v>202</v>
       </c>
+      <c r="J220" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="K220" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="L220" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="M220" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="N220" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="O220" s="1" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="221" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="222" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28816,7 +29554,7 @@
     </row>
     <row r="223" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="1" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="B223" s="1" t="n">
         <v>0.3</v>
@@ -28845,31 +29583,31 @@
     </row>
     <row r="224" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="1" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="G224" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="H224" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="I224" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="J224" s="24" t="s">
         <v>201</v>
       </c>
       <c r="K224" s="24" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28888,8 +29626,8 @@
       <c r="E225" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="F225" s="68" t="s">
-        <v>230</v>
+      <c r="F225" s="71" t="s">
+        <v>245</v>
       </c>
       <c r="J225" s="57" t="s">
         <v>107</v>
@@ -29193,7 +29931,7 @@
     </row>
     <row r="245" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="1" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="B245" s="1" t="n">
         <v>0.4</v>
@@ -29213,21 +29951,21 @@
     </row>
     <row r="246" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="1" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="J246" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G247" s="1" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="H247" s="24" t="s">
         <v>201</v>
@@ -29235,7 +29973,7 @@
     </row>
     <row r="248" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="2" t="s">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="B248" s="17" t="s">
         <v>102</v>
@@ -29654,7 +30392,7 @@
     </row>
     <row r="268" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="1" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="B268" s="1" t="n">
         <v>0.4</v>
@@ -29680,33 +30418,33 @@
     </row>
     <row r="269" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="1" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="G269" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="H269" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="2" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="B270" s="17" t="s">
         <v>102</v>
@@ -30103,7 +30841,7 @@
       </c>
     </row>
     <row r="288" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N288" s="68"/>
+      <c r="N288" s="71"/>
     </row>
     <row r="289" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B289" s="1" t="n">
@@ -30130,7 +30868,7 @@
     </row>
     <row r="290" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="1" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="B290" s="1" t="n">
         <v>0.4</v>
@@ -30159,31 +30897,31 @@
     </row>
     <row r="291" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="1" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="G291" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="H291" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="I291" s="1" t="s">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="J291" s="24" t="s">
         <v>201</v>
@@ -30191,7 +30929,7 @@
     </row>
     <row r="292" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="2" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="B292" s="17" t="s">
         <v>102</v>
@@ -30704,7 +31442,7 @@
     </row>
     <row r="312" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A312" s="1" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="B312" s="1" t="n">
         <v>0.4</v>
@@ -30736,39 +31474,39 @@
     </row>
     <row r="313" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="1" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="G313" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="H313" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="I313" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="J313" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
     </row>
     <row r="314" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A314" s="69" t="s">
-        <v>236</v>
+      <c r="A314" s="72" t="s">
+        <v>251</v>
       </c>
       <c r="B314" s="17" t="s">
         <v>102</v>
@@ -30777,11 +31515,11 @@
         <v>103</v>
       </c>
       <c r="D314" s="24" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
     </row>
     <row r="315" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A315" s="69" t="s">
+      <c r="A315" s="72" t="s">
         <v>80</v>
       </c>
       <c r="B315" s="17" t="n">
@@ -30792,28 +31530,28 @@
       </c>
     </row>
     <row r="316" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A316" s="69" t="s">
+      <c r="A316" s="72" t="s">
         <v>120</v>
       </c>
       <c r="B316" s="23"/>
       <c r="C316" s="23"/>
     </row>
     <row r="317" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A317" s="69" t="s">
+      <c r="A317" s="72" t="s">
         <v>82</v>
       </c>
       <c r="B317" s="23"/>
       <c r="C317" s="23"/>
     </row>
     <row r="318" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A318" s="69" t="s">
+      <c r="A318" s="72" t="s">
         <v>121</v>
       </c>
       <c r="B318" s="23"/>
       <c r="C318" s="23"/>
     </row>
     <row r="319" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A319" s="69" t="s">
+      <c r="A319" s="72" t="s">
         <v>84</v>
       </c>
       <c r="B319" s="17" t="n">
@@ -30824,7 +31562,7 @@
       </c>
     </row>
     <row r="320" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A320" s="69" t="s">
+      <c r="A320" s="72" t="s">
         <v>79</v>
       </c>
       <c r="B320" s="17" t="n">
@@ -30835,7 +31573,7 @@
       </c>
     </row>
     <row r="321" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A321" s="69" t="s">
+      <c r="A321" s="72" t="s">
         <v>85</v>
       </c>
       <c r="B321" s="17" t="n">
@@ -30846,7 +31584,7 @@
       </c>
     </row>
     <row r="322" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A322" s="69" t="s">
+      <c r="A322" s="72" t="s">
         <v>122</v>
       </c>
       <c r="B322" s="17" t="n">
@@ -30857,7 +31595,7 @@
       </c>
     </row>
     <row r="323" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A323" s="69" t="s">
+      <c r="A323" s="72" t="s">
         <v>123</v>
       </c>
       <c r="B323" s="17" t="n">
@@ -30868,7 +31606,7 @@
       </c>
     </row>
     <row r="324" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A324" s="69" t="s">
+      <c r="A324" s="72" t="s">
         <v>124</v>
       </c>
       <c r="B324" s="17" t="n">
@@ -30879,7 +31617,7 @@
       </c>
     </row>
     <row r="325" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A325" s="69" t="s">
+      <c r="A325" s="72" t="s">
         <v>125</v>
       </c>
       <c r="B325" s="17" t="n">
@@ -30890,21 +31628,21 @@
       </c>
     </row>
     <row r="326" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A326" s="69" t="s">
+      <c r="A326" s="72" t="s">
         <v>126</v>
       </c>
       <c r="B326" s="29"/>
       <c r="C326" s="29"/>
     </row>
     <row r="327" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A327" s="70" t="s">
+      <c r="A327" s="73" t="s">
         <v>128</v>
       </c>
       <c r="B327" s="31"/>
       <c r="C327" s="31"/>
     </row>
     <row r="328" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A328" s="69" t="s">
+      <c r="A328" s="72" t="s">
         <v>134</v>
       </c>
       <c r="B328" s="17" t="n">
@@ -30915,7 +31653,7 @@
       </c>
     </row>
     <row r="329" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A329" s="69" t="s">
+      <c r="A329" s="72" t="s">
         <v>136</v>
       </c>
       <c r="B329" s="17" t="n">
@@ -30926,7 +31664,7 @@
       </c>
     </row>
     <row r="330" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A330" s="71" t="s">
+      <c r="A330" s="74" t="s">
         <v>157</v>
       </c>
       <c r="B330" s="5" t="n">
@@ -30955,7 +31693,7 @@
     </row>
     <row r="334" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A334" s="1" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="B334" s="1" t="n">
         <v>0.4</v>
@@ -30966,25 +31704,25 @@
     </row>
     <row r="335" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A335" s="1" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
     </row>
     <row r="336" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A336" s="69" t="s">
-        <v>238</v>
+      <c r="A336" s="72" t="s">
+        <v>253</v>
       </c>
       <c r="B336" s="17" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="337" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A337" s="69" t="s">
+      <c r="A337" s="72" t="s">
         <v>80</v>
       </c>
       <c r="B337" s="17" t="n">
@@ -30992,25 +31730,25 @@
       </c>
     </row>
     <row r="338" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A338" s="69" t="s">
+      <c r="A338" s="72" t="s">
         <v>120</v>
       </c>
       <c r="B338" s="23"/>
     </row>
     <row r="339" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A339" s="69" t="s">
+      <c r="A339" s="72" t="s">
         <v>82</v>
       </c>
       <c r="B339" s="23"/>
     </row>
     <row r="340" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A340" s="69" t="s">
+      <c r="A340" s="72" t="s">
         <v>121</v>
       </c>
       <c r="B340" s="23"/>
     </row>
     <row r="341" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A341" s="69" t="s">
+      <c r="A341" s="72" t="s">
         <v>84</v>
       </c>
       <c r="B341" s="17" t="n">
@@ -31018,7 +31756,7 @@
       </c>
     </row>
     <row r="342" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A342" s="69" t="s">
+      <c r="A342" s="72" t="s">
         <v>79</v>
       </c>
       <c r="B342" s="17" t="n">
@@ -31026,7 +31764,7 @@
       </c>
     </row>
     <row r="343" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A343" s="69" t="s">
+      <c r="A343" s="72" t="s">
         <v>85</v>
       </c>
       <c r="B343" s="17" t="n">
@@ -31034,7 +31772,7 @@
       </c>
     </row>
     <row r="344" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A344" s="69" t="s">
+      <c r="A344" s="72" t="s">
         <v>122</v>
       </c>
       <c r="B344" s="17" t="n">
@@ -31042,7 +31780,7 @@
       </c>
     </row>
     <row r="345" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A345" s="69" t="s">
+      <c r="A345" s="72" t="s">
         <v>123</v>
       </c>
       <c r="B345" s="17" t="n">
@@ -31050,7 +31788,7 @@
       </c>
     </row>
     <row r="346" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A346" s="69" t="s">
+      <c r="A346" s="72" t="s">
         <v>124</v>
       </c>
       <c r="B346" s="17" t="n">
@@ -31058,7 +31796,7 @@
       </c>
     </row>
     <row r="347" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A347" s="69" t="s">
+      <c r="A347" s="72" t="s">
         <v>125</v>
       </c>
       <c r="B347" s="17" t="n">
@@ -31066,19 +31804,19 @@
       </c>
     </row>
     <row r="348" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A348" s="69" t="s">
+      <c r="A348" s="72" t="s">
         <v>126</v>
       </c>
       <c r="B348" s="29"/>
     </row>
     <row r="349" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A349" s="70" t="s">
+      <c r="A349" s="73" t="s">
         <v>128</v>
       </c>
       <c r="B349" s="31"/>
     </row>
     <row r="350" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A350" s="69" t="s">
+      <c r="A350" s="72" t="s">
         <v>134</v>
       </c>
       <c r="B350" s="17" t="n">
@@ -31086,7 +31824,7 @@
       </c>
     </row>
     <row r="351" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A351" s="69" t="s">
+      <c r="A351" s="72" t="s">
         <v>136</v>
       </c>
       <c r="B351" s="17" t="n">
@@ -31094,7 +31832,7 @@
       </c>
     </row>
     <row r="352" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A352" s="71" t="s">
+      <c r="A352" s="74" t="s">
         <v>157</v>
       </c>
       <c r="B352" s="5" t="n">
@@ -31114,7 +31852,7 @@
     </row>
     <row r="356" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="1" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="B356" s="1" t="n">
         <v>0.4</v>
@@ -31122,18 +31860,18 @@
     </row>
     <row r="357" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A357" s="1" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="G357" s="24" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
     </row>
     <row r="358" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="2" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="B358" s="17" t="s">
         <v>102</v>
@@ -31505,7 +32243,7 @@
     </row>
     <row r="378" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A378" s="1" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="B378" s="1" t="n">
         <v>0.4</v>
@@ -31528,30 +32266,30 @@
     </row>
     <row r="379" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A379" s="1" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="B379" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="C379" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="D379" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="E379" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="F379" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="G379" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
     </row>
     <row r="380" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A380" s="2" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="B380" s="17" t="s">
         <v>102</v>
@@ -31833,7 +32571,7 @@
     </row>
     <row r="400" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A400" s="1" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="B400" s="1" t="n">
         <v>0.4</v>
@@ -31850,10 +32588,10 @@
     </row>
     <row r="401" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A401" s="1" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="K401" s="24" t="s">
         <v>201</v>
@@ -31861,7 +32599,7 @@
     </row>
     <row r="402" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A402" s="2" t="s">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="B402" s="17" t="s">
         <v>102</v>
@@ -32421,7 +33159,7 @@
     </row>
     <row r="422" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A422" s="1" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="B422" s="1" t="n">
         <v>0.4</v>
@@ -32456,37 +33194,37 @@
     </row>
     <row r="423" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A423" s="1" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="C423" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="D423" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="E423" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="F423" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="G423" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="H423" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="I423" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="J423" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="K423" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
     </row>
   </sheetData>

--- a/parameters script.xlsx
+++ b/parameters script.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2065" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2181" uniqueCount="271">
   <si>
     <t xml:space="preserve">6h 3</t>
   </si>
@@ -669,10 +669,19 @@
     <t xml:space="preserve">17-5</t>
   </si>
   <si>
+    <t xml:space="preserve">LAST ONE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-6-26-OH</t>
+  </si>
+  <si>
     <t xml:space="preserve">V2</t>
   </si>
   <si>
     <t xml:space="preserve">3 may V3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEFINITIVO</t>
   </si>
   <si>
     <t xml:space="preserve">12H-4</t>
@@ -756,6 +765,33 @@
     <t xml:space="preserve">T32</t>
   </si>
   <si>
+    <t xml:space="preserve">T33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DILATION</t>
+  </si>
+  <si>
     <t xml:space="preserve">*1</t>
   </si>
   <si>
@@ -772,9 +808,6 @@
   </si>
   <si>
     <t xml:space="preserve">THICKNESS 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DEFINITIVO</t>
   </si>
   <si>
     <t xml:space="preserve">25-5 0H</t>
@@ -810,6 +843,9 @@
     <t xml:space="preserve">4H-2</t>
   </si>
   <si>
+    <t xml:space="preserve">dilation</t>
+  </si>
+  <si>
     <t xml:space="preserve">MY COMPUTER</t>
   </si>
   <si>
@@ -826,6 +862,9 @@
   </si>
   <si>
     <t xml:space="preserve">17-5 no funciona en mi computadora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOT WORK IN MY COMPUTER</t>
   </si>
   <si>
     <t xml:space="preserve">6H-3</t>
@@ -847,7 +886,7 @@
     <numFmt numFmtId="166" formatCode="0.00%"/>
     <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -904,6 +943,21 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFFF4000"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF4000"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -952,7 +1006,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
-        <bgColor rgb="FF993300"/>
+        <bgColor rgb="FFFF4000"/>
       </patternFill>
     </fill>
     <fill>
@@ -1149,7 +1203,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="91">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1382,6 +1436,26 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1394,7 +1468,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="15" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="15" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1414,16 +1488,56 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="22" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="22" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="15" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="15" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="16" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="16" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -1431,6 +1545,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1513,7 +1631,7 @@
       <rgbColor rgb="FF5B9BD5"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FFFF4000"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
@@ -22334,7 +22452,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AG423"/>
+  <dimension ref="A1:AO423"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22711,53 +22829,62 @@
       <c r="H17" s="5" t="n">
         <v>0.5</v>
       </c>
+      <c r="N17" s="58" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="1" t="s">
         <v>69</v>
       </c>
+      <c r="N18" s="59" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="M19" s="24" t="s">
         <v>201</v>
       </c>
+      <c r="N19" s="49" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B20" s="17" t="s">
         <v>102</v>
@@ -22794,6 +22921,9 @@
       </c>
       <c r="M20" s="27" t="s">
         <v>113</v>
+      </c>
+      <c r="N20" s="60" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22834,6 +22964,9 @@
         <v>0.5</v>
       </c>
       <c r="M21" s="27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N21" s="60" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -22853,6 +22986,7 @@
       <c r="K22" s="23"/>
       <c r="L22" s="23"/>
       <c r="M22" s="23"/>
+      <c r="N22" s="61"/>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
@@ -22870,6 +23004,7 @@
       <c r="K23" s="23"/>
       <c r="L23" s="23"/>
       <c r="M23" s="23"/>
+      <c r="N23" s="61"/>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
@@ -22887,6 +23022,7 @@
       <c r="K24" s="23"/>
       <c r="L24" s="23"/>
       <c r="M24" s="23"/>
+      <c r="N24" s="61"/>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
@@ -22928,6 +23064,9 @@
       <c r="M25" s="27" t="n">
         <v>0.0125</v>
       </c>
+      <c r="N25" s="60" t="n">
+        <v>0.0125</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
@@ -22969,6 +23108,9 @@
       <c r="M26" s="27" t="n">
         <v>0.4</v>
       </c>
+      <c r="N26" s="60" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
@@ -23010,6 +23152,9 @@
       <c r="M27" s="27" t="n">
         <v>1</v>
       </c>
+      <c r="N27" s="60" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
@@ -23051,6 +23196,9 @@
       <c r="M28" s="27" t="n">
         <v>8</v>
       </c>
+      <c r="N28" s="60" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
@@ -23092,6 +23240,9 @@
       <c r="M29" s="27" t="n">
         <v>1.2</v>
       </c>
+      <c r="N29" s="60" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
@@ -23133,6 +23284,9 @@
       <c r="M30" s="27" t="n">
         <v>0.6</v>
       </c>
+      <c r="N30" s="60" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
@@ -23172,6 +23326,9 @@
         <v>15000</v>
       </c>
       <c r="M31" s="27" t="n">
+        <v>15000</v>
+      </c>
+      <c r="N31" s="60" t="n">
         <v>15000</v>
       </c>
     </row>
@@ -23191,6 +23348,7 @@
       <c r="K32" s="29"/>
       <c r="L32" s="29"/>
       <c r="M32" s="29"/>
+      <c r="N32" s="62"/>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="22" t="s">
@@ -23208,6 +23366,7 @@
       <c r="K33" s="31"/>
       <c r="L33" s="31"/>
       <c r="M33" s="31"/>
+      <c r="N33" s="62"/>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="17" t="s">
@@ -23249,6 +23408,9 @@
       <c r="M34" s="27" t="n">
         <v>4</v>
       </c>
+      <c r="N34" s="60" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="17" t="s">
@@ -23290,6 +23452,9 @@
       <c r="M35" s="27" t="n">
         <v>4</v>
       </c>
+      <c r="N35" s="60" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
@@ -23331,19 +23496,22 @@
       <c r="M36" s="5" t="n">
         <v>0.5</v>
       </c>
+      <c r="N36" s="5" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>201</v>
@@ -23363,7 +23531,7 @@
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B38" s="17" t="s">
         <v>102</v>
@@ -23378,7 +23546,7 @@
         <v>105</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G38" s="27" t="s">
         <v>107</v>
@@ -23394,6 +23562,9 @@
       </c>
       <c r="K38" s="56" t="s">
         <v>111</v>
+      </c>
+      <c r="L38" s="58" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23421,11 +23592,14 @@
       <c r="I39" s="27" t="n">
         <v>0.5</v>
       </c>
-      <c r="J39" s="58" t="n">
+      <c r="J39" s="63" t="n">
         <v>0.5</v>
       </c>
       <c r="K39" s="56" t="n">
         <v>0.5</v>
+      </c>
+      <c r="L39" s="59" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23441,6 +23615,9 @@
       <c r="I40" s="23"/>
       <c r="J40" s="23"/>
       <c r="K40" s="23"/>
+      <c r="L40" s="49" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
@@ -23495,7 +23672,7 @@
       <c r="I43" s="56" t="n">
         <v>0.0025</v>
       </c>
-      <c r="J43" s="58" t="n">
+      <c r="J43" s="63" t="n">
         <v>0.00225</v>
       </c>
       <c r="K43" s="56" t="n">
@@ -23527,7 +23704,7 @@
       <c r="I44" s="27" t="n">
         <v>0.4</v>
       </c>
-      <c r="J44" s="58" t="n">
+      <c r="J44" s="63" t="n">
         <v>0.4</v>
       </c>
       <c r="K44" s="56" t="n">
@@ -23559,7 +23736,7 @@
       <c r="I45" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="J45" s="58" t="n">
+      <c r="J45" s="63" t="n">
         <v>1</v>
       </c>
       <c r="K45" s="56" t="n">
@@ -23591,10 +23768,13 @@
       <c r="I46" s="56" t="n">
         <v>12</v>
       </c>
-      <c r="J46" s="58" t="n">
+      <c r="J46" s="63" t="n">
         <v>14</v>
       </c>
       <c r="K46" s="56" t="n">
+        <v>16</v>
+      </c>
+      <c r="L46" s="0" t="n">
         <v>14</v>
       </c>
     </row>
@@ -23623,11 +23803,11 @@
       <c r="I47" s="27" t="n">
         <v>1.2</v>
       </c>
-      <c r="J47" s="58" t="n">
+      <c r="J47" s="63" t="n">
         <v>1.2</v>
       </c>
       <c r="K47" s="56" t="n">
-        <v>1.2</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23655,11 +23835,11 @@
       <c r="I48" s="27" t="n">
         <v>0.6</v>
       </c>
-      <c r="J48" s="58" t="n">
+      <c r="J48" s="63" t="n">
         <v>0.6</v>
       </c>
       <c r="K48" s="56" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23687,7 +23867,7 @@
       <c r="I49" s="27" t="n">
         <v>22000</v>
       </c>
-      <c r="J49" s="58" t="n">
+      <c r="J49" s="63" t="n">
         <v>22000</v>
       </c>
       <c r="K49" s="56" t="n">
@@ -23747,11 +23927,11 @@
       <c r="I52" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="J52" s="58" t="n">
+      <c r="J52" s="63" t="n">
         <v>4</v>
       </c>
       <c r="K52" s="56" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23779,11 +23959,11 @@
       <c r="I53" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="J53" s="58" t="n">
+      <c r="J53" s="63" t="n">
         <v>4</v>
       </c>
       <c r="K53" s="56" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23822,10 +24002,16 @@
       <c r="H55" s="1" t="s">
         <v>201</v>
       </c>
+      <c r="J55" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="K55" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B56" s="17" t="s">
         <v>102</v>
@@ -23836,14 +24022,14 @@
       <c r="D56" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="E56" s="59" t="s">
+      <c r="E56" s="64" t="s">
         <v>105</v>
       </c>
       <c r="F56" s="18" t="s">
         <v>106</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="H56" s="56" t="s">
         <v>108</v>
@@ -23862,7 +24048,7 @@
       <c r="D57" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="E57" s="59" t="n">
+      <c r="E57" s="64" t="n">
         <v>0.5</v>
       </c>
       <c r="F57" s="18" t="n">
@@ -23918,7 +24104,7 @@
       <c r="D61" s="17" t="n">
         <v>0.004</v>
       </c>
-      <c r="E61" s="59" t="n">
+      <c r="E61" s="64" t="n">
         <v>0.0045</v>
       </c>
       <c r="F61" s="18" t="n">
@@ -23941,7 +24127,7 @@
       <c r="D62" s="17" t="n">
         <v>0.4</v>
       </c>
-      <c r="E62" s="59" t="n">
+      <c r="E62" s="64" t="n">
         <v>0.4</v>
       </c>
       <c r="F62" s="18" t="n">
@@ -23964,7 +24150,7 @@
       <c r="D63" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="E63" s="59" t="n">
+      <c r="E63" s="64" t="n">
         <v>1</v>
       </c>
       <c r="F63" s="18" t="n">
@@ -23987,7 +24173,7 @@
       <c r="D64" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="E64" s="59" t="n">
+      <c r="E64" s="64" t="n">
         <v>10</v>
       </c>
       <c r="F64" s="18" t="n">
@@ -24010,7 +24196,7 @@
       <c r="D65" s="17" t="n">
         <v>1.2</v>
       </c>
-      <c r="E65" s="59" t="n">
+      <c r="E65" s="64" t="n">
         <v>1.2</v>
       </c>
       <c r="F65" s="18" t="n">
@@ -24033,7 +24219,7 @@
       <c r="D66" s="17" t="n">
         <v>0.6</v>
       </c>
-      <c r="E66" s="59" t="n">
+      <c r="E66" s="64" t="n">
         <v>0.6</v>
       </c>
       <c r="F66" s="18" t="n">
@@ -24056,7 +24242,7 @@
       <c r="D67" s="17" t="n">
         <v>20000</v>
       </c>
-      <c r="E67" s="59" t="n">
+      <c r="E67" s="64" t="n">
         <v>25000</v>
       </c>
       <c r="F67" s="18" t="n">
@@ -24101,7 +24287,7 @@
       <c r="D70" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="E70" s="59" t="n">
+      <c r="E70" s="64" t="n">
         <v>4</v>
       </c>
       <c r="F70" s="18" t="n">
@@ -24124,7 +24310,7 @@
       <c r="D71" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="E71" s="59" t="n">
+      <c r="E71" s="64" t="n">
         <v>4</v>
       </c>
       <c r="F71" s="18" t="n">
@@ -24159,22 +24345,22 @@
     </row>
     <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B73" s="1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24188,9 +24374,9 @@
     </row>
     <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="B75" s="60" t="s">
+        <v>213</v>
+      </c>
+      <c r="B75" s="65" t="s">
         <v>102</v>
       </c>
       <c r="C75" s="17" t="s">
@@ -24238,7 +24424,7 @@
       <c r="Q75" s="31" t="s">
         <v>117</v>
       </c>
-      <c r="R75" s="61" t="s">
+      <c r="R75" s="66" t="s">
         <v>118</v>
       </c>
       <c r="S75" s="56" t="s">
@@ -24249,7 +24435,7 @@
       <c r="A76" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B76" s="60" t="n">
+      <c r="B76" s="65" t="n">
         <v>0.5</v>
       </c>
       <c r="C76" s="17" t="n">
@@ -24294,10 +24480,10 @@
       <c r="P76" s="18" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q76" s="62" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R76" s="63" t="n">
+      <c r="Q76" s="67" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R76" s="68" t="n">
         <v>0.5</v>
       </c>
       <c r="S76" s="56" t="n">
@@ -24377,7 +24563,7 @@
       <c r="A80" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B80" s="60" t="n">
+      <c r="B80" s="65" t="n">
         <v>0.006</v>
       </c>
       <c r="C80" s="17" t="n">
@@ -24422,10 +24608,10 @@
       <c r="P80" s="18" t="n">
         <v>0.015</v>
       </c>
-      <c r="Q80" s="62" t="n">
+      <c r="Q80" s="67" t="n">
         <v>0.015</v>
       </c>
-      <c r="R80" s="63" t="n">
+      <c r="R80" s="68" t="n">
         <v>0.015</v>
       </c>
       <c r="S80" s="56" t="n">
@@ -24436,7 +24622,7 @@
       <c r="A81" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B81" s="60" t="n">
+      <c r="B81" s="65" t="n">
         <v>0.4</v>
       </c>
       <c r="C81" s="17" t="n">
@@ -24481,10 +24667,10 @@
       <c r="P81" s="18" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q81" s="62" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="R81" s="63" t="n">
+      <c r="Q81" s="67" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R81" s="68" t="n">
         <v>0.4</v>
       </c>
       <c r="S81" s="56" t="n">
@@ -24495,7 +24681,7 @@
       <c r="A82" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B82" s="60" t="n">
+      <c r="B82" s="65" t="n">
         <v>1</v>
       </c>
       <c r="C82" s="17" t="n">
@@ -24540,10 +24726,10 @@
       <c r="P82" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="Q82" s="62" t="n">
-        <v>1</v>
-      </c>
-      <c r="R82" s="63" t="n">
+      <c r="Q82" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="R82" s="68" t="n">
         <v>1</v>
       </c>
       <c r="S82" s="56" t="n">
@@ -24554,7 +24740,7 @@
       <c r="A83" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B83" s="60" t="n">
+      <c r="B83" s="65" t="n">
         <v>8</v>
       </c>
       <c r="C83" s="17" t="n">
@@ -24599,10 +24785,10 @@
       <c r="P83" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="Q83" s="62" t="n">
+      <c r="Q83" s="67" t="n">
         <v>8</v>
       </c>
-      <c r="R83" s="63" t="n">
+      <c r="R83" s="68" t="n">
         <v>8</v>
       </c>
       <c r="S83" s="56" t="n">
@@ -24613,7 +24799,7 @@
       <c r="A84" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B84" s="60" t="n">
+      <c r="B84" s="65" t="n">
         <v>1.2</v>
       </c>
       <c r="C84" s="17" t="n">
@@ -24658,10 +24844,10 @@
       <c r="P84" s="18" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q84" s="62" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="R84" s="63" t="n">
+      <c r="Q84" s="67" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R84" s="68" t="n">
         <v>1.2</v>
       </c>
       <c r="S84" s="56" t="n">
@@ -24672,7 +24858,7 @@
       <c r="A85" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B85" s="60" t="n">
+      <c r="B85" s="65" t="n">
         <v>0.6</v>
       </c>
       <c r="C85" s="17" t="n">
@@ -24717,10 +24903,10 @@
       <c r="P85" s="18" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q85" s="62" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="R85" s="63" t="n">
+      <c r="Q85" s="67" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R85" s="68" t="n">
         <v>0.6</v>
       </c>
       <c r="S85" s="56" t="n">
@@ -24731,7 +24917,7 @@
       <c r="A86" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B86" s="60" t="n">
+      <c r="B86" s="65" t="n">
         <v>15000</v>
       </c>
       <c r="C86" s="17" t="n">
@@ -24776,10 +24962,10 @@
       <c r="P86" s="18" t="n">
         <v>10000</v>
       </c>
-      <c r="Q86" s="62" t="n">
+      <c r="Q86" s="67" t="n">
         <v>10000</v>
       </c>
-      <c r="R86" s="63" t="n">
+      <c r="R86" s="68" t="n">
         <v>10000</v>
       </c>
       <c r="S86" s="56" t="n">
@@ -24836,7 +25022,7 @@
       <c r="A89" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="B89" s="60" t="n">
+      <c r="B89" s="65" t="n">
         <v>4</v>
       </c>
       <c r="C89" s="17" t="n">
@@ -24881,10 +25067,10 @@
       <c r="P89" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="Q89" s="62" t="n">
-        <v>2</v>
-      </c>
-      <c r="R89" s="63" t="n">
+      <c r="Q89" s="67" t="n">
+        <v>2</v>
+      </c>
+      <c r="R89" s="68" t="n">
         <v>2</v>
       </c>
       <c r="S89" s="56" t="n">
@@ -24895,7 +25081,7 @@
       <c r="A90" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="B90" s="60" t="n">
+      <c r="B90" s="65" t="n">
         <v>4</v>
       </c>
       <c r="C90" s="17" t="n">
@@ -24940,10 +25126,10 @@
       <c r="P90" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="Q90" s="62" t="n">
-        <v>2</v>
-      </c>
-      <c r="R90" s="63" t="n">
+      <c r="Q90" s="67" t="n">
+        <v>2</v>
+      </c>
+      <c r="R90" s="68" t="n">
         <v>2</v>
       </c>
       <c r="S90" s="56" t="n">
@@ -25011,58 +25197,58 @@
     </row>
     <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B92" s="1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="M92" s="5" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="N92" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="O92" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="P92" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q92" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="R92" s="1" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="S92" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25072,7 +25258,7 @@
     </row>
     <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B94" s="17" t="s">
         <v>102</v>
@@ -25567,39 +25753,39 @@
     </row>
     <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B111" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="J111" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D112" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25609,7 +25795,7 @@
     </row>
     <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B114" s="17" t="s">
         <v>102</v>
@@ -25629,7 +25815,7 @@
       <c r="G114" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="H114" s="60" t="s">
+      <c r="H114" s="65" t="s">
         <v>108</v>
       </c>
       <c r="I114" s="56" t="s">
@@ -25661,7 +25847,7 @@
       <c r="G115" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="H115" s="60" t="n">
+      <c r="H115" s="65" t="n">
         <v>0.5</v>
       </c>
       <c r="I115" s="56" t="n">
@@ -25683,7 +25869,7 @@
       <c r="G116" s="23"/>
       <c r="H116" s="23"/>
       <c r="I116" s="40"/>
-      <c r="J116" s="64"/>
+      <c r="J116" s="69"/>
     </row>
     <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="2" t="s">
@@ -25697,7 +25883,7 @@
       <c r="G117" s="23"/>
       <c r="H117" s="23"/>
       <c r="I117" s="40"/>
-      <c r="J117" s="64"/>
+      <c r="J117" s="69"/>
     </row>
     <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="2" t="s">
@@ -25711,7 +25897,7 @@
       <c r="G118" s="23"/>
       <c r="H118" s="23"/>
       <c r="I118" s="40"/>
-      <c r="J118" s="64"/>
+      <c r="J118" s="69"/>
     </row>
     <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="2" t="s">
@@ -25735,7 +25921,7 @@
       <c r="G119" s="17" t="n">
         <v>0.025</v>
       </c>
-      <c r="H119" s="60" t="n">
+      <c r="H119" s="65" t="n">
         <v>0.025</v>
       </c>
       <c r="I119" s="56" t="n">
@@ -25767,7 +25953,7 @@
       <c r="G120" s="17" t="n">
         <v>0.4</v>
       </c>
-      <c r="H120" s="60" t="n">
+      <c r="H120" s="65" t="n">
         <v>0.4</v>
       </c>
       <c r="I120" s="56" t="n">
@@ -25799,7 +25985,7 @@
       <c r="G121" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="H121" s="60" t="n">
+      <c r="H121" s="65" t="n">
         <v>1</v>
       </c>
       <c r="I121" s="56" t="n">
@@ -25831,7 +26017,7 @@
       <c r="G122" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="H122" s="60" t="n">
+      <c r="H122" s="65" t="n">
         <v>4</v>
       </c>
       <c r="I122" s="56" t="n">
@@ -25863,7 +26049,7 @@
       <c r="G123" s="17" t="n">
         <v>1.2</v>
       </c>
-      <c r="H123" s="60" t="n">
+      <c r="H123" s="65" t="n">
         <v>1.2</v>
       </c>
       <c r="I123" s="56" t="n">
@@ -25895,7 +26081,7 @@
       <c r="G124" s="17" t="n">
         <v>0.6</v>
       </c>
-      <c r="H124" s="60" t="n">
+      <c r="H124" s="65" t="n">
         <v>0.6</v>
       </c>
       <c r="I124" s="56" t="n">
@@ -25927,7 +26113,7 @@
       <c r="G125" s="17" t="n">
         <v>10000</v>
       </c>
-      <c r="H125" s="60" t="n">
+      <c r="H125" s="65" t="n">
         <v>10000</v>
       </c>
       <c r="I125" s="56" t="n">
@@ -25949,7 +26135,7 @@
       <c r="G126" s="29"/>
       <c r="H126" s="29"/>
       <c r="I126" s="33"/>
-      <c r="J126" s="65"/>
+      <c r="J126" s="70"/>
     </row>
     <row r="127" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="22" t="s">
@@ -25963,7 +26149,7 @@
       <c r="G127" s="31"/>
       <c r="H127" s="31"/>
       <c r="I127" s="33"/>
-      <c r="J127" s="65"/>
+      <c r="J127" s="70"/>
     </row>
     <row r="128" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="17" t="s">
@@ -25987,7 +26173,7 @@
       <c r="G128" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="H128" s="60" t="n">
+      <c r="H128" s="65" t="n">
         <v>4</v>
       </c>
       <c r="I128" s="56" t="n">
@@ -26019,7 +26205,7 @@
       <c r="G129" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="H129" s="60" t="n">
+      <c r="H129" s="65" t="n">
         <v>4</v>
       </c>
       <c r="I129" s="56" t="n">
@@ -26057,40 +26243,53 @@
       <c r="I130" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="J130" s="66" t="n">
+      <c r="J130" s="71" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B131" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="G131" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="H131" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="I131" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="J131" s="71" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AL132" s="58" t="s">
         <v>202</v>
       </c>
-      <c r="C131" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="F131" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="G131" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="H131" s="1" t="s">
+      <c r="AM132" s="58" t="s">
         <v>202</v>
       </c>
-      <c r="I131" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="J131" s="66" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="132" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="AN132" s="59" t="s">
+        <v>202</v>
+      </c>
+      <c r="AO132" s="72" t="s">
+        <v>202</v>
+      </c>
+    </row>
     <row r="133" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D133" s="1" t="n">
         <v>0.025</v>
@@ -26102,16 +26301,28 @@
         <v>0.0225</v>
       </c>
       <c r="AD133" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="AE133" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="AF133" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="AG133" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
+      </c>
+      <c r="AL133" s="59" t="s">
+        <v>203</v>
+      </c>
+      <c r="AM133" s="59" t="s">
+        <v>203</v>
+      </c>
+      <c r="AN133" s="59" t="s">
+        <v>203</v>
+      </c>
+      <c r="AO133" s="72" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26119,40 +26330,52 @@
         <v>201</v>
       </c>
       <c r="V134" s="24" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="W134" s="24" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="X134" s="24" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Y134" s="24" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Z134" s="24" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="AA134" s="24" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="AB134" s="24" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="AC134" s="24" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="AD134" s="24" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="AE134" s="24" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="AF134" s="24" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="AG134" s="24" t="s">
-        <v>222</v>
+        <v>225</v>
+      </c>
+      <c r="AL134" s="49" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM134" s="49" t="s">
+        <v>69</v>
+      </c>
+      <c r="AN134" s="73" t="s">
+        <v>69</v>
+      </c>
+      <c r="AO134" s="74" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26216,44 +26439,68 @@
       <c r="T135" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="U135" s="67" t="s">
+      <c r="U135" s="75" t="s">
         <v>152</v>
       </c>
-      <c r="V135" s="57" t="s">
+      <c r="V135" s="76" t="s">
         <v>153</v>
       </c>
-      <c r="W135" s="57" t="s">
+      <c r="W135" s="76" t="s">
         <v>154</v>
       </c>
-      <c r="X135" s="57" t="s">
+      <c r="X135" s="76" t="s">
         <v>155</v>
       </c>
-      <c r="Y135" s="57" t="s">
+      <c r="Y135" s="76" t="s">
         <v>156</v>
       </c>
-      <c r="Z135" s="56" t="s">
-        <v>223</v>
-      </c>
-      <c r="AA135" s="57" t="s">
-        <v>224</v>
-      </c>
-      <c r="AB135" s="57" t="s">
-        <v>225</v>
-      </c>
-      <c r="AC135" s="57" t="s">
+      <c r="Z135" s="63" t="s">
         <v>226</v>
       </c>
-      <c r="AD135" s="57" t="s">
+      <c r="AA135" s="76" t="s">
         <v>227</v>
       </c>
-      <c r="AE135" s="68" t="s">
+      <c r="AB135" s="76" t="s">
         <v>228</v>
       </c>
-      <c r="AF135" s="57" t="s">
+      <c r="AC135" s="76" t="s">
         <v>229</v>
       </c>
-      <c r="AG135" s="57" t="s">
+      <c r="AD135" s="76" t="s">
         <v>230</v>
+      </c>
+      <c r="AE135" s="77" t="s">
+        <v>231</v>
+      </c>
+      <c r="AF135" s="76" t="s">
+        <v>232</v>
+      </c>
+      <c r="AG135" s="76" t="s">
+        <v>233</v>
+      </c>
+      <c r="AH135" s="78" t="s">
+        <v>234</v>
+      </c>
+      <c r="AI135" s="78" t="s">
+        <v>235</v>
+      </c>
+      <c r="AJ135" s="78" t="s">
+        <v>236</v>
+      </c>
+      <c r="AK135" s="78" t="s">
+        <v>237</v>
+      </c>
+      <c r="AL135" s="79" t="s">
+        <v>238</v>
+      </c>
+      <c r="AM135" s="79" t="s">
+        <v>239</v>
+      </c>
+      <c r="AN135" s="79" t="s">
+        <v>240</v>
+      </c>
+      <c r="AO135" s="79" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26317,43 +26564,67 @@
       <c r="T136" s="18" t="n">
         <v>0.5</v>
       </c>
-      <c r="U136" s="67" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V136" s="57" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="W136" s="57" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="X136" s="57" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y136" s="57" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z136" s="56" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AA136" s="57" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB136" s="57" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AC136" s="57" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AD136" s="57" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AE136" s="68" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AF136" s="57" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AG136" s="57" t="n">
+      <c r="U136" s="75" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V136" s="76" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W136" s="76" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X136" s="76" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y136" s="76" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z136" s="63" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA136" s="76" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB136" s="76" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC136" s="76" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD136" s="76" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE136" s="77" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF136" s="76" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG136" s="76" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH136" s="78" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AI136" s="78" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AJ136" s="78" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK136" s="78" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AL136" s="79" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AM136" s="79" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AN136" s="79" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AO136" s="79" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -26393,6 +26664,14 @@
       <c r="AE137" s="23"/>
       <c r="AF137" s="23"/>
       <c r="AG137" s="23"/>
+      <c r="AH137" s="23"/>
+      <c r="AI137" s="23"/>
+      <c r="AJ137" s="80"/>
+      <c r="AK137" s="80"/>
+      <c r="AL137" s="23"/>
+      <c r="AM137" s="23"/>
+      <c r="AN137" s="23"/>
+      <c r="AO137" s="23"/>
     </row>
     <row r="138" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="2" t="s">
@@ -26430,6 +26709,14 @@
       <c r="AE138" s="23"/>
       <c r="AF138" s="23"/>
       <c r="AG138" s="23"/>
+      <c r="AH138" s="23"/>
+      <c r="AI138" s="23"/>
+      <c r="AJ138" s="80"/>
+      <c r="AK138" s="80"/>
+      <c r="AL138" s="23"/>
+      <c r="AM138" s="23"/>
+      <c r="AN138" s="23"/>
+      <c r="AO138" s="23"/>
     </row>
     <row r="139" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="2" t="s">
@@ -26467,6 +26754,14 @@
       <c r="AE139" s="23"/>
       <c r="AF139" s="23"/>
       <c r="AG139" s="23"/>
+      <c r="AH139" s="23"/>
+      <c r="AI139" s="23"/>
+      <c r="AJ139" s="80"/>
+      <c r="AK139" s="80"/>
+      <c r="AL139" s="23"/>
+      <c r="AM139" s="23"/>
+      <c r="AN139" s="23"/>
+      <c r="AO139" s="23"/>
     </row>
     <row r="140" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="2" t="s">
@@ -26529,43 +26824,67 @@
       <c r="T140" s="18" t="n">
         <v>0.05</v>
       </c>
-      <c r="U140" s="67" t="n">
+      <c r="U140" s="75" t="n">
         <v>0.05</v>
       </c>
-      <c r="V140" s="57" t="n">
+      <c r="V140" s="76" t="n">
         <v>0.05</v>
       </c>
-      <c r="W140" s="57" t="n">
+      <c r="W140" s="76" t="n">
         <v>0.05</v>
       </c>
-      <c r="X140" s="57" t="n">
+      <c r="X140" s="76" t="n">
         <v>0.05</v>
       </c>
-      <c r="Y140" s="57" t="n">
+      <c r="Y140" s="76" t="n">
         <v>0.05</v>
       </c>
-      <c r="Z140" s="56" t="n">
+      <c r="Z140" s="63" t="n">
         <v>0.05</v>
       </c>
-      <c r="AA140" s="57" t="n">
+      <c r="AA140" s="76" t="n">
         <v>0.05</v>
       </c>
-      <c r="AB140" s="57" t="n">
+      <c r="AB140" s="76" t="n">
         <v>0.05</v>
       </c>
-      <c r="AC140" s="57" t="n">
+      <c r="AC140" s="76" t="n">
         <v>0.05</v>
       </c>
-      <c r="AD140" s="57" t="n">
+      <c r="AD140" s="76" t="n">
         <v>0.05</v>
       </c>
-      <c r="AE140" s="68" t="n">
+      <c r="AE140" s="77" t="n">
         <v>0.05</v>
       </c>
-      <c r="AF140" s="57" t="n">
+      <c r="AF140" s="76" t="n">
         <v>0.05</v>
       </c>
-      <c r="AG140" s="57" t="n">
+      <c r="AG140" s="76" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AH140" s="78" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AI140" s="78" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AJ140" s="78" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AK140" s="78" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AL140" s="79" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AM140" s="79" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AN140" s="79" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AO140" s="79" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -26630,43 +26949,67 @@
       <c r="T141" s="18" t="n">
         <v>0.4</v>
       </c>
-      <c r="U141" s="67" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="V141" s="57" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="W141" s="57" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="X141" s="57" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Y141" s="57" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Z141" s="56" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AA141" s="57" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AB141" s="57" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AC141" s="57" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AD141" s="57" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AE141" s="68" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AF141" s="57" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AG141" s="57" t="n">
+      <c r="U141" s="75" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="V141" s="76" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W141" s="76" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="X141" s="76" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y141" s="76" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z141" s="63" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AA141" s="76" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AB141" s="76" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC141" s="76" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AD141" s="76" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AE141" s="77" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AF141" s="76" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AG141" s="76" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AH141" s="78" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AI141" s="78" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AJ141" s="78" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AK141" s="78" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AL141" s="79" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AM141" s="79" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AN141" s="79" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AO141" s="79" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -26731,43 +27074,67 @@
       <c r="T142" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="U142" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="V142" s="57" t="n">
-        <v>1</v>
-      </c>
-      <c r="W142" s="57" t="n">
-        <v>1</v>
-      </c>
-      <c r="X142" s="57" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y142" s="57" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z142" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA142" s="57" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB142" s="57" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC142" s="57" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD142" s="57" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE142" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF142" s="57" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG142" s="57" t="n">
+      <c r="U142" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V142" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="W142" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="X142" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y142" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z142" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA142" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB142" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC142" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD142" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE142" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF142" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG142" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH142" s="78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI142" s="78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ142" s="78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK142" s="78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL142" s="79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM142" s="79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN142" s="79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO142" s="79" t="n">
         <v>1</v>
       </c>
     </row>
@@ -26832,44 +27199,68 @@
       <c r="T143" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="U143" s="67" t="n">
+      <c r="U143" s="75" t="n">
         <v>4</v>
       </c>
-      <c r="V143" s="57" t="n">
+      <c r="V143" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="W143" s="57" t="n">
-        <v>1</v>
-      </c>
-      <c r="X143" s="57" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y143" s="57" t="n">
+      <c r="W143" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="X143" s="76" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y143" s="76" t="n">
         <v>4</v>
       </c>
-      <c r="Z143" s="56" t="n">
+      <c r="Z143" s="63" t="n">
         <v>3</v>
       </c>
-      <c r="AA143" s="57" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB143" s="57" t="n">
+      <c r="AA143" s="76" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB143" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="AC143" s="57" t="n">
+      <c r="AC143" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="AD143" s="57" t="n">
+      <c r="AD143" s="76" t="n">
         <v>3</v>
       </c>
-      <c r="AE143" s="68" t="n">
+      <c r="AE143" s="77" t="n">
         <v>0</v>
       </c>
-      <c r="AF143" s="57" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG143" s="57" t="n">
-        <v>1</v>
+      <c r="AF143" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG143" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH143" s="78" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI143" s="78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ143" s="78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK143" s="78" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL143" s="79" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM143" s="79" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN143" s="79" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO143" s="79" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26921,56 +27312,80 @@
       <c r="P144" s="17" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q144" s="63" t="n">
+      <c r="Q144" s="68" t="n">
         <v>0.8</v>
       </c>
-      <c r="R144" s="63" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S144" s="63" t="n">
+      <c r="R144" s="68" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S144" s="68" t="n">
         <v>0.4</v>
       </c>
       <c r="T144" s="18" t="n">
         <v>0.3</v>
       </c>
-      <c r="U144" s="67" t="n">
+      <c r="U144" s="75" t="n">
         <v>0.3</v>
       </c>
-      <c r="V144" s="57" t="n">
+      <c r="V144" s="76" t="n">
         <v>0.3</v>
       </c>
-      <c r="W144" s="57" t="n">
+      <c r="W144" s="76" t="n">
         <v>0.3</v>
       </c>
-      <c r="X144" s="57" t="n">
+      <c r="X144" s="76" t="n">
         <v>0.3</v>
       </c>
-      <c r="Y144" s="57" t="n">
+      <c r="Y144" s="76" t="n">
         <v>0.3</v>
       </c>
-      <c r="Z144" s="56" t="n">
+      <c r="Z144" s="63" t="n">
         <v>0.3</v>
       </c>
-      <c r="AA144" s="57" t="n">
+      <c r="AA144" s="76" t="n">
         <v>0.3</v>
       </c>
-      <c r="AB144" s="57" t="n">
+      <c r="AB144" s="76" t="n">
         <v>0.3</v>
       </c>
-      <c r="AC144" s="57" t="n">
+      <c r="AC144" s="76" t="n">
         <v>0.3</v>
       </c>
-      <c r="AD144" s="57" t="n">
+      <c r="AD144" s="76" t="n">
         <v>0.3</v>
       </c>
-      <c r="AE144" s="68" t="n">
+      <c r="AE144" s="77" t="n">
         <v>0.3</v>
       </c>
-      <c r="AF144" s="57" t="n">
+      <c r="AF144" s="76" t="n">
         <v>0.3</v>
       </c>
-      <c r="AG144" s="57" t="n">
+      <c r="AG144" s="76" t="n">
         <v>0.3</v>
+      </c>
+      <c r="AH144" s="78" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI144" s="78" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AJ144" s="78" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK144" s="78" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL144" s="79" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AM144" s="79" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN144" s="79" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO144" s="79" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27034,43 +27449,67 @@
       <c r="T145" s="18" t="n">
         <v>0.6</v>
       </c>
-      <c r="U145" s="67" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="V145" s="57" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="W145" s="57" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="X145" s="57" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Y145" s="57" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Z145" s="56" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AA145" s="57" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AB145" s="57" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AC145" s="57" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AD145" s="57" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AE145" s="68" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AF145" s="57" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AG145" s="57" t="n">
+      <c r="U145" s="75" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="V145" s="76" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="W145" s="76" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="X145" s="76" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Y145" s="76" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Z145" s="63" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA145" s="76" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AB145" s="76" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AC145" s="76" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AD145" s="76" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AE145" s="77" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AF145" s="76" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AG145" s="76" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AH145" s="78" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AI145" s="78" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AJ145" s="78" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AK145" s="78" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AL145" s="79" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AM145" s="79" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AN145" s="79" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AO145" s="79" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -27135,44 +27574,68 @@
       <c r="T146" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="U146" s="67" t="n">
+      <c r="U146" s="75" t="n">
         <v>12000</v>
       </c>
-      <c r="V146" s="57" t="n">
+      <c r="V146" s="76" t="n">
         <v>2000</v>
       </c>
-      <c r="W146" s="57" t="n">
+      <c r="W146" s="76" t="n">
         <v>5000</v>
       </c>
-      <c r="X146" s="57" t="n">
+      <c r="X146" s="76" t="n">
         <v>5000</v>
       </c>
-      <c r="Y146" s="57" t="n">
+      <c r="Y146" s="76" t="n">
         <v>5000</v>
       </c>
-      <c r="Z146" s="56" t="n">
+      <c r="Z146" s="63" t="n">
         <v>5000</v>
       </c>
-      <c r="AA146" s="57" t="n">
+      <c r="AA146" s="76" t="n">
         <v>2000</v>
       </c>
-      <c r="AB146" s="57" t="n">
+      <c r="AB146" s="76" t="n">
         <v>2000</v>
       </c>
-      <c r="AC146" s="57" t="n">
+      <c r="AC146" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="AD146" s="57" t="n">
+      <c r="AD146" s="76" t="n">
         <v>5000</v>
       </c>
-      <c r="AE146" s="68" t="n">
+      <c r="AE146" s="77" t="n">
         <v>0</v>
       </c>
-      <c r="AF146" s="57" t="n">
+      <c r="AF146" s="76" t="n">
         <v>1000</v>
       </c>
-      <c r="AG146" s="57" t="n">
+      <c r="AG146" s="76" t="n">
         <v>0</v>
+      </c>
+      <c r="AH146" s="78" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AI146" s="78" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AJ146" s="78" t="n">
+        <v>5000</v>
+      </c>
+      <c r="AK146" s="78" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AL146" s="79" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AM146" s="79" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AN146" s="79" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AO146" s="79" t="n">
+        <v>10000</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27211,6 +27674,14 @@
       <c r="AE147" s="21"/>
       <c r="AF147" s="29"/>
       <c r="AG147" s="29"/>
+      <c r="AH147" s="29"/>
+      <c r="AI147" s="29"/>
+      <c r="AJ147" s="81"/>
+      <c r="AK147" s="81"/>
+      <c r="AL147" s="29"/>
+      <c r="AM147" s="29"/>
+      <c r="AN147" s="29"/>
+      <c r="AO147" s="29"/>
     </row>
     <row r="148" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="22" t="s">
@@ -27248,6 +27719,14 @@
       <c r="AE148" s="23"/>
       <c r="AF148" s="31"/>
       <c r="AG148" s="31"/>
+      <c r="AH148" s="31"/>
+      <c r="AI148" s="31"/>
+      <c r="AJ148" s="81"/>
+      <c r="AK148" s="81"/>
+      <c r="AL148" s="31"/>
+      <c r="AM148" s="31"/>
+      <c r="AN148" s="31"/>
+      <c r="AO148" s="31"/>
     </row>
     <row r="149" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="17" t="s">
@@ -27307,47 +27786,71 @@
       <c r="S149" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="T149" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="U149" s="67" t="n">
-        <v>2</v>
-      </c>
-      <c r="V149" s="57" t="n">
-        <v>2</v>
-      </c>
-      <c r="W149" s="57" t="n">
+      <c r="T149" s="82" t="n">
+        <v>2</v>
+      </c>
+      <c r="U149" s="75" t="n">
+        <v>2</v>
+      </c>
+      <c r="V149" s="76" t="n">
+        <v>2</v>
+      </c>
+      <c r="W149" s="76" t="n">
         <v>5</v>
       </c>
-      <c r="X149" s="57" t="n">
+      <c r="X149" s="76" t="n">
         <v>5</v>
       </c>
-      <c r="Y149" s="57" t="n">
+      <c r="Y149" s="76" t="n">
         <v>5</v>
       </c>
-      <c r="Z149" s="56" t="n">
+      <c r="Z149" s="63" t="n">
         <v>5</v>
       </c>
-      <c r="AA149" s="57" t="n">
+      <c r="AA149" s="76" t="n">
         <v>5</v>
       </c>
-      <c r="AB149" s="57" t="n">
+      <c r="AB149" s="76" t="n">
         <v>5</v>
       </c>
-      <c r="AC149" s="57" t="n">
+      <c r="AC149" s="76" t="n">
         <v>5</v>
       </c>
-      <c r="AD149" s="57" t="n">
+      <c r="AD149" s="76" t="n">
         <v>5</v>
       </c>
-      <c r="AE149" s="68" t="n">
+      <c r="AE149" s="77" t="n">
         <v>5</v>
       </c>
-      <c r="AF149" s="57" t="n">
+      <c r="AF149" s="76" t="n">
         <v>5</v>
       </c>
-      <c r="AG149" s="57" t="n">
+      <c r="AG149" s="76" t="n">
         <v>5</v>
+      </c>
+      <c r="AH149" s="78" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI149" s="78" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ149" s="78" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK149" s="78" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL149" s="79" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM149" s="79" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN149" s="79" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO149" s="79" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27408,47 +27911,71 @@
       <c r="S150" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="T150" s="18" t="n">
+      <c r="T150" s="82" t="n">
         <v>3</v>
       </c>
-      <c r="U150" s="67" t="n">
+      <c r="U150" s="75" t="n">
         <v>3</v>
       </c>
-      <c r="V150" s="57" t="n">
+      <c r="V150" s="76" t="n">
         <v>3</v>
       </c>
-      <c r="W150" s="57" t="n">
+      <c r="W150" s="76" t="n">
         <v>5</v>
       </c>
-      <c r="X150" s="57" t="n">
+      <c r="X150" s="76" t="n">
         <v>5</v>
       </c>
-      <c r="Y150" s="57" t="n">
+      <c r="Y150" s="76" t="n">
         <v>5</v>
       </c>
-      <c r="Z150" s="56" t="n">
+      <c r="Z150" s="63" t="n">
         <v>5</v>
       </c>
-      <c r="AA150" s="57" t="n">
+      <c r="AA150" s="76" t="n">
         <v>5</v>
       </c>
-      <c r="AB150" s="57" t="n">
+      <c r="AB150" s="76" t="n">
         <v>5</v>
       </c>
-      <c r="AC150" s="57" t="n">
+      <c r="AC150" s="76" t="n">
         <v>5</v>
       </c>
-      <c r="AD150" s="57" t="n">
+      <c r="AD150" s="76" t="n">
         <v>5</v>
       </c>
-      <c r="AE150" s="68" t="n">
+      <c r="AE150" s="77" t="n">
         <v>5</v>
       </c>
-      <c r="AF150" s="57" t="n">
+      <c r="AF150" s="76" t="n">
         <v>5</v>
       </c>
-      <c r="AG150" s="57" t="n">
+      <c r="AG150" s="76" t="n">
         <v>5</v>
+      </c>
+      <c r="AH150" s="78" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI150" s="78" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ150" s="78" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK150" s="78" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL150" s="79" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM150" s="79" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN150" s="79" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO150" s="79" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27551,103 +28078,151 @@
       <c r="AG151" s="1" t="n">
         <v>0.6</v>
       </c>
+      <c r="AH151" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AI151" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AJ151" s="83" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AK151" s="83" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AL151" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AM151" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AN151" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AO151" s="5" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="152" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B152" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="H152" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I152" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J152" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K152" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L152" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="M152" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="N152" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="O152" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="P152" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q152" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="R152" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="S152" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="T152" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="U152" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="V152" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="W152" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="X152" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Y152" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Z152" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AA152" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AB152" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AC152" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AD152" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AE152" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AF152" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AG152" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
+      </c>
+      <c r="AH152" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="AI152" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="AJ152" s="83" t="s">
+        <v>204</v>
+      </c>
+      <c r="AK152" s="83" t="s">
+        <v>204</v>
+      </c>
+      <c r="AL152" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="AM152" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="AN152" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="AO152" s="1" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27660,19 +28235,34 @@
       <c r="G153" s="1" t="s">
         <v>197</v>
       </c>
+      <c r="AK153" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="AL153" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM153" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN153" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO153" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="154" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F154" s="1" t="s">
         <v>137</v>
       </c>
       <c r="H154" s="1" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="I154" s="1" t="s">
         <v>138</v>
       </c>
       <c r="J154" s="1" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="K154" s="1" t="n">
         <v>1</v>
@@ -27743,10 +28333,16 @@
       <c r="AG154" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AK154" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="AO154" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="155" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="1" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="B155" s="1" t="n">
         <v>0.4</v>
@@ -28351,34 +28947,34 @@
     </row>
     <row r="175" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B175" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="H175" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I175" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J175" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K175" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -28416,7 +29012,7 @@
     </row>
     <row r="178" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="1" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="B178" s="1" t="n">
         <v>0.3</v>
@@ -28746,27 +29342,27 @@
     </row>
     <row r="197" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B197" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E198" s="69" t="s">
-        <v>234</v>
-      </c>
-      <c r="F198" s="69" t="s">
-        <v>235</v>
+      <c r="E198" s="84" t="s">
+        <v>246</v>
+      </c>
+      <c r="F198" s="84" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28788,7 +29384,7 @@
     </row>
     <row r="200" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="1" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="B200" s="1" t="n">
         <v>0.3</v>
@@ -28805,42 +29401,55 @@
       <c r="F200" s="1" t="n">
         <v>0.3</v>
       </c>
+      <c r="Q200" s="58" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="201" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="M201" s="70" t="s">
-        <v>236</v>
-      </c>
-      <c r="N201" s="70" t="s">
-        <v>236</v>
-      </c>
-      <c r="O201" s="70" t="s">
-        <v>236</v>
+      <c r="M201" s="85" t="s">
+        <v>248</v>
+      </c>
+      <c r="N201" s="85" t="s">
+        <v>248</v>
+      </c>
+      <c r="O201" s="85" t="s">
+        <v>248</v>
+      </c>
+      <c r="P201" s="86" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q201" s="59" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H202" s="24" t="s">
-        <v>237</v>
-      </c>
+      <c r="H202" s="24"/>
       <c r="I202" s="24" t="s">
         <v>201</v>
       </c>
       <c r="J202" s="24" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="K202" s="24" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="L202" s="24" t="s">
-        <v>239</v>
-      </c>
-      <c r="M202" s="70" t="s">
-        <v>240</v>
-      </c>
-      <c r="N202" s="70" t="s">
-        <v>240</v>
-      </c>
-      <c r="O202" s="70" t="s">
-        <v>240</v>
+        <v>250</v>
+      </c>
+      <c r="M202" s="85" t="s">
+        <v>251</v>
+      </c>
+      <c r="N202" s="85" t="s">
+        <v>251</v>
+      </c>
+      <c r="O202" s="85" t="s">
+        <v>251</v>
+      </c>
+      <c r="P202" s="24" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q202" s="49" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28889,6 +29498,12 @@
       <c r="O203" s="27" t="s">
         <v>115</v>
       </c>
+      <c r="P203" s="45" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q203" s="79" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="204" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="2" t="s">
@@ -28934,6 +29549,12 @@
         <v>0.5</v>
       </c>
       <c r="O204" s="27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P204" s="45" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q204" s="79" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -28955,6 +29576,8 @@
       <c r="M205" s="23"/>
       <c r="N205" s="23"/>
       <c r="O205" s="23"/>
+      <c r="P205" s="23"/>
+      <c r="Q205" s="23"/>
     </row>
     <row r="206" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="2" t="s">
@@ -28974,6 +29597,8 @@
       <c r="M206" s="23"/>
       <c r="N206" s="23"/>
       <c r="O206" s="23"/>
+      <c r="P206" s="23"/>
+      <c r="Q206" s="23"/>
     </row>
     <row r="207" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="2" t="s">
@@ -28993,6 +29618,8 @@
       <c r="M207" s="23"/>
       <c r="N207" s="23"/>
       <c r="O207" s="23"/>
+      <c r="P207" s="23"/>
+      <c r="Q207" s="23"/>
     </row>
     <row r="208" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="2" t="s">
@@ -29040,6 +29667,12 @@
       <c r="O208" s="27" t="n">
         <v>0.005</v>
       </c>
+      <c r="P208" s="45" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="Q208" s="79" t="n">
+        <v>0.005</v>
+      </c>
     </row>
     <row r="209" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="2" t="s">
@@ -29087,6 +29720,12 @@
       <c r="O209" s="27" t="n">
         <v>0.4</v>
       </c>
+      <c r="P209" s="45" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q209" s="79" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="210" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="2" t="s">
@@ -29134,6 +29773,12 @@
       <c r="O210" s="27" t="n">
         <v>1</v>
       </c>
+      <c r="P210" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q210" s="79" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="211" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="2" t="s">
@@ -29181,6 +29826,12 @@
       <c r="O211" s="27" t="n">
         <v>0</v>
       </c>
+      <c r="P211" s="45" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q211" s="79" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="212" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="2" t="s">
@@ -29228,6 +29879,12 @@
       <c r="O212" s="27" t="n">
         <v>1.2</v>
       </c>
+      <c r="P212" s="45" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q212" s="79" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="213" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="2" t="s">
@@ -29275,6 +29932,12 @@
       <c r="O213" s="27" t="n">
         <v>0.6</v>
       </c>
+      <c r="P213" s="45" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q213" s="79" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="214" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="2" t="s">
@@ -29321,6 +29984,12 @@
       </c>
       <c r="O214" s="27" t="n">
         <v>15000</v>
+      </c>
+      <c r="P214" s="45" t="n">
+        <v>20000</v>
+      </c>
+      <c r="Q214" s="79" t="n">
+        <v>20000</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29341,6 +30010,8 @@
       <c r="M215" s="29"/>
       <c r="N215" s="29"/>
       <c r="O215" s="29"/>
+      <c r="P215" s="29"/>
+      <c r="Q215" s="29"/>
     </row>
     <row r="216" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="22" t="s">
@@ -29360,6 +30031,8 @@
       <c r="M216" s="31"/>
       <c r="N216" s="31"/>
       <c r="O216" s="31"/>
+      <c r="P216" s="31"/>
+      <c r="Q216" s="31"/>
     </row>
     <row r="217" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="17" t="s">
@@ -29407,6 +30080,12 @@
       <c r="O217" s="27" t="n">
         <v>5</v>
       </c>
+      <c r="P217" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q217" s="79" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="218" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="17" t="s">
@@ -29454,6 +30133,12 @@
       <c r="O218" s="27" t="n">
         <v>5</v>
       </c>
+      <c r="P218" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q218" s="79" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="219" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="1" t="s">
@@ -29501,49 +30186,61 @@
       <c r="O219" s="5" t="n">
         <v>0.6</v>
       </c>
+      <c r="P219" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q219" s="5" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="220" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B220" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G220" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="H220" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I220" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J220" s="1" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="K220" s="1" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="L220" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="M220" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="N220" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="O220" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
+      </c>
+      <c r="P220" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q220" s="1" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -29554,7 +30251,7 @@
     </row>
     <row r="223" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="1" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="B223" s="1" t="n">
         <v>0.3</v>
@@ -29583,31 +30280,31 @@
     </row>
     <row r="224" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="1" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="G224" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="H224" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="I224" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="J224" s="24" t="s">
         <v>201</v>
       </c>
       <c r="K224" s="24" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29626,8 +30323,8 @@
       <c r="E225" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="F225" s="71" t="s">
-        <v>245</v>
+      <c r="F225" s="87" t="s">
+        <v>256</v>
       </c>
       <c r="J225" s="57" t="s">
         <v>107</v>
@@ -29905,19 +30602,19 @@
     </row>
     <row r="242" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B242" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J242" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -29931,7 +30628,7 @@
     </row>
     <row r="245" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="1" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="B245" s="1" t="n">
         <v>0.4</v>
@@ -29951,21 +30648,21 @@
     </row>
     <row r="246" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="1" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="J246" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G247" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="H247" s="24" t="s">
         <v>201</v>
@@ -29973,7 +30670,7 @@
     </row>
     <row r="248" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="2" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="B248" s="17" t="s">
         <v>102</v>
@@ -29993,8 +30690,44 @@
       <c r="G248" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="H248" s="57" t="s">
+      <c r="H248" s="76" t="s">
         <v>108</v>
+      </c>
+      <c r="I248" s="63" t="s">
+        <v>109</v>
+      </c>
+      <c r="J248" s="63" t="s">
+        <v>110</v>
+      </c>
+      <c r="K248" s="63" t="s">
+        <v>111</v>
+      </c>
+      <c r="L248" s="63" t="s">
+        <v>112</v>
+      </c>
+      <c r="M248" s="63" t="s">
+        <v>113</v>
+      </c>
+      <c r="N248" s="63" t="s">
+        <v>114</v>
+      </c>
+      <c r="O248" s="63" t="s">
+        <v>115</v>
+      </c>
+      <c r="P248" s="63" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q248" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="R248" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="S248" s="56" t="s">
+        <v>150</v>
+      </c>
+      <c r="T248" s="58" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30019,8 +30752,44 @@
       <c r="G249" s="27" t="n">
         <v>0.5</v>
       </c>
-      <c r="H249" s="57" t="n">
-        <v>0.5</v>
+      <c r="H249" s="76" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I249" s="63" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J249" s="63" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K249" s="63" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L249" s="63" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M249" s="63" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N249" s="63" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O249" s="63" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P249" s="63" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q249" s="63" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R249" s="63" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S249" s="56" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T249" s="59" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30034,6 +30803,20 @@
       <c r="F250" s="23"/>
       <c r="G250" s="23"/>
       <c r="H250" s="23"/>
+      <c r="I250" s="23"/>
+      <c r="J250" s="23"/>
+      <c r="K250" s="23"/>
+      <c r="L250" s="23"/>
+      <c r="M250" s="23"/>
+      <c r="N250" s="23"/>
+      <c r="O250" s="23"/>
+      <c r="P250" s="23"/>
+      <c r="Q250" s="23"/>
+      <c r="R250" s="23"/>
+      <c r="S250" s="23"/>
+      <c r="T250" s="49" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="251" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="2" t="s">
@@ -30046,6 +30829,17 @@
       <c r="F251" s="23"/>
       <c r="G251" s="23"/>
       <c r="H251" s="23"/>
+      <c r="I251" s="23"/>
+      <c r="J251" s="23"/>
+      <c r="K251" s="23"/>
+      <c r="L251" s="23"/>
+      <c r="M251" s="23"/>
+      <c r="N251" s="23"/>
+      <c r="O251" s="23"/>
+      <c r="P251" s="23"/>
+      <c r="Q251" s="23"/>
+      <c r="R251" s="23"/>
+      <c r="S251" s="23"/>
     </row>
     <row r="252" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="2" t="s">
@@ -30058,6 +30852,17 @@
       <c r="F252" s="23"/>
       <c r="G252" s="23"/>
       <c r="H252" s="23"/>
+      <c r="I252" s="23"/>
+      <c r="J252" s="23"/>
+      <c r="K252" s="23"/>
+      <c r="L252" s="23"/>
+      <c r="M252" s="23"/>
+      <c r="N252" s="23"/>
+      <c r="O252" s="23"/>
+      <c r="P252" s="23"/>
+      <c r="Q252" s="23"/>
+      <c r="R252" s="23"/>
+      <c r="S252" s="23"/>
     </row>
     <row r="253" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="2" t="s">
@@ -30081,7 +30886,40 @@
       <c r="G253" s="27" t="n">
         <v>0.004</v>
       </c>
-      <c r="H253" s="57" t="n">
+      <c r="H253" s="76" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="I253" s="63" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="J253" s="63" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="K253" s="63" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="L253" s="63" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="M253" s="63" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="N253" s="63" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="O253" s="63" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="P253" s="63" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="Q253" s="63" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="R253" s="63" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="S253" s="56" t="n">
         <v>0.004</v>
       </c>
     </row>
@@ -30107,7 +30945,40 @@
       <c r="G254" s="27" t="n">
         <v>0.4</v>
       </c>
-      <c r="H254" s="57" t="n">
+      <c r="H254" s="76" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I254" s="63" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J254" s="63" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K254" s="63" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L254" s="63" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M254" s="63" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N254" s="63" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O254" s="63" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P254" s="63" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q254" s="63" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R254" s="63" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S254" s="56" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -30133,7 +31004,40 @@
       <c r="G255" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="H255" s="57" t="n">
+      <c r="H255" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="I255" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="J255" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="K255" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L255" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="M255" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="N255" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="O255" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="P255" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q255" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="R255" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="S255" s="56" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30159,8 +31063,41 @@
       <c r="G256" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="H256" s="57" t="n">
+      <c r="H256" s="76" t="n">
         <v>4</v>
+      </c>
+      <c r="I256" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="J256" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="K256" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L256" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M256" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N256" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O256" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P256" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q256" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R256" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="S256" s="56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30185,8 +31122,41 @@
       <c r="G257" s="27" t="n">
         <v>1.2</v>
       </c>
-      <c r="H257" s="57" t="n">
-        <v>1.2</v>
+      <c r="H257" s="76" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I257" s="63" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J257" s="63" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K257" s="63" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L257" s="63" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M257" s="63" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N257" s="63" t="n">
+        <v>10</v>
+      </c>
+      <c r="O257" s="63" t="n">
+        <v>10</v>
+      </c>
+      <c r="P257" s="63" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q257" s="63" t="n">
+        <v>10</v>
+      </c>
+      <c r="R257" s="63" t="n">
+        <v>10</v>
+      </c>
+      <c r="S257" s="56" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30211,8 +31181,41 @@
       <c r="G258" s="27" t="n">
         <v>0.6</v>
       </c>
-      <c r="H258" s="57" t="n">
-        <v>0.6</v>
+      <c r="H258" s="76" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I258" s="63" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J258" s="63" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K258" s="63" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L258" s="63" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M258" s="63" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N258" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O258" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P258" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q258" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R258" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S258" s="56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30237,8 +31240,41 @@
       <c r="G259" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="H259" s="57" t="n">
+      <c r="H259" s="76" t="n">
         <v>10000</v>
+      </c>
+      <c r="I259" s="63" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J259" s="63" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K259" s="63" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L259" s="63" t="n">
+        <v>2000</v>
+      </c>
+      <c r="M259" s="63" t="n">
+        <v>5000</v>
+      </c>
+      <c r="N259" s="63" t="n">
+        <v>5000</v>
+      </c>
+      <c r="O259" s="63" t="n">
+        <v>10000</v>
+      </c>
+      <c r="P259" s="63" t="n">
+        <v>10000</v>
+      </c>
+      <c r="Q259" s="63" t="n">
+        <v>10000</v>
+      </c>
+      <c r="R259" s="63" t="n">
+        <v>10000</v>
+      </c>
+      <c r="S259" s="56" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30252,6 +31288,17 @@
       <c r="F260" s="29"/>
       <c r="G260" s="29"/>
       <c r="H260" s="29"/>
+      <c r="I260" s="29"/>
+      <c r="J260" s="29"/>
+      <c r="K260" s="29"/>
+      <c r="L260" s="29"/>
+      <c r="M260" s="29"/>
+      <c r="N260" s="29"/>
+      <c r="O260" s="29"/>
+      <c r="P260" s="29"/>
+      <c r="Q260" s="29"/>
+      <c r="R260" s="29"/>
+      <c r="S260" s="29"/>
     </row>
     <row r="261" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="22" t="s">
@@ -30264,6 +31311,17 @@
       <c r="F261" s="31"/>
       <c r="G261" s="31"/>
       <c r="H261" s="31"/>
+      <c r="I261" s="31"/>
+      <c r="J261" s="31"/>
+      <c r="K261" s="31"/>
+      <c r="L261" s="31"/>
+      <c r="M261" s="31"/>
+      <c r="N261" s="31"/>
+      <c r="O261" s="31"/>
+      <c r="P261" s="31"/>
+      <c r="Q261" s="31"/>
+      <c r="R261" s="31"/>
+      <c r="S261" s="31"/>
     </row>
     <row r="262" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="17" t="s">
@@ -30287,7 +31345,40 @@
       <c r="G262" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="H262" s="57" t="n">
+      <c r="H262" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="I262" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="J262" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="K262" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="L262" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="M262" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="N262" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="O262" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="P262" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q262" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="R262" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="S262" s="56" t="n">
         <v>3</v>
       </c>
     </row>
@@ -30313,7 +31404,40 @@
       <c r="G263" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="H263" s="57" t="n">
+      <c r="H263" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="I263" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="J263" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="K263" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="L263" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="M263" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="N263" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="O263" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="P263" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q263" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="R263" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="S263" s="56" t="n">
         <v>3</v>
       </c>
     </row>
@@ -30342,31 +31466,113 @@
       <c r="H264" s="5" t="n">
         <v>0.5</v>
       </c>
+      <c r="I264" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J264" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K264" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L264" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M264" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N264" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O264" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P264" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q264" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R264" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S264" s="5" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="265" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B265" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G265" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="H265" s="1" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="266" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+        <v>204</v>
+      </c>
+      <c r="I265" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="J265" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="K265" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="L265" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="M265" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="N265" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="O265" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="P265" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q265" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="R265" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="S265" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="266" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M266" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N266" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="O266" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="P266" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q266" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
     <row r="267" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B267" s="1" t="n">
         <v>1</v>
@@ -30389,10 +31595,22 @@
       <c r="H267" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="O267" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="P267" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q267" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="S267" s="58" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="268" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="1" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="B268" s="1" t="n">
         <v>0.4</v>
@@ -30414,37 +31632,43 @@
       </c>
       <c r="H268" s="1" t="n">
         <v>0.4</v>
+      </c>
+      <c r="S268" s="59" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="1" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="G269" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="H269" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
+      </c>
+      <c r="S269" s="49" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="2" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="B270" s="17" t="s">
         <v>102</v>
@@ -30467,8 +31691,38 @@
       <c r="H270" s="57" t="s">
         <v>108</v>
       </c>
-      <c r="I270" s="24" t="s">
-        <v>201</v>
+      <c r="I270" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="J270" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="K270" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="L270" s="27" t="s">
+        <v>112</v>
+      </c>
+      <c r="M270" s="27" t="s">
+        <v>113</v>
+      </c>
+      <c r="N270" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="O270" s="27" t="s">
+        <v>115</v>
+      </c>
+      <c r="P270" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q270" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="R270" s="45" t="s">
+        <v>118</v>
+      </c>
+      <c r="S270" s="79" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="271" customFormat="false" ht="41.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30494,6 +31748,39 @@
         <v>0.5</v>
       </c>
       <c r="H271" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I271" s="27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J271" s="27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K271" s="27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L271" s="27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M271" s="27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N271" s="27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O271" s="27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P271" s="27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q271" s="27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R271" s="45" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S271" s="79" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -30508,6 +31795,17 @@
       <c r="F272" s="23"/>
       <c r="G272" s="23"/>
       <c r="H272" s="23"/>
+      <c r="I272" s="23"/>
+      <c r="J272" s="23"/>
+      <c r="K272" s="23"/>
+      <c r="L272" s="23"/>
+      <c r="M272" s="23"/>
+      <c r="N272" s="23"/>
+      <c r="O272" s="23"/>
+      <c r="P272" s="23"/>
+      <c r="Q272" s="23"/>
+      <c r="R272" s="23"/>
+      <c r="S272" s="23"/>
     </row>
     <row r="273" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="2" t="s">
@@ -30520,6 +31818,17 @@
       <c r="F273" s="23"/>
       <c r="G273" s="23"/>
       <c r="H273" s="23"/>
+      <c r="I273" s="23"/>
+      <c r="J273" s="23"/>
+      <c r="K273" s="23"/>
+      <c r="L273" s="23"/>
+      <c r="M273" s="23"/>
+      <c r="N273" s="23"/>
+      <c r="O273" s="23"/>
+      <c r="P273" s="23"/>
+      <c r="Q273" s="23"/>
+      <c r="R273" s="23"/>
+      <c r="S273" s="23"/>
     </row>
     <row r="274" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="2" t="s">
@@ -30532,6 +31841,17 @@
       <c r="F274" s="23"/>
       <c r="G274" s="23"/>
       <c r="H274" s="23"/>
+      <c r="I274" s="23"/>
+      <c r="J274" s="23"/>
+      <c r="K274" s="23"/>
+      <c r="L274" s="23"/>
+      <c r="M274" s="23"/>
+      <c r="N274" s="23"/>
+      <c r="O274" s="23"/>
+      <c r="P274" s="23"/>
+      <c r="Q274" s="23"/>
+      <c r="R274" s="23"/>
+      <c r="S274" s="23"/>
     </row>
     <row r="275" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="2" t="s">
@@ -30558,6 +31878,39 @@
       <c r="H275" s="57" t="n">
         <v>0.003</v>
       </c>
+      <c r="I275" s="27" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="J275" s="27" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="K275" s="27" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="L275" s="27" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="M275" s="27" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="N275" s="27" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="O275" s="27" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="P275" s="27" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="Q275" s="27" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="R275" s="45" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="S275" s="79" t="n">
+        <v>0.003</v>
+      </c>
     </row>
     <row r="276" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="2" t="s">
@@ -30584,6 +31937,39 @@
       <c r="H276" s="57" t="n">
         <v>0.4</v>
       </c>
+      <c r="I276" s="27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J276" s="27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K276" s="27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L276" s="27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M276" s="27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N276" s="27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O276" s="27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P276" s="27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q276" s="27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R276" s="45" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S276" s="79" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="277" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="2" t="s">
@@ -30610,6 +31996,39 @@
       <c r="H277" s="57" t="n">
         <v>1</v>
       </c>
+      <c r="I277" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J277" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K277" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L277" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M277" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="N277" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="O277" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="P277" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q277" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="R277" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="S277" s="79" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="278" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="2" t="s">
@@ -30636,6 +32055,39 @@
       <c r="H278" s="57" t="n">
         <v>10</v>
       </c>
+      <c r="I278" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="J278" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="K278" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L278" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M278" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N278" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O278" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P278" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q278" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R278" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S278" s="79" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="279" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="2" t="s">
@@ -30662,6 +32114,39 @@
       <c r="H279" s="57" t="n">
         <v>1.2</v>
       </c>
+      <c r="I279" s="27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J279" s="27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K279" s="27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L279" s="27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M279" s="27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N279" s="27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O279" s="27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P279" s="27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q279" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="R279" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="S279" s="79" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="280" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="2" t="s">
@@ -30688,6 +32173,39 @@
       <c r="H280" s="57" t="n">
         <v>0.6</v>
       </c>
+      <c r="I280" s="27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J280" s="27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K280" s="27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L280" s="27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M280" s="27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N280" s="27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O280" s="27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P280" s="27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q280" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R280" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S280" s="79" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="281" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="2" t="s">
@@ -30712,6 +32230,39 @@
         <v>10000</v>
       </c>
       <c r="H281" s="57" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I281" s="27" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J281" s="27" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K281" s="27" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L281" s="27" t="n">
+        <v>10000</v>
+      </c>
+      <c r="M281" s="27" t="n">
+        <v>10000</v>
+      </c>
+      <c r="N281" s="27" t="n">
+        <v>10000</v>
+      </c>
+      <c r="O281" s="27" t="n">
+        <v>10000</v>
+      </c>
+      <c r="P281" s="27" t="n">
+        <v>10000</v>
+      </c>
+      <c r="Q281" s="27" t="n">
+        <v>10000</v>
+      </c>
+      <c r="R281" s="45" t="n">
+        <v>10000</v>
+      </c>
+      <c r="S281" s="79" t="n">
         <v>10000</v>
       </c>
     </row>
@@ -30726,6 +32277,17 @@
       <c r="F282" s="29"/>
       <c r="G282" s="29"/>
       <c r="H282" s="29"/>
+      <c r="I282" s="29"/>
+      <c r="J282" s="29"/>
+      <c r="K282" s="29"/>
+      <c r="L282" s="29"/>
+      <c r="M282" s="29"/>
+      <c r="N282" s="29"/>
+      <c r="O282" s="29"/>
+      <c r="P282" s="29"/>
+      <c r="Q282" s="29"/>
+      <c r="R282" s="29"/>
+      <c r="S282" s="29"/>
     </row>
     <row r="283" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="22" t="s">
@@ -30738,6 +32300,17 @@
       <c r="F283" s="31"/>
       <c r="G283" s="31"/>
       <c r="H283" s="31"/>
+      <c r="I283" s="31"/>
+      <c r="J283" s="31"/>
+      <c r="K283" s="31"/>
+      <c r="L283" s="31"/>
+      <c r="M283" s="31"/>
+      <c r="N283" s="31"/>
+      <c r="O283" s="31"/>
+      <c r="P283" s="31"/>
+      <c r="Q283" s="31"/>
+      <c r="R283" s="31"/>
+      <c r="S283" s="31"/>
     </row>
     <row r="284" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="17" t="s">
@@ -30764,6 +32337,39 @@
       <c r="H284" s="57" t="n">
         <v>1</v>
       </c>
+      <c r="I284" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="J284" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K284" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="L284" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="M284" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N284" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="O284" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="P284" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q284" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="R284" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="S284" s="79" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="285" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="17" t="s">
@@ -30790,6 +32396,39 @@
       <c r="H285" s="57" t="n">
         <v>1</v>
       </c>
+      <c r="I285" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="J285" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K285" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="L285" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="M285" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N285" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="O285" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="P285" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q285" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="R285" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="S285" s="79" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="286" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="1" t="s">
@@ -30816,32 +32455,121 @@
       <c r="H286" s="5" t="n">
         <v>0.5</v>
       </c>
+      <c r="I286" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J286" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K286" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L286" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M286" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N286" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O286" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P286" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q286" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R286" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S286" s="5" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="287" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B287" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G287" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="H287" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
+      </c>
+      <c r="I287" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="J287" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="K287" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="L287" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="M287" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="N287" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="O287" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="P287" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q287" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="R287" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="S287" s="1" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="288" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N288" s="71"/>
+      <c r="L288" s="0" t="s">
+        <v>260</v>
+      </c>
+      <c r="M288" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N288" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="O288" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="P288" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q288" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="R288" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="S288" s="0" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="289" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B289" s="1" t="n">
@@ -30865,10 +32593,13 @@
       <c r="H289" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="M289" s="72" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="290" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="1" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="B290" s="1" t="n">
         <v>0.4</v>
@@ -30894,42 +32625,48 @@
       <c r="I290" s="1" t="s">
         <v>141</v>
       </c>
+      <c r="M290" s="72" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="291" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="1" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="G291" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="H291" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="I291" s="1" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="J291" s="24" t="s">
         <v>201</v>
       </c>
+      <c r="M291" s="74" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="292" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="2" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="B292" s="17" t="s">
         <v>102</v>
@@ -30955,8 +32692,17 @@
       <c r="I292" s="27" t="s">
         <v>109</v>
       </c>
-      <c r="J292" s="57" t="s">
+      <c r="J292" s="76" t="s">
         <v>110</v>
+      </c>
+      <c r="K292" s="63" t="s">
+        <v>111</v>
+      </c>
+      <c r="L292" s="63" t="s">
+        <v>112</v>
+      </c>
+      <c r="M292" s="56" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="293" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30987,7 +32733,16 @@
       <c r="I293" s="27" t="n">
         <v>0.5</v>
       </c>
-      <c r="J293" s="57" t="n">
+      <c r="J293" s="76" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K293" s="63" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L293" s="63" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M293" s="56" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -31004,6 +32759,9 @@
       <c r="H294" s="23"/>
       <c r="I294" s="23"/>
       <c r="J294" s="23"/>
+      <c r="K294" s="23"/>
+      <c r="L294" s="23"/>
+      <c r="M294" s="23"/>
     </row>
     <row r="295" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="2" t="s">
@@ -31018,6 +32776,9 @@
       <c r="H295" s="23"/>
       <c r="I295" s="23"/>
       <c r="J295" s="23"/>
+      <c r="K295" s="23"/>
+      <c r="L295" s="23"/>
+      <c r="M295" s="23"/>
     </row>
     <row r="296" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="2" t="s">
@@ -31032,6 +32793,9 @@
       <c r="H296" s="23"/>
       <c r="I296" s="23"/>
       <c r="J296" s="23"/>
+      <c r="K296" s="23"/>
+      <c r="L296" s="23"/>
+      <c r="M296" s="23"/>
     </row>
     <row r="297" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A297" s="2" t="s">
@@ -31061,7 +32825,16 @@
       <c r="I297" s="27" t="n">
         <v>0.02</v>
       </c>
-      <c r="J297" s="57" t="n">
+      <c r="J297" s="76" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K297" s="63" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L297" s="63" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M297" s="56" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -31093,7 +32866,16 @@
       <c r="I298" s="27" t="n">
         <v>0.4</v>
       </c>
-      <c r="J298" s="57" t="n">
+      <c r="J298" s="76" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K298" s="63" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L298" s="63" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M298" s="56" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -31125,7 +32907,16 @@
       <c r="I299" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="J299" s="57" t="n">
+      <c r="J299" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="K299" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L299" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="M299" s="56" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31157,8 +32948,17 @@
       <c r="I300" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="J300" s="57" t="n">
+      <c r="J300" s="76" t="n">
         <v>5</v>
+      </c>
+      <c r="K300" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="L300" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M300" s="56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="301" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31189,7 +32989,16 @@
       <c r="I301" s="27" t="n">
         <v>1.2</v>
       </c>
-      <c r="J301" s="57" t="n">
+      <c r="J301" s="76" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K301" s="63" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L301" s="63" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M301" s="56" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -31221,7 +33030,16 @@
       <c r="I302" s="27" t="n">
         <v>0.6</v>
       </c>
-      <c r="J302" s="57" t="n">
+      <c r="J302" s="76" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K302" s="63" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L302" s="63" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M302" s="56" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -31253,8 +33071,17 @@
       <c r="I303" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="J303" s="57" t="n">
+      <c r="J303" s="76" t="n">
         <v>10000</v>
+      </c>
+      <c r="K303" s="63" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L303" s="63" t="n">
+        <v>2000</v>
+      </c>
+      <c r="M303" s="56" t="n">
+        <v>5000</v>
       </c>
     </row>
     <row r="304" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31269,7 +33096,10 @@
       <c r="G304" s="29"/>
       <c r="H304" s="29"/>
       <c r="I304" s="29"/>
-      <c r="J304" s="29"/>
+      <c r="J304" s="81"/>
+      <c r="K304" s="29"/>
+      <c r="L304" s="29"/>
+      <c r="M304" s="29"/>
     </row>
     <row r="305" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="22" t="s">
@@ -31283,7 +33113,10 @@
       <c r="G305" s="31"/>
       <c r="H305" s="31"/>
       <c r="I305" s="31"/>
-      <c r="J305" s="31"/>
+      <c r="J305" s="81"/>
+      <c r="K305" s="31"/>
+      <c r="L305" s="31"/>
+      <c r="M305" s="31"/>
     </row>
     <row r="306" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="17" t="s">
@@ -31313,8 +33146,17 @@
       <c r="I306" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="J306" s="57" t="n">
-        <v>2</v>
+      <c r="J306" s="76" t="n">
+        <v>2</v>
+      </c>
+      <c r="K306" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="L306" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="M306" s="56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="307" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31345,8 +33187,17 @@
       <c r="I307" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="J307" s="57" t="n">
-        <v>2</v>
+      <c r="J307" s="76" t="n">
+        <v>2</v>
+      </c>
+      <c r="K307" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="L307" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="M307" s="56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="308" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31380,34 +33231,52 @@
       <c r="J308" s="5" t="n">
         <v>0.5</v>
       </c>
+      <c r="K308" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L308" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M308" s="5" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="309" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B309" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F309" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G309" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="H309" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I309" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J309" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
+      </c>
+      <c r="K309" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="L309" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="M309" s="1" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="310" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -31439,10 +33308,11 @@
       <c r="J311" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="K311" s="1"/>
     </row>
     <row r="312" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A312" s="1" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="B312" s="1" t="n">
         <v>0.4</v>
@@ -31471,42 +33341,44 @@
       <c r="J312" s="1" t="n">
         <v>0.4</v>
       </c>
+      <c r="K312" s="1"/>
     </row>
     <row r="313" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="1" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="G313" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="H313" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="I313" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="J313" s="1" t="s">
-        <v>243</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="K313" s="1"/>
     </row>
     <row r="314" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A314" s="72" t="s">
-        <v>251</v>
+      <c r="A314" s="88" t="s">
+        <v>263</v>
       </c>
       <c r="B314" s="17" t="s">
         <v>102</v>
@@ -31515,11 +33387,11 @@
         <v>103</v>
       </c>
       <c r="D314" s="24" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
     </row>
     <row r="315" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A315" s="72" t="s">
+      <c r="A315" s="88" t="s">
         <v>80</v>
       </c>
       <c r="B315" s="17" t="n">
@@ -31530,28 +33402,28 @@
       </c>
     </row>
     <row r="316" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A316" s="72" t="s">
+      <c r="A316" s="88" t="s">
         <v>120</v>
       </c>
       <c r="B316" s="23"/>
       <c r="C316" s="23"/>
     </row>
     <row r="317" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A317" s="72" t="s">
+      <c r="A317" s="88" t="s">
         <v>82</v>
       </c>
       <c r="B317" s="23"/>
       <c r="C317" s="23"/>
     </row>
     <row r="318" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A318" s="72" t="s">
+      <c r="A318" s="88" t="s">
         <v>121</v>
       </c>
       <c r="B318" s="23"/>
       <c r="C318" s="23"/>
     </row>
     <row r="319" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A319" s="72" t="s">
+      <c r="A319" s="88" t="s">
         <v>84</v>
       </c>
       <c r="B319" s="17" t="n">
@@ -31562,7 +33434,7 @@
       </c>
     </row>
     <row r="320" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A320" s="72" t="s">
+      <c r="A320" s="88" t="s">
         <v>79</v>
       </c>
       <c r="B320" s="17" t="n">
@@ -31573,7 +33445,7 @@
       </c>
     </row>
     <row r="321" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A321" s="72" t="s">
+      <c r="A321" s="88" t="s">
         <v>85</v>
       </c>
       <c r="B321" s="17" t="n">
@@ -31584,7 +33456,7 @@
       </c>
     </row>
     <row r="322" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A322" s="72" t="s">
+      <c r="A322" s="88" t="s">
         <v>122</v>
       </c>
       <c r="B322" s="17" t="n">
@@ -31595,7 +33467,7 @@
       </c>
     </row>
     <row r="323" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A323" s="72" t="s">
+      <c r="A323" s="88" t="s">
         <v>123</v>
       </c>
       <c r="B323" s="17" t="n">
@@ -31606,7 +33478,7 @@
       </c>
     </row>
     <row r="324" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A324" s="72" t="s">
+      <c r="A324" s="88" t="s">
         <v>124</v>
       </c>
       <c r="B324" s="17" t="n">
@@ -31617,7 +33489,7 @@
       </c>
     </row>
     <row r="325" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A325" s="72" t="s">
+      <c r="A325" s="88" t="s">
         <v>125</v>
       </c>
       <c r="B325" s="17" t="n">
@@ -31628,21 +33500,21 @@
       </c>
     </row>
     <row r="326" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A326" s="72" t="s">
+      <c r="A326" s="88" t="s">
         <v>126</v>
       </c>
       <c r="B326" s="29"/>
       <c r="C326" s="29"/>
     </row>
     <row r="327" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A327" s="73" t="s">
+      <c r="A327" s="89" t="s">
         <v>128</v>
       </c>
       <c r="B327" s="31"/>
       <c r="C327" s="31"/>
     </row>
     <row r="328" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A328" s="72" t="s">
+      <c r="A328" s="88" t="s">
         <v>134</v>
       </c>
       <c r="B328" s="17" t="n">
@@ -31653,7 +33525,7 @@
       </c>
     </row>
     <row r="329" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A329" s="72" t="s">
+      <c r="A329" s="88" t="s">
         <v>136</v>
       </c>
       <c r="B329" s="17" t="n">
@@ -31664,7 +33536,7 @@
       </c>
     </row>
     <row r="330" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A330" s="74" t="s">
+      <c r="A330" s="90" t="s">
         <v>157</v>
       </c>
       <c r="B330" s="5" t="n">
@@ -31676,10 +33548,10 @@
     </row>
     <row r="331" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B331" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C331" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="332" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -31693,7 +33565,7 @@
     </row>
     <row r="334" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A334" s="1" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="B334" s="1" t="n">
         <v>0.4</v>
@@ -31704,25 +33576,25 @@
     </row>
     <row r="335" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A335" s="1" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
     </row>
     <row r="336" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A336" s="72" t="s">
-        <v>253</v>
+      <c r="A336" s="88" t="s">
+        <v>265</v>
       </c>
       <c r="B336" s="17" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="337" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A337" s="72" t="s">
+      <c r="A337" s="88" t="s">
         <v>80</v>
       </c>
       <c r="B337" s="17" t="n">
@@ -31730,25 +33602,25 @@
       </c>
     </row>
     <row r="338" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A338" s="72" t="s">
+      <c r="A338" s="88" t="s">
         <v>120</v>
       </c>
       <c r="B338" s="23"/>
     </row>
     <row r="339" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A339" s="72" t="s">
+      <c r="A339" s="88" t="s">
         <v>82</v>
       </c>
       <c r="B339" s="23"/>
     </row>
     <row r="340" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A340" s="72" t="s">
+      <c r="A340" s="88" t="s">
         <v>121</v>
       </c>
       <c r="B340" s="23"/>
     </row>
     <row r="341" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A341" s="72" t="s">
+      <c r="A341" s="88" t="s">
         <v>84</v>
       </c>
       <c r="B341" s="17" t="n">
@@ -31756,7 +33628,7 @@
       </c>
     </row>
     <row r="342" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A342" s="72" t="s">
+      <c r="A342" s="88" t="s">
         <v>79</v>
       </c>
       <c r="B342" s="17" t="n">
@@ -31764,7 +33636,7 @@
       </c>
     </row>
     <row r="343" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A343" s="72" t="s">
+      <c r="A343" s="88" t="s">
         <v>85</v>
       </c>
       <c r="B343" s="17" t="n">
@@ -31772,7 +33644,7 @@
       </c>
     </row>
     <row r="344" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A344" s="72" t="s">
+      <c r="A344" s="88" t="s">
         <v>122</v>
       </c>
       <c r="B344" s="17" t="n">
@@ -31780,7 +33652,7 @@
       </c>
     </row>
     <row r="345" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A345" s="72" t="s">
+      <c r="A345" s="88" t="s">
         <v>123</v>
       </c>
       <c r="B345" s="17" t="n">
@@ -31788,7 +33660,7 @@
       </c>
     </row>
     <row r="346" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A346" s="72" t="s">
+      <c r="A346" s="88" t="s">
         <v>124</v>
       </c>
       <c r="B346" s="17" t="n">
@@ -31796,7 +33668,7 @@
       </c>
     </row>
     <row r="347" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A347" s="72" t="s">
+      <c r="A347" s="88" t="s">
         <v>125</v>
       </c>
       <c r="B347" s="17" t="n">
@@ -31804,19 +33676,19 @@
       </c>
     </row>
     <row r="348" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A348" s="72" t="s">
+      <c r="A348" s="88" t="s">
         <v>126</v>
       </c>
       <c r="B348" s="29"/>
     </row>
     <row r="349" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A349" s="73" t="s">
+      <c r="A349" s="89" t="s">
         <v>128</v>
       </c>
       <c r="B349" s="31"/>
     </row>
     <row r="350" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A350" s="72" t="s">
+      <c r="A350" s="88" t="s">
         <v>134</v>
       </c>
       <c r="B350" s="17" t="n">
@@ -31824,7 +33696,7 @@
       </c>
     </row>
     <row r="351" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A351" s="72" t="s">
+      <c r="A351" s="88" t="s">
         <v>136</v>
       </c>
       <c r="B351" s="17" t="n">
@@ -31832,7 +33704,7 @@
       </c>
     </row>
     <row r="352" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A352" s="74" t="s">
+      <c r="A352" s="90" t="s">
         <v>157</v>
       </c>
       <c r="B352" s="5" t="n">
@@ -31841,7 +33713,7 @@
     </row>
     <row r="353" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B353" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="354" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -31849,29 +33721,38 @@
       <c r="B355" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="H355" s="58" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="356" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="1" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="B356" s="1" t="n">
         <v>0.4</v>
+      </c>
+      <c r="H356" s="59" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="357" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A357" s="1" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="G357" s="24" t="s">
-        <v>254</v>
+        <v>266</v>
+      </c>
+      <c r="H357" s="49" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="358" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="2" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="B358" s="17" t="s">
         <v>102</v>
@@ -31888,8 +33769,11 @@
       <c r="F358" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="G358" s="57" t="s">
+      <c r="G358" s="76" t="s">
         <v>107</v>
+      </c>
+      <c r="H358" s="57" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="359" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31911,7 +33795,10 @@
       <c r="F359" s="18" t="n">
         <v>0.5</v>
       </c>
-      <c r="G359" s="57" t="n">
+      <c r="G359" s="76" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H359" s="57" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -31925,6 +33812,7 @@
       <c r="E360" s="23"/>
       <c r="F360" s="23"/>
       <c r="G360" s="23"/>
+      <c r="H360" s="23"/>
     </row>
     <row r="361" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A361" s="2" t="s">
@@ -31936,6 +33824,7 @@
       <c r="E361" s="23"/>
       <c r="F361" s="23"/>
       <c r="G361" s="23"/>
+      <c r="H361" s="23"/>
     </row>
     <row r="362" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A362" s="2" t="s">
@@ -31947,6 +33836,7 @@
       <c r="E362" s="23"/>
       <c r="F362" s="23"/>
       <c r="G362" s="23"/>
+      <c r="H362" s="23"/>
     </row>
     <row r="363" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A363" s="2" t="s">
@@ -31967,7 +33857,10 @@
       <c r="F363" s="18" t="n">
         <v>0.008</v>
       </c>
-      <c r="G363" s="57" t="n">
+      <c r="G363" s="76" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="H363" s="57" t="n">
         <v>0.008</v>
       </c>
     </row>
@@ -31990,7 +33883,10 @@
       <c r="F364" s="18" t="n">
         <v>0.4</v>
       </c>
-      <c r="G364" s="57" t="n">
+      <c r="G364" s="76" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H364" s="57" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -32013,7 +33909,10 @@
       <c r="F365" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G365" s="57" t="n">
+      <c r="G365" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="H365" s="57" t="n">
         <v>1</v>
       </c>
     </row>
@@ -32036,8 +33935,11 @@
       <c r="F366" s="18" t="n">
         <v>9</v>
       </c>
-      <c r="G366" s="57" t="n">
+      <c r="G366" s="76" t="n">
         <v>9</v>
+      </c>
+      <c r="H366" s="57" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="367" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32059,7 +33961,10 @@
       <c r="F367" s="18" t="n">
         <v>1.2</v>
       </c>
-      <c r="G367" s="57" t="n">
+      <c r="G367" s="76" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H367" s="57" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -32082,7 +33987,10 @@
       <c r="F368" s="18" t="n">
         <v>0.6</v>
       </c>
-      <c r="G368" s="57" t="n">
+      <c r="G368" s="76" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H368" s="57" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -32105,8 +34013,11 @@
       <c r="F369" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="G369" s="57" t="n">
+      <c r="G369" s="76" t="n">
         <v>12000</v>
+      </c>
+      <c r="H369" s="57" t="n">
+        <v>6000</v>
       </c>
     </row>
     <row r="370" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32119,6 +34030,7 @@
       <c r="E370" s="29"/>
       <c r="F370" s="29"/>
       <c r="G370" s="29"/>
+      <c r="H370" s="29"/>
     </row>
     <row r="371" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A371" s="22" t="s">
@@ -32129,7 +34041,8 @@
       <c r="D371" s="31"/>
       <c r="E371" s="31"/>
       <c r="F371" s="31"/>
-      <c r="G371" s="31"/>
+      <c r="G371" s="81"/>
+      <c r="H371" s="31"/>
     </row>
     <row r="372" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A372" s="17" t="s">
@@ -32150,7 +34063,10 @@
       <c r="F372" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="G372" s="57" t="n">
+      <c r="G372" s="76" t="n">
+        <v>4</v>
+      </c>
+      <c r="H372" s="57" t="n">
         <v>4</v>
       </c>
     </row>
@@ -32173,7 +34089,10 @@
       <c r="F373" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="G373" s="57" t="n">
+      <c r="G373" s="76" t="n">
+        <v>4</v>
+      </c>
+      <c r="H373" s="57" t="n">
         <v>4</v>
       </c>
     </row>
@@ -32199,25 +34118,31 @@
       <c r="G374" s="5" t="n">
         <v>0.5</v>
       </c>
+      <c r="H374" s="5" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="375" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B375" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C375" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D375" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E375" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F375" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G375" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
+      </c>
+      <c r="H375" s="1" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="376" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -32243,7 +34168,7 @@
     </row>
     <row r="378" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A378" s="1" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="B378" s="1" t="n">
         <v>0.4</v>
@@ -32266,30 +34191,30 @@
     </row>
     <row r="379" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A379" s="1" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B379" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="C379" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="D379" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="E379" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="F379" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="G379" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
     </row>
     <row r="380" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A380" s="2" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="B380" s="17" t="s">
         <v>102</v>
@@ -32300,8 +34225,14 @@
       <c r="D380" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="E380" s="57" t="s">
+      <c r="E380" s="76" t="s">
         <v>105</v>
+      </c>
+      <c r="F380" s="57" t="s">
+        <v>106</v>
+      </c>
+      <c r="G380" s="58" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="381" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32317,8 +34248,14 @@
       <c r="D381" s="27" t="n">
         <v>0.5</v>
       </c>
-      <c r="E381" s="57" t="n">
-        <v>0.5</v>
+      <c r="E381" s="76" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F381" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G381" s="59" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="382" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32329,6 +34266,10 @@
       <c r="C382" s="23"/>
       <c r="D382" s="23"/>
       <c r="E382" s="23"/>
+      <c r="F382" s="23"/>
+      <c r="G382" s="49" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="383" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A383" s="2" t="s">
@@ -32338,6 +34279,7 @@
       <c r="C383" s="23"/>
       <c r="D383" s="23"/>
       <c r="E383" s="23"/>
+      <c r="F383" s="23"/>
     </row>
     <row r="384" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A384" s="2" t="s">
@@ -32347,6 +34289,7 @@
       <c r="C384" s="23"/>
       <c r="D384" s="23"/>
       <c r="E384" s="23"/>
+      <c r="F384" s="23"/>
     </row>
     <row r="385" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A385" s="2" t="s">
@@ -32361,7 +34304,10 @@
       <c r="D385" s="27" t="n">
         <v>0.005</v>
       </c>
-      <c r="E385" s="57" t="n">
+      <c r="E385" s="76" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F385" s="57" t="n">
         <v>0.005</v>
       </c>
     </row>
@@ -32378,7 +34324,10 @@
       <c r="D386" s="27" t="n">
         <v>0.4</v>
       </c>
-      <c r="E386" s="57" t="n">
+      <c r="E386" s="76" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F386" s="57" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -32395,7 +34344,10 @@
       <c r="D387" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="E387" s="57" t="n">
+      <c r="E387" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="F387" s="57" t="n">
         <v>1</v>
       </c>
     </row>
@@ -32412,7 +34364,10 @@
       <c r="D388" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="E388" s="57" t="n">
+      <c r="E388" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="F388" s="57" t="n">
         <v>3</v>
       </c>
     </row>
@@ -32429,7 +34384,10 @@
       <c r="D389" s="27" t="n">
         <v>1.2</v>
       </c>
-      <c r="E389" s="57" t="n">
+      <c r="E389" s="76" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F389" s="57" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -32446,7 +34404,10 @@
       <c r="D390" s="27" t="n">
         <v>0.6</v>
       </c>
-      <c r="E390" s="57" t="n">
+      <c r="E390" s="76" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F390" s="57" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -32463,7 +34424,10 @@
       <c r="D391" s="27" t="n">
         <v>25000</v>
       </c>
-      <c r="E391" s="57" t="n">
+      <c r="E391" s="76" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F391" s="57" t="n">
         <v>25000</v>
       </c>
     </row>
@@ -32475,6 +34439,7 @@
       <c r="C392" s="29"/>
       <c r="D392" s="29"/>
       <c r="E392" s="29"/>
+      <c r="F392" s="29"/>
     </row>
     <row r="393" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A393" s="22" t="s">
@@ -32484,6 +34449,7 @@
       <c r="C393" s="31"/>
       <c r="D393" s="31"/>
       <c r="E393" s="31"/>
+      <c r="F393" s="31"/>
     </row>
     <row r="394" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A394" s="17" t="s">
@@ -32498,7 +34464,10 @@
       <c r="D394" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="E394" s="57" t="n">
+      <c r="E394" s="76" t="n">
+        <v>2</v>
+      </c>
+      <c r="F394" s="57" t="n">
         <v>2</v>
       </c>
     </row>
@@ -32515,7 +34484,10 @@
       <c r="D395" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="E395" s="57" t="n">
+      <c r="E395" s="76" t="n">
+        <v>2</v>
+      </c>
+      <c r="F395" s="57" t="n">
         <v>2</v>
       </c>
     </row>
@@ -32535,25 +34507,34 @@
       <c r="E396" s="5" t="n">
         <v>0.5</v>
       </c>
+      <c r="F396" s="5" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="397" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B397" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C397" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D397" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E397" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
+      </c>
+      <c r="F397" s="1" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="398" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E398" s="24" t="s">
         <v>201</v>
       </c>
+      <c r="F398" s="24" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="399" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B399" s="1" t="n">
@@ -32568,10 +34549,13 @@
       <c r="E399" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="F399" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="400" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A400" s="1" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="B400" s="1" t="n">
         <v>0.4</v>
@@ -32583,15 +34567,18 @@
         <v>0.4</v>
       </c>
       <c r="E400" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F400" s="1" t="n">
         <v>0.4</v>
       </c>
     </row>
     <row r="401" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A401" s="1" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="K401" s="24" t="s">
         <v>201</v>
@@ -32599,7 +34586,7 @@
     </row>
     <row r="402" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A402" s="2" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="B402" s="17" t="s">
         <v>102</v>
@@ -33094,34 +35081,34 @@
     </row>
     <row r="419" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B419" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C419" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D419" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E419" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F419" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G419" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="H419" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I419" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J419" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K419" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="420" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -33159,7 +35146,7 @@
     </row>
     <row r="422" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A422" s="1" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="B422" s="1" t="n">
         <v>0.4</v>
@@ -33194,37 +35181,37 @@
     </row>
     <row r="423" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A423" s="1" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="C423" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="D423" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="E423" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="F423" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="G423" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="H423" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="I423" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="J423" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="K423" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>

--- a/parameters script.xlsx
+++ b/parameters script.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2181" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2213" uniqueCount="276">
   <si>
     <t xml:space="preserve">6h 3</t>
   </si>
@@ -666,10 +666,13 @@
     <t xml:space="preserve">12H-3</t>
   </si>
   <si>
-    <t xml:space="preserve">17-5</t>
+    <t xml:space="preserve">LAST ONE</t>
   </si>
   <si>
-    <t xml:space="preserve">LAST ONE</t>
+    <t xml:space="preserve">7-6-26-V3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEFINITIVO</t>
   </si>
   <si>
     <t xml:space="preserve">3-6-26-OH</t>
@@ -681,7 +684,10 @@
     <t xml:space="preserve">3 may V3</t>
   </si>
   <si>
-    <t xml:space="preserve">DEFINITIVO</t>
+    <t xml:space="preserve">V3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17-5</t>
   </si>
   <si>
     <t xml:space="preserve">12H-4</t>
@@ -705,10 +711,10 @@
     <t xml:space="preserve">18H-2</t>
   </si>
   <si>
-    <t xml:space="preserve">4 may V3(INV MASK)</t>
+    <t xml:space="preserve">8 good</t>
   </si>
   <si>
-    <t xml:space="preserve">V3</t>
+    <t xml:space="preserve">4 may V3(INV MASK)</t>
   </si>
   <si>
     <t xml:space="preserve">V2(INV MASK)</t>
@@ -720,7 +726,16 @@
     <t xml:space="preserve">V2(INV MASK) LAST</t>
   </si>
   <si>
+    <t xml:space="preserve">V3(INV MASK) LAST</t>
+  </si>
+  <si>
     <t xml:space="preserve">18H-2-VAMP7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INTENTAR MAS EROSION 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V3(INV MASK)</t>
   </si>
   <si>
     <t xml:space="preserve">no funciona</t>
@@ -943,6 +958,13 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="11"/>
       <color rgb="FFFF4000"/>
@@ -953,13 +975,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF4000"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1203,7 +1218,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="96">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1428,7 +1443,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1444,20 +1463,40 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="19" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -1468,7 +1507,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="15" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="15" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1478,6 +1517,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="15" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -1508,10 +1551,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="15" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1524,20 +1563,8 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -1566,6 +1593,14 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -22480,7 +22515,13 @@
       <c r="H1" s="57" t="s">
         <v>108</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="57" t="s">
+        <v>109</v>
+      </c>
+      <c r="J1" s="58" t="s">
+        <v>110</v>
+      </c>
+      <c r="K1" s="59" t="s">
         <v>201</v>
       </c>
     </row>
@@ -22508,6 +22549,15 @@
       </c>
       <c r="H2" s="57" t="n">
         <v>0.5</v>
+      </c>
+      <c r="I2" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J2" s="58" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K2" s="60" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22520,7 +22570,12 @@
       <c r="E3" s="23"/>
       <c r="F3" s="23"/>
       <c r="G3" s="23"/>
-      <c r="H3" s="23"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="49" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
@@ -22532,7 +22587,9 @@
       <c r="E4" s="23"/>
       <c r="F4" s="23"/>
       <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
@@ -22544,7 +22601,9 @@
       <c r="E5" s="23"/>
       <c r="F5" s="23"/>
       <c r="G5" s="23"/>
-      <c r="H5" s="23"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
@@ -22571,6 +22630,12 @@
       <c r="H6" s="57" t="n">
         <v>0.0085</v>
       </c>
+      <c r="I6" s="57" t="n">
+        <v>0.0085</v>
+      </c>
+      <c r="J6" s="58" t="n">
+        <v>0.0085</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
@@ -22597,6 +22662,12 @@
       <c r="H7" s="57" t="n">
         <v>0.4</v>
       </c>
+      <c r="I7" s="57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J7" s="58" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
@@ -22623,6 +22694,12 @@
       <c r="H8" s="57" t="n">
         <v>1</v>
       </c>
+      <c r="I8" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="58" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
@@ -22649,6 +22726,12 @@
       <c r="H9" s="57" t="n">
         <v>9</v>
       </c>
+      <c r="I9" s="57" t="n">
+        <v>6</v>
+      </c>
+      <c r="J9" s="58" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
@@ -22675,6 +22758,12 @@
       <c r="H10" s="57" t="n">
         <v>1.2</v>
       </c>
+      <c r="I10" s="57" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J10" s="58" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
@@ -22701,6 +22790,12 @@
       <c r="H11" s="57" t="n">
         <v>0.6</v>
       </c>
+      <c r="I11" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J11" s="58" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
@@ -22725,6 +22820,12 @@
         <v>20000</v>
       </c>
       <c r="H12" s="57" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I12" s="57" t="n">
+        <v>20000</v>
+      </c>
+      <c r="J12" s="58" t="n">
         <v>20000</v>
       </c>
     </row>
@@ -22738,7 +22839,9 @@
       <c r="E13" s="29"/>
       <c r="F13" s="29"/>
       <c r="G13" s="29"/>
-      <c r="H13" s="29"/>
+      <c r="H13" s="62"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="29"/>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="22" t="s">
@@ -22749,8 +22852,10 @@
       <c r="D14" s="31"/>
       <c r="E14" s="31"/>
       <c r="F14" s="31"/>
-      <c r="G14" s="31"/>
-      <c r="H14" s="31"/>
+      <c r="G14" s="62"/>
+      <c r="H14" s="62"/>
+      <c r="I14" s="31"/>
+      <c r="J14" s="31"/>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
@@ -22777,6 +22882,12 @@
       <c r="H15" s="57" t="n">
         <v>4</v>
       </c>
+      <c r="I15" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="J15" s="58" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="17" t="s">
@@ -22803,6 +22914,12 @@
       <c r="H16" s="57" t="n">
         <v>4</v>
       </c>
+      <c r="I16" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="J16" s="58" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
@@ -22829,62 +22946,63 @@
       <c r="H17" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="N17" s="58" t="s">
-        <v>202</v>
+      <c r="I17" s="63"/>
+      <c r="N17" s="59" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="N18" s="59" t="s">
-        <v>203</v>
+      <c r="N18" s="60" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E19" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="G19" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="H19" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="G19" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>204</v>
-      </c>
       <c r="I19" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="K19" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="J19" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>204</v>
-      </c>
       <c r="L19" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M19" s="24" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="N19" s="49" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B20" s="17" t="s">
         <v>102</v>
@@ -22922,7 +23040,7 @@
       <c r="M20" s="27" t="s">
         <v>113</v>
       </c>
-      <c r="N20" s="60" t="s">
+      <c r="N20" s="64" t="s">
         <v>114</v>
       </c>
     </row>
@@ -22966,7 +23084,7 @@
       <c r="M21" s="27" t="n">
         <v>0.5</v>
       </c>
-      <c r="N21" s="60" t="n">
+      <c r="N21" s="64" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -22986,7 +23104,7 @@
       <c r="K22" s="23"/>
       <c r="L22" s="23"/>
       <c r="M22" s="23"/>
-      <c r="N22" s="61"/>
+      <c r="N22" s="65"/>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
@@ -23004,7 +23122,7 @@
       <c r="K23" s="23"/>
       <c r="L23" s="23"/>
       <c r="M23" s="23"/>
-      <c r="N23" s="61"/>
+      <c r="N23" s="65"/>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
@@ -23022,7 +23140,7 @@
       <c r="K24" s="23"/>
       <c r="L24" s="23"/>
       <c r="M24" s="23"/>
-      <c r="N24" s="61"/>
+      <c r="N24" s="65"/>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
@@ -23064,7 +23182,7 @@
       <c r="M25" s="27" t="n">
         <v>0.0125</v>
       </c>
-      <c r="N25" s="60" t="n">
+      <c r="N25" s="64" t="n">
         <v>0.0125</v>
       </c>
     </row>
@@ -23108,7 +23226,7 @@
       <c r="M26" s="27" t="n">
         <v>0.4</v>
       </c>
-      <c r="N26" s="60" t="n">
+      <c r="N26" s="64" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -23152,7 +23270,7 @@
       <c r="M27" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="N27" s="60" t="n">
+      <c r="N27" s="64" t="n">
         <v>1</v>
       </c>
     </row>
@@ -23196,7 +23314,7 @@
       <c r="M28" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="N28" s="60" t="n">
+      <c r="N28" s="64" t="n">
         <v>8</v>
       </c>
     </row>
@@ -23240,7 +23358,7 @@
       <c r="M29" s="27" t="n">
         <v>1.2</v>
       </c>
-      <c r="N29" s="60" t="n">
+      <c r="N29" s="64" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -23284,7 +23402,7 @@
       <c r="M30" s="27" t="n">
         <v>0.6</v>
       </c>
-      <c r="N30" s="60" t="n">
+      <c r="N30" s="64" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -23328,7 +23446,7 @@
       <c r="M31" s="27" t="n">
         <v>15000</v>
       </c>
-      <c r="N31" s="60" t="n">
+      <c r="N31" s="64" t="n">
         <v>15000</v>
       </c>
     </row>
@@ -23348,7 +23466,7 @@
       <c r="K32" s="29"/>
       <c r="L32" s="29"/>
       <c r="M32" s="29"/>
-      <c r="N32" s="62"/>
+      <c r="N32" s="66"/>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="22" t="s">
@@ -23366,7 +23484,7 @@
       <c r="K33" s="31"/>
       <c r="L33" s="31"/>
       <c r="M33" s="31"/>
-      <c r="N33" s="62"/>
+      <c r="N33" s="66"/>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="17" t="s">
@@ -23408,7 +23526,7 @@
       <c r="M34" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="N34" s="60" t="n">
+      <c r="N34" s="64" t="n">
         <v>4</v>
       </c>
     </row>
@@ -23452,7 +23570,7 @@
       <c r="M35" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="N35" s="60" t="n">
+      <c r="N35" s="64" t="n">
         <v>4</v>
       </c>
     </row>
@@ -23502,36 +23620,36 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B38" s="17" t="s">
         <v>102</v>
@@ -23546,7 +23664,7 @@
         <v>105</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G38" s="27" t="s">
         <v>107</v>
@@ -23563,8 +23681,17 @@
       <c r="K38" s="56" t="s">
         <v>111</v>
       </c>
-      <c r="L38" s="58" t="s">
-        <v>202</v>
+      <c r="L38" s="56" t="s">
+        <v>112</v>
+      </c>
+      <c r="M38" s="56" t="s">
+        <v>113</v>
+      </c>
+      <c r="N38" s="67" t="s">
+        <v>114</v>
+      </c>
+      <c r="O38" s="59" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23586,20 +23713,29 @@
       <c r="G39" s="27" t="n">
         <v>0.5</v>
       </c>
-      <c r="H39" s="27" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I39" s="27" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J39" s="63" t="n">
+      <c r="H39" s="56" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I39" s="56" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J39" s="56" t="n">
         <v>0.5</v>
       </c>
       <c r="K39" s="56" t="n">
         <v>0.5</v>
       </c>
-      <c r="L39" s="59" t="s">
-        <v>203</v>
+      <c r="L39" s="56" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M39" s="56" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N39" s="67" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O39" s="60" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23611,12 +23747,15 @@
       <c r="D40" s="23"/>
       <c r="E40" s="23"/>
       <c r="G40" s="23"/>
-      <c r="H40" s="23"/>
-      <c r="I40" s="23"/>
-      <c r="J40" s="23"/>
-      <c r="K40" s="23"/>
-      <c r="L40" s="49" t="s">
-        <v>206</v>
+      <c r="H40" s="61"/>
+      <c r="I40" s="61"/>
+      <c r="J40" s="61"/>
+      <c r="K40" s="61"/>
+      <c r="L40" s="61"/>
+      <c r="M40" s="61"/>
+      <c r="N40" s="23"/>
+      <c r="O40" s="49" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23628,10 +23767,13 @@
       <c r="D41" s="23"/>
       <c r="E41" s="23"/>
       <c r="G41" s="23"/>
-      <c r="H41" s="23"/>
-      <c r="I41" s="23"/>
-      <c r="J41" s="23"/>
-      <c r="K41" s="23"/>
+      <c r="H41" s="61"/>
+      <c r="I41" s="61"/>
+      <c r="J41" s="61"/>
+      <c r="K41" s="61"/>
+      <c r="L41" s="61"/>
+      <c r="M41" s="61"/>
+      <c r="N41" s="23"/>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
@@ -23642,10 +23784,13 @@
       <c r="D42" s="23"/>
       <c r="E42" s="23"/>
       <c r="G42" s="23"/>
-      <c r="H42" s="23"/>
-      <c r="I42" s="23"/>
-      <c r="J42" s="23"/>
-      <c r="K42" s="23"/>
+      <c r="H42" s="61"/>
+      <c r="I42" s="61"/>
+      <c r="J42" s="61"/>
+      <c r="K42" s="61"/>
+      <c r="L42" s="61"/>
+      <c r="M42" s="61"/>
+      <c r="N42" s="23"/>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
@@ -23672,10 +23817,19 @@
       <c r="I43" s="56" t="n">
         <v>0.0025</v>
       </c>
-      <c r="J43" s="63" t="n">
+      <c r="J43" s="56" t="n">
         <v>0.00225</v>
       </c>
       <c r="K43" s="56" t="n">
+        <v>0.00225</v>
+      </c>
+      <c r="L43" s="56" t="n">
+        <v>0.00225</v>
+      </c>
+      <c r="M43" s="56" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="N43" s="67" t="n">
         <v>0.00225</v>
       </c>
     </row>
@@ -23698,16 +23852,25 @@
       <c r="G44" s="27" t="n">
         <v>0.4</v>
       </c>
-      <c r="H44" s="27" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I44" s="27" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J44" s="63" t="n">
+      <c r="H44" s="56" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I44" s="56" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J44" s="56" t="n">
         <v>0.4</v>
       </c>
       <c r="K44" s="56" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L44" s="56" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M44" s="56" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N44" s="67" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -23730,16 +23893,25 @@
       <c r="G45" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="H45" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="I45" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="J45" s="63" t="n">
+      <c r="H45" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" s="56" t="n">
         <v>1</v>
       </c>
       <c r="K45" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="M45" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="N45" s="67" t="n">
         <v>1</v>
       </c>
     </row>
@@ -23768,14 +23940,20 @@
       <c r="I46" s="56" t="n">
         <v>12</v>
       </c>
-      <c r="J46" s="63" t="n">
+      <c r="J46" s="56" t="n">
         <v>14</v>
       </c>
       <c r="K46" s="56" t="n">
         <v>16</v>
       </c>
-      <c r="L46" s="0" t="n">
-        <v>14</v>
+      <c r="L46" s="56" t="n">
+        <v>16</v>
+      </c>
+      <c r="M46" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="N46" s="67" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23797,17 +23975,26 @@
       <c r="G47" s="27" t="n">
         <v>1.2</v>
       </c>
-      <c r="H47" s="27" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I47" s="27" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J47" s="63" t="n">
+      <c r="H47" s="56" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I47" s="56" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J47" s="56" t="n">
         <v>1.2</v>
       </c>
       <c r="K47" s="56" t="n">
         <v>100</v>
+      </c>
+      <c r="L47" s="56" t="n">
+        <v>100</v>
+      </c>
+      <c r="M47" s="56" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N47" s="67" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23829,17 +24016,26 @@
       <c r="G48" s="27" t="n">
         <v>0.6</v>
       </c>
-      <c r="H48" s="27" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I48" s="27" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J48" s="63" t="n">
+      <c r="H48" s="56" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I48" s="56" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J48" s="56" t="n">
         <v>0.6</v>
       </c>
       <c r="K48" s="56" t="n">
         <v>0</v>
+      </c>
+      <c r="L48" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="56" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N48" s="67" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23861,16 +24057,25 @@
       <c r="G49" s="27" t="n">
         <v>22000</v>
       </c>
-      <c r="H49" s="27" t="n">
+      <c r="H49" s="56" t="n">
         <v>22000</v>
       </c>
-      <c r="I49" s="27" t="n">
+      <c r="I49" s="56" t="n">
         <v>22000</v>
       </c>
-      <c r="J49" s="63" t="n">
+      <c r="J49" s="56" t="n">
         <v>22000</v>
       </c>
       <c r="K49" s="56" t="n">
+        <v>22000</v>
+      </c>
+      <c r="L49" s="56" t="n">
+        <v>22000</v>
+      </c>
+      <c r="M49" s="56" t="n">
+        <v>22000</v>
+      </c>
+      <c r="N49" s="67" t="n">
         <v>22000</v>
       </c>
     </row>
@@ -23883,10 +24088,13 @@
       <c r="D50" s="29"/>
       <c r="E50" s="29"/>
       <c r="G50" s="29"/>
-      <c r="H50" s="29"/>
-      <c r="I50" s="29"/>
-      <c r="J50" s="29"/>
-      <c r="K50" s="29"/>
+      <c r="H50" s="62"/>
+      <c r="I50" s="62"/>
+      <c r="J50" s="62"/>
+      <c r="K50" s="62"/>
+      <c r="L50" s="62"/>
+      <c r="M50" s="62"/>
+      <c r="N50" s="29"/>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="22" t="s">
@@ -23897,10 +24105,13 @@
       <c r="D51" s="31"/>
       <c r="E51" s="31"/>
       <c r="G51" s="31"/>
-      <c r="H51" s="31"/>
-      <c r="I51" s="31"/>
-      <c r="J51" s="31"/>
-      <c r="K51" s="31"/>
+      <c r="H51" s="62"/>
+      <c r="I51" s="62"/>
+      <c r="J51" s="62"/>
+      <c r="K51" s="62"/>
+      <c r="L51" s="62"/>
+      <c r="M51" s="62"/>
+      <c r="N51" s="31"/>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="17" t="s">
@@ -23921,16 +24132,25 @@
       <c r="G52" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="H52" s="27" t="n">
+      <c r="H52" s="56" t="n">
         <v>4</v>
       </c>
-      <c r="I52" s="27" t="n">
+      <c r="I52" s="56" t="n">
         <v>4</v>
       </c>
-      <c r="J52" s="63" t="n">
+      <c r="J52" s="56" t="n">
         <v>4</v>
       </c>
       <c r="K52" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="L52" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="M52" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="N52" s="67" t="n">
         <v>1</v>
       </c>
     </row>
@@ -23953,16 +24173,25 @@
       <c r="G53" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="H53" s="27" t="n">
+      <c r="H53" s="56" t="n">
         <v>4</v>
       </c>
-      <c r="I53" s="27" t="n">
+      <c r="I53" s="56" t="n">
         <v>4</v>
       </c>
-      <c r="J53" s="63" t="n">
+      <c r="J53" s="56" t="n">
         <v>4</v>
       </c>
       <c r="K53" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="L53" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="M53" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="N53" s="67" t="n">
         <v>1</v>
       </c>
     </row>
@@ -23994,24 +24223,42 @@
       <c r="J54" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="K54" s="5" t="n">
+      <c r="K54" s="68" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M54" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N54" s="5" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H55" s="1" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="J55" s="0" t="s">
         <v>122</v>
       </c>
-      <c r="K55" s="0" t="n">
-        <v>1</v>
+      <c r="K55" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="L55" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M55" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B56" s="17" t="s">
         <v>102</v>
@@ -24022,17 +24269,23 @@
       <c r="D56" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="E56" s="64" t="s">
+      <c r="E56" s="70" t="s">
         <v>105</v>
       </c>
       <c r="F56" s="18" t="s">
         <v>106</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H56" s="56" t="s">
         <v>108</v>
+      </c>
+      <c r="I56" s="67" t="s">
+        <v>109</v>
+      </c>
+      <c r="J56" s="59" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24048,7 +24301,7 @@
       <c r="D57" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="E57" s="64" t="n">
+      <c r="E57" s="70" t="n">
         <v>0.5</v>
       </c>
       <c r="F57" s="18" t="n">
@@ -24056,6 +24309,12 @@
       </c>
       <c r="H57" s="56" t="n">
         <v>0.5</v>
+      </c>
+      <c r="I57" s="67" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J57" s="60" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24067,7 +24326,11 @@
       <c r="D58" s="23"/>
       <c r="E58" s="23"/>
       <c r="F58" s="23"/>
-      <c r="H58" s="23"/>
+      <c r="H58" s="61"/>
+      <c r="I58" s="23"/>
+      <c r="J58" s="49" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
@@ -24078,7 +24341,8 @@
       <c r="D59" s="23"/>
       <c r="E59" s="23"/>
       <c r="F59" s="23"/>
-      <c r="H59" s="23"/>
+      <c r="H59" s="61"/>
+      <c r="I59" s="23"/>
     </row>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
@@ -24089,7 +24353,8 @@
       <c r="D60" s="23"/>
       <c r="E60" s="23"/>
       <c r="F60" s="23"/>
-      <c r="H60" s="23"/>
+      <c r="H60" s="61"/>
+      <c r="I60" s="23"/>
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="s">
@@ -24104,13 +24369,16 @@
       <c r="D61" s="17" t="n">
         <v>0.004</v>
       </c>
-      <c r="E61" s="64" t="n">
+      <c r="E61" s="70" t="n">
         <v>0.0045</v>
       </c>
       <c r="F61" s="18" t="n">
         <v>0.0045</v>
       </c>
       <c r="H61" s="56" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="I61" s="67" t="n">
         <v>0.0045</v>
       </c>
     </row>
@@ -24127,13 +24395,16 @@
       <c r="D62" s="17" t="n">
         <v>0.4</v>
       </c>
-      <c r="E62" s="64" t="n">
+      <c r="E62" s="70" t="n">
         <v>0.4</v>
       </c>
       <c r="F62" s="18" t="n">
         <v>0.4</v>
       </c>
       <c r="H62" s="56" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I62" s="67" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -24150,13 +24421,16 @@
       <c r="D63" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="E63" s="64" t="n">
+      <c r="E63" s="70" t="n">
         <v>1</v>
       </c>
       <c r="F63" s="18" t="n">
         <v>1</v>
       </c>
       <c r="H63" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="I63" s="67" t="n">
         <v>1</v>
       </c>
     </row>
@@ -24173,7 +24447,7 @@
       <c r="D64" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="E64" s="64" t="n">
+      <c r="E64" s="70" t="n">
         <v>10</v>
       </c>
       <c r="F64" s="18" t="n">
@@ -24181,6 +24455,9 @@
       </c>
       <c r="H64" s="56" t="n">
         <v>10</v>
+      </c>
+      <c r="I64" s="67" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24196,13 +24473,16 @@
       <c r="D65" s="17" t="n">
         <v>1.2</v>
       </c>
-      <c r="E65" s="64" t="n">
+      <c r="E65" s="70" t="n">
         <v>1.2</v>
       </c>
       <c r="F65" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="H65" s="56" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I65" s="67" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -24219,13 +24499,16 @@
       <c r="D66" s="17" t="n">
         <v>0.6</v>
       </c>
-      <c r="E66" s="64" t="n">
+      <c r="E66" s="70" t="n">
         <v>0.6</v>
       </c>
       <c r="F66" s="18" t="n">
         <v>0.6</v>
       </c>
       <c r="H66" s="56" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I66" s="67" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -24242,13 +24525,16 @@
       <c r="D67" s="17" t="n">
         <v>20000</v>
       </c>
-      <c r="E67" s="64" t="n">
+      <c r="E67" s="70" t="n">
         <v>25000</v>
       </c>
       <c r="F67" s="18" t="n">
         <v>25000</v>
       </c>
       <c r="H67" s="56" t="n">
+        <v>25000</v>
+      </c>
+      <c r="I67" s="67" t="n">
         <v>25000</v>
       </c>
     </row>
@@ -24261,7 +24547,8 @@
       <c r="D68" s="29"/>
       <c r="E68" s="29"/>
       <c r="F68" s="29"/>
-      <c r="H68" s="29"/>
+      <c r="H68" s="62"/>
+      <c r="I68" s="29"/>
     </row>
     <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="22" t="s">
@@ -24272,7 +24559,8 @@
       <c r="D69" s="31"/>
       <c r="E69" s="31"/>
       <c r="F69" s="31"/>
-      <c r="H69" s="31"/>
+      <c r="H69" s="62"/>
+      <c r="I69" s="31"/>
     </row>
     <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="17" t="s">
@@ -24287,13 +24575,16 @@
       <c r="D70" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="E70" s="64" t="n">
+      <c r="E70" s="70" t="n">
         <v>4</v>
       </c>
       <c r="F70" s="18" t="n">
         <v>4</v>
       </c>
       <c r="H70" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="I70" s="67" t="n">
         <v>4</v>
       </c>
     </row>
@@ -24310,13 +24601,16 @@
       <c r="D71" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="E71" s="64" t="n">
+      <c r="E71" s="70" t="n">
         <v>4</v>
       </c>
       <c r="F71" s="18" t="n">
         <v>4</v>
       </c>
       <c r="H71" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="I71" s="67" t="n">
         <v>4</v>
       </c>
     </row>
@@ -24339,44 +24633,59 @@
       <c r="F72" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="H72" s="5" t="n">
-        <v>0.5</v>
+      <c r="H72" s="68" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I72" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T72" s="59" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B73" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="H73" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
+      </c>
+      <c r="H73" s="68" t="s">
+        <v>205</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="T73" s="60" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E74" s="1"/>
       <c r="R74" s="1" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="S74" s="1" t="s">
-        <v>201</v>
+        <v>208</v>
+      </c>
+      <c r="T74" s="49" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B75" s="65" t="s">
+        <v>215</v>
+      </c>
+      <c r="B75" s="71" t="s">
         <v>102</v>
       </c>
       <c r="C75" s="17" t="s">
@@ -24424,18 +24733,21 @@
       <c r="Q75" s="31" t="s">
         <v>117</v>
       </c>
-      <c r="R75" s="66" t="s">
+      <c r="R75" s="72" t="s">
         <v>118</v>
       </c>
       <c r="S75" s="56" t="s">
         <v>150</v>
+      </c>
+      <c r="T75" s="67" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B76" s="65" t="n">
+      <c r="B76" s="71" t="n">
         <v>0.5</v>
       </c>
       <c r="C76" s="17" t="n">
@@ -24480,13 +24792,16 @@
       <c r="P76" s="18" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q76" s="67" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R76" s="68" t="n">
+      <c r="Q76" s="73" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R76" s="74" t="n">
         <v>0.5</v>
       </c>
       <c r="S76" s="56" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T76" s="67" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -24511,7 +24826,8 @@
       <c r="P77" s="23"/>
       <c r="Q77" s="23"/>
       <c r="R77" s="23"/>
-      <c r="S77" s="23"/>
+      <c r="S77" s="61"/>
+      <c r="T77" s="23"/>
     </row>
     <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2" t="s">
@@ -24534,7 +24850,8 @@
       <c r="P78" s="23"/>
       <c r="Q78" s="23"/>
       <c r="R78" s="23"/>
-      <c r="S78" s="23"/>
+      <c r="S78" s="61"/>
+      <c r="T78" s="23"/>
     </row>
     <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2" t="s">
@@ -24557,13 +24874,14 @@
       <c r="P79" s="23"/>
       <c r="Q79" s="23"/>
       <c r="R79" s="23"/>
-      <c r="S79" s="23"/>
+      <c r="S79" s="61"/>
+      <c r="T79" s="23"/>
     </row>
     <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B80" s="65" t="n">
+      <c r="B80" s="71" t="n">
         <v>0.006</v>
       </c>
       <c r="C80" s="17" t="n">
@@ -24608,13 +24926,16 @@
       <c r="P80" s="18" t="n">
         <v>0.015</v>
       </c>
-      <c r="Q80" s="67" t="n">
+      <c r="Q80" s="73" t="n">
         <v>0.015</v>
       </c>
-      <c r="R80" s="68" t="n">
+      <c r="R80" s="74" t="n">
         <v>0.015</v>
       </c>
       <c r="S80" s="56" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="T80" s="67" t="n">
         <v>0.015</v>
       </c>
     </row>
@@ -24622,7 +24943,7 @@
       <c r="A81" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B81" s="65" t="n">
+      <c r="B81" s="71" t="n">
         <v>0.4</v>
       </c>
       <c r="C81" s="17" t="n">
@@ -24667,13 +24988,16 @@
       <c r="P81" s="18" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q81" s="67" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="R81" s="68" t="n">
+      <c r="Q81" s="73" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R81" s="74" t="n">
         <v>0.4</v>
       </c>
       <c r="S81" s="56" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T81" s="67" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -24681,7 +25005,7 @@
       <c r="A82" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B82" s="65" t="n">
+      <c r="B82" s="71" t="n">
         <v>1</v>
       </c>
       <c r="C82" s="17" t="n">
@@ -24726,13 +25050,16 @@
       <c r="P82" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="Q82" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="R82" s="68" t="n">
+      <c r="Q82" s="73" t="n">
+        <v>1</v>
+      </c>
+      <c r="R82" s="74" t="n">
         <v>1</v>
       </c>
       <c r="S82" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="T82" s="67" t="n">
         <v>1</v>
       </c>
     </row>
@@ -24740,7 +25067,7 @@
       <c r="A83" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B83" s="65" t="n">
+      <c r="B83" s="71" t="n">
         <v>8</v>
       </c>
       <c r="C83" s="17" t="n">
@@ -24785,21 +25112,27 @@
       <c r="P83" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="Q83" s="67" t="n">
+      <c r="Q83" s="73" t="n">
         <v>8</v>
       </c>
-      <c r="R83" s="68" t="n">
+      <c r="R83" s="74" t="n">
         <v>8</v>
       </c>
       <c r="S83" s="56" t="n">
         <v>8</v>
+      </c>
+      <c r="T83" s="67" t="n">
+        <v>8</v>
+      </c>
+      <c r="U83" s="0" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B84" s="65" t="n">
+      <c r="B84" s="71" t="n">
         <v>1.2</v>
       </c>
       <c r="C84" s="17" t="n">
@@ -24844,13 +25177,16 @@
       <c r="P84" s="18" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q84" s="67" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="R84" s="68" t="n">
+      <c r="Q84" s="73" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R84" s="74" t="n">
         <v>1.2</v>
       </c>
       <c r="S84" s="56" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T84" s="67" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -24858,7 +25194,7 @@
       <c r="A85" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B85" s="65" t="n">
+      <c r="B85" s="71" t="n">
         <v>0.6</v>
       </c>
       <c r="C85" s="17" t="n">
@@ -24903,13 +25239,16 @@
       <c r="P85" s="18" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q85" s="67" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="R85" s="68" t="n">
+      <c r="Q85" s="73" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R85" s="74" t="n">
         <v>0.6</v>
       </c>
       <c r="S85" s="56" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T85" s="67" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -24917,7 +25256,7 @@
       <c r="A86" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B86" s="65" t="n">
+      <c r="B86" s="71" t="n">
         <v>15000</v>
       </c>
       <c r="C86" s="17" t="n">
@@ -24962,13 +25301,16 @@
       <c r="P86" s="18" t="n">
         <v>10000</v>
       </c>
-      <c r="Q86" s="67" t="n">
+      <c r="Q86" s="73" t="n">
         <v>10000</v>
       </c>
-      <c r="R86" s="68" t="n">
+      <c r="R86" s="74" t="n">
         <v>10000</v>
       </c>
       <c r="S86" s="56" t="n">
+        <v>10000</v>
+      </c>
+      <c r="T86" s="67" t="n">
         <v>10000</v>
       </c>
     </row>
@@ -24993,7 +25335,8 @@
       <c r="P87" s="29"/>
       <c r="Q87" s="29"/>
       <c r="R87" s="29"/>
-      <c r="S87" s="21"/>
+      <c r="S87" s="61"/>
+      <c r="T87" s="21"/>
     </row>
     <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="22" t="s">
@@ -25016,13 +25359,14 @@
       <c r="P88" s="31"/>
       <c r="Q88" s="31"/>
       <c r="R88" s="31"/>
-      <c r="S88" s="23"/>
+      <c r="S88" s="61"/>
+      <c r="T88" s="23"/>
     </row>
     <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="B89" s="65" t="n">
+      <c r="B89" s="71" t="n">
         <v>4</v>
       </c>
       <c r="C89" s="17" t="n">
@@ -25067,21 +25411,24 @@
       <c r="P89" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="Q89" s="67" t="n">
-        <v>2</v>
-      </c>
-      <c r="R89" s="68" t="n">
+      <c r="Q89" s="73" t="n">
+        <v>2</v>
+      </c>
+      <c r="R89" s="74" t="n">
         <v>2</v>
       </c>
       <c r="S89" s="56" t="n">
         <v>2</v>
+      </c>
+      <c r="T89" s="67" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="B90" s="65" t="n">
+      <c r="B90" s="71" t="n">
         <v>4</v>
       </c>
       <c r="C90" s="17" t="n">
@@ -25126,14 +25473,17 @@
       <c r="P90" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="Q90" s="67" t="n">
-        <v>2</v>
-      </c>
-      <c r="R90" s="68" t="n">
+      <c r="Q90" s="73" t="n">
+        <v>2</v>
+      </c>
+      <c r="R90" s="74" t="n">
         <v>2</v>
       </c>
       <c r="S90" s="56" t="n">
         <v>2</v>
+      </c>
+      <c r="T90" s="67" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25194,71 +25544,77 @@
       <c r="S91" s="5" t="n">
         <v>0.5</v>
       </c>
+      <c r="T91" s="5" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B92" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D92" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="G92" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="E92" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="F92" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="G92" s="1" t="s">
-        <v>212</v>
-      </c>
       <c r="H92" s="1" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="M92" s="5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N92" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O92" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P92" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q92" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="R92" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="S92" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
+      </c>
+      <c r="T92" s="1" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K93" s="1" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B94" s="17" t="s">
         <v>102</v>
@@ -25289,6 +25645,12 @@
       </c>
       <c r="K94" s="56" t="s">
         <v>111</v>
+      </c>
+      <c r="L94" s="67" t="s">
+        <v>112</v>
+      </c>
+      <c r="M94" s="59" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25324,6 +25686,12 @@
       </c>
       <c r="K95" s="56" t="n">
         <v>0.5</v>
+      </c>
+      <c r="L95" s="67" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M95" s="60" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25339,7 +25707,11 @@
       <c r="H96" s="23"/>
       <c r="I96" s="23"/>
       <c r="J96" s="23"/>
-      <c r="K96" s="23"/>
+      <c r="K96" s="61"/>
+      <c r="L96" s="23"/>
+      <c r="M96" s="49" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2" t="s">
@@ -25354,7 +25726,11 @@
       <c r="H97" s="23"/>
       <c r="I97" s="23"/>
       <c r="J97" s="23"/>
-      <c r="K97" s="23"/>
+      <c r="K97" s="61"/>
+      <c r="L97" s="23"/>
+      <c r="M97" s="75" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2" t="s">
@@ -25369,7 +25745,8 @@
       <c r="H98" s="23"/>
       <c r="I98" s="23"/>
       <c r="J98" s="23"/>
-      <c r="K98" s="23"/>
+      <c r="K98" s="61"/>
+      <c r="L98" s="23"/>
     </row>
     <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2" t="s">
@@ -25405,6 +25782,9 @@
       <c r="K99" s="56" t="n">
         <v>0.04</v>
       </c>
+      <c r="L99" s="67" t="n">
+        <v>0.04</v>
+      </c>
     </row>
     <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2" t="s">
@@ -25440,6 +25820,9 @@
       <c r="K100" s="56" t="n">
         <v>0.4</v>
       </c>
+      <c r="L100" s="67" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2" t="s">
@@ -25475,6 +25858,9 @@
       <c r="K101" s="56" t="n">
         <v>1</v>
       </c>
+      <c r="L101" s="67" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2" t="s">
@@ -25510,6 +25896,9 @@
       <c r="K102" s="56" t="n">
         <v>4</v>
       </c>
+      <c r="L102" s="67" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2" t="s">
@@ -25545,6 +25934,9 @@
       <c r="K103" s="56" t="n">
         <v>1.2</v>
       </c>
+      <c r="L103" s="67" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="s">
@@ -25580,6 +25972,9 @@
       <c r="K104" s="56" t="n">
         <v>0.6</v>
       </c>
+      <c r="L104" s="67" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2" t="s">
@@ -25613,6 +26008,9 @@
         <v>10000</v>
       </c>
       <c r="K105" s="56" t="n">
+        <v>20000</v>
+      </c>
+      <c r="L105" s="67" t="n">
         <v>20000</v>
       </c>
     </row>
@@ -25629,7 +26027,8 @@
       <c r="H106" s="29"/>
       <c r="I106" s="29"/>
       <c r="J106" s="29"/>
-      <c r="K106" s="29"/>
+      <c r="K106" s="62"/>
+      <c r="L106" s="29"/>
     </row>
     <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="22" t="s">
@@ -25644,7 +26043,8 @@
       <c r="H107" s="31"/>
       <c r="I107" s="31"/>
       <c r="J107" s="31"/>
-      <c r="K107" s="31"/>
+      <c r="K107" s="62"/>
+      <c r="L107" s="31"/>
     </row>
     <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="17" t="s">
@@ -25680,6 +26080,9 @@
       <c r="K108" s="56" t="n">
         <v>4</v>
       </c>
+      <c r="L108" s="67" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="17" t="s">
@@ -25715,6 +26118,9 @@
       <c r="K109" s="56" t="n">
         <v>4</v>
       </c>
+      <c r="L109" s="67" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="s">
@@ -25750,52 +26156,58 @@
       <c r="K110" s="5" t="n">
         <v>0.5</v>
       </c>
+      <c r="L110" s="5" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B111" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="J111" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
+      </c>
+      <c r="L111" s="1" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D112" s="1" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J113" s="24" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="2" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B114" s="17" t="s">
         <v>102</v>
@@ -25815,13 +26227,13 @@
       <c r="G114" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="H114" s="65" t="s">
+      <c r="H114" s="71" t="s">
         <v>108</v>
       </c>
-      <c r="I114" s="56" t="s">
+      <c r="I114" s="67" t="s">
         <v>109</v>
       </c>
-      <c r="J114" s="57" t="s">
+      <c r="J114" s="58" t="s">
         <v>110</v>
       </c>
     </row>
@@ -25847,13 +26259,13 @@
       <c r="G115" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="H115" s="65" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I115" s="56" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J115" s="57" t="n">
+      <c r="H115" s="71" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I115" s="67" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J115" s="58" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -25869,7 +26281,7 @@
       <c r="G116" s="23"/>
       <c r="H116" s="23"/>
       <c r="I116" s="40"/>
-      <c r="J116" s="69"/>
+      <c r="J116" s="76"/>
     </row>
     <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="2" t="s">
@@ -25883,7 +26295,7 @@
       <c r="G117" s="23"/>
       <c r="H117" s="23"/>
       <c r="I117" s="40"/>
-      <c r="J117" s="69"/>
+      <c r="J117" s="76"/>
     </row>
     <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="2" t="s">
@@ -25897,7 +26309,7 @@
       <c r="G118" s="23"/>
       <c r="H118" s="23"/>
       <c r="I118" s="40"/>
-      <c r="J118" s="69"/>
+      <c r="J118" s="76"/>
     </row>
     <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="2" t="s">
@@ -25921,13 +26333,13 @@
       <c r="G119" s="17" t="n">
         <v>0.025</v>
       </c>
-      <c r="H119" s="65" t="n">
+      <c r="H119" s="71" t="n">
         <v>0.025</v>
       </c>
-      <c r="I119" s="56" t="n">
+      <c r="I119" s="67" t="n">
         <v>0.025</v>
       </c>
-      <c r="J119" s="57" t="n">
+      <c r="J119" s="58" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -25953,13 +26365,13 @@
       <c r="G120" s="17" t="n">
         <v>0.4</v>
       </c>
-      <c r="H120" s="65" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I120" s="56" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J120" s="57" t="n">
+      <c r="H120" s="71" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I120" s="67" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J120" s="58" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -25985,13 +26397,13 @@
       <c r="G121" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="H121" s="65" t="n">
-        <v>1</v>
-      </c>
-      <c r="I121" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="J121" s="57" t="n">
+      <c r="H121" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="I121" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J121" s="58" t="n">
         <v>1</v>
       </c>
     </row>
@@ -26017,13 +26429,13 @@
       <c r="G122" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="H122" s="65" t="n">
+      <c r="H122" s="71" t="n">
         <v>4</v>
       </c>
-      <c r="I122" s="56" t="n">
+      <c r="I122" s="67" t="n">
         <v>4</v>
       </c>
-      <c r="J122" s="57" t="n">
+      <c r="J122" s="58" t="n">
         <v>4</v>
       </c>
     </row>
@@ -26049,13 +26461,13 @@
       <c r="G123" s="17" t="n">
         <v>1.2</v>
       </c>
-      <c r="H123" s="65" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I123" s="56" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J123" s="57" t="n">
+      <c r="H123" s="71" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I123" s="67" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J123" s="58" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -26081,13 +26493,13 @@
       <c r="G124" s="17" t="n">
         <v>0.6</v>
       </c>
-      <c r="H124" s="65" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I124" s="56" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J124" s="57" t="n">
+      <c r="H124" s="71" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I124" s="67" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J124" s="58" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -26113,13 +26525,13 @@
       <c r="G125" s="17" t="n">
         <v>10000</v>
       </c>
-      <c r="H125" s="65" t="n">
+      <c r="H125" s="71" t="n">
         <v>10000</v>
       </c>
-      <c r="I125" s="56" t="n">
+      <c r="I125" s="67" t="n">
         <v>10000</v>
       </c>
-      <c r="J125" s="57" t="n">
+      <c r="J125" s="58" t="n">
         <v>10000</v>
       </c>
     </row>
@@ -26135,7 +26547,7 @@
       <c r="G126" s="29"/>
       <c r="H126" s="29"/>
       <c r="I126" s="33"/>
-      <c r="J126" s="70"/>
+      <c r="J126" s="77"/>
     </row>
     <row r="127" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="22" t="s">
@@ -26149,7 +26561,7 @@
       <c r="G127" s="31"/>
       <c r="H127" s="31"/>
       <c r="I127" s="33"/>
-      <c r="J127" s="70"/>
+      <c r="J127" s="77"/>
     </row>
     <row r="128" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="17" t="s">
@@ -26173,13 +26585,13 @@
       <c r="G128" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="H128" s="65" t="n">
+      <c r="H128" s="71" t="n">
         <v>4</v>
       </c>
-      <c r="I128" s="56" t="n">
+      <c r="I128" s="67" t="n">
         <v>4</v>
       </c>
-      <c r="J128" s="57" t="n">
+      <c r="J128" s="58" t="n">
         <v>4</v>
       </c>
     </row>
@@ -26205,13 +26617,13 @@
       <c r="G129" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="H129" s="65" t="n">
+      <c r="H129" s="71" t="n">
         <v>4</v>
       </c>
-      <c r="I129" s="56" t="n">
+      <c r="I129" s="67" t="n">
         <v>4</v>
       </c>
-      <c r="J129" s="57" t="n">
+      <c r="J129" s="58" t="n">
         <v>4</v>
       </c>
     </row>
@@ -26243,51 +26655,51 @@
       <c r="I130" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="J130" s="71" t="n">
+      <c r="J130" s="78" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B131" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I131" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="J131" s="71" t="s">
-        <v>216</v>
+        <v>218</v>
+      </c>
+      <c r="J131" s="78" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AL132" s="58" t="s">
-        <v>202</v>
-      </c>
-      <c r="AM132" s="58" t="s">
-        <v>202</v>
-      </c>
-      <c r="AN132" s="59" t="s">
-        <v>202</v>
-      </c>
-      <c r="AO132" s="72" t="s">
-        <v>202</v>
+      <c r="AL132" s="59" t="s">
+        <v>201</v>
+      </c>
+      <c r="AM132" s="59" t="s">
+        <v>201</v>
+      </c>
+      <c r="AN132" s="60" t="s">
+        <v>201</v>
+      </c>
+      <c r="AO132" s="79" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26301,69 +26713,69 @@
         <v>0.0225</v>
       </c>
       <c r="AD133" s="1" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="AE133" s="1" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="AF133" s="1" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="AG133" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="AL133" s="59" t="s">
-        <v>203</v>
-      </c>
-      <c r="AM133" s="59" t="s">
-        <v>203</v>
-      </c>
-      <c r="AN133" s="59" t="s">
-        <v>203</v>
-      </c>
-      <c r="AO133" s="72" t="s">
-        <v>203</v>
+        <v>227</v>
+      </c>
+      <c r="AL133" s="60" t="s">
+        <v>204</v>
+      </c>
+      <c r="AM133" s="60" t="s">
+        <v>204</v>
+      </c>
+      <c r="AN133" s="60" t="s">
+        <v>204</v>
+      </c>
+      <c r="AO133" s="79" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="U134" s="24" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="V134" s="24" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="W134" s="24" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="X134" s="24" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="Y134" s="24" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="Z134" s="24" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="AA134" s="24" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="AB134" s="24" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="AC134" s="24" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="AD134" s="24" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="AE134" s="24" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="AF134" s="24" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="AG134" s="24" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="AL134" s="49" t="s">
         <v>69</v>
@@ -26371,10 +26783,10 @@
       <c r="AM134" s="49" t="s">
         <v>69</v>
       </c>
-      <c r="AN134" s="73" t="s">
+      <c r="AN134" s="80" t="s">
         <v>69</v>
       </c>
-      <c r="AO134" s="74" t="s">
+      <c r="AO134" s="81" t="s">
         <v>69</v>
       </c>
     </row>
@@ -26439,68 +26851,68 @@
       <c r="T135" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="U135" s="75" t="s">
+      <c r="U135" s="82" t="s">
         <v>152</v>
       </c>
-      <c r="V135" s="76" t="s">
+      <c r="V135" s="57" t="s">
         <v>153</v>
       </c>
-      <c r="W135" s="76" t="s">
+      <c r="W135" s="57" t="s">
         <v>154</v>
       </c>
-      <c r="X135" s="76" t="s">
+      <c r="X135" s="57" t="s">
         <v>155</v>
       </c>
-      <c r="Y135" s="76" t="s">
+      <c r="Y135" s="57" t="s">
         <v>156</v>
       </c>
-      <c r="Z135" s="63" t="s">
-        <v>226</v>
-      </c>
-      <c r="AA135" s="76" t="s">
-        <v>227</v>
-      </c>
-      <c r="AB135" s="76" t="s">
-        <v>228</v>
-      </c>
-      <c r="AC135" s="76" t="s">
-        <v>229</v>
-      </c>
-      <c r="AD135" s="76" t="s">
-        <v>230</v>
-      </c>
-      <c r="AE135" s="77" t="s">
+      <c r="Z135" s="56" t="s">
         <v>231</v>
       </c>
-      <c r="AF135" s="76" t="s">
+      <c r="AA135" s="57" t="s">
         <v>232</v>
       </c>
-      <c r="AG135" s="76" t="s">
+      <c r="AB135" s="57" t="s">
         <v>233</v>
       </c>
-      <c r="AH135" s="78" t="s">
+      <c r="AC135" s="57" t="s">
         <v>234</v>
       </c>
-      <c r="AI135" s="78" t="s">
+      <c r="AD135" s="57" t="s">
         <v>235</v>
       </c>
-      <c r="AJ135" s="78" t="s">
+      <c r="AE135" s="83" t="s">
         <v>236</v>
       </c>
-      <c r="AK135" s="78" t="s">
+      <c r="AF135" s="57" t="s">
         <v>237</v>
       </c>
-      <c r="AL135" s="79" t="s">
+      <c r="AG135" s="57" t="s">
         <v>238</v>
       </c>
-      <c r="AM135" s="79" t="s">
+      <c r="AH135" s="84" t="s">
         <v>239</v>
       </c>
-      <c r="AN135" s="79" t="s">
+      <c r="AI135" s="84" t="s">
         <v>240</v>
       </c>
-      <c r="AO135" s="79" t="s">
+      <c r="AJ135" s="84" t="s">
         <v>241</v>
+      </c>
+      <c r="AK135" s="84" t="s">
+        <v>242</v>
+      </c>
+      <c r="AL135" s="85" t="s">
+        <v>243</v>
+      </c>
+      <c r="AM135" s="85" t="s">
+        <v>244</v>
+      </c>
+      <c r="AN135" s="85" t="s">
+        <v>245</v>
+      </c>
+      <c r="AO135" s="85" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26564,67 +26976,67 @@
       <c r="T136" s="18" t="n">
         <v>0.5</v>
       </c>
-      <c r="U136" s="75" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V136" s="76" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="W136" s="76" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="X136" s="76" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y136" s="76" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z136" s="63" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AA136" s="76" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB136" s="76" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AC136" s="76" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AD136" s="76" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AE136" s="77" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AF136" s="76" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AG136" s="76" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AH136" s="78" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AI136" s="78" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AJ136" s="78" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AK136" s="78" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AL136" s="79" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AM136" s="79" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AN136" s="79" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AO136" s="79" t="n">
+      <c r="U136" s="82" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V136" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W136" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X136" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y136" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z136" s="56" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA136" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB136" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC136" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD136" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE136" s="83" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF136" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG136" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH136" s="84" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AI136" s="84" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AJ136" s="84" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK136" s="84" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AL136" s="85" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AM136" s="85" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AN136" s="85" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AO136" s="85" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -26666,8 +27078,8 @@
       <c r="AG137" s="23"/>
       <c r="AH137" s="23"/>
       <c r="AI137" s="23"/>
-      <c r="AJ137" s="80"/>
-      <c r="AK137" s="80"/>
+      <c r="AJ137" s="61"/>
+      <c r="AK137" s="61"/>
       <c r="AL137" s="23"/>
       <c r="AM137" s="23"/>
       <c r="AN137" s="23"/>
@@ -26711,8 +27123,8 @@
       <c r="AG138" s="23"/>
       <c r="AH138" s="23"/>
       <c r="AI138" s="23"/>
-      <c r="AJ138" s="80"/>
-      <c r="AK138" s="80"/>
+      <c r="AJ138" s="61"/>
+      <c r="AK138" s="61"/>
       <c r="AL138" s="23"/>
       <c r="AM138" s="23"/>
       <c r="AN138" s="23"/>
@@ -26756,8 +27168,8 @@
       <c r="AG139" s="23"/>
       <c r="AH139" s="23"/>
       <c r="AI139" s="23"/>
-      <c r="AJ139" s="80"/>
-      <c r="AK139" s="80"/>
+      <c r="AJ139" s="61"/>
+      <c r="AK139" s="61"/>
       <c r="AL139" s="23"/>
       <c r="AM139" s="23"/>
       <c r="AN139" s="23"/>
@@ -26824,67 +27236,67 @@
       <c r="T140" s="18" t="n">
         <v>0.05</v>
       </c>
-      <c r="U140" s="75" t="n">
+      <c r="U140" s="82" t="n">
         <v>0.05</v>
       </c>
-      <c r="V140" s="76" t="n">
+      <c r="V140" s="57" t="n">
         <v>0.05</v>
       </c>
-      <c r="W140" s="76" t="n">
+      <c r="W140" s="57" t="n">
         <v>0.05</v>
       </c>
-      <c r="X140" s="76" t="n">
+      <c r="X140" s="57" t="n">
         <v>0.05</v>
       </c>
-      <c r="Y140" s="76" t="n">
+      <c r="Y140" s="57" t="n">
         <v>0.05</v>
       </c>
-      <c r="Z140" s="63" t="n">
+      <c r="Z140" s="56" t="n">
         <v>0.05</v>
       </c>
-      <c r="AA140" s="76" t="n">
+      <c r="AA140" s="57" t="n">
         <v>0.05</v>
       </c>
-      <c r="AB140" s="76" t="n">
+      <c r="AB140" s="57" t="n">
         <v>0.05</v>
       </c>
-      <c r="AC140" s="76" t="n">
+      <c r="AC140" s="57" t="n">
         <v>0.05</v>
       </c>
-      <c r="AD140" s="76" t="n">
+      <c r="AD140" s="57" t="n">
         <v>0.05</v>
       </c>
-      <c r="AE140" s="77" t="n">
+      <c r="AE140" s="83" t="n">
         <v>0.05</v>
       </c>
-      <c r="AF140" s="76" t="n">
+      <c r="AF140" s="57" t="n">
         <v>0.05</v>
       </c>
-      <c r="AG140" s="76" t="n">
+      <c r="AG140" s="57" t="n">
         <v>0.05</v>
       </c>
-      <c r="AH140" s="78" t="n">
+      <c r="AH140" s="84" t="n">
         <v>0.05</v>
       </c>
-      <c r="AI140" s="78" t="n">
+      <c r="AI140" s="84" t="n">
         <v>0.05</v>
       </c>
-      <c r="AJ140" s="78" t="n">
+      <c r="AJ140" s="84" t="n">
         <v>0.05</v>
       </c>
-      <c r="AK140" s="78" t="n">
+      <c r="AK140" s="84" t="n">
         <v>0.05</v>
       </c>
-      <c r="AL140" s="79" t="n">
+      <c r="AL140" s="85" t="n">
         <v>0.05</v>
       </c>
-      <c r="AM140" s="79" t="n">
+      <c r="AM140" s="85" t="n">
         <v>0.05</v>
       </c>
-      <c r="AN140" s="79" t="n">
+      <c r="AN140" s="85" t="n">
         <v>0.05</v>
       </c>
-      <c r="AO140" s="79" t="n">
+      <c r="AO140" s="85" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -26949,67 +27361,67 @@
       <c r="T141" s="18" t="n">
         <v>0.4</v>
       </c>
-      <c r="U141" s="75" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="V141" s="76" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="W141" s="76" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="X141" s="76" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Y141" s="76" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Z141" s="63" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AA141" s="76" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AB141" s="76" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AC141" s="76" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AD141" s="76" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AE141" s="77" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AF141" s="76" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AG141" s="76" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AH141" s="78" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AI141" s="78" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AJ141" s="78" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AK141" s="78" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AL141" s="79" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AM141" s="79" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AN141" s="79" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AO141" s="79" t="n">
+      <c r="U141" s="82" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="V141" s="57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W141" s="57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="X141" s="57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y141" s="57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z141" s="56" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AA141" s="57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AB141" s="57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC141" s="57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AD141" s="57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AE141" s="83" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AF141" s="57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AG141" s="57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AH141" s="84" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AI141" s="84" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AJ141" s="84" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AK141" s="84" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AL141" s="85" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AM141" s="85" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AN141" s="85" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AO141" s="85" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -27074,67 +27486,67 @@
       <c r="T142" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="U142" s="75" t="n">
-        <v>1</v>
-      </c>
-      <c r="V142" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="W142" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="X142" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y142" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z142" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA142" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB142" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC142" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD142" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE142" s="77" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF142" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG142" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH142" s="78" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI142" s="78" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ142" s="78" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK142" s="78" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL142" s="79" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM142" s="79" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN142" s="79" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO142" s="79" t="n">
+      <c r="U142" s="82" t="n">
+        <v>1</v>
+      </c>
+      <c r="V142" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="W142" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="X142" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y142" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z142" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA142" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB142" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC142" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD142" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE142" s="83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF142" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG142" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH142" s="84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI142" s="84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ142" s="84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK142" s="84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL142" s="85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM142" s="85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN142" s="85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO142" s="85" t="n">
         <v>1</v>
       </c>
     </row>
@@ -27199,67 +27611,67 @@
       <c r="T143" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="U143" s="75" t="n">
+      <c r="U143" s="82" t="n">
         <v>4</v>
       </c>
-      <c r="V143" s="76" t="n">
+      <c r="V143" s="57" t="n">
         <v>0</v>
       </c>
-      <c r="W143" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="X143" s="76" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y143" s="76" t="n">
+      <c r="W143" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="X143" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y143" s="57" t="n">
         <v>4</v>
       </c>
-      <c r="Z143" s="63" t="n">
+      <c r="Z143" s="56" t="n">
         <v>3</v>
       </c>
-      <c r="AA143" s="76" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB143" s="76" t="n">
+      <c r="AA143" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB143" s="57" t="n">
         <v>0</v>
       </c>
-      <c r="AC143" s="76" t="n">
+      <c r="AC143" s="57" t="n">
         <v>0</v>
       </c>
-      <c r="AD143" s="76" t="n">
+      <c r="AD143" s="57" t="n">
         <v>3</v>
       </c>
-      <c r="AE143" s="77" t="n">
+      <c r="AE143" s="83" t="n">
         <v>0</v>
       </c>
-      <c r="AF143" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG143" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH143" s="78" t="n">
+      <c r="AF143" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG143" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH143" s="84" t="n">
         <v>3</v>
       </c>
-      <c r="AI143" s="78" t="n">
+      <c r="AI143" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="AJ143" s="78" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK143" s="78" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL143" s="79" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM143" s="79" t="n">
-        <v>2</v>
-      </c>
-      <c r="AN143" s="79" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO143" s="79" t="n">
+      <c r="AJ143" s="84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK143" s="84" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL143" s="85" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM143" s="85" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN143" s="85" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO143" s="85" t="n">
         <v>2</v>
       </c>
     </row>
@@ -27312,79 +27724,79 @@
       <c r="P144" s="17" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q144" s="68" t="n">
+      <c r="Q144" s="74" t="n">
         <v>0.8</v>
       </c>
-      <c r="R144" s="68" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S144" s="68" t="n">
+      <c r="R144" s="74" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S144" s="74" t="n">
         <v>0.4</v>
       </c>
       <c r="T144" s="18" t="n">
         <v>0.3</v>
       </c>
-      <c r="U144" s="75" t="n">
+      <c r="U144" s="82" t="n">
         <v>0.3</v>
       </c>
-      <c r="V144" s="76" t="n">
+      <c r="V144" s="57" t="n">
         <v>0.3</v>
       </c>
-      <c r="W144" s="76" t="n">
+      <c r="W144" s="57" t="n">
         <v>0.3</v>
       </c>
-      <c r="X144" s="76" t="n">
+      <c r="X144" s="57" t="n">
         <v>0.3</v>
       </c>
-      <c r="Y144" s="76" t="n">
+      <c r="Y144" s="57" t="n">
         <v>0.3</v>
       </c>
-      <c r="Z144" s="63" t="n">
+      <c r="Z144" s="56" t="n">
         <v>0.3</v>
       </c>
-      <c r="AA144" s="76" t="n">
+      <c r="AA144" s="57" t="n">
         <v>0.3</v>
       </c>
-      <c r="AB144" s="76" t="n">
+      <c r="AB144" s="57" t="n">
         <v>0.3</v>
       </c>
-      <c r="AC144" s="76" t="n">
+      <c r="AC144" s="57" t="n">
         <v>0.3</v>
       </c>
-      <c r="AD144" s="76" t="n">
+      <c r="AD144" s="57" t="n">
         <v>0.3</v>
       </c>
-      <c r="AE144" s="77" t="n">
+      <c r="AE144" s="83" t="n">
         <v>0.3</v>
       </c>
-      <c r="AF144" s="76" t="n">
+      <c r="AF144" s="57" t="n">
         <v>0.3</v>
       </c>
-      <c r="AG144" s="76" t="n">
+      <c r="AG144" s="57" t="n">
         <v>0.3</v>
       </c>
-      <c r="AH144" s="78" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI144" s="78" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AJ144" s="78" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK144" s="78" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AL144" s="79" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AM144" s="79" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN144" s="79" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AO144" s="79" t="n">
+      <c r="AH144" s="84" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI144" s="84" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AJ144" s="84" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK144" s="84" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL144" s="85" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AM144" s="85" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN144" s="85" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO144" s="85" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -27449,67 +27861,67 @@
       <c r="T145" s="18" t="n">
         <v>0.6</v>
       </c>
-      <c r="U145" s="75" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="V145" s="76" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="W145" s="76" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="X145" s="76" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Y145" s="76" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Z145" s="63" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AA145" s="76" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AB145" s="76" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AC145" s="76" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AD145" s="76" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AE145" s="77" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AF145" s="76" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AG145" s="76" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AH145" s="78" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AI145" s="78" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AJ145" s="78" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AK145" s="78" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AL145" s="79" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AM145" s="79" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AN145" s="79" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AO145" s="79" t="n">
+      <c r="U145" s="82" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="V145" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="W145" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="X145" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Y145" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Z145" s="56" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA145" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AB145" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AC145" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AD145" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AE145" s="83" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AF145" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AG145" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AH145" s="84" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AI145" s="84" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AJ145" s="84" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AK145" s="84" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AL145" s="85" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AM145" s="85" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AN145" s="85" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AO145" s="85" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -27574,67 +27986,67 @@
       <c r="T146" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="U146" s="75" t="n">
+      <c r="U146" s="82" t="n">
         <v>12000</v>
       </c>
-      <c r="V146" s="76" t="n">
+      <c r="V146" s="57" t="n">
         <v>2000</v>
       </c>
-      <c r="W146" s="76" t="n">
+      <c r="W146" s="57" t="n">
         <v>5000</v>
       </c>
-      <c r="X146" s="76" t="n">
+      <c r="X146" s="57" t="n">
         <v>5000</v>
       </c>
-      <c r="Y146" s="76" t="n">
+      <c r="Y146" s="57" t="n">
         <v>5000</v>
       </c>
-      <c r="Z146" s="63" t="n">
+      <c r="Z146" s="56" t="n">
         <v>5000</v>
       </c>
-      <c r="AA146" s="76" t="n">
+      <c r="AA146" s="57" t="n">
         <v>2000</v>
       </c>
-      <c r="AB146" s="76" t="n">
+      <c r="AB146" s="57" t="n">
         <v>2000</v>
       </c>
-      <c r="AC146" s="76" t="n">
+      <c r="AC146" s="57" t="n">
         <v>0</v>
       </c>
-      <c r="AD146" s="76" t="n">
+      <c r="AD146" s="57" t="n">
         <v>5000</v>
       </c>
-      <c r="AE146" s="77" t="n">
+      <c r="AE146" s="83" t="n">
         <v>0</v>
       </c>
-      <c r="AF146" s="76" t="n">
+      <c r="AF146" s="57" t="n">
         <v>1000</v>
       </c>
-      <c r="AG146" s="76" t="n">
+      <c r="AG146" s="57" t="n">
         <v>0</v>
       </c>
-      <c r="AH146" s="78" t="n">
+      <c r="AH146" s="84" t="n">
         <v>10000</v>
       </c>
-      <c r="AI146" s="78" t="n">
+      <c r="AI146" s="84" t="n">
         <v>2000</v>
       </c>
-      <c r="AJ146" s="78" t="n">
+      <c r="AJ146" s="84" t="n">
         <v>5000</v>
       </c>
-      <c r="AK146" s="78" t="n">
+      <c r="AK146" s="84" t="n">
         <v>10000</v>
       </c>
-      <c r="AL146" s="79" t="n">
+      <c r="AL146" s="85" t="n">
         <v>10000</v>
       </c>
-      <c r="AM146" s="79" t="n">
+      <c r="AM146" s="85" t="n">
         <v>10000</v>
       </c>
-      <c r="AN146" s="79" t="n">
+      <c r="AN146" s="85" t="n">
         <v>10000</v>
       </c>
-      <c r="AO146" s="79" t="n">
+      <c r="AO146" s="85" t="n">
         <v>10000</v>
       </c>
     </row>
@@ -27676,8 +28088,8 @@
       <c r="AG147" s="29"/>
       <c r="AH147" s="29"/>
       <c r="AI147" s="29"/>
-      <c r="AJ147" s="81"/>
-      <c r="AK147" s="81"/>
+      <c r="AJ147" s="62"/>
+      <c r="AK147" s="62"/>
       <c r="AL147" s="29"/>
       <c r="AM147" s="29"/>
       <c r="AN147" s="29"/>
@@ -27721,8 +28133,8 @@
       <c r="AG148" s="31"/>
       <c r="AH148" s="31"/>
       <c r="AI148" s="31"/>
-      <c r="AJ148" s="81"/>
-      <c r="AK148" s="81"/>
+      <c r="AJ148" s="62"/>
+      <c r="AK148" s="62"/>
       <c r="AL148" s="31"/>
       <c r="AM148" s="31"/>
       <c r="AN148" s="31"/>
@@ -27786,70 +28198,70 @@
       <c r="S149" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="T149" s="82" t="n">
-        <v>2</v>
-      </c>
-      <c r="U149" s="75" t="n">
-        <v>2</v>
-      </c>
-      <c r="V149" s="76" t="n">
-        <v>2</v>
-      </c>
-      <c r="W149" s="76" t="n">
+      <c r="T149" s="86" t="n">
+        <v>2</v>
+      </c>
+      <c r="U149" s="82" t="n">
+        <v>2</v>
+      </c>
+      <c r="V149" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="W149" s="57" t="n">
         <v>5</v>
       </c>
-      <c r="X149" s="76" t="n">
+      <c r="X149" s="57" t="n">
         <v>5</v>
       </c>
-      <c r="Y149" s="76" t="n">
+      <c r="Y149" s="57" t="n">
         <v>5</v>
       </c>
-      <c r="Z149" s="63" t="n">
+      <c r="Z149" s="56" t="n">
         <v>5</v>
       </c>
-      <c r="AA149" s="76" t="n">
+      <c r="AA149" s="57" t="n">
         <v>5</v>
       </c>
-      <c r="AB149" s="76" t="n">
+      <c r="AB149" s="57" t="n">
         <v>5</v>
       </c>
-      <c r="AC149" s="76" t="n">
+      <c r="AC149" s="57" t="n">
         <v>5</v>
       </c>
-      <c r="AD149" s="76" t="n">
+      <c r="AD149" s="57" t="n">
         <v>5</v>
       </c>
-      <c r="AE149" s="77" t="n">
+      <c r="AE149" s="83" t="n">
         <v>5</v>
       </c>
-      <c r="AF149" s="76" t="n">
+      <c r="AF149" s="57" t="n">
         <v>5</v>
       </c>
-      <c r="AG149" s="76" t="n">
+      <c r="AG149" s="57" t="n">
         <v>5</v>
       </c>
-      <c r="AH149" s="78" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI149" s="78" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ149" s="78" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK149" s="78" t="n">
+      <c r="AH149" s="84" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI149" s="84" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ149" s="84" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK149" s="84" t="n">
         <v>3</v>
       </c>
-      <c r="AL149" s="79" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM149" s="79" t="n">
-        <v>2</v>
-      </c>
-      <c r="AN149" s="79" t="n">
+      <c r="AL149" s="85" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM149" s="85" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN149" s="85" t="n">
         <v>3</v>
       </c>
-      <c r="AO149" s="79" t="n">
+      <c r="AO149" s="85" t="n">
         <v>3</v>
       </c>
     </row>
@@ -27911,70 +28323,70 @@
       <c r="S150" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="T150" s="82" t="n">
+      <c r="T150" s="86" t="n">
         <v>3</v>
       </c>
-      <c r="U150" s="75" t="n">
+      <c r="U150" s="82" t="n">
         <v>3</v>
       </c>
-      <c r="V150" s="76" t="n">
+      <c r="V150" s="57" t="n">
         <v>3</v>
       </c>
-      <c r="W150" s="76" t="n">
+      <c r="W150" s="57" t="n">
         <v>5</v>
       </c>
-      <c r="X150" s="76" t="n">
+      <c r="X150" s="57" t="n">
         <v>5</v>
       </c>
-      <c r="Y150" s="76" t="n">
+      <c r="Y150" s="57" t="n">
         <v>5</v>
       </c>
-      <c r="Z150" s="63" t="n">
+      <c r="Z150" s="56" t="n">
         <v>5</v>
       </c>
-      <c r="AA150" s="76" t="n">
+      <c r="AA150" s="57" t="n">
         <v>5</v>
       </c>
-      <c r="AB150" s="76" t="n">
+      <c r="AB150" s="57" t="n">
         <v>5</v>
       </c>
-      <c r="AC150" s="76" t="n">
+      <c r="AC150" s="57" t="n">
         <v>5</v>
       </c>
-      <c r="AD150" s="76" t="n">
+      <c r="AD150" s="57" t="n">
         <v>5</v>
       </c>
-      <c r="AE150" s="77" t="n">
+      <c r="AE150" s="83" t="n">
         <v>5</v>
       </c>
-      <c r="AF150" s="76" t="n">
+      <c r="AF150" s="57" t="n">
         <v>5</v>
       </c>
-      <c r="AG150" s="76" t="n">
+      <c r="AG150" s="57" t="n">
         <v>5</v>
       </c>
-      <c r="AH150" s="78" t="n">
+      <c r="AH150" s="84" t="n">
         <v>3</v>
       </c>
-      <c r="AI150" s="78" t="n">
+      <c r="AI150" s="84" t="n">
         <v>3</v>
       </c>
-      <c r="AJ150" s="78" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK150" s="78" t="n">
+      <c r="AJ150" s="84" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK150" s="84" t="n">
         <v>3</v>
       </c>
-      <c r="AL150" s="79" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM150" s="79" t="n">
-        <v>2</v>
-      </c>
-      <c r="AN150" s="79" t="n">
+      <c r="AL150" s="85" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM150" s="85" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN150" s="85" t="n">
         <v>3</v>
       </c>
-      <c r="AO150" s="79" t="n">
+      <c r="AO150" s="85" t="n">
         <v>3</v>
       </c>
     </row>
@@ -28084,10 +28496,10 @@
       <c r="AI151" s="5" t="n">
         <v>0.6</v>
       </c>
-      <c r="AJ151" s="83" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AK151" s="83" t="n">
+      <c r="AJ151" s="68" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AK151" s="68" t="n">
         <v>0.6</v>
       </c>
       <c r="AL151" s="5" t="n">
@@ -28105,124 +28517,124 @@
     </row>
     <row r="152" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B152" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H152" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I152" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J152" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K152" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L152" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M152" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N152" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O152" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P152" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q152" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="R152" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="S152" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="T152" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="U152" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="V152" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="W152" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="X152" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Y152" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Z152" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AA152" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AB152" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AC152" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AD152" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AE152" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AF152" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AG152" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AH152" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AI152" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="AJ152" s="83" t="s">
-        <v>204</v>
-      </c>
-      <c r="AK152" s="83" t="s">
-        <v>204</v>
+        <v>205</v>
+      </c>
+      <c r="AJ152" s="68" t="s">
+        <v>205</v>
+      </c>
+      <c r="AK152" s="68" t="s">
+        <v>205</v>
       </c>
       <c r="AL152" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AM152" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AN152" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AO152" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28236,7 +28648,7 @@
         <v>197</v>
       </c>
       <c r="AK153" s="0" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="AL153" s="0" t="n">
         <v>1</v>
@@ -28256,13 +28668,13 @@
         <v>137</v>
       </c>
       <c r="H154" s="1" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="I154" s="1" t="s">
         <v>138</v>
       </c>
       <c r="J154" s="1" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="K154" s="1" t="n">
         <v>1</v>
@@ -28342,7 +28754,7 @@
     </row>
     <row r="155" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="1" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B155" s="1" t="n">
         <v>0.4</v>
@@ -28444,10 +28856,10 @@
     <row r="156" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="157" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J157" s="24" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="K157" s="24" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28478,10 +28890,10 @@
       <c r="I158" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="J158" s="57" t="s">
+      <c r="J158" s="58" t="s">
         <v>111</v>
       </c>
-      <c r="K158" s="56" t="s">
+      <c r="K158" s="67" t="s">
         <v>112</v>
       </c>
     </row>
@@ -28513,10 +28925,10 @@
       <c r="I159" s="18" t="n">
         <v>0.5</v>
       </c>
-      <c r="J159" s="57" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K159" s="56" t="n">
+      <c r="J159" s="58" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K159" s="67" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -28593,10 +29005,10 @@
       <c r="I163" s="18" t="n">
         <v>0.02</v>
       </c>
-      <c r="J163" s="57" t="n">
+      <c r="J163" s="58" t="n">
         <v>0.02</v>
       </c>
-      <c r="K163" s="56" t="n">
+      <c r="K163" s="67" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -28628,10 +29040,10 @@
       <c r="I164" s="18" t="n">
         <v>0.4</v>
       </c>
-      <c r="J164" s="57" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K164" s="56" t="n">
+      <c r="J164" s="58" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K164" s="67" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -28663,10 +29075,10 @@
       <c r="I165" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="J165" s="57" t="n">
-        <v>1</v>
-      </c>
-      <c r="K165" s="56" t="n">
+      <c r="J165" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="K165" s="67" t="n">
         <v>1</v>
       </c>
     </row>
@@ -28698,10 +29110,10 @@
       <c r="I166" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="J166" s="57" t="n">
-        <v>2</v>
-      </c>
-      <c r="K166" s="56" t="n">
+      <c r="J166" s="58" t="n">
+        <v>2</v>
+      </c>
+      <c r="K166" s="67" t="n">
         <v>2</v>
       </c>
     </row>
@@ -28733,10 +29145,10 @@
       <c r="I167" s="18" t="n">
         <v>1.2</v>
       </c>
-      <c r="J167" s="57" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K167" s="56" t="n">
+      <c r="J167" s="58" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K167" s="67" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -28768,10 +29180,10 @@
       <c r="I168" s="18" t="n">
         <v>0.6</v>
       </c>
-      <c r="J168" s="57" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K168" s="56" t="n">
+      <c r="J168" s="58" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K168" s="67" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -28803,10 +29215,10 @@
       <c r="I169" s="18" t="n">
         <v>15000</v>
       </c>
-      <c r="J169" s="57" t="n">
+      <c r="J169" s="58" t="n">
         <v>15000</v>
       </c>
-      <c r="K169" s="56" t="n">
+      <c r="K169" s="67" t="n">
         <v>15000</v>
       </c>
     </row>
@@ -28868,10 +29280,10 @@
       <c r="I172" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="J172" s="57" t="n">
-        <v>2</v>
-      </c>
-      <c r="K172" s="56" t="n">
+      <c r="J172" s="58" t="n">
+        <v>2</v>
+      </c>
+      <c r="K172" s="67" t="n">
         <v>2</v>
       </c>
     </row>
@@ -28903,10 +29315,10 @@
       <c r="I173" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="J173" s="57" t="n">
-        <v>2</v>
-      </c>
-      <c r="K173" s="56" t="n">
+      <c r="J173" s="58" t="n">
+        <v>2</v>
+      </c>
+      <c r="K173" s="67" t="n">
         <v>2</v>
       </c>
     </row>
@@ -28947,34 +29359,34 @@
     </row>
     <row r="175" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B175" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H175" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I175" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J175" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K175" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -29012,7 +29424,7 @@
     </row>
     <row r="178" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="1" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B178" s="1" t="n">
         <v>0.3</v>
@@ -29047,7 +29459,7 @@
     </row>
     <row r="179" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F179" s="24" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29066,7 +29478,7 @@
       <c r="E180" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="F180" s="57" t="s">
+      <c r="F180" s="58" t="s">
         <v>106</v>
       </c>
     </row>
@@ -29086,7 +29498,7 @@
       <c r="E181" s="27" t="n">
         <v>0.5</v>
       </c>
-      <c r="F181" s="57" t="n">
+      <c r="F181" s="58" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -29136,7 +29548,7 @@
       <c r="E185" s="27" t="n">
         <v>0.015</v>
       </c>
-      <c r="F185" s="57" t="n">
+      <c r="F185" s="58" t="n">
         <v>0.015</v>
       </c>
     </row>
@@ -29156,7 +29568,7 @@
       <c r="E186" s="27" t="n">
         <v>0.4</v>
       </c>
-      <c r="F186" s="57" t="n">
+      <c r="F186" s="58" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -29176,7 +29588,7 @@
       <c r="E187" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="F187" s="57" t="n">
+      <c r="F187" s="58" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29196,7 +29608,7 @@
       <c r="E188" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="F188" s="57" t="n">
+      <c r="F188" s="58" t="n">
         <v>6</v>
       </c>
     </row>
@@ -29216,7 +29628,7 @@
       <c r="E189" s="27" t="n">
         <v>1.2</v>
       </c>
-      <c r="F189" s="57" t="n">
+      <c r="F189" s="58" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -29236,7 +29648,7 @@
       <c r="E190" s="27" t="n">
         <v>0.6</v>
       </c>
-      <c r="F190" s="57" t="n">
+      <c r="F190" s="58" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -29256,7 +29668,7 @@
       <c r="E191" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="F191" s="57" t="n">
+      <c r="F191" s="58" t="n">
         <v>10000</v>
       </c>
     </row>
@@ -29296,7 +29708,7 @@
       <c r="E194" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="F194" s="57" t="n">
+      <c r="F194" s="58" t="n">
         <v>2</v>
       </c>
     </row>
@@ -29316,7 +29728,7 @@
       <c r="E195" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="F195" s="57" t="n">
+      <c r="F195" s="58" t="n">
         <v>2</v>
       </c>
     </row>
@@ -29342,27 +29754,27 @@
     </row>
     <row r="197" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B197" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E198" s="84" t="s">
-        <v>246</v>
-      </c>
-      <c r="F198" s="84" t="s">
-        <v>247</v>
+      <c r="E198" s="87" t="s">
+        <v>251</v>
+      </c>
+      <c r="F198" s="87" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29384,7 +29796,7 @@
     </row>
     <row r="200" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="1" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B200" s="1" t="n">
         <v>0.3</v>
@@ -29401,55 +29813,55 @@
       <c r="F200" s="1" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q200" s="58" t="s">
-        <v>202</v>
+      <c r="Q200" s="59" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="M201" s="85" t="s">
-        <v>248</v>
-      </c>
-      <c r="N201" s="85" t="s">
-        <v>248</v>
-      </c>
-      <c r="O201" s="85" t="s">
-        <v>248</v>
-      </c>
-      <c r="P201" s="86" t="s">
-        <v>203</v>
-      </c>
-      <c r="Q201" s="59" t="s">
-        <v>203</v>
+      <c r="M201" s="88" t="s">
+        <v>253</v>
+      </c>
+      <c r="N201" s="88" t="s">
+        <v>253</v>
+      </c>
+      <c r="O201" s="88" t="s">
+        <v>253</v>
+      </c>
+      <c r="P201" s="89" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q201" s="60" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H202" s="24"/>
       <c r="I202" s="24" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="J202" s="24" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="K202" s="24" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="L202" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="M202" s="85" t="s">
-        <v>251</v>
-      </c>
-      <c r="N202" s="85" t="s">
-        <v>251</v>
-      </c>
-      <c r="O202" s="85" t="s">
-        <v>251</v>
+        <v>255</v>
+      </c>
+      <c r="M202" s="88" t="s">
+        <v>256</v>
+      </c>
+      <c r="N202" s="88" t="s">
+        <v>256</v>
+      </c>
+      <c r="O202" s="88" t="s">
+        <v>256</v>
       </c>
       <c r="P202" s="24" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="Q202" s="49" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29477,7 +29889,7 @@
       <c r="H203" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="I203" s="57" t="s">
+      <c r="I203" s="58" t="s">
         <v>109</v>
       </c>
       <c r="J203" s="32" t="s">
@@ -29501,7 +29913,7 @@
       <c r="P203" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="Q203" s="79" t="s">
+      <c r="Q203" s="85" t="s">
         <v>117</v>
       </c>
     </row>
@@ -29530,7 +29942,7 @@
       <c r="H204" s="27" t="n">
         <v>0.5</v>
       </c>
-      <c r="I204" s="57" t="n">
+      <c r="I204" s="58" t="n">
         <v>0.5</v>
       </c>
       <c r="J204" s="32" t="n">
@@ -29554,7 +29966,7 @@
       <c r="P204" s="45" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q204" s="79" t="n">
+      <c r="Q204" s="85" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -29646,7 +30058,7 @@
       <c r="H208" s="27" t="n">
         <v>0.005</v>
       </c>
-      <c r="I208" s="57" t="n">
+      <c r="I208" s="58" t="n">
         <v>0.005</v>
       </c>
       <c r="J208" s="32" t="n">
@@ -29670,7 +30082,7 @@
       <c r="P208" s="45" t="n">
         <v>0.005</v>
       </c>
-      <c r="Q208" s="79" t="n">
+      <c r="Q208" s="85" t="n">
         <v>0.005</v>
       </c>
     </row>
@@ -29699,7 +30111,7 @@
       <c r="H209" s="27" t="n">
         <v>0.4</v>
       </c>
-      <c r="I209" s="57" t="n">
+      <c r="I209" s="58" t="n">
         <v>0.4</v>
       </c>
       <c r="J209" s="32" t="n">
@@ -29723,7 +30135,7 @@
       <c r="P209" s="45" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q209" s="79" t="n">
+      <c r="Q209" s="85" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -29752,7 +30164,7 @@
       <c r="H210" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="I210" s="57" t="n">
+      <c r="I210" s="58" t="n">
         <v>1</v>
       </c>
       <c r="J210" s="32" t="n">
@@ -29776,7 +30188,7 @@
       <c r="P210" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="Q210" s="79" t="n">
+      <c r="Q210" s="85" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29805,7 +30217,7 @@
       <c r="H211" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="I211" s="57" t="n">
+      <c r="I211" s="58" t="n">
         <v>9</v>
       </c>
       <c r="J211" s="32" t="n">
@@ -29829,7 +30241,7 @@
       <c r="P211" s="45" t="n">
         <v>9</v>
       </c>
-      <c r="Q211" s="79" t="n">
+      <c r="Q211" s="85" t="n">
         <v>6</v>
       </c>
     </row>
@@ -29858,7 +30270,7 @@
       <c r="H212" s="27" t="n">
         <v>1.2</v>
       </c>
-      <c r="I212" s="57" t="n">
+      <c r="I212" s="58" t="n">
         <v>1.2</v>
       </c>
       <c r="J212" s="32" t="n">
@@ -29882,7 +30294,7 @@
       <c r="P212" s="45" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q212" s="79" t="n">
+      <c r="Q212" s="85" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -29911,7 +30323,7 @@
       <c r="H213" s="27" t="n">
         <v>0.6</v>
       </c>
-      <c r="I213" s="57" t="n">
+      <c r="I213" s="58" t="n">
         <v>0.6</v>
       </c>
       <c r="J213" s="32" t="n">
@@ -29935,7 +30347,7 @@
       <c r="P213" s="45" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q213" s="79" t="n">
+      <c r="Q213" s="85" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -29964,7 +30376,7 @@
       <c r="H214" s="27" t="n">
         <v>27000</v>
       </c>
-      <c r="I214" s="57" t="n">
+      <c r="I214" s="58" t="n">
         <v>27000</v>
       </c>
       <c r="J214" s="32" t="n">
@@ -29988,7 +30400,7 @@
       <c r="P214" s="45" t="n">
         <v>20000</v>
       </c>
-      <c r="Q214" s="79" t="n">
+      <c r="Q214" s="85" t="n">
         <v>20000</v>
       </c>
     </row>
@@ -30059,7 +30471,7 @@
       <c r="H217" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="I217" s="57" t="n">
+      <c r="I217" s="58" t="n">
         <v>2</v>
       </c>
       <c r="J217" s="32" t="n">
@@ -30083,7 +30495,7 @@
       <c r="P217" s="45" t="n">
         <v>2</v>
       </c>
-      <c r="Q217" s="79" t="n">
+      <c r="Q217" s="85" t="n">
         <v>5</v>
       </c>
     </row>
@@ -30112,7 +30524,7 @@
       <c r="H218" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="I218" s="57" t="n">
+      <c r="I218" s="58" t="n">
         <v>2</v>
       </c>
       <c r="J218" s="32" t="n">
@@ -30136,7 +30548,7 @@
       <c r="P218" s="45" t="n">
         <v>2</v>
       </c>
-      <c r="Q218" s="79" t="n">
+      <c r="Q218" s="85" t="n">
         <v>5</v>
       </c>
     </row>
@@ -30195,52 +30607,52 @@
     </row>
     <row r="220" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B220" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G220" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H220" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I220" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J220" s="1" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="K220" s="1" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="L220" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M220" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N220" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O220" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P220" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q220" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -30251,7 +30663,7 @@
     </row>
     <row r="223" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="1" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B223" s="1" t="n">
         <v>0.3</v>
@@ -30280,31 +30692,31 @@
     </row>
     <row r="224" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="1" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="G224" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="H224" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="I224" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="J224" s="24" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="K224" s="24" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30323,10 +30735,10 @@
       <c r="E225" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="F225" s="87" t="s">
-        <v>256</v>
-      </c>
-      <c r="J225" s="57" t="s">
+      <c r="F225" s="90" t="s">
+        <v>261</v>
+      </c>
+      <c r="J225" s="58" t="s">
         <v>107</v>
       </c>
     </row>
@@ -30602,19 +31014,19 @@
     </row>
     <row r="242" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B242" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J242" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -30628,7 +31040,7 @@
     </row>
     <row r="245" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="1" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B245" s="1" t="n">
         <v>0.4</v>
@@ -30648,29 +31060,29 @@
     </row>
     <row r="246" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="1" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="J246" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G247" s="1" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="H247" s="24" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="2" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B248" s="17" t="s">
         <v>102</v>
@@ -30690,44 +31102,44 @@
       <c r="G248" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="H248" s="76" t="s">
+      <c r="H248" s="57" t="s">
         <v>108</v>
       </c>
-      <c r="I248" s="63" t="s">
+      <c r="I248" s="56" t="s">
         <v>109</v>
       </c>
-      <c r="J248" s="63" t="s">
+      <c r="J248" s="56" t="s">
         <v>110</v>
       </c>
-      <c r="K248" s="63" t="s">
+      <c r="K248" s="56" t="s">
         <v>111</v>
       </c>
-      <c r="L248" s="63" t="s">
+      <c r="L248" s="56" t="s">
         <v>112</v>
       </c>
-      <c r="M248" s="63" t="s">
+      <c r="M248" s="56" t="s">
         <v>113</v>
       </c>
-      <c r="N248" s="63" t="s">
+      <c r="N248" s="56" t="s">
         <v>114</v>
       </c>
-      <c r="O248" s="63" t="s">
+      <c r="O248" s="56" t="s">
         <v>115</v>
       </c>
-      <c r="P248" s="63" t="s">
+      <c r="P248" s="56" t="s">
         <v>116</v>
       </c>
-      <c r="Q248" s="63" t="s">
+      <c r="Q248" s="56" t="s">
         <v>117</v>
       </c>
-      <c r="R248" s="63" t="s">
+      <c r="R248" s="56" t="s">
         <v>118</v>
       </c>
-      <c r="S248" s="56" t="s">
+      <c r="S248" s="67" t="s">
         <v>150</v>
       </c>
-      <c r="T248" s="58" t="s">
-        <v>202</v>
+      <c r="T248" s="59" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30752,44 +31164,44 @@
       <c r="G249" s="27" t="n">
         <v>0.5</v>
       </c>
-      <c r="H249" s="76" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I249" s="63" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J249" s="63" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K249" s="63" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L249" s="63" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M249" s="63" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N249" s="63" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O249" s="63" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P249" s="63" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q249" s="63" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R249" s="63" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S249" s="56" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T249" s="59" t="s">
-        <v>203</v>
+      <c r="H249" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I249" s="56" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J249" s="56" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K249" s="56" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L249" s="56" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M249" s="56" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N249" s="56" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O249" s="56" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P249" s="56" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q249" s="56" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R249" s="56" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S249" s="67" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T249" s="60" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30815,7 +31227,7 @@
       <c r="R250" s="23"/>
       <c r="S250" s="23"/>
       <c r="T250" s="49" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30886,40 +31298,40 @@
       <c r="G253" s="27" t="n">
         <v>0.004</v>
       </c>
-      <c r="H253" s="76" t="n">
+      <c r="H253" s="57" t="n">
         <v>0.004</v>
       </c>
-      <c r="I253" s="63" t="n">
+      <c r="I253" s="56" t="n">
         <v>0.004</v>
       </c>
-      <c r="J253" s="63" t="n">
+      <c r="J253" s="56" t="n">
         <v>0.004</v>
       </c>
-      <c r="K253" s="63" t="n">
+      <c r="K253" s="56" t="n">
         <v>0.004</v>
       </c>
-      <c r="L253" s="63" t="n">
+      <c r="L253" s="56" t="n">
         <v>0.004</v>
       </c>
-      <c r="M253" s="63" t="n">
+      <c r="M253" s="56" t="n">
         <v>0.004</v>
       </c>
-      <c r="N253" s="63" t="n">
+      <c r="N253" s="56" t="n">
         <v>0.004</v>
       </c>
-      <c r="O253" s="63" t="n">
+      <c r="O253" s="56" t="n">
         <v>0.004</v>
       </c>
-      <c r="P253" s="63" t="n">
+      <c r="P253" s="56" t="n">
         <v>0.004</v>
       </c>
-      <c r="Q253" s="63" t="n">
+      <c r="Q253" s="56" t="n">
         <v>0.004</v>
       </c>
-      <c r="R253" s="63" t="n">
+      <c r="R253" s="56" t="n">
         <v>0.004</v>
       </c>
-      <c r="S253" s="56" t="n">
+      <c r="S253" s="67" t="n">
         <v>0.004</v>
       </c>
     </row>
@@ -30945,40 +31357,40 @@
       <c r="G254" s="27" t="n">
         <v>0.4</v>
       </c>
-      <c r="H254" s="76" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I254" s="63" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J254" s="63" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K254" s="63" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L254" s="63" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M254" s="63" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N254" s="63" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O254" s="63" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="P254" s="63" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q254" s="63" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="R254" s="63" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="S254" s="56" t="n">
+      <c r="H254" s="57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I254" s="56" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J254" s="56" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K254" s="56" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L254" s="56" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M254" s="56" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N254" s="56" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O254" s="56" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P254" s="56" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q254" s="56" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R254" s="56" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S254" s="67" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -31004,40 +31416,40 @@
       <c r="G255" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="H255" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="I255" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="J255" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="K255" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="L255" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="M255" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="N255" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="O255" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="P255" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q255" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="R255" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="S255" s="56" t="n">
+      <c r="H255" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I255" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J255" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="K255" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="L255" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="M255" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="N255" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="O255" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="P255" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q255" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="R255" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="S255" s="67" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31063,40 +31475,40 @@
       <c r="G256" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="H256" s="76" t="n">
+      <c r="H256" s="57" t="n">
         <v>4</v>
       </c>
-      <c r="I256" s="63" t="n">
+      <c r="I256" s="56" t="n">
         <v>4</v>
       </c>
-      <c r="J256" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="K256" s="63" t="n">
+      <c r="J256" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="K256" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="L256" s="63" t="n">
+      <c r="L256" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="M256" s="63" t="n">
+      <c r="M256" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="N256" s="63" t="n">
+      <c r="N256" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="O256" s="63" t="n">
+      <c r="O256" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="P256" s="63" t="n">
+      <c r="P256" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="Q256" s="63" t="n">
+      <c r="Q256" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="R256" s="63" t="n">
-        <v>2</v>
-      </c>
-      <c r="S256" s="56" t="n">
+      <c r="R256" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="S256" s="67" t="n">
         <v>2</v>
       </c>
     </row>
@@ -31122,40 +31534,40 @@
       <c r="G257" s="27" t="n">
         <v>1.2</v>
       </c>
-      <c r="H257" s="76" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I257" s="63" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J257" s="63" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K257" s="63" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L257" s="63" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="M257" s="63" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="N257" s="63" t="n">
+      <c r="H257" s="57" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I257" s="56" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J257" s="56" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K257" s="56" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L257" s="56" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M257" s="56" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N257" s="56" t="n">
         <v>10</v>
       </c>
-      <c r="O257" s="63" t="n">
+      <c r="O257" s="56" t="n">
         <v>10</v>
       </c>
-      <c r="P257" s="63" t="n">
+      <c r="P257" s="56" t="n">
         <v>10</v>
       </c>
-      <c r="Q257" s="63" t="n">
+      <c r="Q257" s="56" t="n">
         <v>10</v>
       </c>
-      <c r="R257" s="63" t="n">
+      <c r="R257" s="56" t="n">
         <v>10</v>
       </c>
-      <c r="S257" s="56" t="n">
+      <c r="S257" s="67" t="n">
         <v>10</v>
       </c>
     </row>
@@ -31181,40 +31593,40 @@
       <c r="G258" s="27" t="n">
         <v>0.6</v>
       </c>
-      <c r="H258" s="76" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I258" s="63" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J258" s="63" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K258" s="63" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L258" s="63" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M258" s="63" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N258" s="63" t="n">
+      <c r="H258" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I258" s="56" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J258" s="56" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K258" s="56" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L258" s="56" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M258" s="56" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N258" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="O258" s="63" t="n">
+      <c r="O258" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="P258" s="63" t="n">
+      <c r="P258" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="Q258" s="63" t="n">
+      <c r="Q258" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="R258" s="63" t="n">
+      <c r="R258" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="S258" s="56" t="n">
+      <c r="S258" s="67" t="n">
         <v>0</v>
       </c>
     </row>
@@ -31240,40 +31652,40 @@
       <c r="G259" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="H259" s="76" t="n">
+      <c r="H259" s="57" t="n">
         <v>10000</v>
       </c>
-      <c r="I259" s="63" t="n">
+      <c r="I259" s="56" t="n">
         <v>10000</v>
       </c>
-      <c r="J259" s="63" t="n">
+      <c r="J259" s="56" t="n">
         <v>10000</v>
       </c>
-      <c r="K259" s="63" t="n">
+      <c r="K259" s="56" t="n">
         <v>5000</v>
       </c>
-      <c r="L259" s="63" t="n">
+      <c r="L259" s="56" t="n">
         <v>2000</v>
       </c>
-      <c r="M259" s="63" t="n">
+      <c r="M259" s="56" t="n">
         <v>5000</v>
       </c>
-      <c r="N259" s="63" t="n">
+      <c r="N259" s="56" t="n">
         <v>5000</v>
       </c>
-      <c r="O259" s="63" t="n">
+      <c r="O259" s="56" t="n">
         <v>10000</v>
       </c>
-      <c r="P259" s="63" t="n">
+      <c r="P259" s="56" t="n">
         <v>10000</v>
       </c>
-      <c r="Q259" s="63" t="n">
+      <c r="Q259" s="56" t="n">
         <v>10000</v>
       </c>
-      <c r="R259" s="63" t="n">
+      <c r="R259" s="56" t="n">
         <v>10000</v>
       </c>
-      <c r="S259" s="56" t="n">
+      <c r="S259" s="67" t="n">
         <v>2000</v>
       </c>
     </row>
@@ -31345,40 +31757,40 @@
       <c r="G262" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="H262" s="76" t="n">
+      <c r="H262" s="57" t="n">
         <v>3</v>
       </c>
-      <c r="I262" s="63" t="n">
+      <c r="I262" s="56" t="n">
         <v>3</v>
       </c>
-      <c r="J262" s="63" t="n">
+      <c r="J262" s="56" t="n">
         <v>3</v>
       </c>
-      <c r="K262" s="63" t="n">
-        <v>2</v>
-      </c>
-      <c r="L262" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="M262" s="63" t="n">
-        <v>2</v>
-      </c>
-      <c r="N262" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="O262" s="63" t="n">
-        <v>2</v>
-      </c>
-      <c r="P262" s="63" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q262" s="63" t="n">
-        <v>2</v>
-      </c>
-      <c r="R262" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="S262" s="56" t="n">
+      <c r="K262" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="L262" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="M262" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="N262" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="O262" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="P262" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q262" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="R262" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="S262" s="67" t="n">
         <v>3</v>
       </c>
     </row>
@@ -31404,40 +31816,40 @@
       <c r="G263" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="H263" s="76" t="n">
+      <c r="H263" s="57" t="n">
         <v>3</v>
       </c>
-      <c r="I263" s="63" t="n">
+      <c r="I263" s="56" t="n">
         <v>3</v>
       </c>
-      <c r="J263" s="63" t="n">
+      <c r="J263" s="56" t="n">
         <v>3</v>
       </c>
-      <c r="K263" s="63" t="n">
-        <v>2</v>
-      </c>
-      <c r="L263" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="M263" s="63" t="n">
-        <v>2</v>
-      </c>
-      <c r="N263" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="O263" s="63" t="n">
-        <v>2</v>
-      </c>
-      <c r="P263" s="63" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q263" s="63" t="n">
-        <v>2</v>
-      </c>
-      <c r="R263" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="S263" s="56" t="n">
+      <c r="K263" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="L263" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="M263" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="N263" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="O263" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="P263" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q263" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="R263" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="S263" s="67" t="n">
         <v>3</v>
       </c>
     </row>
@@ -31502,58 +31914,58 @@
     </row>
     <row r="265" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B265" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G265" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H265" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I265" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J265" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K265" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L265" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M265" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N265" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O265" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P265" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q265" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="R265" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="S265" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31604,13 +32016,13 @@
       <c r="Q267" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="S267" s="58" t="s">
-        <v>202</v>
+      <c r="S267" s="59" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="268" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="1" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B268" s="1" t="n">
         <v>0.4</v>
@@ -31633,42 +32045,42 @@
       <c r="H268" s="1" t="n">
         <v>0.4</v>
       </c>
-      <c r="S268" s="59" t="s">
-        <v>203</v>
+      <c r="S268" s="60" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="1" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="G269" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="H269" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="S269" s="49" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="2" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="B270" s="17" t="s">
         <v>102</v>
@@ -31688,7 +32100,7 @@
       <c r="G270" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="H270" s="57" t="s">
+      <c r="H270" s="58" t="s">
         <v>108</v>
       </c>
       <c r="I270" s="27" t="s">
@@ -31721,7 +32133,7 @@
       <c r="R270" s="45" t="s">
         <v>118</v>
       </c>
-      <c r="S270" s="79" t="s">
+      <c r="S270" s="85" t="s">
         <v>150</v>
       </c>
     </row>
@@ -31747,7 +32159,7 @@
       <c r="G271" s="27" t="n">
         <v>0.5</v>
       </c>
-      <c r="H271" s="57" t="n">
+      <c r="H271" s="58" t="n">
         <v>0.5</v>
       </c>
       <c r="I271" s="27" t="n">
@@ -31780,7 +32192,7 @@
       <c r="R271" s="45" t="n">
         <v>0.5</v>
       </c>
-      <c r="S271" s="79" t="n">
+      <c r="S271" s="85" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -31875,7 +32287,7 @@
       <c r="G275" s="27" t="n">
         <v>0.003</v>
       </c>
-      <c r="H275" s="57" t="n">
+      <c r="H275" s="58" t="n">
         <v>0.003</v>
       </c>
       <c r="I275" s="27" t="n">
@@ -31908,7 +32320,7 @@
       <c r="R275" s="45" t="n">
         <v>0.003</v>
       </c>
-      <c r="S275" s="79" t="n">
+      <c r="S275" s="85" t="n">
         <v>0.003</v>
       </c>
     </row>
@@ -31934,7 +32346,7 @@
       <c r="G276" s="27" t="n">
         <v>0.4</v>
       </c>
-      <c r="H276" s="57" t="n">
+      <c r="H276" s="58" t="n">
         <v>0.4</v>
       </c>
       <c r="I276" s="27" t="n">
@@ -31967,7 +32379,7 @@
       <c r="R276" s="45" t="n">
         <v>0.4</v>
       </c>
-      <c r="S276" s="79" t="n">
+      <c r="S276" s="85" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -31993,7 +32405,7 @@
       <c r="G277" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="H277" s="57" t="n">
+      <c r="H277" s="58" t="n">
         <v>1</v>
       </c>
       <c r="I277" s="27" t="n">
@@ -32026,7 +32438,7 @@
       <c r="R277" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="S277" s="79" t="n">
+      <c r="S277" s="85" t="n">
         <v>1</v>
       </c>
     </row>
@@ -32052,7 +32464,7 @@
       <c r="G278" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="H278" s="57" t="n">
+      <c r="H278" s="58" t="n">
         <v>10</v>
       </c>
       <c r="I278" s="27" t="n">
@@ -32085,7 +32497,7 @@
       <c r="R278" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="S278" s="79" t="n">
+      <c r="S278" s="85" t="n">
         <v>0</v>
       </c>
     </row>
@@ -32111,7 +32523,7 @@
       <c r="G279" s="27" t="n">
         <v>1.2</v>
       </c>
-      <c r="H279" s="57" t="n">
+      <c r="H279" s="58" t="n">
         <v>1.2</v>
       </c>
       <c r="I279" s="27" t="n">
@@ -32144,7 +32556,7 @@
       <c r="R279" s="45" t="n">
         <v>10</v>
       </c>
-      <c r="S279" s="79" t="n">
+      <c r="S279" s="85" t="n">
         <v>10</v>
       </c>
     </row>
@@ -32170,7 +32582,7 @@
       <c r="G280" s="27" t="n">
         <v>0.6</v>
       </c>
-      <c r="H280" s="57" t="n">
+      <c r="H280" s="58" t="n">
         <v>0.6</v>
       </c>
       <c r="I280" s="27" t="n">
@@ -32203,7 +32615,7 @@
       <c r="R280" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="S280" s="79" t="n">
+      <c r="S280" s="85" t="n">
         <v>0</v>
       </c>
     </row>
@@ -32229,7 +32641,7 @@
       <c r="G281" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="H281" s="57" t="n">
+      <c r="H281" s="58" t="n">
         <v>10000</v>
       </c>
       <c r="I281" s="27" t="n">
@@ -32262,7 +32674,7 @@
       <c r="R281" s="45" t="n">
         <v>10000</v>
       </c>
-      <c r="S281" s="79" t="n">
+      <c r="S281" s="85" t="n">
         <v>10000</v>
       </c>
     </row>
@@ -32334,7 +32746,7 @@
       <c r="G284" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="H284" s="57" t="n">
+      <c r="H284" s="58" t="n">
         <v>1</v>
       </c>
       <c r="I284" s="27" t="n">
@@ -32367,7 +32779,7 @@
       <c r="R284" s="45" t="n">
         <v>2</v>
       </c>
-      <c r="S284" s="79" t="n">
+      <c r="S284" s="85" t="n">
         <v>1</v>
       </c>
     </row>
@@ -32393,7 +32805,7 @@
       <c r="G285" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="H285" s="57" t="n">
+      <c r="H285" s="58" t="n">
         <v>1</v>
       </c>
       <c r="I285" s="27" t="n">
@@ -32426,7 +32838,7 @@
       <c r="R285" s="45" t="n">
         <v>2</v>
       </c>
-      <c r="S285" s="79" t="n">
+      <c r="S285" s="85" t="n">
         <v>1</v>
       </c>
     </row>
@@ -32491,63 +32903,63 @@
     </row>
     <row r="287" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B287" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G287" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H287" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I287" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J287" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K287" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L287" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M287" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N287" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O287" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P287" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q287" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="R287" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="S287" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="288" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L288" s="0" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="M288" s="0" t="n">
         <v>1</v>
@@ -32593,13 +33005,13 @@
       <c r="H289" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="M289" s="72" t="s">
-        <v>202</v>
+      <c r="M289" s="79" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="290" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="1" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B290" s="1" t="n">
         <v>0.4</v>
@@ -32625,48 +33037,48 @@
       <c r="I290" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="M290" s="72" t="s">
-        <v>203</v>
+      <c r="M290" s="79" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="291" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="1" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="G291" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="H291" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="I291" s="1" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="J291" s="24" t="s">
-        <v>201</v>
-      </c>
-      <c r="M291" s="74" t="s">
-        <v>247</v>
+        <v>208</v>
+      </c>
+      <c r="M291" s="81" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="292" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="2" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B292" s="17" t="s">
         <v>102</v>
@@ -32692,16 +33104,16 @@
       <c r="I292" s="27" t="s">
         <v>109</v>
       </c>
-      <c r="J292" s="76" t="s">
+      <c r="J292" s="57" t="s">
         <v>110</v>
       </c>
-      <c r="K292" s="63" t="s">
+      <c r="K292" s="56" t="s">
         <v>111</v>
       </c>
-      <c r="L292" s="63" t="s">
+      <c r="L292" s="56" t="s">
         <v>112</v>
       </c>
-      <c r="M292" s="56" t="s">
+      <c r="M292" s="67" t="s">
         <v>113</v>
       </c>
     </row>
@@ -32733,16 +33145,16 @@
       <c r="I293" s="27" t="n">
         <v>0.5</v>
       </c>
-      <c r="J293" s="76" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K293" s="63" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L293" s="63" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M293" s="56" t="n">
+      <c r="J293" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K293" s="56" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L293" s="56" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M293" s="67" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -32825,16 +33237,16 @@
       <c r="I297" s="27" t="n">
         <v>0.02</v>
       </c>
-      <c r="J297" s="76" t="n">
+      <c r="J297" s="57" t="n">
         <v>0.02</v>
       </c>
-      <c r="K297" s="63" t="n">
+      <c r="K297" s="56" t="n">
         <v>0.02</v>
       </c>
-      <c r="L297" s="63" t="n">
+      <c r="L297" s="56" t="n">
         <v>0.02</v>
       </c>
-      <c r="M297" s="56" t="n">
+      <c r="M297" s="67" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -32866,16 +33278,16 @@
       <c r="I298" s="27" t="n">
         <v>0.4</v>
       </c>
-      <c r="J298" s="76" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K298" s="63" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L298" s="63" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M298" s="56" t="n">
+      <c r="J298" s="57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K298" s="56" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L298" s="56" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M298" s="67" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -32907,16 +33319,16 @@
       <c r="I299" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="J299" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="K299" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="L299" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="M299" s="56" t="n">
+      <c r="J299" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="K299" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="L299" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="M299" s="67" t="n">
         <v>1</v>
       </c>
     </row>
@@ -32948,16 +33360,16 @@
       <c r="I300" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="J300" s="76" t="n">
+      <c r="J300" s="57" t="n">
         <v>5</v>
       </c>
-      <c r="K300" s="63" t="n">
+      <c r="K300" s="56" t="n">
         <v>3</v>
       </c>
-      <c r="L300" s="63" t="n">
+      <c r="L300" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="M300" s="56" t="n">
+      <c r="M300" s="67" t="n">
         <v>2</v>
       </c>
     </row>
@@ -32989,16 +33401,16 @@
       <c r="I301" s="27" t="n">
         <v>1.2</v>
       </c>
-      <c r="J301" s="76" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K301" s="63" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L301" s="63" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="M301" s="56" t="n">
+      <c r="J301" s="57" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K301" s="56" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L301" s="56" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M301" s="67" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -33030,16 +33442,16 @@
       <c r="I302" s="27" t="n">
         <v>0.6</v>
       </c>
-      <c r="J302" s="76" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K302" s="63" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L302" s="63" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M302" s="56" t="n">
+      <c r="J302" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K302" s="56" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L302" s="56" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M302" s="67" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -33071,16 +33483,16 @@
       <c r="I303" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="J303" s="76" t="n">
+      <c r="J303" s="57" t="n">
         <v>10000</v>
       </c>
-      <c r="K303" s="63" t="n">
+      <c r="K303" s="56" t="n">
         <v>10000</v>
       </c>
-      <c r="L303" s="63" t="n">
+      <c r="L303" s="56" t="n">
         <v>2000</v>
       </c>
-      <c r="M303" s="56" t="n">
+      <c r="M303" s="67" t="n">
         <v>5000</v>
       </c>
     </row>
@@ -33096,7 +33508,7 @@
       <c r="G304" s="29"/>
       <c r="H304" s="29"/>
       <c r="I304" s="29"/>
-      <c r="J304" s="81"/>
+      <c r="J304" s="62"/>
       <c r="K304" s="29"/>
       <c r="L304" s="29"/>
       <c r="M304" s="29"/>
@@ -33113,7 +33525,7 @@
       <c r="G305" s="31"/>
       <c r="H305" s="31"/>
       <c r="I305" s="31"/>
-      <c r="J305" s="81"/>
+      <c r="J305" s="62"/>
       <c r="K305" s="31"/>
       <c r="L305" s="31"/>
       <c r="M305" s="31"/>
@@ -33146,16 +33558,16 @@
       <c r="I306" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="J306" s="76" t="n">
-        <v>2</v>
-      </c>
-      <c r="K306" s="63" t="n">
-        <v>2</v>
-      </c>
-      <c r="L306" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="M306" s="56" t="n">
+      <c r="J306" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="K306" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="L306" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="M306" s="67" t="n">
         <v>1</v>
       </c>
     </row>
@@ -33187,16 +33599,16 @@
       <c r="I307" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="J307" s="76" t="n">
-        <v>2</v>
-      </c>
-      <c r="K307" s="63" t="n">
-        <v>2</v>
-      </c>
-      <c r="L307" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="M307" s="56" t="n">
+      <c r="J307" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="K307" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="L307" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="M307" s="67" t="n">
         <v>1</v>
       </c>
     </row>
@@ -33243,40 +33655,40 @@
     </row>
     <row r="309" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B309" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F309" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G309" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H309" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I309" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J309" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K309" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L309" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M309" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="310" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -33312,7 +33724,7 @@
     </row>
     <row r="312" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A312" s="1" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B312" s="1" t="n">
         <v>0.4</v>
@@ -33345,40 +33757,40 @@
     </row>
     <row r="313" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="1" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="G313" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="H313" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="I313" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="J313" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="K313" s="1"/>
     </row>
     <row r="314" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A314" s="88" t="s">
-        <v>263</v>
+      <c r="A314" s="91" t="s">
+        <v>268</v>
       </c>
       <c r="B314" s="17" t="s">
         <v>102</v>
@@ -33387,11 +33799,11 @@
         <v>103</v>
       </c>
       <c r="D314" s="24" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
     </row>
     <row r="315" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A315" s="88" t="s">
+      <c r="A315" s="91" t="s">
         <v>80</v>
       </c>
       <c r="B315" s="17" t="n">
@@ -33402,28 +33814,28 @@
       </c>
     </row>
     <row r="316" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A316" s="88" t="s">
+      <c r="A316" s="91" t="s">
         <v>120</v>
       </c>
       <c r="B316" s="23"/>
       <c r="C316" s="23"/>
     </row>
     <row r="317" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A317" s="88" t="s">
+      <c r="A317" s="91" t="s">
         <v>82</v>
       </c>
       <c r="B317" s="23"/>
       <c r="C317" s="23"/>
     </row>
     <row r="318" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A318" s="88" t="s">
+      <c r="A318" s="91" t="s">
         <v>121</v>
       </c>
       <c r="B318" s="23"/>
       <c r="C318" s="23"/>
     </row>
     <row r="319" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A319" s="88" t="s">
+      <c r="A319" s="91" t="s">
         <v>84</v>
       </c>
       <c r="B319" s="17" t="n">
@@ -33434,7 +33846,7 @@
       </c>
     </row>
     <row r="320" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A320" s="88" t="s">
+      <c r="A320" s="91" t="s">
         <v>79</v>
       </c>
       <c r="B320" s="17" t="n">
@@ -33445,7 +33857,7 @@
       </c>
     </row>
     <row r="321" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A321" s="88" t="s">
+      <c r="A321" s="91" t="s">
         <v>85</v>
       </c>
       <c r="B321" s="17" t="n">
@@ -33456,7 +33868,7 @@
       </c>
     </row>
     <row r="322" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A322" s="88" t="s">
+      <c r="A322" s="91" t="s">
         <v>122</v>
       </c>
       <c r="B322" s="17" t="n">
@@ -33467,7 +33879,7 @@
       </c>
     </row>
     <row r="323" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A323" s="88" t="s">
+      <c r="A323" s="91" t="s">
         <v>123</v>
       </c>
       <c r="B323" s="17" t="n">
@@ -33478,7 +33890,7 @@
       </c>
     </row>
     <row r="324" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A324" s="88" t="s">
+      <c r="A324" s="91" t="s">
         <v>124</v>
       </c>
       <c r="B324" s="17" t="n">
@@ -33489,7 +33901,7 @@
       </c>
     </row>
     <row r="325" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A325" s="88" t="s">
+      <c r="A325" s="91" t="s">
         <v>125</v>
       </c>
       <c r="B325" s="17" t="n">
@@ -33500,21 +33912,21 @@
       </c>
     </row>
     <row r="326" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A326" s="88" t="s">
+      <c r="A326" s="91" t="s">
         <v>126</v>
       </c>
       <c r="B326" s="29"/>
       <c r="C326" s="29"/>
     </row>
     <row r="327" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A327" s="89" t="s">
+      <c r="A327" s="92" t="s">
         <v>128</v>
       </c>
       <c r="B327" s="31"/>
       <c r="C327" s="31"/>
     </row>
     <row r="328" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A328" s="88" t="s">
+      <c r="A328" s="91" t="s">
         <v>134</v>
       </c>
       <c r="B328" s="17" t="n">
@@ -33525,7 +33937,7 @@
       </c>
     </row>
     <row r="329" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A329" s="88" t="s">
+      <c r="A329" s="91" t="s">
         <v>136</v>
       </c>
       <c r="B329" s="17" t="n">
@@ -33536,7 +33948,7 @@
       </c>
     </row>
     <row r="330" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A330" s="90" t="s">
+      <c r="A330" s="93" t="s">
         <v>157</v>
       </c>
       <c r="B330" s="5" t="n">
@@ -33548,10 +33960,10 @@
     </row>
     <row r="331" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B331" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C331" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="332" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -33565,7 +33977,7 @@
     </row>
     <row r="334" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A334" s="1" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B334" s="1" t="n">
         <v>0.4</v>
@@ -33576,25 +33988,25 @@
     </row>
     <row r="335" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A335" s="1" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
     </row>
     <row r="336" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A336" s="88" t="s">
-        <v>265</v>
+      <c r="A336" s="91" t="s">
+        <v>270</v>
       </c>
       <c r="B336" s="17" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="337" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A337" s="88" t="s">
+      <c r="A337" s="91" t="s">
         <v>80</v>
       </c>
       <c r="B337" s="17" t="n">
@@ -33602,25 +34014,25 @@
       </c>
     </row>
     <row r="338" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A338" s="88" t="s">
+      <c r="A338" s="91" t="s">
         <v>120</v>
       </c>
       <c r="B338" s="23"/>
     </row>
     <row r="339" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A339" s="88" t="s">
+      <c r="A339" s="91" t="s">
         <v>82</v>
       </c>
       <c r="B339" s="23"/>
     </row>
     <row r="340" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A340" s="88" t="s">
+      <c r="A340" s="91" t="s">
         <v>121</v>
       </c>
       <c r="B340" s="23"/>
     </row>
     <row r="341" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A341" s="88" t="s">
+      <c r="A341" s="91" t="s">
         <v>84</v>
       </c>
       <c r="B341" s="17" t="n">
@@ -33628,7 +34040,7 @@
       </c>
     </row>
     <row r="342" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A342" s="88" t="s">
+      <c r="A342" s="91" t="s">
         <v>79</v>
       </c>
       <c r="B342" s="17" t="n">
@@ -33636,7 +34048,7 @@
       </c>
     </row>
     <row r="343" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A343" s="88" t="s">
+      <c r="A343" s="91" t="s">
         <v>85</v>
       </c>
       <c r="B343" s="17" t="n">
@@ -33644,7 +34056,7 @@
       </c>
     </row>
     <row r="344" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A344" s="88" t="s">
+      <c r="A344" s="91" t="s">
         <v>122</v>
       </c>
       <c r="B344" s="17" t="n">
@@ -33652,7 +34064,7 @@
       </c>
     </row>
     <row r="345" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A345" s="88" t="s">
+      <c r="A345" s="91" t="s">
         <v>123</v>
       </c>
       <c r="B345" s="17" t="n">
@@ -33660,7 +34072,7 @@
       </c>
     </row>
     <row r="346" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A346" s="88" t="s">
+      <c r="A346" s="91" t="s">
         <v>124</v>
       </c>
       <c r="B346" s="17" t="n">
@@ -33668,7 +34080,7 @@
       </c>
     </row>
     <row r="347" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A347" s="88" t="s">
+      <c r="A347" s="91" t="s">
         <v>125</v>
       </c>
       <c r="B347" s="17" t="n">
@@ -33676,19 +34088,19 @@
       </c>
     </row>
     <row r="348" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A348" s="88" t="s">
+      <c r="A348" s="91" t="s">
         <v>126</v>
       </c>
       <c r="B348" s="29"/>
     </row>
     <row r="349" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A349" s="89" t="s">
+      <c r="A349" s="92" t="s">
         <v>128</v>
       </c>
       <c r="B349" s="31"/>
     </row>
     <row r="350" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A350" s="88" t="s">
+      <c r="A350" s="91" t="s">
         <v>134</v>
       </c>
       <c r="B350" s="17" t="n">
@@ -33696,7 +34108,7 @@
       </c>
     </row>
     <row r="351" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A351" s="88" t="s">
+      <c r="A351" s="91" t="s">
         <v>136</v>
       </c>
       <c r="B351" s="17" t="n">
@@ -33704,7 +34116,7 @@
       </c>
     </row>
     <row r="352" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A352" s="90" t="s">
+      <c r="A352" s="93" t="s">
         <v>157</v>
       </c>
       <c r="B352" s="5" t="n">
@@ -33713,7 +34125,7 @@
     </row>
     <row r="353" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B353" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="354" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -33721,38 +34133,38 @@
       <c r="B355" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H355" s="58" t="s">
-        <v>202</v>
+      <c r="L355" s="59" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="356" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="1" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B356" s="1" t="n">
         <v>0.4</v>
       </c>
-      <c r="H356" s="59" t="s">
-        <v>203</v>
+      <c r="L356" s="60" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="357" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A357" s="1" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="G357" s="24" t="s">
-        <v>266</v>
-      </c>
-      <c r="H357" s="49" t="s">
-        <v>267</v>
+        <v>271</v>
+      </c>
+      <c r="L357" s="49" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="358" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="2" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="B358" s="17" t="s">
         <v>102</v>
@@ -33769,11 +34181,23 @@
       <c r="F358" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="G358" s="76" t="s">
+      <c r="G358" s="57" t="s">
         <v>107</v>
       </c>
       <c r="H358" s="57" t="s">
         <v>108</v>
+      </c>
+      <c r="I358" s="57" t="s">
+        <v>109</v>
+      </c>
+      <c r="J358" s="57" t="s">
+        <v>110</v>
+      </c>
+      <c r="K358" s="57" t="s">
+        <v>111</v>
+      </c>
+      <c r="L358" s="58" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="359" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33795,10 +34219,22 @@
       <c r="F359" s="18" t="n">
         <v>0.5</v>
       </c>
-      <c r="G359" s="76" t="n">
+      <c r="G359" s="57" t="n">
         <v>0.5</v>
       </c>
       <c r="H359" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I359" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J359" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K359" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L359" s="58" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -33812,7 +34248,11 @@
       <c r="E360" s="23"/>
       <c r="F360" s="23"/>
       <c r="G360" s="23"/>
-      <c r="H360" s="23"/>
+      <c r="H360" s="61"/>
+      <c r="I360" s="23"/>
+      <c r="J360" s="94"/>
+      <c r="K360" s="61"/>
+      <c r="L360" s="94"/>
     </row>
     <row r="361" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A361" s="2" t="s">
@@ -33824,7 +34264,11 @@
       <c r="E361" s="23"/>
       <c r="F361" s="23"/>
       <c r="G361" s="23"/>
-      <c r="H361" s="23"/>
+      <c r="H361" s="61"/>
+      <c r="I361" s="23"/>
+      <c r="J361" s="94"/>
+      <c r="K361" s="61"/>
+      <c r="L361" s="94"/>
     </row>
     <row r="362" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A362" s="2" t="s">
@@ -33836,7 +34280,11 @@
       <c r="E362" s="23"/>
       <c r="F362" s="23"/>
       <c r="G362" s="23"/>
-      <c r="H362" s="23"/>
+      <c r="H362" s="61"/>
+      <c r="I362" s="23"/>
+      <c r="J362" s="94"/>
+      <c r="K362" s="61"/>
+      <c r="L362" s="94"/>
     </row>
     <row r="363" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A363" s="2" t="s">
@@ -33857,10 +34305,22 @@
       <c r="F363" s="18" t="n">
         <v>0.008</v>
       </c>
-      <c r="G363" s="76" t="n">
+      <c r="G363" s="57" t="n">
         <v>0.008</v>
       </c>
       <c r="H363" s="57" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="I363" s="57" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="J363" s="57" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="K363" s="57" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="L363" s="58" t="n">
         <v>0.008</v>
       </c>
     </row>
@@ -33883,10 +34343,22 @@
       <c r="F364" s="18" t="n">
         <v>0.4</v>
       </c>
-      <c r="G364" s="76" t="n">
+      <c r="G364" s="57" t="n">
         <v>0.4</v>
       </c>
       <c r="H364" s="57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I364" s="57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J364" s="57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K364" s="57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L364" s="58" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -33909,10 +34381,22 @@
       <c r="F365" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G365" s="76" t="n">
+      <c r="G365" s="57" t="n">
         <v>1</v>
       </c>
       <c r="H365" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I365" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J365" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="K365" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L365" s="58" t="n">
         <v>1</v>
       </c>
     </row>
@@ -33935,11 +34419,23 @@
       <c r="F366" s="18" t="n">
         <v>9</v>
       </c>
-      <c r="G366" s="76" t="n">
+      <c r="G366" s="57" t="n">
         <v>9</v>
       </c>
       <c r="H366" s="57" t="n">
         <v>5</v>
+      </c>
+      <c r="I366" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="J366" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="K366" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="L366" s="58" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="367" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33961,10 +34457,22 @@
       <c r="F367" s="18" t="n">
         <v>1.2</v>
       </c>
-      <c r="G367" s="76" t="n">
+      <c r="G367" s="57" t="n">
         <v>1.2</v>
       </c>
       <c r="H367" s="57" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I367" s="57" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J367" s="57" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K367" s="57" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L367" s="58" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -33987,10 +34495,22 @@
       <c r="F368" s="18" t="n">
         <v>0.6</v>
       </c>
-      <c r="G368" s="76" t="n">
+      <c r="G368" s="57" t="n">
         <v>0.6</v>
       </c>
       <c r="H368" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I368" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J368" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K368" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L368" s="58" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -34013,11 +34533,23 @@
       <c r="F369" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="G369" s="76" t="n">
+      <c r="G369" s="57" t="n">
         <v>12000</v>
       </c>
       <c r="H369" s="57" t="n">
         <v>6000</v>
+      </c>
+      <c r="I369" s="57" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J369" s="57" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K369" s="57" t="n">
+        <v>4000</v>
+      </c>
+      <c r="L369" s="58" t="n">
+        <v>4000</v>
       </c>
     </row>
     <row r="370" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34030,7 +34562,11 @@
       <c r="E370" s="29"/>
       <c r="F370" s="29"/>
       <c r="G370" s="29"/>
-      <c r="H370" s="29"/>
+      <c r="H370" s="62"/>
+      <c r="I370" s="29"/>
+      <c r="J370" s="95"/>
+      <c r="K370" s="62"/>
+      <c r="L370" s="95"/>
     </row>
     <row r="371" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A371" s="22" t="s">
@@ -34041,8 +34577,12 @@
       <c r="D371" s="31"/>
       <c r="E371" s="31"/>
       <c r="F371" s="31"/>
-      <c r="G371" s="81"/>
-      <c r="H371" s="31"/>
+      <c r="G371" s="62"/>
+      <c r="H371" s="62"/>
+      <c r="I371" s="31"/>
+      <c r="J371" s="95"/>
+      <c r="K371" s="62"/>
+      <c r="L371" s="95"/>
     </row>
     <row r="372" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A372" s="17" t="s">
@@ -34063,11 +34603,23 @@
       <c r="F372" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="G372" s="76" t="n">
+      <c r="G372" s="57" t="n">
         <v>4</v>
       </c>
       <c r="H372" s="57" t="n">
         <v>4</v>
+      </c>
+      <c r="I372" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="J372" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="K372" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="L372" s="58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="373" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34089,11 +34641,23 @@
       <c r="F373" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="G373" s="76" t="n">
+      <c r="G373" s="57" t="n">
         <v>4</v>
       </c>
       <c r="H373" s="57" t="n">
         <v>4</v>
+      </c>
+      <c r="I373" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="J373" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="K373" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="L373" s="58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="374" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34121,31 +34685,57 @@
       <c r="H374" s="5" t="n">
         <v>0.5</v>
       </c>
+      <c r="I374" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J374" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K374" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L374" s="5" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="375" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B375" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C375" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D375" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E375" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F375" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G375" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H375" s="1" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="376" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+        <v>205</v>
+      </c>
+      <c r="I375" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="J375" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K375" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="L375" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="376" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K376" s="63"/>
+    </row>
     <row r="377" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B377" s="1" t="n">
         <v>1</v>
@@ -34168,7 +34758,7 @@
     </row>
     <row r="378" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A378" s="1" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B378" s="1" t="n">
         <v>0.4</v>
@@ -34191,30 +34781,30 @@
     </row>
     <row r="379" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A379" s="1" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B379" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C379" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="D379" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="E379" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F379" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="G379" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
     </row>
     <row r="380" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A380" s="2" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B380" s="17" t="s">
         <v>102</v>
@@ -34225,14 +34815,14 @@
       <c r="D380" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="E380" s="76" t="s">
+      <c r="E380" s="57" t="s">
         <v>105</v>
       </c>
-      <c r="F380" s="57" t="s">
+      <c r="F380" s="58" t="s">
         <v>106</v>
       </c>
-      <c r="G380" s="58" t="s">
-        <v>202</v>
+      <c r="G380" s="59" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="381" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34248,14 +34838,14 @@
       <c r="D381" s="27" t="n">
         <v>0.5</v>
       </c>
-      <c r="E381" s="76" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F381" s="57" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G381" s="59" t="s">
-        <v>203</v>
+      <c r="E381" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F381" s="58" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G381" s="60" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="382" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34268,7 +34858,7 @@
       <c r="E382" s="23"/>
       <c r="F382" s="23"/>
       <c r="G382" s="49" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="383" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34304,10 +34894,10 @@
       <c r="D385" s="27" t="n">
         <v>0.005</v>
       </c>
-      <c r="E385" s="76" t="n">
+      <c r="E385" s="57" t="n">
         <v>0.005</v>
       </c>
-      <c r="F385" s="57" t="n">
+      <c r="F385" s="58" t="n">
         <v>0.005</v>
       </c>
     </row>
@@ -34324,10 +34914,10 @@
       <c r="D386" s="27" t="n">
         <v>0.4</v>
       </c>
-      <c r="E386" s="76" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F386" s="57" t="n">
+      <c r="E386" s="57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F386" s="58" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -34344,10 +34934,10 @@
       <c r="D387" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="E387" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="F387" s="57" t="n">
+      <c r="E387" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="F387" s="58" t="n">
         <v>1</v>
       </c>
     </row>
@@ -34364,10 +34954,10 @@
       <c r="D388" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="E388" s="76" t="n">
+      <c r="E388" s="57" t="n">
         <v>3</v>
       </c>
-      <c r="F388" s="57" t="n">
+      <c r="F388" s="58" t="n">
         <v>3</v>
       </c>
     </row>
@@ -34384,10 +34974,10 @@
       <c r="D389" s="27" t="n">
         <v>1.2</v>
       </c>
-      <c r="E389" s="76" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F389" s="57" t="n">
+      <c r="E389" s="57" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F389" s="58" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -34404,10 +34994,10 @@
       <c r="D390" s="27" t="n">
         <v>0.6</v>
       </c>
-      <c r="E390" s="76" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F390" s="57" t="n">
+      <c r="E390" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F390" s="58" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -34424,10 +35014,10 @@
       <c r="D391" s="27" t="n">
         <v>25000</v>
       </c>
-      <c r="E391" s="76" t="n">
+      <c r="E391" s="57" t="n">
         <v>25000</v>
       </c>
-      <c r="F391" s="57" t="n">
+      <c r="F391" s="58" t="n">
         <v>25000</v>
       </c>
     </row>
@@ -34464,10 +35054,10 @@
       <c r="D394" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="E394" s="76" t="n">
-        <v>2</v>
-      </c>
-      <c r="F394" s="57" t="n">
+      <c r="E394" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="F394" s="58" t="n">
         <v>2</v>
       </c>
     </row>
@@ -34484,10 +35074,10 @@
       <c r="D395" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="E395" s="76" t="n">
-        <v>2</v>
-      </c>
-      <c r="F395" s="57" t="n">
+      <c r="E395" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="F395" s="58" t="n">
         <v>2</v>
       </c>
     </row>
@@ -34513,27 +35103,27 @@
     </row>
     <row r="397" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B397" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C397" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D397" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E397" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F397" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="398" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E398" s="24" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="F398" s="24" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
     </row>
     <row r="399" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34555,7 +35145,7 @@
     </row>
     <row r="400" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A400" s="1" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B400" s="1" t="n">
         <v>0.4</v>
@@ -34575,18 +35165,18 @@
     </row>
     <row r="401" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A401" s="1" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="K401" s="24" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
     </row>
     <row r="402" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A402" s="2" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="B402" s="17" t="s">
         <v>102</v>
@@ -34615,7 +35205,7 @@
       <c r="J402" s="27" t="s">
         <v>110</v>
       </c>
-      <c r="K402" s="57" t="s">
+      <c r="K402" s="58" t="s">
         <v>111</v>
       </c>
     </row>
@@ -34650,7 +35240,7 @@
       <c r="J403" s="27" t="n">
         <v>0.5</v>
       </c>
-      <c r="K403" s="57" t="n">
+      <c r="K403" s="58" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -34730,7 +35320,7 @@
       <c r="J407" s="27" t="n">
         <v>0.00425</v>
       </c>
-      <c r="K407" s="57" t="n">
+      <c r="K407" s="58" t="n">
         <v>0.00425</v>
       </c>
     </row>
@@ -34765,7 +35355,7 @@
       <c r="J408" s="27" t="n">
         <v>0.4</v>
       </c>
-      <c r="K408" s="57" t="n">
+      <c r="K408" s="58" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -34800,7 +35390,7 @@
       <c r="J409" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="K409" s="57" t="n">
+      <c r="K409" s="58" t="n">
         <v>1</v>
       </c>
     </row>
@@ -34835,7 +35425,7 @@
       <c r="J410" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="K410" s="57" t="n">
+      <c r="K410" s="58" t="n">
         <v>6</v>
       </c>
     </row>
@@ -34870,7 +35460,7 @@
       <c r="J411" s="27" t="n">
         <v>1.2</v>
       </c>
-      <c r="K411" s="57" t="n">
+      <c r="K411" s="58" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -34905,7 +35495,7 @@
       <c r="J412" s="27" t="n">
         <v>0.6</v>
       </c>
-      <c r="K412" s="57" t="n">
+      <c r="K412" s="58" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -34940,7 +35530,7 @@
       <c r="J413" s="27" t="n">
         <v>25000</v>
       </c>
-      <c r="K413" s="57" t="n">
+      <c r="K413" s="58" t="n">
         <v>25000</v>
       </c>
     </row>
@@ -35005,7 +35595,7 @@
       <c r="J416" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="K416" s="57" t="n">
+      <c r="K416" s="58" t="n">
         <v>5</v>
       </c>
     </row>
@@ -35040,7 +35630,7 @@
       <c r="J417" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="K417" s="57" t="n">
+      <c r="K417" s="58" t="n">
         <v>5</v>
       </c>
     </row>
@@ -35081,34 +35671,34 @@
     </row>
     <row r="419" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B419" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C419" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D419" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E419" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F419" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G419" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H419" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I419" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J419" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K419" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="420" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -35146,7 +35736,7 @@
     </row>
     <row r="422" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A422" s="1" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B422" s="1" t="n">
         <v>0.4</v>
@@ -35181,37 +35771,37 @@
     </row>
     <row r="423" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A423" s="1" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C423" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="D423" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="E423" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F423" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="G423" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="H423" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="I423" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="J423" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="K423" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
     </row>
   </sheetData>

--- a/parameters script.xlsx
+++ b/parameters script.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2213" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2223" uniqueCount="277">
   <si>
     <t xml:space="preserve">6h 3</t>
   </si>
@@ -804,6 +804,9 @@
     <t xml:space="preserve">T40</t>
   </si>
   <si>
+    <t xml:space="preserve">T41</t>
+  </si>
+  <si>
     <t xml:space="preserve">DILATION</t>
   </si>
   <si>
@@ -1218,7 +1221,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="92">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1455,11 +1458,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1495,10 +1494,6 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="19" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1519,11 +1514,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1532,14 +1531,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1572,10 +1563,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1686,9 +1673,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>457560</xdr:colOff>
+      <xdr:colOff>457200</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>14760</xdr:rowOff>
+      <xdr:rowOff>14400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1702,7 +1689,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6183720" y="130320"/>
-          <a:ext cx="7978320" cy="250200"/>
+          <a:ext cx="7977960" cy="249840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1729,9 +1716,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>211680</xdr:colOff>
+      <xdr:colOff>211320</xdr:colOff>
       <xdr:row>85</xdr:row>
-      <xdr:rowOff>18000</xdr:rowOff>
+      <xdr:rowOff>17640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1745,7 +1732,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="10345680" y="13525560"/>
-          <a:ext cx="10137240" cy="2037240"/>
+          <a:ext cx="10136880" cy="2036880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1767,9 +1754,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>876600</xdr:colOff>
+      <xdr:colOff>876240</xdr:colOff>
       <xdr:row>121</xdr:row>
-      <xdr:rowOff>130320</xdr:rowOff>
+      <xdr:rowOff>129960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1783,7 +1770,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6275880" y="20154960"/>
-          <a:ext cx="10173960" cy="2103840"/>
+          <a:ext cx="10173600" cy="2103480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -22487,7 +22474,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AO423"/>
+  <dimension ref="A1:AP423"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22521,7 +22508,7 @@
       <c r="J1" s="58" t="s">
         <v>110</v>
       </c>
-      <c r="K1" s="59" t="s">
+      <c r="K1" s="49" t="s">
         <v>201</v>
       </c>
     </row>
@@ -22556,7 +22543,7 @@
       <c r="J2" s="58" t="n">
         <v>0.5</v>
       </c>
-      <c r="K2" s="60" t="s">
+      <c r="K2" s="59" t="s">
         <v>202</v>
       </c>
     </row>
@@ -22570,7 +22557,7 @@
       <c r="E3" s="23"/>
       <c r="F3" s="23"/>
       <c r="G3" s="23"/>
-      <c r="H3" s="61"/>
+      <c r="H3" s="60"/>
       <c r="I3" s="23"/>
       <c r="J3" s="23"/>
       <c r="K3" s="49" t="s">
@@ -22587,7 +22574,7 @@
       <c r="E4" s="23"/>
       <c r="F4" s="23"/>
       <c r="G4" s="23"/>
-      <c r="H4" s="61"/>
+      <c r="H4" s="60"/>
       <c r="I4" s="23"/>
       <c r="J4" s="23"/>
     </row>
@@ -22601,7 +22588,7 @@
       <c r="E5" s="23"/>
       <c r="F5" s="23"/>
       <c r="G5" s="23"/>
-      <c r="H5" s="61"/>
+      <c r="H5" s="60"/>
       <c r="I5" s="23"/>
       <c r="J5" s="23"/>
     </row>
@@ -22839,7 +22826,7 @@
       <c r="E13" s="29"/>
       <c r="F13" s="29"/>
       <c r="G13" s="29"/>
-      <c r="H13" s="62"/>
+      <c r="H13" s="61"/>
       <c r="I13" s="29"/>
       <c r="J13" s="29"/>
     </row>
@@ -22852,8 +22839,8 @@
       <c r="D14" s="31"/>
       <c r="E14" s="31"/>
       <c r="F14" s="31"/>
-      <c r="G14" s="62"/>
-      <c r="H14" s="62"/>
+      <c r="G14" s="61"/>
+      <c r="H14" s="61"/>
       <c r="I14" s="31"/>
       <c r="J14" s="31"/>
     </row>
@@ -22946,8 +22933,8 @@
       <c r="H17" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="I17" s="63"/>
-      <c r="N17" s="59" t="s">
+      <c r="I17" s="62"/>
+      <c r="N17" s="49" t="s">
         <v>201</v>
       </c>
     </row>
@@ -22955,7 +22942,7 @@
       <c r="B18" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="N18" s="60" t="s">
+      <c r="N18" s="59" t="s">
         <v>204</v>
       </c>
     </row>
@@ -23040,7 +23027,7 @@
       <c r="M20" s="27" t="s">
         <v>113</v>
       </c>
-      <c r="N20" s="64" t="s">
+      <c r="N20" s="63" t="s">
         <v>114</v>
       </c>
     </row>
@@ -23084,7 +23071,7 @@
       <c r="M21" s="27" t="n">
         <v>0.5</v>
       </c>
-      <c r="N21" s="64" t="n">
+      <c r="N21" s="63" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -23104,7 +23091,7 @@
       <c r="K22" s="23"/>
       <c r="L22" s="23"/>
       <c r="M22" s="23"/>
-      <c r="N22" s="65"/>
+      <c r="N22" s="64"/>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
@@ -23122,7 +23109,7 @@
       <c r="K23" s="23"/>
       <c r="L23" s="23"/>
       <c r="M23" s="23"/>
-      <c r="N23" s="65"/>
+      <c r="N23" s="64"/>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
@@ -23140,7 +23127,7 @@
       <c r="K24" s="23"/>
       <c r="L24" s="23"/>
       <c r="M24" s="23"/>
-      <c r="N24" s="65"/>
+      <c r="N24" s="64"/>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
@@ -23182,7 +23169,7 @@
       <c r="M25" s="27" t="n">
         <v>0.0125</v>
       </c>
-      <c r="N25" s="64" t="n">
+      <c r="N25" s="63" t="n">
         <v>0.0125</v>
       </c>
     </row>
@@ -23226,7 +23213,7 @@
       <c r="M26" s="27" t="n">
         <v>0.4</v>
       </c>
-      <c r="N26" s="64" t="n">
+      <c r="N26" s="63" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -23270,7 +23257,7 @@
       <c r="M27" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="N27" s="64" t="n">
+      <c r="N27" s="63" t="n">
         <v>1</v>
       </c>
     </row>
@@ -23314,7 +23301,7 @@
       <c r="M28" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="N28" s="64" t="n">
+      <c r="N28" s="63" t="n">
         <v>8</v>
       </c>
     </row>
@@ -23358,7 +23345,7 @@
       <c r="M29" s="27" t="n">
         <v>1.2</v>
       </c>
-      <c r="N29" s="64" t="n">
+      <c r="N29" s="63" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -23402,7 +23389,7 @@
       <c r="M30" s="27" t="n">
         <v>0.6</v>
       </c>
-      <c r="N30" s="64" t="n">
+      <c r="N30" s="63" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -23446,7 +23433,7 @@
       <c r="M31" s="27" t="n">
         <v>15000</v>
       </c>
-      <c r="N31" s="64" t="n">
+      <c r="N31" s="63" t="n">
         <v>15000</v>
       </c>
     </row>
@@ -23466,7 +23453,7 @@
       <c r="K32" s="29"/>
       <c r="L32" s="29"/>
       <c r="M32" s="29"/>
-      <c r="N32" s="66"/>
+      <c r="N32" s="65"/>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="22" t="s">
@@ -23484,7 +23471,7 @@
       <c r="K33" s="31"/>
       <c r="L33" s="31"/>
       <c r="M33" s="31"/>
-      <c r="N33" s="66"/>
+      <c r="N33" s="65"/>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="17" t="s">
@@ -23526,7 +23513,7 @@
       <c r="M34" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="N34" s="64" t="n">
+      <c r="N34" s="63" t="n">
         <v>4</v>
       </c>
     </row>
@@ -23570,7 +23557,7 @@
       <c r="M35" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="N35" s="64" t="n">
+      <c r="N35" s="63" t="n">
         <v>4</v>
       </c>
     </row>
@@ -23687,10 +23674,10 @@
       <c r="M38" s="56" t="s">
         <v>113</v>
       </c>
-      <c r="N38" s="67" t="s">
+      <c r="N38" s="66" t="s">
         <v>114</v>
       </c>
-      <c r="O38" s="59" t="s">
+      <c r="O38" s="49" t="s">
         <v>201</v>
       </c>
     </row>
@@ -23731,10 +23718,10 @@
       <c r="M39" s="56" t="n">
         <v>0.5</v>
       </c>
-      <c r="N39" s="67" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O39" s="60" t="s">
+      <c r="N39" s="66" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O39" s="59" t="s">
         <v>202</v>
       </c>
     </row>
@@ -23747,12 +23734,12 @@
       <c r="D40" s="23"/>
       <c r="E40" s="23"/>
       <c r="G40" s="23"/>
-      <c r="H40" s="61"/>
-      <c r="I40" s="61"/>
-      <c r="J40" s="61"/>
-      <c r="K40" s="61"/>
-      <c r="L40" s="61"/>
-      <c r="M40" s="61"/>
+      <c r="H40" s="60"/>
+      <c r="I40" s="60"/>
+      <c r="J40" s="60"/>
+      <c r="K40" s="60"/>
+      <c r="L40" s="60"/>
+      <c r="M40" s="60"/>
       <c r="N40" s="23"/>
       <c r="O40" s="49" t="s">
         <v>203</v>
@@ -23767,12 +23754,12 @@
       <c r="D41" s="23"/>
       <c r="E41" s="23"/>
       <c r="G41" s="23"/>
-      <c r="H41" s="61"/>
-      <c r="I41" s="61"/>
-      <c r="J41" s="61"/>
-      <c r="K41" s="61"/>
-      <c r="L41" s="61"/>
-      <c r="M41" s="61"/>
+      <c r="H41" s="60"/>
+      <c r="I41" s="60"/>
+      <c r="J41" s="60"/>
+      <c r="K41" s="60"/>
+      <c r="L41" s="60"/>
+      <c r="M41" s="60"/>
       <c r="N41" s="23"/>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23784,12 +23771,12 @@
       <c r="D42" s="23"/>
       <c r="E42" s="23"/>
       <c r="G42" s="23"/>
-      <c r="H42" s="61"/>
-      <c r="I42" s="61"/>
-      <c r="J42" s="61"/>
-      <c r="K42" s="61"/>
-      <c r="L42" s="61"/>
-      <c r="M42" s="61"/>
+      <c r="H42" s="60"/>
+      <c r="I42" s="60"/>
+      <c r="J42" s="60"/>
+      <c r="K42" s="60"/>
+      <c r="L42" s="60"/>
+      <c r="M42" s="60"/>
       <c r="N42" s="23"/>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23829,7 +23816,7 @@
       <c r="M43" s="56" t="n">
         <v>0.002</v>
       </c>
-      <c r="N43" s="67" t="n">
+      <c r="N43" s="66" t="n">
         <v>0.00225</v>
       </c>
     </row>
@@ -23870,7 +23857,7 @@
       <c r="M44" s="56" t="n">
         <v>0.4</v>
       </c>
-      <c r="N44" s="67" t="n">
+      <c r="N44" s="66" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -23911,7 +23898,7 @@
       <c r="M45" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="N45" s="67" t="n">
+      <c r="N45" s="66" t="n">
         <v>1</v>
       </c>
     </row>
@@ -23952,7 +23939,7 @@
       <c r="M46" s="56" t="n">
         <v>4</v>
       </c>
-      <c r="N46" s="67" t="n">
+      <c r="N46" s="66" t="n">
         <v>4</v>
       </c>
     </row>
@@ -23993,7 +23980,7 @@
       <c r="M47" s="56" t="n">
         <v>1.2</v>
       </c>
-      <c r="N47" s="67" t="n">
+      <c r="N47" s="66" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -24034,7 +24021,7 @@
       <c r="M48" s="56" t="n">
         <v>0.6</v>
       </c>
-      <c r="N48" s="67" t="n">
+      <c r="N48" s="66" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -24075,7 +24062,7 @@
       <c r="M49" s="56" t="n">
         <v>22000</v>
       </c>
-      <c r="N49" s="67" t="n">
+      <c r="N49" s="66" t="n">
         <v>22000</v>
       </c>
     </row>
@@ -24088,12 +24075,12 @@
       <c r="D50" s="29"/>
       <c r="E50" s="29"/>
       <c r="G50" s="29"/>
-      <c r="H50" s="62"/>
-      <c r="I50" s="62"/>
-      <c r="J50" s="62"/>
-      <c r="K50" s="62"/>
-      <c r="L50" s="62"/>
-      <c r="M50" s="62"/>
+      <c r="H50" s="61"/>
+      <c r="I50" s="61"/>
+      <c r="J50" s="61"/>
+      <c r="K50" s="61"/>
+      <c r="L50" s="61"/>
+      <c r="M50" s="61"/>
       <c r="N50" s="29"/>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24105,12 +24092,12 @@
       <c r="D51" s="31"/>
       <c r="E51" s="31"/>
       <c r="G51" s="31"/>
-      <c r="H51" s="62"/>
-      <c r="I51" s="62"/>
-      <c r="J51" s="62"/>
-      <c r="K51" s="62"/>
-      <c r="L51" s="62"/>
-      <c r="M51" s="62"/>
+      <c r="H51" s="61"/>
+      <c r="I51" s="61"/>
+      <c r="J51" s="61"/>
+      <c r="K51" s="61"/>
+      <c r="L51" s="61"/>
+      <c r="M51" s="61"/>
       <c r="N51" s="31"/>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24150,7 +24137,7 @@
       <c r="M52" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="N52" s="67" t="n">
+      <c r="N52" s="66" t="n">
         <v>1</v>
       </c>
     </row>
@@ -24191,7 +24178,7 @@
       <c r="M53" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="N53" s="67" t="n">
+      <c r="N53" s="66" t="n">
         <v>1</v>
       </c>
     </row>
@@ -24223,7 +24210,7 @@
       <c r="J54" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="K54" s="68" t="n">
+      <c r="K54" s="67" t="n">
         <v>0.5</v>
       </c>
       <c r="L54" s="5" t="n">
@@ -24240,19 +24227,19 @@
       <c r="H55" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="J55" s="0" t="s">
+      <c r="J55" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="K55" s="69" t="n">
-        <v>1</v>
-      </c>
-      <c r="L55" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M55" s="0" t="n">
+      <c r="K55" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="L55" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M55" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="N55" s="0" t="n">
+      <c r="N55" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -24269,7 +24256,7 @@
       <c r="D56" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="E56" s="70" t="s">
+      <c r="E56" s="68" t="s">
         <v>105</v>
       </c>
       <c r="F56" s="18" t="s">
@@ -24281,10 +24268,10 @@
       <c r="H56" s="56" t="s">
         <v>108</v>
       </c>
-      <c r="I56" s="67" t="s">
+      <c r="I56" s="66" t="s">
         <v>109</v>
       </c>
-      <c r="J56" s="59" t="s">
+      <c r="J56" s="49" t="s">
         <v>201</v>
       </c>
     </row>
@@ -24301,7 +24288,7 @@
       <c r="D57" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="E57" s="70" t="n">
+      <c r="E57" s="68" t="n">
         <v>0.5</v>
       </c>
       <c r="F57" s="18" t="n">
@@ -24310,10 +24297,10 @@
       <c r="H57" s="56" t="n">
         <v>0.5</v>
       </c>
-      <c r="I57" s="67" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J57" s="60" t="s">
+      <c r="I57" s="66" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J57" s="59" t="s">
         <v>202</v>
       </c>
     </row>
@@ -24326,7 +24313,7 @@
       <c r="D58" s="23"/>
       <c r="E58" s="23"/>
       <c r="F58" s="23"/>
-      <c r="H58" s="61"/>
+      <c r="H58" s="60"/>
       <c r="I58" s="23"/>
       <c r="J58" s="49" t="s">
         <v>203</v>
@@ -24341,7 +24328,7 @@
       <c r="D59" s="23"/>
       <c r="E59" s="23"/>
       <c r="F59" s="23"/>
-      <c r="H59" s="61"/>
+      <c r="H59" s="60"/>
       <c r="I59" s="23"/>
     </row>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24353,7 +24340,7 @@
       <c r="D60" s="23"/>
       <c r="E60" s="23"/>
       <c r="F60" s="23"/>
-      <c r="H60" s="61"/>
+      <c r="H60" s="60"/>
       <c r="I60" s="23"/>
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24369,7 +24356,7 @@
       <c r="D61" s="17" t="n">
         <v>0.004</v>
       </c>
-      <c r="E61" s="70" t="n">
+      <c r="E61" s="68" t="n">
         <v>0.0045</v>
       </c>
       <c r="F61" s="18" t="n">
@@ -24378,7 +24365,7 @@
       <c r="H61" s="56" t="n">
         <v>0.0045</v>
       </c>
-      <c r="I61" s="67" t="n">
+      <c r="I61" s="66" t="n">
         <v>0.0045</v>
       </c>
     </row>
@@ -24395,7 +24382,7 @@
       <c r="D62" s="17" t="n">
         <v>0.4</v>
       </c>
-      <c r="E62" s="70" t="n">
+      <c r="E62" s="68" t="n">
         <v>0.4</v>
       </c>
       <c r="F62" s="18" t="n">
@@ -24404,7 +24391,7 @@
       <c r="H62" s="56" t="n">
         <v>0.4</v>
       </c>
-      <c r="I62" s="67" t="n">
+      <c r="I62" s="66" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -24421,7 +24408,7 @@
       <c r="D63" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="E63" s="70" t="n">
+      <c r="E63" s="68" t="n">
         <v>1</v>
       </c>
       <c r="F63" s="18" t="n">
@@ -24430,7 +24417,7 @@
       <c r="H63" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="I63" s="67" t="n">
+      <c r="I63" s="66" t="n">
         <v>1</v>
       </c>
     </row>
@@ -24447,7 +24434,7 @@
       <c r="D64" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="E64" s="70" t="n">
+      <c r="E64" s="68" t="n">
         <v>10</v>
       </c>
       <c r="F64" s="18" t="n">
@@ -24456,7 +24443,7 @@
       <c r="H64" s="56" t="n">
         <v>10</v>
       </c>
-      <c r="I64" s="67" t="n">
+      <c r="I64" s="66" t="n">
         <v>5</v>
       </c>
     </row>
@@ -24473,7 +24460,7 @@
       <c r="D65" s="17" t="n">
         <v>1.2</v>
       </c>
-      <c r="E65" s="70" t="n">
+      <c r="E65" s="68" t="n">
         <v>1.2</v>
       </c>
       <c r="F65" s="18" t="n">
@@ -24482,7 +24469,7 @@
       <c r="H65" s="56" t="n">
         <v>1.2</v>
       </c>
-      <c r="I65" s="67" t="n">
+      <c r="I65" s="66" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -24499,7 +24486,7 @@
       <c r="D66" s="17" t="n">
         <v>0.6</v>
       </c>
-      <c r="E66" s="70" t="n">
+      <c r="E66" s="68" t="n">
         <v>0.6</v>
       </c>
       <c r="F66" s="18" t="n">
@@ -24508,7 +24495,7 @@
       <c r="H66" s="56" t="n">
         <v>0.6</v>
       </c>
-      <c r="I66" s="67" t="n">
+      <c r="I66" s="66" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -24525,7 +24512,7 @@
       <c r="D67" s="17" t="n">
         <v>20000</v>
       </c>
-      <c r="E67" s="70" t="n">
+      <c r="E67" s="68" t="n">
         <v>25000</v>
       </c>
       <c r="F67" s="18" t="n">
@@ -24534,7 +24521,7 @@
       <c r="H67" s="56" t="n">
         <v>25000</v>
       </c>
-      <c r="I67" s="67" t="n">
+      <c r="I67" s="66" t="n">
         <v>25000</v>
       </c>
     </row>
@@ -24547,7 +24534,7 @@
       <c r="D68" s="29"/>
       <c r="E68" s="29"/>
       <c r="F68" s="29"/>
-      <c r="H68" s="62"/>
+      <c r="H68" s="61"/>
       <c r="I68" s="29"/>
     </row>
     <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24559,7 +24546,7 @@
       <c r="D69" s="31"/>
       <c r="E69" s="31"/>
       <c r="F69" s="31"/>
-      <c r="H69" s="62"/>
+      <c r="H69" s="61"/>
       <c r="I69" s="31"/>
     </row>
     <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24575,7 +24562,7 @@
       <c r="D70" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="E70" s="70" t="n">
+      <c r="E70" s="68" t="n">
         <v>4</v>
       </c>
       <c r="F70" s="18" t="n">
@@ -24584,7 +24571,7 @@
       <c r="H70" s="56" t="n">
         <v>4</v>
       </c>
-      <c r="I70" s="67" t="n">
+      <c r="I70" s="66" t="n">
         <v>4</v>
       </c>
     </row>
@@ -24601,7 +24588,7 @@
       <c r="D71" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="E71" s="70" t="n">
+      <c r="E71" s="68" t="n">
         <v>4</v>
       </c>
       <c r="F71" s="18" t="n">
@@ -24610,7 +24597,7 @@
       <c r="H71" s="56" t="n">
         <v>4</v>
       </c>
-      <c r="I71" s="67" t="n">
+      <c r="I71" s="66" t="n">
         <v>4</v>
       </c>
     </row>
@@ -24633,13 +24620,13 @@
       <c r="F72" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="H72" s="68" t="n">
+      <c r="H72" s="67" t="n">
         <v>0.5</v>
       </c>
       <c r="I72" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="T72" s="59" t="s">
+      <c r="T72" s="49" t="s">
         <v>201</v>
       </c>
     </row>
@@ -24659,13 +24646,13 @@
       <c r="F73" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="H73" s="68" t="s">
+      <c r="H73" s="67" t="s">
         <v>205</v>
       </c>
       <c r="I73" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="T73" s="60" t="s">
+      <c r="T73" s="59" t="s">
         <v>202</v>
       </c>
     </row>
@@ -24685,7 +24672,7 @@
       <c r="A75" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="B75" s="71" t="s">
+      <c r="B75" s="69" t="s">
         <v>102</v>
       </c>
       <c r="C75" s="17" t="s">
@@ -24733,13 +24720,13 @@
       <c r="Q75" s="31" t="s">
         <v>117</v>
       </c>
-      <c r="R75" s="72" t="s">
+      <c r="R75" s="70" t="s">
         <v>118</v>
       </c>
       <c r="S75" s="56" t="s">
         <v>150</v>
       </c>
-      <c r="T75" s="67" t="s">
+      <c r="T75" s="66" t="s">
         <v>151</v>
       </c>
     </row>
@@ -24747,7 +24734,7 @@
       <c r="A76" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B76" s="71" t="n">
+      <c r="B76" s="69" t="n">
         <v>0.5</v>
       </c>
       <c r="C76" s="17" t="n">
@@ -24792,16 +24779,16 @@
       <c r="P76" s="18" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q76" s="73" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R76" s="74" t="n">
+      <c r="Q76" s="71" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R76" s="72" t="n">
         <v>0.5</v>
       </c>
       <c r="S76" s="56" t="n">
         <v>0.5</v>
       </c>
-      <c r="T76" s="67" t="n">
+      <c r="T76" s="66" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -24826,7 +24813,7 @@
       <c r="P77" s="23"/>
       <c r="Q77" s="23"/>
       <c r="R77" s="23"/>
-      <c r="S77" s="61"/>
+      <c r="S77" s="60"/>
       <c r="T77" s="23"/>
     </row>
     <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24850,7 +24837,7 @@
       <c r="P78" s="23"/>
       <c r="Q78" s="23"/>
       <c r="R78" s="23"/>
-      <c r="S78" s="61"/>
+      <c r="S78" s="60"/>
       <c r="T78" s="23"/>
     </row>
     <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24874,14 +24861,14 @@
       <c r="P79" s="23"/>
       <c r="Q79" s="23"/>
       <c r="R79" s="23"/>
-      <c r="S79" s="61"/>
+      <c r="S79" s="60"/>
       <c r="T79" s="23"/>
     </row>
     <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B80" s="71" t="n">
+      <c r="B80" s="69" t="n">
         <v>0.006</v>
       </c>
       <c r="C80" s="17" t="n">
@@ -24926,16 +24913,16 @@
       <c r="P80" s="18" t="n">
         <v>0.015</v>
       </c>
-      <c r="Q80" s="73" t="n">
+      <c r="Q80" s="71" t="n">
         <v>0.015</v>
       </c>
-      <c r="R80" s="74" t="n">
+      <c r="R80" s="72" t="n">
         <v>0.015</v>
       </c>
       <c r="S80" s="56" t="n">
         <v>0.015</v>
       </c>
-      <c r="T80" s="67" t="n">
+      <c r="T80" s="66" t="n">
         <v>0.015</v>
       </c>
     </row>
@@ -24943,7 +24930,7 @@
       <c r="A81" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B81" s="71" t="n">
+      <c r="B81" s="69" t="n">
         <v>0.4</v>
       </c>
       <c r="C81" s="17" t="n">
@@ -24988,16 +24975,16 @@
       <c r="P81" s="18" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q81" s="73" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="R81" s="74" t="n">
+      <c r="Q81" s="71" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R81" s="72" t="n">
         <v>0.4</v>
       </c>
       <c r="S81" s="56" t="n">
         <v>0.4</v>
       </c>
-      <c r="T81" s="67" t="n">
+      <c r="T81" s="66" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -25005,7 +24992,7 @@
       <c r="A82" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B82" s="71" t="n">
+      <c r="B82" s="69" t="n">
         <v>1</v>
       </c>
       <c r="C82" s="17" t="n">
@@ -25050,16 +25037,16 @@
       <c r="P82" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="Q82" s="73" t="n">
-        <v>1</v>
-      </c>
-      <c r="R82" s="74" t="n">
+      <c r="Q82" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="R82" s="72" t="n">
         <v>1</v>
       </c>
       <c r="S82" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="T82" s="67" t="n">
+      <c r="T82" s="66" t="n">
         <v>1</v>
       </c>
     </row>
@@ -25067,7 +25054,7 @@
       <c r="A83" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B83" s="71" t="n">
+      <c r="B83" s="69" t="n">
         <v>8</v>
       </c>
       <c r="C83" s="17" t="n">
@@ -25112,19 +25099,19 @@
       <c r="P83" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="Q83" s="73" t="n">
+      <c r="Q83" s="71" t="n">
         <v>8</v>
       </c>
-      <c r="R83" s="74" t="n">
+      <c r="R83" s="72" t="n">
         <v>8</v>
       </c>
       <c r="S83" s="56" t="n">
         <v>8</v>
       </c>
-      <c r="T83" s="67" t="n">
+      <c r="T83" s="66" t="n">
         <v>8</v>
       </c>
-      <c r="U83" s="0" t="s">
+      <c r="U83" s="1" t="s">
         <v>216</v>
       </c>
     </row>
@@ -25132,7 +25119,7 @@
       <c r="A84" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B84" s="71" t="n">
+      <c r="B84" s="69" t="n">
         <v>1.2</v>
       </c>
       <c r="C84" s="17" t="n">
@@ -25177,16 +25164,16 @@
       <c r="P84" s="18" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q84" s="73" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="R84" s="74" t="n">
+      <c r="Q84" s="71" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R84" s="72" t="n">
         <v>1.2</v>
       </c>
       <c r="S84" s="56" t="n">
         <v>1.2</v>
       </c>
-      <c r="T84" s="67" t="n">
+      <c r="T84" s="66" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -25194,7 +25181,7 @@
       <c r="A85" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B85" s="71" t="n">
+      <c r="B85" s="69" t="n">
         <v>0.6</v>
       </c>
       <c r="C85" s="17" t="n">
@@ -25239,16 +25226,16 @@
       <c r="P85" s="18" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q85" s="73" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="R85" s="74" t="n">
+      <c r="Q85" s="71" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R85" s="72" t="n">
         <v>0.6</v>
       </c>
       <c r="S85" s="56" t="n">
         <v>0.6</v>
       </c>
-      <c r="T85" s="67" t="n">
+      <c r="T85" s="66" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -25256,7 +25243,7 @@
       <c r="A86" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B86" s="71" t="n">
+      <c r="B86" s="69" t="n">
         <v>15000</v>
       </c>
       <c r="C86" s="17" t="n">
@@ -25301,16 +25288,16 @@
       <c r="P86" s="18" t="n">
         <v>10000</v>
       </c>
-      <c r="Q86" s="73" t="n">
+      <c r="Q86" s="71" t="n">
         <v>10000</v>
       </c>
-      <c r="R86" s="74" t="n">
+      <c r="R86" s="72" t="n">
         <v>10000</v>
       </c>
       <c r="S86" s="56" t="n">
         <v>10000</v>
       </c>
-      <c r="T86" s="67" t="n">
+      <c r="T86" s="66" t="n">
         <v>10000</v>
       </c>
     </row>
@@ -25335,7 +25322,7 @@
       <c r="P87" s="29"/>
       <c r="Q87" s="29"/>
       <c r="R87" s="29"/>
-      <c r="S87" s="61"/>
+      <c r="S87" s="60"/>
       <c r="T87" s="21"/>
     </row>
     <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25359,14 +25346,14 @@
       <c r="P88" s="31"/>
       <c r="Q88" s="31"/>
       <c r="R88" s="31"/>
-      <c r="S88" s="61"/>
+      <c r="S88" s="60"/>
       <c r="T88" s="23"/>
     </row>
     <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="B89" s="71" t="n">
+      <c r="B89" s="69" t="n">
         <v>4</v>
       </c>
       <c r="C89" s="17" t="n">
@@ -25411,16 +25398,16 @@
       <c r="P89" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="Q89" s="73" t="n">
-        <v>2</v>
-      </c>
-      <c r="R89" s="74" t="n">
+      <c r="Q89" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="R89" s="72" t="n">
         <v>2</v>
       </c>
       <c r="S89" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="T89" s="67" t="n">
+      <c r="T89" s="66" t="n">
         <v>4</v>
       </c>
     </row>
@@ -25428,7 +25415,7 @@
       <c r="A90" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="B90" s="71" t="n">
+      <c r="B90" s="69" t="n">
         <v>4</v>
       </c>
       <c r="C90" s="17" t="n">
@@ -25473,16 +25460,16 @@
       <c r="P90" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="Q90" s="73" t="n">
-        <v>2</v>
-      </c>
-      <c r="R90" s="74" t="n">
+      <c r="Q90" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="R90" s="72" t="n">
         <v>2</v>
       </c>
       <c r="S90" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="T90" s="67" t="n">
+      <c r="T90" s="66" t="n">
         <v>4</v>
       </c>
     </row>
@@ -25646,10 +25633,10 @@
       <c r="K94" s="56" t="s">
         <v>111</v>
       </c>
-      <c r="L94" s="67" t="s">
+      <c r="L94" s="66" t="s">
         <v>112</v>
       </c>
-      <c r="M94" s="59" t="s">
+      <c r="M94" s="49" t="s">
         <v>201</v>
       </c>
     </row>
@@ -25687,10 +25674,10 @@
       <c r="K95" s="56" t="n">
         <v>0.5</v>
       </c>
-      <c r="L95" s="67" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M95" s="60" t="s">
+      <c r="L95" s="66" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M95" s="59" t="s">
         <v>202</v>
       </c>
     </row>
@@ -25707,7 +25694,7 @@
       <c r="H96" s="23"/>
       <c r="I96" s="23"/>
       <c r="J96" s="23"/>
-      <c r="K96" s="61"/>
+      <c r="K96" s="60"/>
       <c r="L96" s="23"/>
       <c r="M96" s="49" t="s">
         <v>203</v>
@@ -25726,9 +25713,9 @@
       <c r="H97" s="23"/>
       <c r="I97" s="23"/>
       <c r="J97" s="23"/>
-      <c r="K97" s="61"/>
+      <c r="K97" s="60"/>
       <c r="L97" s="23"/>
-      <c r="M97" s="75" t="s">
+      <c r="M97" s="24" t="s">
         <v>223</v>
       </c>
     </row>
@@ -25745,7 +25732,7 @@
       <c r="H98" s="23"/>
       <c r="I98" s="23"/>
       <c r="J98" s="23"/>
-      <c r="K98" s="61"/>
+      <c r="K98" s="60"/>
       <c r="L98" s="23"/>
     </row>
     <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25782,7 +25769,7 @@
       <c r="K99" s="56" t="n">
         <v>0.04</v>
       </c>
-      <c r="L99" s="67" t="n">
+      <c r="L99" s="66" t="n">
         <v>0.04</v>
       </c>
     </row>
@@ -25820,7 +25807,7 @@
       <c r="K100" s="56" t="n">
         <v>0.4</v>
       </c>
-      <c r="L100" s="67" t="n">
+      <c r="L100" s="66" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -25858,7 +25845,7 @@
       <c r="K101" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="L101" s="67" t="n">
+      <c r="L101" s="66" t="n">
         <v>1</v>
       </c>
     </row>
@@ -25896,7 +25883,7 @@
       <c r="K102" s="56" t="n">
         <v>4</v>
       </c>
-      <c r="L102" s="67" t="n">
+      <c r="L102" s="66" t="n">
         <v>4</v>
       </c>
     </row>
@@ -25934,7 +25921,7 @@
       <c r="K103" s="56" t="n">
         <v>1.2</v>
       </c>
-      <c r="L103" s="67" t="n">
+      <c r="L103" s="66" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -25972,7 +25959,7 @@
       <c r="K104" s="56" t="n">
         <v>0.6</v>
       </c>
-      <c r="L104" s="67" t="n">
+      <c r="L104" s="66" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -26010,7 +25997,7 @@
       <c r="K105" s="56" t="n">
         <v>20000</v>
       </c>
-      <c r="L105" s="67" t="n">
+      <c r="L105" s="66" t="n">
         <v>20000</v>
       </c>
     </row>
@@ -26027,7 +26014,7 @@
       <c r="H106" s="29"/>
       <c r="I106" s="29"/>
       <c r="J106" s="29"/>
-      <c r="K106" s="62"/>
+      <c r="K106" s="61"/>
       <c r="L106" s="29"/>
     </row>
     <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26043,7 +26030,7 @@
       <c r="H107" s="31"/>
       <c r="I107" s="31"/>
       <c r="J107" s="31"/>
-      <c r="K107" s="62"/>
+      <c r="K107" s="61"/>
       <c r="L107" s="31"/>
     </row>
     <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26080,7 +26067,7 @@
       <c r="K108" s="56" t="n">
         <v>4</v>
       </c>
-      <c r="L108" s="67" t="n">
+      <c r="L108" s="66" t="n">
         <v>4</v>
       </c>
     </row>
@@ -26118,7 +26105,7 @@
       <c r="K109" s="56" t="n">
         <v>4</v>
       </c>
-      <c r="L109" s="67" t="n">
+      <c r="L109" s="66" t="n">
         <v>4</v>
       </c>
     </row>
@@ -26227,14 +26214,20 @@
       <c r="G114" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="H114" s="71" t="s">
+      <c r="H114" s="69" t="s">
         <v>108</v>
       </c>
-      <c r="I114" s="67" t="s">
+      <c r="I114" s="56" t="s">
         <v>109</v>
       </c>
-      <c r="J114" s="58" t="s">
+      <c r="J114" s="57" t="s">
         <v>110</v>
+      </c>
+      <c r="K114" s="58" t="s">
+        <v>111</v>
+      </c>
+      <c r="L114" s="49" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26259,14 +26252,20 @@
       <c r="G115" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="H115" s="71" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I115" s="67" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J115" s="58" t="n">
-        <v>0.5</v>
+      <c r="H115" s="69" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I115" s="56" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J115" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K115" s="58" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L115" s="59" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26280,8 +26279,12 @@
       <c r="F116" s="23"/>
       <c r="G116" s="23"/>
       <c r="H116" s="23"/>
-      <c r="I116" s="40"/>
-      <c r="J116" s="76"/>
+      <c r="I116" s="73"/>
+      <c r="J116" s="73"/>
+      <c r="K116" s="74"/>
+      <c r="L116" s="49" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="2" t="s">
@@ -26294,8 +26297,9 @@
       <c r="F117" s="23"/>
       <c r="G117" s="23"/>
       <c r="H117" s="23"/>
-      <c r="I117" s="40"/>
-      <c r="J117" s="76"/>
+      <c r="I117" s="73"/>
+      <c r="J117" s="73"/>
+      <c r="K117" s="74"/>
     </row>
     <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="2" t="s">
@@ -26308,8 +26312,9 @@
       <c r="F118" s="23"/>
       <c r="G118" s="23"/>
       <c r="H118" s="23"/>
-      <c r="I118" s="40"/>
-      <c r="J118" s="76"/>
+      <c r="I118" s="73"/>
+      <c r="J118" s="73"/>
+      <c r="K118" s="74"/>
     </row>
     <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="2" t="s">
@@ -26333,13 +26338,16 @@
       <c r="G119" s="17" t="n">
         <v>0.025</v>
       </c>
-      <c r="H119" s="71" t="n">
+      <c r="H119" s="69" t="n">
         <v>0.025</v>
       </c>
-      <c r="I119" s="67" t="n">
+      <c r="I119" s="56" t="n">
         <v>0.025</v>
       </c>
-      <c r="J119" s="58" t="n">
+      <c r="J119" s="57" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="K119" s="58" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -26365,13 +26373,16 @@
       <c r="G120" s="17" t="n">
         <v>0.4</v>
       </c>
-      <c r="H120" s="71" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I120" s="67" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J120" s="58" t="n">
+      <c r="H120" s="69" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I120" s="56" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J120" s="57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K120" s="58" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -26397,13 +26408,16 @@
       <c r="G121" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="H121" s="71" t="n">
-        <v>1</v>
-      </c>
-      <c r="I121" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="J121" s="58" t="n">
+      <c r="H121" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="I121" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J121" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="K121" s="58" t="n">
         <v>1</v>
       </c>
     </row>
@@ -26429,13 +26443,16 @@
       <c r="G122" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="H122" s="71" t="n">
+      <c r="H122" s="69" t="n">
         <v>4</v>
       </c>
-      <c r="I122" s="67" t="n">
+      <c r="I122" s="56" t="n">
         <v>4</v>
       </c>
-      <c r="J122" s="58" t="n">
+      <c r="J122" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="K122" s="58" t="n">
         <v>4</v>
       </c>
     </row>
@@ -26461,13 +26478,16 @@
       <c r="G123" s="17" t="n">
         <v>1.2</v>
       </c>
-      <c r="H123" s="71" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I123" s="67" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J123" s="58" t="n">
+      <c r="H123" s="69" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I123" s="56" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J123" s="57" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K123" s="58" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -26493,13 +26513,16 @@
       <c r="G124" s="17" t="n">
         <v>0.6</v>
       </c>
-      <c r="H124" s="71" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I124" s="67" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J124" s="58" t="n">
+      <c r="H124" s="69" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I124" s="56" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J124" s="57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K124" s="58" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -26525,13 +26548,16 @@
       <c r="G125" s="17" t="n">
         <v>10000</v>
       </c>
-      <c r="H125" s="71" t="n">
+      <c r="H125" s="69" t="n">
         <v>10000</v>
       </c>
-      <c r="I125" s="67" t="n">
+      <c r="I125" s="56" t="n">
         <v>10000</v>
       </c>
-      <c r="J125" s="58" t="n">
+      <c r="J125" s="57" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K125" s="58" t="n">
         <v>10000</v>
       </c>
     </row>
@@ -26546,8 +26572,9 @@
       <c r="F126" s="29"/>
       <c r="G126" s="29"/>
       <c r="H126" s="29"/>
-      <c r="I126" s="33"/>
-      <c r="J126" s="77"/>
+      <c r="I126" s="75"/>
+      <c r="J126" s="75"/>
+      <c r="K126" s="76"/>
     </row>
     <row r="127" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="22" t="s">
@@ -26560,8 +26587,9 @@
       <c r="F127" s="31"/>
       <c r="G127" s="31"/>
       <c r="H127" s="31"/>
-      <c r="I127" s="33"/>
-      <c r="J127" s="77"/>
+      <c r="I127" s="75"/>
+      <c r="J127" s="75"/>
+      <c r="K127" s="76"/>
     </row>
     <row r="128" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="17" t="s">
@@ -26585,14 +26613,17 @@
       <c r="G128" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="H128" s="71" t="n">
+      <c r="H128" s="69" t="n">
         <v>4</v>
       </c>
-      <c r="I128" s="67" t="n">
+      <c r="I128" s="56" t="n">
         <v>4</v>
       </c>
-      <c r="J128" s="58" t="n">
+      <c r="J128" s="57" t="n">
         <v>4</v>
+      </c>
+      <c r="K128" s="58" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26617,14 +26648,17 @@
       <c r="G129" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="H129" s="71" t="n">
+      <c r="H129" s="69" t="n">
         <v>4</v>
       </c>
-      <c r="I129" s="67" t="n">
+      <c r="I129" s="56" t="n">
         <v>4</v>
       </c>
-      <c r="J129" s="58" t="n">
+      <c r="J129" s="57" t="n">
         <v>4</v>
+      </c>
+      <c r="K129" s="58" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26652,10 +26686,13 @@
       <c r="H130" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="I130" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J130" s="78" t="n">
+      <c r="I130" s="67" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J130" s="67" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K130" s="77" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -26681,24 +26718,30 @@
       <c r="H131" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="I131" s="1" t="s">
+      <c r="I131" s="67" t="s">
         <v>218</v>
       </c>
-      <c r="J131" s="78" t="s">
+      <c r="J131" s="67" t="s">
         <v>218</v>
       </c>
+      <c r="K131" s="77" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="132" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AL132" s="59" t="s">
+      <c r="AL132" s="49" t="s">
         <v>201</v>
       </c>
-      <c r="AM132" s="59" t="s">
+      <c r="AM132" s="49" t="s">
         <v>201</v>
       </c>
-      <c r="AN132" s="60" t="s">
+      <c r="AN132" s="59" t="s">
         <v>201</v>
       </c>
-      <c r="AO132" s="79" t="s">
+      <c r="AO132" s="59" t="s">
+        <v>201</v>
+      </c>
+      <c r="AP132" s="78" t="s">
         <v>201</v>
       </c>
     </row>
@@ -26724,16 +26767,19 @@
       <c r="AG133" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="AL133" s="60" t="s">
+      <c r="AL133" s="59" t="s">
         <v>204</v>
       </c>
-      <c r="AM133" s="60" t="s">
+      <c r="AM133" s="59" t="s">
         <v>204</v>
       </c>
-      <c r="AN133" s="60" t="s">
+      <c r="AN133" s="59" t="s">
         <v>204</v>
       </c>
-      <c r="AO133" s="79" t="s">
+      <c r="AO133" s="59" t="s">
+        <v>204</v>
+      </c>
+      <c r="AP133" s="78" t="s">
         <v>204</v>
       </c>
     </row>
@@ -26783,10 +26829,13 @@
       <c r="AM134" s="49" t="s">
         <v>69</v>
       </c>
-      <c r="AN134" s="80" t="s">
+      <c r="AN134" s="59" t="s">
         <v>69</v>
       </c>
-      <c r="AO134" s="81" t="s">
+      <c r="AO134" s="59" t="s">
+        <v>69</v>
+      </c>
+      <c r="AP134" s="78" t="s">
         <v>69</v>
       </c>
     </row>
@@ -26851,7 +26900,7 @@
       <c r="T135" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="U135" s="82" t="s">
+      <c r="U135" s="79" t="s">
         <v>152</v>
       </c>
       <c r="V135" s="57" t="s">
@@ -26881,7 +26930,7 @@
       <c r="AD135" s="57" t="s">
         <v>235</v>
       </c>
-      <c r="AE135" s="83" t="s">
+      <c r="AE135" s="80" t="s">
         <v>236</v>
       </c>
       <c r="AF135" s="57" t="s">
@@ -26890,29 +26939,32 @@
       <c r="AG135" s="57" t="s">
         <v>238</v>
       </c>
-      <c r="AH135" s="84" t="s">
+      <c r="AH135" s="81" t="s">
         <v>239</v>
       </c>
-      <c r="AI135" s="84" t="s">
+      <c r="AI135" s="81" t="s">
         <v>240</v>
       </c>
-      <c r="AJ135" s="84" t="s">
+      <c r="AJ135" s="81" t="s">
         <v>241</v>
       </c>
-      <c r="AK135" s="84" t="s">
+      <c r="AK135" s="81" t="s">
         <v>242</v>
       </c>
-      <c r="AL135" s="85" t="s">
+      <c r="AL135" s="81" t="s">
         <v>243</v>
       </c>
-      <c r="AM135" s="85" t="s">
+      <c r="AM135" s="81" t="s">
         <v>244</v>
       </c>
-      <c r="AN135" s="85" t="s">
+      <c r="AN135" s="81" t="s">
         <v>245</v>
       </c>
-      <c r="AO135" s="85" t="s">
+      <c r="AO135" s="81" t="s">
         <v>246</v>
+      </c>
+      <c r="AP135" s="82" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26976,7 +27028,7 @@
       <c r="T136" s="18" t="n">
         <v>0.5</v>
       </c>
-      <c r="U136" s="82" t="n">
+      <c r="U136" s="79" t="n">
         <v>0.5</v>
       </c>
       <c r="V136" s="57" t="n">
@@ -27006,7 +27058,7 @@
       <c r="AD136" s="57" t="n">
         <v>0.5</v>
       </c>
-      <c r="AE136" s="83" t="n">
+      <c r="AE136" s="80" t="n">
         <v>0.5</v>
       </c>
       <c r="AF136" s="57" t="n">
@@ -27015,28 +27067,31 @@
       <c r="AG136" s="57" t="n">
         <v>0.5</v>
       </c>
-      <c r="AH136" s="84" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AI136" s="84" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AJ136" s="84" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AK136" s="84" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AL136" s="85" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AM136" s="85" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AN136" s="85" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AO136" s="85" t="n">
+      <c r="AH136" s="81" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AI136" s="81" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AJ136" s="81" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK136" s="81" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AL136" s="81" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AM136" s="81" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AN136" s="81" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AO136" s="81" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP136" s="82" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -27078,12 +27133,13 @@
       <c r="AG137" s="23"/>
       <c r="AH137" s="23"/>
       <c r="AI137" s="23"/>
-      <c r="AJ137" s="61"/>
-      <c r="AK137" s="61"/>
-      <c r="AL137" s="23"/>
-      <c r="AM137" s="23"/>
-      <c r="AN137" s="23"/>
-      <c r="AO137" s="23"/>
+      <c r="AJ137" s="60"/>
+      <c r="AK137" s="60"/>
+      <c r="AL137" s="60"/>
+      <c r="AM137" s="60"/>
+      <c r="AN137" s="60"/>
+      <c r="AO137" s="60"/>
+      <c r="AP137" s="23"/>
     </row>
     <row r="138" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="2" t="s">
@@ -27123,12 +27179,13 @@
       <c r="AG138" s="23"/>
       <c r="AH138" s="23"/>
       <c r="AI138" s="23"/>
-      <c r="AJ138" s="61"/>
-      <c r="AK138" s="61"/>
-      <c r="AL138" s="23"/>
-      <c r="AM138" s="23"/>
-      <c r="AN138" s="23"/>
-      <c r="AO138" s="23"/>
+      <c r="AJ138" s="60"/>
+      <c r="AK138" s="60"/>
+      <c r="AL138" s="60"/>
+      <c r="AM138" s="60"/>
+      <c r="AN138" s="60"/>
+      <c r="AO138" s="60"/>
+      <c r="AP138" s="23"/>
     </row>
     <row r="139" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="2" t="s">
@@ -27168,12 +27225,13 @@
       <c r="AG139" s="23"/>
       <c r="AH139" s="23"/>
       <c r="AI139" s="23"/>
-      <c r="AJ139" s="61"/>
-      <c r="AK139" s="61"/>
-      <c r="AL139" s="23"/>
-      <c r="AM139" s="23"/>
-      <c r="AN139" s="23"/>
-      <c r="AO139" s="23"/>
+      <c r="AJ139" s="60"/>
+      <c r="AK139" s="60"/>
+      <c r="AL139" s="60"/>
+      <c r="AM139" s="60"/>
+      <c r="AN139" s="60"/>
+      <c r="AO139" s="60"/>
+      <c r="AP139" s="23"/>
     </row>
     <row r="140" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="2" t="s">
@@ -27236,7 +27294,7 @@
       <c r="T140" s="18" t="n">
         <v>0.05</v>
       </c>
-      <c r="U140" s="82" t="n">
+      <c r="U140" s="79" t="n">
         <v>0.05</v>
       </c>
       <c r="V140" s="57" t="n">
@@ -27266,7 +27324,7 @@
       <c r="AD140" s="57" t="n">
         <v>0.05</v>
       </c>
-      <c r="AE140" s="83" t="n">
+      <c r="AE140" s="80" t="n">
         <v>0.05</v>
       </c>
       <c r="AF140" s="57" t="n">
@@ -27275,28 +27333,31 @@
       <c r="AG140" s="57" t="n">
         <v>0.05</v>
       </c>
-      <c r="AH140" s="84" t="n">
+      <c r="AH140" s="81" t="n">
         <v>0.05</v>
       </c>
-      <c r="AI140" s="84" t="n">
+      <c r="AI140" s="81" t="n">
         <v>0.05</v>
       </c>
-      <c r="AJ140" s="84" t="n">
+      <c r="AJ140" s="81" t="n">
         <v>0.05</v>
       </c>
-      <c r="AK140" s="84" t="n">
+      <c r="AK140" s="81" t="n">
         <v>0.05</v>
       </c>
-      <c r="AL140" s="85" t="n">
+      <c r="AL140" s="81" t="n">
         <v>0.05</v>
       </c>
-      <c r="AM140" s="85" t="n">
+      <c r="AM140" s="81" t="n">
         <v>0.05</v>
       </c>
-      <c r="AN140" s="85" t="n">
+      <c r="AN140" s="81" t="n">
         <v>0.05</v>
       </c>
-      <c r="AO140" s="85" t="n">
+      <c r="AO140" s="81" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AP140" s="82" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -27361,7 +27422,7 @@
       <c r="T141" s="18" t="n">
         <v>0.4</v>
       </c>
-      <c r="U141" s="82" t="n">
+      <c r="U141" s="79" t="n">
         <v>0.4</v>
       </c>
       <c r="V141" s="57" t="n">
@@ -27391,7 +27452,7 @@
       <c r="AD141" s="57" t="n">
         <v>0.4</v>
       </c>
-      <c r="AE141" s="83" t="n">
+      <c r="AE141" s="80" t="n">
         <v>0.4</v>
       </c>
       <c r="AF141" s="57" t="n">
@@ -27400,28 +27461,31 @@
       <c r="AG141" s="57" t="n">
         <v>0.4</v>
       </c>
-      <c r="AH141" s="84" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AI141" s="84" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AJ141" s="84" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AK141" s="84" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AL141" s="85" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AM141" s="85" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AN141" s="85" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AO141" s="85" t="n">
+      <c r="AH141" s="81" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AI141" s="81" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AJ141" s="81" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AK141" s="81" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AL141" s="81" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AM141" s="81" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AN141" s="81" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AO141" s="81" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AP141" s="82" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -27486,7 +27550,7 @@
       <c r="T142" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="U142" s="82" t="n">
+      <c r="U142" s="79" t="n">
         <v>1</v>
       </c>
       <c r="V142" s="57" t="n">
@@ -27516,7 +27580,7 @@
       <c r="AD142" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="AE142" s="83" t="n">
+      <c r="AE142" s="80" t="n">
         <v>1</v>
       </c>
       <c r="AF142" s="57" t="n">
@@ -27525,28 +27589,31 @@
       <c r="AG142" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="AH142" s="84" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI142" s="84" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ142" s="84" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK142" s="84" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL142" s="85" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM142" s="85" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN142" s="85" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO142" s="85" t="n">
+      <c r="AH142" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI142" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ142" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK142" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL142" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM142" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN142" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO142" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP142" s="82" t="n">
         <v>1</v>
       </c>
     </row>
@@ -27611,7 +27678,7 @@
       <c r="T143" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="U143" s="82" t="n">
+      <c r="U143" s="79" t="n">
         <v>4</v>
       </c>
       <c r="V143" s="57" t="n">
@@ -27641,7 +27708,7 @@
       <c r="AD143" s="57" t="n">
         <v>3</v>
       </c>
-      <c r="AE143" s="83" t="n">
+      <c r="AE143" s="80" t="n">
         <v>0</v>
       </c>
       <c r="AF143" s="57" t="n">
@@ -27650,29 +27717,32 @@
       <c r="AG143" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="AH143" s="84" t="n">
+      <c r="AH143" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="AI143" s="84" t="n">
+      <c r="AI143" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="AJ143" s="84" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK143" s="84" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL143" s="85" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM143" s="85" t="n">
-        <v>2</v>
-      </c>
-      <c r="AN143" s="85" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO143" s="85" t="n">
-        <v>2</v>
+      <c r="AJ143" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK143" s="81" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL143" s="81" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM143" s="81" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN143" s="81" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO143" s="81" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP143" s="82" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27724,19 +27794,19 @@
       <c r="P144" s="17" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q144" s="74" t="n">
+      <c r="Q144" s="72" t="n">
         <v>0.8</v>
       </c>
-      <c r="R144" s="74" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S144" s="74" t="n">
+      <c r="R144" s="72" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S144" s="72" t="n">
         <v>0.4</v>
       </c>
       <c r="T144" s="18" t="n">
         <v>0.3</v>
       </c>
-      <c r="U144" s="82" t="n">
+      <c r="U144" s="79" t="n">
         <v>0.3</v>
       </c>
       <c r="V144" s="57" t="n">
@@ -27766,7 +27836,7 @@
       <c r="AD144" s="57" t="n">
         <v>0.3</v>
       </c>
-      <c r="AE144" s="83" t="n">
+      <c r="AE144" s="80" t="n">
         <v>0.3</v>
       </c>
       <c r="AF144" s="57" t="n">
@@ -27775,28 +27845,31 @@
       <c r="AG144" s="57" t="n">
         <v>0.3</v>
       </c>
-      <c r="AH144" s="84" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI144" s="84" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AJ144" s="84" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK144" s="84" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AL144" s="85" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AM144" s="85" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN144" s="85" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AO144" s="85" t="n">
+      <c r="AH144" s="81" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI144" s="81" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AJ144" s="81" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK144" s="81" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL144" s="81" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AM144" s="81" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN144" s="81" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO144" s="81" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AP144" s="82" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -27861,7 +27934,7 @@
       <c r="T145" s="18" t="n">
         <v>0.6</v>
       </c>
-      <c r="U145" s="82" t="n">
+      <c r="U145" s="79" t="n">
         <v>0.6</v>
       </c>
       <c r="V145" s="57" t="n">
@@ -27891,7 +27964,7 @@
       <c r="AD145" s="57" t="n">
         <v>0.6</v>
       </c>
-      <c r="AE145" s="83" t="n">
+      <c r="AE145" s="80" t="n">
         <v>0.6</v>
       </c>
       <c r="AF145" s="57" t="n">
@@ -27900,28 +27973,31 @@
       <c r="AG145" s="57" t="n">
         <v>0.6</v>
       </c>
-      <c r="AH145" s="84" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AI145" s="84" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AJ145" s="84" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AK145" s="84" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AL145" s="85" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AM145" s="85" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AN145" s="85" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AO145" s="85" t="n">
+      <c r="AH145" s="81" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AI145" s="81" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AJ145" s="81" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AK145" s="81" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AL145" s="81" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AM145" s="81" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AN145" s="81" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AO145" s="81" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AP145" s="82" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -27986,7 +28062,7 @@
       <c r="T146" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="U146" s="82" t="n">
+      <c r="U146" s="79" t="n">
         <v>12000</v>
       </c>
       <c r="V146" s="57" t="n">
@@ -28016,7 +28092,7 @@
       <c r="AD146" s="57" t="n">
         <v>5000</v>
       </c>
-      <c r="AE146" s="83" t="n">
+      <c r="AE146" s="80" t="n">
         <v>0</v>
       </c>
       <c r="AF146" s="57" t="n">
@@ -28025,28 +28101,31 @@
       <c r="AG146" s="57" t="n">
         <v>0</v>
       </c>
-      <c r="AH146" s="84" t="n">
+      <c r="AH146" s="81" t="n">
         <v>10000</v>
       </c>
-      <c r="AI146" s="84" t="n">
+      <c r="AI146" s="81" t="n">
         <v>2000</v>
       </c>
-      <c r="AJ146" s="84" t="n">
+      <c r="AJ146" s="81" t="n">
         <v>5000</v>
       </c>
-      <c r="AK146" s="84" t="n">
+      <c r="AK146" s="81" t="n">
         <v>10000</v>
       </c>
-      <c r="AL146" s="85" t="n">
+      <c r="AL146" s="81" t="n">
         <v>10000</v>
       </c>
-      <c r="AM146" s="85" t="n">
+      <c r="AM146" s="81" t="n">
         <v>10000</v>
       </c>
-      <c r="AN146" s="85" t="n">
+      <c r="AN146" s="81" t="n">
         <v>10000</v>
       </c>
-      <c r="AO146" s="85" t="n">
+      <c r="AO146" s="81" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AP146" s="82" t="n">
         <v>10000</v>
       </c>
     </row>
@@ -28088,12 +28167,13 @@
       <c r="AG147" s="29"/>
       <c r="AH147" s="29"/>
       <c r="AI147" s="29"/>
-      <c r="AJ147" s="62"/>
-      <c r="AK147" s="62"/>
-      <c r="AL147" s="29"/>
-      <c r="AM147" s="29"/>
-      <c r="AN147" s="29"/>
-      <c r="AO147" s="29"/>
+      <c r="AJ147" s="61"/>
+      <c r="AK147" s="61"/>
+      <c r="AL147" s="61"/>
+      <c r="AM147" s="61"/>
+      <c r="AN147" s="61"/>
+      <c r="AO147" s="61"/>
+      <c r="AP147" s="29"/>
     </row>
     <row r="148" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="22" t="s">
@@ -28133,12 +28213,13 @@
       <c r="AG148" s="31"/>
       <c r="AH148" s="31"/>
       <c r="AI148" s="31"/>
-      <c r="AJ148" s="62"/>
-      <c r="AK148" s="62"/>
-      <c r="AL148" s="31"/>
-      <c r="AM148" s="31"/>
-      <c r="AN148" s="31"/>
-      <c r="AO148" s="31"/>
+      <c r="AJ148" s="61"/>
+      <c r="AK148" s="61"/>
+      <c r="AL148" s="61"/>
+      <c r="AM148" s="61"/>
+      <c r="AN148" s="61"/>
+      <c r="AO148" s="61"/>
+      <c r="AP148" s="31"/>
     </row>
     <row r="149" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="17" t="s">
@@ -28198,10 +28279,10 @@
       <c r="S149" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="T149" s="86" t="n">
-        <v>2</v>
-      </c>
-      <c r="U149" s="82" t="n">
+      <c r="T149" s="83" t="n">
+        <v>2</v>
+      </c>
+      <c r="U149" s="79" t="n">
         <v>2</v>
       </c>
       <c r="V149" s="57" t="n">
@@ -28231,7 +28312,7 @@
       <c r="AD149" s="57" t="n">
         <v>5</v>
       </c>
-      <c r="AE149" s="83" t="n">
+      <c r="AE149" s="80" t="n">
         <v>5</v>
       </c>
       <c r="AF149" s="57" t="n">
@@ -28240,28 +28321,31 @@
       <c r="AG149" s="57" t="n">
         <v>5</v>
       </c>
-      <c r="AH149" s="84" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI149" s="84" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ149" s="84" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK149" s="84" t="n">
+      <c r="AH149" s="81" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI149" s="81" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ149" s="81" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK149" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="AL149" s="85" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM149" s="85" t="n">
-        <v>2</v>
-      </c>
-      <c r="AN149" s="85" t="n">
+      <c r="AL149" s="81" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM149" s="81" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN149" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="AO149" s="85" t="n">
+      <c r="AO149" s="81" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP149" s="82" t="n">
         <v>3</v>
       </c>
     </row>
@@ -28323,10 +28407,10 @@
       <c r="S150" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="T150" s="86" t="n">
+      <c r="T150" s="83" t="n">
         <v>3</v>
       </c>
-      <c r="U150" s="82" t="n">
+      <c r="U150" s="79" t="n">
         <v>3</v>
       </c>
       <c r="V150" s="57" t="n">
@@ -28356,7 +28440,7 @@
       <c r="AD150" s="57" t="n">
         <v>5</v>
       </c>
-      <c r="AE150" s="83" t="n">
+      <c r="AE150" s="80" t="n">
         <v>5</v>
       </c>
       <c r="AF150" s="57" t="n">
@@ -28365,28 +28449,31 @@
       <c r="AG150" s="57" t="n">
         <v>5</v>
       </c>
-      <c r="AH150" s="84" t="n">
+      <c r="AH150" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="AI150" s="84" t="n">
+      <c r="AI150" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="AJ150" s="84" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK150" s="84" t="n">
+      <c r="AJ150" s="81" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK150" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="AL150" s="85" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM150" s="85" t="n">
-        <v>2</v>
-      </c>
-      <c r="AN150" s="85" t="n">
+      <c r="AL150" s="81" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM150" s="81" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN150" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="AO150" s="85" t="n">
+      <c r="AO150" s="81" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP150" s="82" t="n">
         <v>3</v>
       </c>
     </row>
@@ -28496,10 +28583,10 @@
       <c r="AI151" s="5" t="n">
         <v>0.6</v>
       </c>
-      <c r="AJ151" s="68" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AK151" s="68" t="n">
+      <c r="AJ151" s="67" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AK151" s="67" t="n">
         <v>0.6</v>
       </c>
       <c r="AL151" s="5" t="n">
@@ -28512,6 +28599,9 @@
         <v>0.6</v>
       </c>
       <c r="AO151" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AP151" s="5" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -28618,10 +28708,10 @@
       <c r="AI152" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="AJ152" s="68" t="s">
+      <c r="AJ152" s="67" t="s">
         <v>205</v>
       </c>
-      <c r="AK152" s="68" t="s">
+      <c r="AK152" s="67" t="s">
         <v>205</v>
       </c>
       <c r="AL152" s="1" t="s">
@@ -28634,6 +28724,9 @@
         <v>205</v>
       </c>
       <c r="AO152" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="AP152" s="1" t="s">
         <v>205</v>
       </c>
     </row>
@@ -28647,20 +28740,23 @@
       <c r="G153" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="AK153" s="0" t="s">
-        <v>247</v>
-      </c>
-      <c r="AL153" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM153" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="AN153" s="0" t="n">
+      <c r="AK153" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="AL153" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM153" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN153" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="AO153" s="0" t="n">
-        <v>2</v>
+      <c r="AO153" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP153" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28668,13 +28764,13 @@
         <v>137</v>
       </c>
       <c r="H154" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I154" s="1" t="s">
         <v>138</v>
       </c>
       <c r="J154" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K154" s="1" t="n">
         <v>1</v>
@@ -28745,16 +28841,17 @@
       <c r="AG154" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AK154" s="0" t="s">
+      <c r="AK154" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="AO154" s="0" t="n">
-        <v>2</v>
-      </c>
+      <c r="AO154" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP154" s="1"/>
     </row>
     <row r="155" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B155" s="1" t="n">
         <v>0.4</v>
@@ -28893,7 +28990,7 @@
       <c r="J158" s="58" t="s">
         <v>111</v>
       </c>
-      <c r="K158" s="67" t="s">
+      <c r="K158" s="66" t="s">
         <v>112</v>
       </c>
     </row>
@@ -28928,7 +29025,7 @@
       <c r="J159" s="58" t="n">
         <v>0.5</v>
       </c>
-      <c r="K159" s="67" t="n">
+      <c r="K159" s="66" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -29008,7 +29105,7 @@
       <c r="J163" s="58" t="n">
         <v>0.02</v>
       </c>
-      <c r="K163" s="67" t="n">
+      <c r="K163" s="66" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -29043,7 +29140,7 @@
       <c r="J164" s="58" t="n">
         <v>0.4</v>
       </c>
-      <c r="K164" s="67" t="n">
+      <c r="K164" s="66" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -29078,7 +29175,7 @@
       <c r="J165" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="K165" s="67" t="n">
+      <c r="K165" s="66" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29113,7 +29210,7 @@
       <c r="J166" s="58" t="n">
         <v>2</v>
       </c>
-      <c r="K166" s="67" t="n">
+      <c r="K166" s="66" t="n">
         <v>2</v>
       </c>
     </row>
@@ -29148,7 +29245,7 @@
       <c r="J167" s="58" t="n">
         <v>1.2</v>
       </c>
-      <c r="K167" s="67" t="n">
+      <c r="K167" s="66" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -29183,7 +29280,7 @@
       <c r="J168" s="58" t="n">
         <v>0.6</v>
       </c>
-      <c r="K168" s="67" t="n">
+      <c r="K168" s="66" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -29218,7 +29315,7 @@
       <c r="J169" s="58" t="n">
         <v>15000</v>
       </c>
-      <c r="K169" s="67" t="n">
+      <c r="K169" s="66" t="n">
         <v>15000</v>
       </c>
     </row>
@@ -29283,7 +29380,7 @@
       <c r="J172" s="58" t="n">
         <v>2</v>
       </c>
-      <c r="K172" s="67" t="n">
+      <c r="K172" s="66" t="n">
         <v>2</v>
       </c>
     </row>
@@ -29318,7 +29415,7 @@
       <c r="J173" s="58" t="n">
         <v>2</v>
       </c>
-      <c r="K173" s="67" t="n">
+      <c r="K173" s="66" t="n">
         <v>2</v>
       </c>
     </row>
@@ -29424,7 +29521,7 @@
     </row>
     <row r="178" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B178" s="1" t="n">
         <v>0.3</v>
@@ -29770,11 +29867,11 @@
       </c>
     </row>
     <row r="198" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E198" s="87" t="s">
-        <v>251</v>
-      </c>
-      <c r="F198" s="87" t="s">
+      <c r="E198" s="84" t="s">
         <v>252</v>
+      </c>
+      <c r="F198" s="84" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29796,7 +29893,7 @@
     </row>
     <row r="200" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B200" s="1" t="n">
         <v>0.3</v>
@@ -29813,24 +29910,24 @@
       <c r="F200" s="1" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q200" s="59" t="s">
+      <c r="Q200" s="49" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="M201" s="88" t="s">
-        <v>253</v>
-      </c>
-      <c r="N201" s="88" t="s">
-        <v>253</v>
-      </c>
-      <c r="O201" s="88" t="s">
-        <v>253</v>
-      </c>
-      <c r="P201" s="89" t="s">
+      <c r="M201" s="85" t="s">
+        <v>254</v>
+      </c>
+      <c r="N201" s="85" t="s">
+        <v>254</v>
+      </c>
+      <c r="O201" s="85" t="s">
+        <v>254</v>
+      </c>
+      <c r="P201" s="85" t="s">
         <v>204</v>
       </c>
-      <c r="Q201" s="60" t="s">
+      <c r="Q201" s="59" t="s">
         <v>204</v>
       </c>
     </row>
@@ -29840,22 +29937,22 @@
         <v>208</v>
       </c>
       <c r="J202" s="24" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K202" s="24" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L202" s="24" t="s">
-        <v>255</v>
-      </c>
-      <c r="M202" s="88" t="s">
         <v>256</v>
       </c>
-      <c r="N202" s="88" t="s">
-        <v>256</v>
-      </c>
-      <c r="O202" s="88" t="s">
-        <v>256</v>
+      <c r="M202" s="85" t="s">
+        <v>257</v>
+      </c>
+      <c r="N202" s="85" t="s">
+        <v>257</v>
+      </c>
+      <c r="O202" s="85" t="s">
+        <v>257</v>
       </c>
       <c r="P202" s="24" t="s">
         <v>203</v>
@@ -29913,7 +30010,7 @@
       <c r="P203" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="Q203" s="85" t="s">
+      <c r="Q203" s="82" t="s">
         <v>117</v>
       </c>
     </row>
@@ -29966,7 +30063,7 @@
       <c r="P204" s="45" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q204" s="85" t="n">
+      <c r="Q204" s="82" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -30082,7 +30179,7 @@
       <c r="P208" s="45" t="n">
         <v>0.005</v>
       </c>
-      <c r="Q208" s="85" t="n">
+      <c r="Q208" s="82" t="n">
         <v>0.005</v>
       </c>
     </row>
@@ -30135,7 +30232,7 @@
       <c r="P209" s="45" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q209" s="85" t="n">
+      <c r="Q209" s="82" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -30188,7 +30285,7 @@
       <c r="P210" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="Q210" s="85" t="n">
+      <c r="Q210" s="82" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30241,7 +30338,7 @@
       <c r="P211" s="45" t="n">
         <v>9</v>
       </c>
-      <c r="Q211" s="85" t="n">
+      <c r="Q211" s="82" t="n">
         <v>6</v>
       </c>
     </row>
@@ -30294,7 +30391,7 @@
       <c r="P212" s="45" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q212" s="85" t="n">
+      <c r="Q212" s="82" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -30347,7 +30444,7 @@
       <c r="P213" s="45" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q213" s="85" t="n">
+      <c r="Q213" s="82" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -30400,7 +30497,7 @@
       <c r="P214" s="45" t="n">
         <v>20000</v>
       </c>
-      <c r="Q214" s="85" t="n">
+      <c r="Q214" s="82" t="n">
         <v>20000</v>
       </c>
     </row>
@@ -30495,7 +30592,7 @@
       <c r="P217" s="45" t="n">
         <v>2</v>
       </c>
-      <c r="Q217" s="85" t="n">
+      <c r="Q217" s="82" t="n">
         <v>5</v>
       </c>
     </row>
@@ -30548,7 +30645,7 @@
       <c r="P218" s="45" t="n">
         <v>2</v>
       </c>
-      <c r="Q218" s="85" t="n">
+      <c r="Q218" s="82" t="n">
         <v>5</v>
       </c>
     </row>
@@ -30631,10 +30728,10 @@
         <v>205</v>
       </c>
       <c r="J220" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K220" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L220" s="1" t="s">
         <v>205</v>
@@ -30663,7 +30760,7 @@
     </row>
     <row r="223" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B223" s="1" t="n">
         <v>0.3</v>
@@ -30692,31 +30789,31 @@
     </row>
     <row r="224" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G224" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H224" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I224" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J224" s="24" t="s">
         <v>208</v>
       </c>
       <c r="K224" s="24" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30735,8 +30832,8 @@
       <c r="E225" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="F225" s="90" t="s">
-        <v>261</v>
+      <c r="F225" s="86" t="s">
+        <v>262</v>
       </c>
       <c r="J225" s="58" t="s">
         <v>107</v>
@@ -31040,7 +31137,7 @@
     </row>
     <row r="245" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B245" s="1" t="n">
         <v>0.4</v>
@@ -31060,21 +31157,21 @@
     </row>
     <row r="246" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J246" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G247" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H247" s="24" t="s">
         <v>208</v>
@@ -31082,7 +31179,7 @@
     </row>
     <row r="248" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B248" s="17" t="s">
         <v>102</v>
@@ -31135,10 +31232,10 @@
       <c r="R248" s="56" t="s">
         <v>118</v>
       </c>
-      <c r="S248" s="67" t="s">
+      <c r="S248" s="66" t="s">
         <v>150</v>
       </c>
-      <c r="T248" s="59" t="s">
+      <c r="T248" s="49" t="s">
         <v>201</v>
       </c>
     </row>
@@ -31197,10 +31294,10 @@
       <c r="R249" s="56" t="n">
         <v>0.5</v>
       </c>
-      <c r="S249" s="67" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T249" s="60" t="s">
+      <c r="S249" s="66" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T249" s="59" t="s">
         <v>204</v>
       </c>
     </row>
@@ -31331,7 +31428,7 @@
       <c r="R253" s="56" t="n">
         <v>0.004</v>
       </c>
-      <c r="S253" s="67" t="n">
+      <c r="S253" s="66" t="n">
         <v>0.004</v>
       </c>
     </row>
@@ -31390,7 +31487,7 @@
       <c r="R254" s="56" t="n">
         <v>0.4</v>
       </c>
-      <c r="S254" s="67" t="n">
+      <c r="S254" s="66" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -31449,7 +31546,7 @@
       <c r="R255" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="S255" s="67" t="n">
+      <c r="S255" s="66" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31508,7 +31605,7 @@
       <c r="R256" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="S256" s="67" t="n">
+      <c r="S256" s="66" t="n">
         <v>2</v>
       </c>
     </row>
@@ -31567,7 +31664,7 @@
       <c r="R257" s="56" t="n">
         <v>10</v>
       </c>
-      <c r="S257" s="67" t="n">
+      <c r="S257" s="66" t="n">
         <v>10</v>
       </c>
     </row>
@@ -31626,7 +31723,7 @@
       <c r="R258" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="S258" s="67" t="n">
+      <c r="S258" s="66" t="n">
         <v>0</v>
       </c>
     </row>
@@ -31685,7 +31782,7 @@
       <c r="R259" s="56" t="n">
         <v>10000</v>
       </c>
-      <c r="S259" s="67" t="n">
+      <c r="S259" s="66" t="n">
         <v>2000</v>
       </c>
     </row>
@@ -31790,7 +31887,7 @@
       <c r="R262" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="S262" s="67" t="n">
+      <c r="S262" s="66" t="n">
         <v>3</v>
       </c>
     </row>
@@ -31849,7 +31946,7 @@
       <c r="R263" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="S263" s="67" t="n">
+      <c r="S263" s="66" t="n">
         <v>3</v>
       </c>
     </row>
@@ -31969,19 +32066,19 @@
       </c>
     </row>
     <row r="266" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="M266" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="N266" s="0" t="n">
+      <c r="M266" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N266" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="O266" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P266" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q266" s="0" t="n">
+      <c r="O266" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P266" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q266" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -32007,22 +32104,22 @@
       <c r="H267" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="O267" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P267" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q267" s="0" t="n">
+      <c r="O267" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P267" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q267" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="S267" s="59" t="s">
+      <c r="S267" s="49" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="268" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B268" s="1" t="n">
         <v>0.4</v>
@@ -32045,34 +32142,34 @@
       <c r="H268" s="1" t="n">
         <v>0.4</v>
       </c>
-      <c r="S268" s="60" t="s">
+      <c r="S268" s="59" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G269" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H269" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="S269" s="49" t="s">
         <v>203</v>
@@ -32080,7 +32177,7 @@
     </row>
     <row r="270" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B270" s="17" t="s">
         <v>102</v>
@@ -32133,7 +32230,7 @@
       <c r="R270" s="45" t="s">
         <v>118</v>
       </c>
-      <c r="S270" s="85" t="s">
+      <c r="S270" s="82" t="s">
         <v>150</v>
       </c>
     </row>
@@ -32192,7 +32289,7 @@
       <c r="R271" s="45" t="n">
         <v>0.5</v>
       </c>
-      <c r="S271" s="85" t="n">
+      <c r="S271" s="82" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -32320,7 +32417,7 @@
       <c r="R275" s="45" t="n">
         <v>0.003</v>
       </c>
-      <c r="S275" s="85" t="n">
+      <c r="S275" s="82" t="n">
         <v>0.003</v>
       </c>
     </row>
@@ -32379,7 +32476,7 @@
       <c r="R276" s="45" t="n">
         <v>0.4</v>
       </c>
-      <c r="S276" s="85" t="n">
+      <c r="S276" s="82" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -32438,7 +32535,7 @@
       <c r="R277" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="S277" s="85" t="n">
+      <c r="S277" s="82" t="n">
         <v>1</v>
       </c>
     </row>
@@ -32497,7 +32594,7 @@
       <c r="R278" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="S278" s="85" t="n">
+      <c r="S278" s="82" t="n">
         <v>0</v>
       </c>
     </row>
@@ -32556,7 +32653,7 @@
       <c r="R279" s="45" t="n">
         <v>10</v>
       </c>
-      <c r="S279" s="85" t="n">
+      <c r="S279" s="82" t="n">
         <v>10</v>
       </c>
     </row>
@@ -32615,7 +32712,7 @@
       <c r="R280" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="S280" s="85" t="n">
+      <c r="S280" s="82" t="n">
         <v>0</v>
       </c>
     </row>
@@ -32674,7 +32771,7 @@
       <c r="R281" s="45" t="n">
         <v>10000</v>
       </c>
-      <c r="S281" s="85" t="n">
+      <c r="S281" s="82" t="n">
         <v>10000</v>
       </c>
     </row>
@@ -32779,7 +32876,7 @@
       <c r="R284" s="45" t="n">
         <v>2</v>
       </c>
-      <c r="S284" s="85" t="n">
+      <c r="S284" s="82" t="n">
         <v>1</v>
       </c>
     </row>
@@ -32838,7 +32935,7 @@
       <c r="R285" s="45" t="n">
         <v>2</v>
       </c>
-      <c r="S285" s="85" t="n">
+      <c r="S285" s="82" t="n">
         <v>1</v>
       </c>
     </row>
@@ -32958,28 +33055,28 @@
       </c>
     </row>
     <row r="288" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L288" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="M288" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="N288" s="0" t="n">
+      <c r="L288" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="M288" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N288" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="O288" s="0" t="n">
+      <c r="O288" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="P288" s="0" t="n">
+      <c r="P288" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="Q288" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="R288" s="0" t="n">
+      <c r="Q288" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R288" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="S288" s="0" t="n">
+      <c r="S288" s="1" t="n">
         <v>3</v>
       </c>
     </row>
@@ -33005,13 +33102,13 @@
       <c r="H289" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="M289" s="79" t="s">
+      <c r="M289" s="78" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="290" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B290" s="1" t="n">
         <v>0.4</v>
@@ -33037,48 +33134,48 @@
       <c r="I290" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="M290" s="79" t="s">
+      <c r="M290" s="78" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="291" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G291" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H291" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I291" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="J291" s="24" t="s">
         <v>208</v>
       </c>
-      <c r="M291" s="81" t="s">
-        <v>252</v>
+      <c r="M291" s="78" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="292" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B292" s="17" t="s">
         <v>102</v>
@@ -33113,7 +33210,7 @@
       <c r="L292" s="56" t="s">
         <v>112</v>
       </c>
-      <c r="M292" s="67" t="s">
+      <c r="M292" s="66" t="s">
         <v>113</v>
       </c>
     </row>
@@ -33154,7 +33251,7 @@
       <c r="L293" s="56" t="n">
         <v>0.5</v>
       </c>
-      <c r="M293" s="67" t="n">
+      <c r="M293" s="66" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -33246,7 +33343,7 @@
       <c r="L297" s="56" t="n">
         <v>0.02</v>
       </c>
-      <c r="M297" s="67" t="n">
+      <c r="M297" s="66" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -33287,7 +33384,7 @@
       <c r="L298" s="56" t="n">
         <v>0.4</v>
       </c>
-      <c r="M298" s="67" t="n">
+      <c r="M298" s="66" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -33328,7 +33425,7 @@
       <c r="L299" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="M299" s="67" t="n">
+      <c r="M299" s="66" t="n">
         <v>1</v>
       </c>
     </row>
@@ -33369,7 +33466,7 @@
       <c r="L300" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="M300" s="67" t="n">
+      <c r="M300" s="66" t="n">
         <v>2</v>
       </c>
     </row>
@@ -33410,7 +33507,7 @@
       <c r="L301" s="56" t="n">
         <v>1.2</v>
       </c>
-      <c r="M301" s="67" t="n">
+      <c r="M301" s="66" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -33451,7 +33548,7 @@
       <c r="L302" s="56" t="n">
         <v>0.6</v>
       </c>
-      <c r="M302" s="67" t="n">
+      <c r="M302" s="66" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -33492,7 +33589,7 @@
       <c r="L303" s="56" t="n">
         <v>2000</v>
       </c>
-      <c r="M303" s="67" t="n">
+      <c r="M303" s="66" t="n">
         <v>5000</v>
       </c>
     </row>
@@ -33508,7 +33605,7 @@
       <c r="G304" s="29"/>
       <c r="H304" s="29"/>
       <c r="I304" s="29"/>
-      <c r="J304" s="62"/>
+      <c r="J304" s="61"/>
       <c r="K304" s="29"/>
       <c r="L304" s="29"/>
       <c r="M304" s="29"/>
@@ -33525,7 +33622,7 @@
       <c r="G305" s="31"/>
       <c r="H305" s="31"/>
       <c r="I305" s="31"/>
-      <c r="J305" s="62"/>
+      <c r="J305" s="61"/>
       <c r="K305" s="31"/>
       <c r="L305" s="31"/>
       <c r="M305" s="31"/>
@@ -33567,7 +33664,7 @@
       <c r="L306" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="M306" s="67" t="n">
+      <c r="M306" s="66" t="n">
         <v>1</v>
       </c>
     </row>
@@ -33608,7 +33705,7 @@
       <c r="L307" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="M307" s="67" t="n">
+      <c r="M307" s="66" t="n">
         <v>1</v>
       </c>
     </row>
@@ -33724,7 +33821,7 @@
     </row>
     <row r="312" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A312" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B312" s="1" t="n">
         <v>0.4</v>
@@ -33757,40 +33854,40 @@
     </row>
     <row r="313" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G313" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H313" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I313" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J313" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K313" s="1"/>
     </row>
     <row r="314" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A314" s="91" t="s">
-        <v>268</v>
+      <c r="A314" s="87" t="s">
+        <v>269</v>
       </c>
       <c r="B314" s="17" t="s">
         <v>102</v>
@@ -33799,11 +33896,11 @@
         <v>103</v>
       </c>
       <c r="D314" s="24" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="315" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A315" s="91" t="s">
+      <c r="A315" s="87" t="s">
         <v>80</v>
       </c>
       <c r="B315" s="17" t="n">
@@ -33814,28 +33911,28 @@
       </c>
     </row>
     <row r="316" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A316" s="91" t="s">
+      <c r="A316" s="87" t="s">
         <v>120</v>
       </c>
       <c r="B316" s="23"/>
       <c r="C316" s="23"/>
     </row>
     <row r="317" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A317" s="91" t="s">
+      <c r="A317" s="87" t="s">
         <v>82</v>
       </c>
       <c r="B317" s="23"/>
       <c r="C317" s="23"/>
     </row>
     <row r="318" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A318" s="91" t="s">
+      <c r="A318" s="87" t="s">
         <v>121</v>
       </c>
       <c r="B318" s="23"/>
       <c r="C318" s="23"/>
     </row>
     <row r="319" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A319" s="91" t="s">
+      <c r="A319" s="87" t="s">
         <v>84</v>
       </c>
       <c r="B319" s="17" t="n">
@@ -33846,7 +33943,7 @@
       </c>
     </row>
     <row r="320" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A320" s="91" t="s">
+      <c r="A320" s="87" t="s">
         <v>79</v>
       </c>
       <c r="B320" s="17" t="n">
@@ -33857,7 +33954,7 @@
       </c>
     </row>
     <row r="321" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A321" s="91" t="s">
+      <c r="A321" s="87" t="s">
         <v>85</v>
       </c>
       <c r="B321" s="17" t="n">
@@ -33868,7 +33965,7 @@
       </c>
     </row>
     <row r="322" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A322" s="91" t="s">
+      <c r="A322" s="87" t="s">
         <v>122</v>
       </c>
       <c r="B322" s="17" t="n">
@@ -33879,7 +33976,7 @@
       </c>
     </row>
     <row r="323" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A323" s="91" t="s">
+      <c r="A323" s="87" t="s">
         <v>123</v>
       </c>
       <c r="B323" s="17" t="n">
@@ -33890,7 +33987,7 @@
       </c>
     </row>
     <row r="324" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A324" s="91" t="s">
+      <c r="A324" s="87" t="s">
         <v>124</v>
       </c>
       <c r="B324" s="17" t="n">
@@ -33901,7 +33998,7 @@
       </c>
     </row>
     <row r="325" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A325" s="91" t="s">
+      <c r="A325" s="87" t="s">
         <v>125</v>
       </c>
       <c r="B325" s="17" t="n">
@@ -33912,21 +34009,21 @@
       </c>
     </row>
     <row r="326" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A326" s="91" t="s">
+      <c r="A326" s="87" t="s">
         <v>126</v>
       </c>
       <c r="B326" s="29"/>
       <c r="C326" s="29"/>
     </row>
     <row r="327" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A327" s="92" t="s">
+      <c r="A327" s="88" t="s">
         <v>128</v>
       </c>
       <c r="B327" s="31"/>
       <c r="C327" s="31"/>
     </row>
     <row r="328" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A328" s="91" t="s">
+      <c r="A328" s="87" t="s">
         <v>134</v>
       </c>
       <c r="B328" s="17" t="n">
@@ -33937,7 +34034,7 @@
       </c>
     </row>
     <row r="329" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A329" s="91" t="s">
+      <c r="A329" s="87" t="s">
         <v>136</v>
       </c>
       <c r="B329" s="17" t="n">
@@ -33948,7 +34045,7 @@
       </c>
     </row>
     <row r="330" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A330" s="93" t="s">
+      <c r="A330" s="89" t="s">
         <v>157</v>
       </c>
       <c r="B330" s="5" t="n">
@@ -33977,7 +34074,7 @@
     </row>
     <row r="334" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A334" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B334" s="1" t="n">
         <v>0.4</v>
@@ -33988,25 +34085,25 @@
     </row>
     <row r="335" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A335" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="336" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A336" s="91" t="s">
-        <v>270</v>
+      <c r="A336" s="87" t="s">
+        <v>271</v>
       </c>
       <c r="B336" s="17" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="337" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A337" s="91" t="s">
+      <c r="A337" s="87" t="s">
         <v>80</v>
       </c>
       <c r="B337" s="17" t="n">
@@ -34014,25 +34111,25 @@
       </c>
     </row>
     <row r="338" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A338" s="91" t="s">
+      <c r="A338" s="87" t="s">
         <v>120</v>
       </c>
       <c r="B338" s="23"/>
     </row>
     <row r="339" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A339" s="91" t="s">
+      <c r="A339" s="87" t="s">
         <v>82</v>
       </c>
       <c r="B339" s="23"/>
     </row>
     <row r="340" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A340" s="91" t="s">
+      <c r="A340" s="87" t="s">
         <v>121</v>
       </c>
       <c r="B340" s="23"/>
     </row>
     <row r="341" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A341" s="91" t="s">
+      <c r="A341" s="87" t="s">
         <v>84</v>
       </c>
       <c r="B341" s="17" t="n">
@@ -34040,7 +34137,7 @@
       </c>
     </row>
     <row r="342" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A342" s="91" t="s">
+      <c r="A342" s="87" t="s">
         <v>79</v>
       </c>
       <c r="B342" s="17" t="n">
@@ -34048,7 +34145,7 @@
       </c>
     </row>
     <row r="343" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A343" s="91" t="s">
+      <c r="A343" s="87" t="s">
         <v>85</v>
       </c>
       <c r="B343" s="17" t="n">
@@ -34056,7 +34153,7 @@
       </c>
     </row>
     <row r="344" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A344" s="91" t="s">
+      <c r="A344" s="87" t="s">
         <v>122</v>
       </c>
       <c r="B344" s="17" t="n">
@@ -34064,7 +34161,7 @@
       </c>
     </row>
     <row r="345" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A345" s="91" t="s">
+      <c r="A345" s="87" t="s">
         <v>123</v>
       </c>
       <c r="B345" s="17" t="n">
@@ -34072,7 +34169,7 @@
       </c>
     </row>
     <row r="346" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A346" s="91" t="s">
+      <c r="A346" s="87" t="s">
         <v>124</v>
       </c>
       <c r="B346" s="17" t="n">
@@ -34080,7 +34177,7 @@
       </c>
     </row>
     <row r="347" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A347" s="91" t="s">
+      <c r="A347" s="87" t="s">
         <v>125</v>
       </c>
       <c r="B347" s="17" t="n">
@@ -34088,19 +34185,19 @@
       </c>
     </row>
     <row r="348" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A348" s="91" t="s">
+      <c r="A348" s="87" t="s">
         <v>126</v>
       </c>
       <c r="B348" s="29"/>
     </row>
     <row r="349" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A349" s="92" t="s">
+      <c r="A349" s="88" t="s">
         <v>128</v>
       </c>
       <c r="B349" s="31"/>
     </row>
     <row r="350" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A350" s="91" t="s">
+      <c r="A350" s="87" t="s">
         <v>134</v>
       </c>
       <c r="B350" s="17" t="n">
@@ -34108,7 +34205,7 @@
       </c>
     </row>
     <row r="351" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A351" s="91" t="s">
+      <c r="A351" s="87" t="s">
         <v>136</v>
       </c>
       <c r="B351" s="17" t="n">
@@ -34116,7 +34213,7 @@
       </c>
     </row>
     <row r="352" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A352" s="93" t="s">
+      <c r="A352" s="89" t="s">
         <v>157</v>
       </c>
       <c r="B352" s="5" t="n">
@@ -34133,38 +34230,38 @@
       <c r="B355" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="L355" s="59" t="s">
+      <c r="L355" s="49" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="356" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B356" s="1" t="n">
         <v>0.4</v>
       </c>
-      <c r="L356" s="60" t="s">
+      <c r="L356" s="59" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="357" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A357" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G357" s="24" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L357" s="49" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="358" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B358" s="17" t="s">
         <v>102</v>
@@ -34248,11 +34345,11 @@
       <c r="E360" s="23"/>
       <c r="F360" s="23"/>
       <c r="G360" s="23"/>
-      <c r="H360" s="61"/>
+      <c r="H360" s="60"/>
       <c r="I360" s="23"/>
-      <c r="J360" s="94"/>
-      <c r="K360" s="61"/>
-      <c r="L360" s="94"/>
+      <c r="J360" s="90"/>
+      <c r="K360" s="60"/>
+      <c r="L360" s="90"/>
     </row>
     <row r="361" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A361" s="2" t="s">
@@ -34264,11 +34361,11 @@
       <c r="E361" s="23"/>
       <c r="F361" s="23"/>
       <c r="G361" s="23"/>
-      <c r="H361" s="61"/>
+      <c r="H361" s="60"/>
       <c r="I361" s="23"/>
-      <c r="J361" s="94"/>
-      <c r="K361" s="61"/>
-      <c r="L361" s="94"/>
+      <c r="J361" s="90"/>
+      <c r="K361" s="60"/>
+      <c r="L361" s="90"/>
     </row>
     <row r="362" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A362" s="2" t="s">
@@ -34280,11 +34377,11 @@
       <c r="E362" s="23"/>
       <c r="F362" s="23"/>
       <c r="G362" s="23"/>
-      <c r="H362" s="61"/>
+      <c r="H362" s="60"/>
       <c r="I362" s="23"/>
-      <c r="J362" s="94"/>
-      <c r="K362" s="61"/>
-      <c r="L362" s="94"/>
+      <c r="J362" s="90"/>
+      <c r="K362" s="60"/>
+      <c r="L362" s="90"/>
     </row>
     <row r="363" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A363" s="2" t="s">
@@ -34562,11 +34659,11 @@
       <c r="E370" s="29"/>
       <c r="F370" s="29"/>
       <c r="G370" s="29"/>
-      <c r="H370" s="62"/>
+      <c r="H370" s="61"/>
       <c r="I370" s="29"/>
-      <c r="J370" s="95"/>
-      <c r="K370" s="62"/>
-      <c r="L370" s="95"/>
+      <c r="J370" s="91"/>
+      <c r="K370" s="61"/>
+      <c r="L370" s="91"/>
     </row>
     <row r="371" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A371" s="22" t="s">
@@ -34577,12 +34674,12 @@
       <c r="D371" s="31"/>
       <c r="E371" s="31"/>
       <c r="F371" s="31"/>
-      <c r="G371" s="62"/>
-      <c r="H371" s="62"/>
+      <c r="G371" s="61"/>
+      <c r="H371" s="61"/>
       <c r="I371" s="31"/>
-      <c r="J371" s="95"/>
-      <c r="K371" s="62"/>
-      <c r="L371" s="95"/>
+      <c r="J371" s="91"/>
+      <c r="K371" s="61"/>
+      <c r="L371" s="91"/>
     </row>
     <row r="372" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A372" s="17" t="s">
@@ -34734,7 +34831,7 @@
       </c>
     </row>
     <row r="376" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K376" s="63"/>
+      <c r="K376" s="62"/>
     </row>
     <row r="377" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B377" s="1" t="n">
@@ -34758,7 +34855,7 @@
     </row>
     <row r="378" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A378" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B378" s="1" t="n">
         <v>0.4</v>
@@ -34781,30 +34878,30 @@
     </row>
     <row r="379" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A379" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B379" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C379" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D379" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E379" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F379" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G379" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="380" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A380" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B380" s="17" t="s">
         <v>102</v>
@@ -34821,7 +34918,7 @@
       <c r="F380" s="58" t="s">
         <v>106</v>
       </c>
-      <c r="G380" s="59" t="s">
+      <c r="G380" s="49" t="s">
         <v>201</v>
       </c>
     </row>
@@ -34844,7 +34941,7 @@
       <c r="F381" s="58" t="n">
         <v>0.5</v>
       </c>
-      <c r="G381" s="60" t="s">
+      <c r="G381" s="59" t="s">
         <v>204</v>
       </c>
     </row>
@@ -35145,7 +35242,7 @@
     </row>
     <row r="400" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A400" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B400" s="1" t="n">
         <v>0.4</v>
@@ -35165,10 +35262,10 @@
     </row>
     <row r="401" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A401" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K401" s="24" t="s">
         <v>208</v>
@@ -35176,7 +35273,7 @@
     </row>
     <row r="402" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A402" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B402" s="17" t="s">
         <v>102</v>
@@ -35736,7 +35833,7 @@
     </row>
     <row r="422" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A422" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B422" s="1" t="n">
         <v>0.4</v>
@@ -35771,37 +35868,37 @@
     </row>
     <row r="423" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A423" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C423" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D423" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E423" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F423" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G423" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H423" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I423" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J423" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K423" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
   </sheetData>
